--- a/database/datas.xlsx
+++ b/database/datas.xlsx
@@ -1,54 +1,66 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="model" sheetId="1" r:id="rId1"/>
-    <sheet name="1ème Primaire" sheetId="2" r:id="rId2"/>
-    <sheet name="2ème Primaire" sheetId="3" r:id="rId3"/>
-    <sheet name="3ème Primaire" sheetId="4" r:id="rId4"/>
-    <sheet name="4ème Primaire" sheetId="5" r:id="rId5"/>
-    <sheet name="5ème Primaire" sheetId="6" r:id="rId6"/>
-    <sheet name="6ème Primaire" sheetId="7" r:id="rId7"/>
+    <sheet sheetId="1" name="model" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="1ème Primaire" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="2ème Primaire" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="3ème Primaire" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="4ème Primaire" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="5ème Primaire" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="6ème Primaire" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="1ère Maternelle" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="2ème Maternelle" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="3ème Maternelle" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="7ème E.B" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="8ème E.B" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="1ère Commerciale et Gestion" state="visible" r:id="rId16"/>
+    <sheet sheetId="14" name="2ème Commerciale et Gestion" state="visible" r:id="rId17"/>
+    <sheet sheetId="15" name="3ème Commerciale et Gestion" state="visible" r:id="rId18"/>
+    <sheet sheetId="16" name="4ème Commerciale et Gestion" state="visible" r:id="rId19"/>
+    <sheet sheetId="17" name="1ère Mécanique Générale" state="visible" r:id="rId20"/>
+    <sheet sheetId="18" name="2ème Mécanique Générale" state="visible" r:id="rId21"/>
+    <sheet sheetId="19" name="3ème Mécanique Générale" state="visible" r:id="rId22"/>
+    <sheet sheetId="20" name="4ème Mécanique Générale" state="visible" r:id="rId23"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="6">
+  <si>
+    <t>Nom</t>
+  </si>
+  <si>
+    <t>Prénom</t>
+  </si>
+  <si>
+    <t>Date de naissance</t>
+  </si>
+  <si>
+    <t>Genre</t>
+  </si>
+  <si>
+    <t>Classe</t>
+  </si>
+  <si>
+    <t>Adresse</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -72,13 +84,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -403,25 +423,3190 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="E1:N450"/>
+  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
-    <row r="10">
-      <c r="E10" t="str">
-        <v>Nom</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Prénom</v>
-      </c>
-      <c r="K10" t="str">
-        <v>Date de naissance</v>
-      </c>
-      <c r="M10" t="str">
-        <v>Genre</v>
-      </c>
-      <c r="N10" t="str">
-        <v>Classe</v>
-      </c>
+    <row r="1" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="F1"/>
+      <c r="G1"/>
+      <c r="H1"/>
+      <c r="I1"/>
+      <c r="J1"/>
+      <c r="K1"/>
+      <c r="L1"/>
+      <c r="M1"/>
+      <c r="N1"/>
+    </row>
+    <row r="2" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E2"/>
+      <c r="F2"/>
+      <c r="G2"/>
+      <c r="H2"/>
+      <c r="I2"/>
+      <c r="J2"/>
+      <c r="K2"/>
+      <c r="L2"/>
+      <c r="M2"/>
+      <c r="N2"/>
+    </row>
+    <row r="3" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="F3"/>
+      <c r="G3"/>
+      <c r="H3"/>
+      <c r="I3"/>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
+      <c r="N3"/>
+    </row>
+    <row r="4" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4"/>
+      <c r="H4"/>
+      <c r="I4"/>
+      <c r="J4"/>
+      <c r="K4"/>
+      <c r="L4"/>
+      <c r="M4"/>
+      <c r="N4"/>
+    </row>
+    <row r="5" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E5"/>
+      <c r="F5"/>
+      <c r="G5"/>
+      <c r="H5"/>
+      <c r="I5"/>
+      <c r="J5"/>
+      <c r="K5"/>
+      <c r="L5"/>
+      <c r="M5"/>
+      <c r="N5"/>
+    </row>
+    <row r="6" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E6"/>
+      <c r="F6"/>
+      <c r="G6"/>
+      <c r="H6"/>
+      <c r="I6"/>
+      <c r="J6"/>
+      <c r="K6"/>
+      <c r="L6"/>
+      <c r="M6"/>
+      <c r="N6"/>
+    </row>
+    <row r="7" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="I7"/>
+      <c r="J7"/>
+    </row>
+    <row r="8" spans="8:10" x14ac:dyDescent="0.25">
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+    </row>
+    <row r="10" spans="5:14" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
+        <v>0</v>
+      </c>
+      <c r="F10"/>
+      <c r="G10"/>
+      <c r="H10"/>
+      <c r="I10" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10"/>
+      <c r="K10" t="s">
+        <v>2</v>
+      </c>
+      <c r="L10"/>
+      <c r="M10" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F11"/>
+      <c r="G11"/>
+      <c r="H11"/>
+      <c r="J11"/>
+      <c r="L11"/>
+    </row>
+    <row r="12" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F12"/>
+      <c r="G12"/>
+      <c r="H12"/>
+      <c r="J12"/>
+      <c r="L12"/>
+    </row>
+    <row r="13" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F13"/>
+      <c r="G13"/>
+      <c r="H13"/>
+      <c r="J13"/>
+      <c r="L13"/>
+    </row>
+    <row r="14" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F14"/>
+      <c r="G14"/>
+      <c r="H14"/>
+      <c r="J14"/>
+      <c r="L14"/>
+    </row>
+    <row r="15" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F15"/>
+      <c r="G15"/>
+      <c r="H15"/>
+      <c r="J15"/>
+      <c r="L15"/>
+    </row>
+    <row r="16" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F16"/>
+      <c r="G16"/>
+      <c r="H16"/>
+      <c r="J16"/>
+      <c r="L16"/>
+    </row>
+    <row r="17" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F17"/>
+      <c r="G17"/>
+      <c r="H17"/>
+      <c r="J17"/>
+      <c r="L17"/>
+    </row>
+    <row r="18" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F18"/>
+      <c r="G18"/>
+      <c r="H18"/>
+      <c r="J18"/>
+      <c r="L18"/>
+    </row>
+    <row r="19" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F19"/>
+      <c r="G19"/>
+      <c r="H19"/>
+      <c r="J19"/>
+      <c r="L19"/>
+    </row>
+    <row r="20" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F20"/>
+      <c r="G20"/>
+      <c r="H20"/>
+      <c r="J20"/>
+      <c r="L20"/>
+    </row>
+    <row r="21" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
+      <c r="J21"/>
+      <c r="L21"/>
+    </row>
+    <row r="22" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
+      <c r="J22"/>
+      <c r="L22"/>
+    </row>
+    <row r="23" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F23"/>
+      <c r="G23"/>
+      <c r="H23"/>
+      <c r="J23"/>
+      <c r="L23"/>
+    </row>
+    <row r="24" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
+      <c r="J24"/>
+      <c r="L24"/>
+    </row>
+    <row r="25" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F25"/>
+      <c r="G25"/>
+      <c r="H25"/>
+      <c r="J25"/>
+      <c r="L25"/>
+    </row>
+    <row r="26" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
+      <c r="J26"/>
+      <c r="L26"/>
+    </row>
+    <row r="27" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27"/>
+      <c r="J27"/>
+      <c r="L27"/>
+    </row>
+    <row r="28" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F28"/>
+      <c r="G28"/>
+      <c r="H28"/>
+      <c r="J28"/>
+      <c r="L28"/>
+    </row>
+    <row r="29" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F29"/>
+      <c r="G29"/>
+      <c r="H29"/>
+      <c r="J29"/>
+      <c r="L29"/>
+    </row>
+    <row r="30" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
+      <c r="J30"/>
+      <c r="L30"/>
+    </row>
+    <row r="31" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
+      <c r="J31"/>
+      <c r="L31"/>
+    </row>
+    <row r="32" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32"/>
+      <c r="J32"/>
+      <c r="L32"/>
+    </row>
+    <row r="33" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F33"/>
+      <c r="G33"/>
+      <c r="H33"/>
+      <c r="J33"/>
+      <c r="L33"/>
+    </row>
+    <row r="34" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34"/>
+      <c r="J34"/>
+      <c r="L34"/>
+    </row>
+    <row r="35" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F35"/>
+      <c r="G35"/>
+      <c r="H35"/>
+      <c r="J35"/>
+      <c r="L35"/>
+    </row>
+    <row r="36" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36"/>
+      <c r="J36"/>
+      <c r="L36"/>
+    </row>
+    <row r="37" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F37"/>
+      <c r="G37"/>
+      <c r="H37"/>
+      <c r="J37"/>
+      <c r="L37"/>
+    </row>
+    <row r="38" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F38"/>
+      <c r="G38"/>
+      <c r="H38"/>
+      <c r="J38"/>
+      <c r="L38"/>
+    </row>
+    <row r="39" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F39"/>
+      <c r="G39"/>
+      <c r="H39"/>
+      <c r="J39"/>
+      <c r="L39"/>
+    </row>
+    <row r="40" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F40"/>
+      <c r="G40"/>
+      <c r="H40"/>
+      <c r="J40"/>
+      <c r="L40"/>
+    </row>
+    <row r="41" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F41"/>
+      <c r="G41"/>
+      <c r="H41"/>
+      <c r="J41"/>
+      <c r="L41"/>
+    </row>
+    <row r="42" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F42"/>
+      <c r="G42"/>
+      <c r="H42"/>
+      <c r="J42"/>
+      <c r="L42"/>
+    </row>
+    <row r="43" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F43"/>
+      <c r="G43"/>
+      <c r="H43"/>
+      <c r="J43"/>
+      <c r="L43"/>
+    </row>
+    <row r="44" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F44"/>
+      <c r="G44"/>
+      <c r="H44"/>
+      <c r="J44"/>
+      <c r="L44"/>
+    </row>
+    <row r="45" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F45"/>
+      <c r="G45"/>
+      <c r="H45"/>
+      <c r="J45"/>
+      <c r="L45"/>
+    </row>
+    <row r="46" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F46"/>
+      <c r="G46"/>
+      <c r="H46"/>
+      <c r="J46"/>
+      <c r="L46"/>
+    </row>
+    <row r="47" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F47"/>
+      <c r="G47"/>
+      <c r="H47"/>
+      <c r="J47"/>
+      <c r="L47"/>
+    </row>
+    <row r="48" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F48"/>
+      <c r="G48"/>
+      <c r="H48"/>
+      <c r="J48"/>
+      <c r="L48"/>
+    </row>
+    <row r="49" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F49"/>
+      <c r="G49"/>
+      <c r="H49"/>
+      <c r="J49"/>
+      <c r="L49"/>
+    </row>
+    <row r="50" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F50"/>
+      <c r="G50"/>
+      <c r="H50"/>
+      <c r="J50"/>
+      <c r="L50"/>
+    </row>
+    <row r="51" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F51"/>
+      <c r="G51"/>
+      <c r="H51"/>
+      <c r="J51"/>
+      <c r="L51"/>
+    </row>
+    <row r="52" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F52"/>
+      <c r="G52"/>
+      <c r="H52"/>
+      <c r="J52"/>
+      <c r="L52"/>
+    </row>
+    <row r="53" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F53"/>
+      <c r="G53"/>
+      <c r="H53"/>
+      <c r="J53"/>
+      <c r="L53"/>
+    </row>
+    <row r="54" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F54"/>
+      <c r="G54"/>
+      <c r="H54"/>
+      <c r="J54"/>
+      <c r="L54"/>
+    </row>
+    <row r="55" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F55"/>
+      <c r="G55"/>
+      <c r="H55"/>
+      <c r="J55"/>
+      <c r="L55"/>
+    </row>
+    <row r="56" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F56"/>
+      <c r="G56"/>
+      <c r="H56"/>
+      <c r="J56"/>
+      <c r="L56"/>
+    </row>
+    <row r="57" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F57"/>
+      <c r="G57"/>
+      <c r="H57"/>
+      <c r="J57"/>
+      <c r="L57"/>
+    </row>
+    <row r="58" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F58"/>
+      <c r="G58"/>
+      <c r="H58"/>
+      <c r="J58"/>
+      <c r="L58"/>
+    </row>
+    <row r="59" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F59"/>
+      <c r="G59"/>
+      <c r="H59"/>
+      <c r="J59"/>
+      <c r="L59"/>
+    </row>
+    <row r="60" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F60"/>
+      <c r="G60"/>
+      <c r="H60"/>
+      <c r="J60"/>
+      <c r="L60"/>
+    </row>
+    <row r="61" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F61"/>
+      <c r="G61"/>
+      <c r="H61"/>
+      <c r="J61"/>
+      <c r="L61"/>
+    </row>
+    <row r="62" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F62"/>
+      <c r="G62"/>
+      <c r="H62"/>
+      <c r="J62"/>
+      <c r="L62"/>
+    </row>
+    <row r="63" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F63"/>
+      <c r="G63"/>
+      <c r="H63"/>
+      <c r="J63"/>
+      <c r="L63"/>
+    </row>
+    <row r="64" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F64"/>
+      <c r="G64"/>
+      <c r="H64"/>
+      <c r="J64"/>
+      <c r="L64"/>
+    </row>
+    <row r="65" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F65"/>
+      <c r="G65"/>
+      <c r="H65"/>
+      <c r="J65"/>
+      <c r="L65"/>
+    </row>
+    <row r="66" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F66"/>
+      <c r="G66"/>
+      <c r="H66"/>
+      <c r="J66"/>
+      <c r="L66"/>
+    </row>
+    <row r="67" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F67"/>
+      <c r="G67"/>
+      <c r="H67"/>
+      <c r="J67"/>
+      <c r="L67"/>
+    </row>
+    <row r="68" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F68"/>
+      <c r="G68"/>
+      <c r="H68"/>
+      <c r="J68"/>
+      <c r="L68"/>
+    </row>
+    <row r="69" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F69"/>
+      <c r="G69"/>
+      <c r="H69"/>
+      <c r="J69"/>
+      <c r="L69"/>
+    </row>
+    <row r="70" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F70"/>
+      <c r="G70"/>
+      <c r="H70"/>
+      <c r="J70"/>
+      <c r="L70"/>
+    </row>
+    <row r="71" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F71"/>
+      <c r="G71"/>
+      <c r="H71"/>
+      <c r="J71"/>
+      <c r="L71"/>
+    </row>
+    <row r="72" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F72"/>
+      <c r="G72"/>
+      <c r="H72"/>
+      <c r="J72"/>
+      <c r="L72"/>
+    </row>
+    <row r="73" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F73"/>
+      <c r="G73"/>
+      <c r="H73"/>
+      <c r="J73"/>
+      <c r="L73"/>
+    </row>
+    <row r="74" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F74"/>
+      <c r="G74"/>
+      <c r="H74"/>
+      <c r="J74"/>
+      <c r="L74"/>
+    </row>
+    <row r="75" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F75"/>
+      <c r="G75"/>
+      <c r="H75"/>
+      <c r="J75"/>
+      <c r="L75"/>
+    </row>
+    <row r="76" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F76"/>
+      <c r="G76"/>
+      <c r="H76"/>
+      <c r="J76"/>
+      <c r="L76"/>
+    </row>
+    <row r="77" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F77"/>
+      <c r="G77"/>
+      <c r="H77"/>
+      <c r="J77"/>
+      <c r="L77"/>
+    </row>
+    <row r="78" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F78"/>
+      <c r="G78"/>
+      <c r="H78"/>
+      <c r="J78"/>
+      <c r="L78"/>
+    </row>
+    <row r="79" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F79"/>
+      <c r="G79"/>
+      <c r="H79"/>
+      <c r="J79"/>
+      <c r="L79"/>
+    </row>
+    <row r="80" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F80"/>
+      <c r="G80"/>
+      <c r="H80"/>
+      <c r="J80"/>
+      <c r="L80"/>
+    </row>
+    <row r="81" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F81"/>
+      <c r="G81"/>
+      <c r="H81"/>
+      <c r="J81"/>
+      <c r="L81"/>
+    </row>
+    <row r="82" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F82"/>
+      <c r="G82"/>
+      <c r="H82"/>
+      <c r="J82"/>
+      <c r="L82"/>
+    </row>
+    <row r="83" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F83"/>
+      <c r="G83"/>
+      <c r="H83"/>
+      <c r="J83"/>
+      <c r="L83"/>
+    </row>
+    <row r="84" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F84"/>
+      <c r="G84"/>
+      <c r="H84"/>
+      <c r="J84"/>
+      <c r="L84"/>
+    </row>
+    <row r="85" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F85"/>
+      <c r="G85"/>
+      <c r="H85"/>
+      <c r="J85"/>
+      <c r="L85"/>
+    </row>
+    <row r="86" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F86"/>
+      <c r="G86"/>
+      <c r="H86"/>
+      <c r="J86"/>
+      <c r="L86"/>
+    </row>
+    <row r="87" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F87"/>
+      <c r="G87"/>
+      <c r="H87"/>
+      <c r="J87"/>
+      <c r="L87"/>
+    </row>
+    <row r="88" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F88"/>
+      <c r="G88"/>
+      <c r="H88"/>
+      <c r="J88"/>
+      <c r="L88"/>
+    </row>
+    <row r="89" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F89"/>
+      <c r="G89"/>
+      <c r="H89"/>
+      <c r="J89"/>
+      <c r="L89"/>
+    </row>
+    <row r="90" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F90"/>
+      <c r="G90"/>
+      <c r="H90"/>
+      <c r="J90"/>
+      <c r="L90"/>
+    </row>
+    <row r="91" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F91"/>
+      <c r="G91"/>
+      <c r="H91"/>
+      <c r="J91"/>
+      <c r="L91"/>
+    </row>
+    <row r="92" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F92"/>
+      <c r="G92"/>
+      <c r="H92"/>
+      <c r="J92"/>
+      <c r="L92"/>
+    </row>
+    <row r="93" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F93"/>
+      <c r="G93"/>
+      <c r="H93"/>
+      <c r="J93"/>
+      <c r="L93"/>
+    </row>
+    <row r="94" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F94"/>
+      <c r="G94"/>
+      <c r="H94"/>
+      <c r="J94"/>
+      <c r="L94"/>
+    </row>
+    <row r="95" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F95"/>
+      <c r="G95"/>
+      <c r="H95"/>
+      <c r="J95"/>
+      <c r="L95"/>
+    </row>
+    <row r="96" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F96"/>
+      <c r="G96"/>
+      <c r="H96"/>
+      <c r="J96"/>
+      <c r="L96"/>
+    </row>
+    <row r="97" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F97"/>
+      <c r="G97"/>
+      <c r="H97"/>
+      <c r="J97"/>
+      <c r="L97"/>
+    </row>
+    <row r="98" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F98"/>
+      <c r="G98"/>
+      <c r="H98"/>
+      <c r="J98"/>
+      <c r="L98"/>
+    </row>
+    <row r="99" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F99"/>
+      <c r="G99"/>
+      <c r="H99"/>
+      <c r="J99"/>
+      <c r="L99"/>
+    </row>
+    <row r="100" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F100"/>
+      <c r="G100"/>
+      <c r="H100"/>
+      <c r="J100"/>
+      <c r="L100"/>
+    </row>
+    <row r="101" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F101"/>
+      <c r="G101"/>
+      <c r="H101"/>
+      <c r="J101"/>
+      <c r="L101"/>
+    </row>
+    <row r="102" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F102"/>
+      <c r="G102"/>
+      <c r="H102"/>
+      <c r="J102"/>
+      <c r="L102"/>
+    </row>
+    <row r="103" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F103"/>
+      <c r="G103"/>
+      <c r="H103"/>
+      <c r="J103"/>
+      <c r="L103"/>
+    </row>
+    <row r="104" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F104"/>
+      <c r="G104"/>
+      <c r="H104"/>
+      <c r="J104"/>
+      <c r="L104"/>
+    </row>
+    <row r="105" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F105"/>
+      <c r="G105"/>
+      <c r="H105"/>
+      <c r="J105"/>
+      <c r="L105"/>
+    </row>
+    <row r="106" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F106"/>
+      <c r="G106"/>
+      <c r="H106"/>
+      <c r="J106"/>
+      <c r="L106"/>
+    </row>
+    <row r="107" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F107"/>
+      <c r="G107"/>
+      <c r="H107"/>
+      <c r="J107"/>
+      <c r="L107"/>
+    </row>
+    <row r="108" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F108"/>
+      <c r="G108"/>
+      <c r="H108"/>
+      <c r="J108"/>
+      <c r="L108"/>
+    </row>
+    <row r="109" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F109"/>
+      <c r="G109"/>
+      <c r="H109"/>
+      <c r="J109"/>
+      <c r="L109"/>
+    </row>
+    <row r="110" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F110"/>
+      <c r="G110"/>
+      <c r="H110"/>
+      <c r="J110"/>
+      <c r="L110"/>
+    </row>
+    <row r="111" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F111"/>
+      <c r="G111"/>
+      <c r="H111"/>
+      <c r="J111"/>
+      <c r="L111"/>
+    </row>
+    <row r="112" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F112"/>
+      <c r="G112"/>
+      <c r="H112"/>
+      <c r="J112"/>
+      <c r="L112"/>
+    </row>
+    <row r="113" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F113"/>
+      <c r="G113"/>
+      <c r="H113"/>
+      <c r="J113"/>
+      <c r="L113"/>
+    </row>
+    <row r="114" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F114"/>
+      <c r="G114"/>
+      <c r="H114"/>
+      <c r="J114"/>
+      <c r="L114"/>
+    </row>
+    <row r="115" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F115"/>
+      <c r="G115"/>
+      <c r="H115"/>
+      <c r="J115"/>
+      <c r="L115"/>
+    </row>
+    <row r="116" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F116"/>
+      <c r="G116"/>
+      <c r="H116"/>
+      <c r="J116"/>
+      <c r="L116"/>
+    </row>
+    <row r="117" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F117"/>
+      <c r="G117"/>
+      <c r="H117"/>
+      <c r="J117"/>
+      <c r="L117"/>
+    </row>
+    <row r="118" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F118"/>
+      <c r="G118"/>
+      <c r="H118"/>
+      <c r="J118"/>
+      <c r="L118"/>
+    </row>
+    <row r="119" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F119"/>
+      <c r="G119"/>
+      <c r="H119"/>
+      <c r="J119"/>
+      <c r="L119"/>
+    </row>
+    <row r="120" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F120"/>
+      <c r="G120"/>
+      <c r="H120"/>
+      <c r="J120"/>
+      <c r="L120"/>
+    </row>
+    <row r="121" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F121"/>
+      <c r="G121"/>
+      <c r="H121"/>
+      <c r="J121"/>
+      <c r="L121"/>
+    </row>
+    <row r="122" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F122"/>
+      <c r="G122"/>
+      <c r="H122"/>
+      <c r="J122"/>
+      <c r="L122"/>
+    </row>
+    <row r="123" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F123"/>
+      <c r="G123"/>
+      <c r="H123"/>
+      <c r="J123"/>
+      <c r="L123"/>
+    </row>
+    <row r="124" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F124"/>
+      <c r="G124"/>
+      <c r="H124"/>
+      <c r="J124"/>
+      <c r="L124"/>
+    </row>
+    <row r="125" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F125"/>
+      <c r="G125"/>
+      <c r="H125"/>
+      <c r="J125"/>
+      <c r="L125"/>
+    </row>
+    <row r="126" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F126"/>
+      <c r="G126"/>
+      <c r="H126"/>
+      <c r="J126"/>
+      <c r="L126"/>
+    </row>
+    <row r="127" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F127"/>
+      <c r="G127"/>
+      <c r="H127"/>
+      <c r="J127"/>
+      <c r="L127"/>
+    </row>
+    <row r="128" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F128"/>
+      <c r="G128"/>
+      <c r="H128"/>
+      <c r="J128"/>
+      <c r="L128"/>
+    </row>
+    <row r="129" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F129"/>
+      <c r="G129"/>
+      <c r="H129"/>
+      <c r="J129"/>
+      <c r="L129"/>
+    </row>
+    <row r="130" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F130"/>
+      <c r="G130"/>
+      <c r="H130"/>
+      <c r="J130"/>
+      <c r="L130"/>
+    </row>
+    <row r="131" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F131"/>
+      <c r="G131"/>
+      <c r="H131"/>
+      <c r="J131"/>
+      <c r="L131"/>
+    </row>
+    <row r="132" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F132"/>
+      <c r="G132"/>
+      <c r="H132"/>
+      <c r="J132"/>
+      <c r="L132"/>
+    </row>
+    <row r="133" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F133"/>
+      <c r="G133"/>
+      <c r="H133"/>
+      <c r="J133"/>
+      <c r="L133"/>
+    </row>
+    <row r="134" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F134"/>
+      <c r="G134"/>
+      <c r="H134"/>
+      <c r="J134"/>
+      <c r="L134"/>
+    </row>
+    <row r="135" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F135"/>
+      <c r="G135"/>
+      <c r="H135"/>
+      <c r="J135"/>
+      <c r="L135"/>
+    </row>
+    <row r="136" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F136"/>
+      <c r="G136"/>
+      <c r="H136"/>
+      <c r="J136"/>
+      <c r="L136"/>
+    </row>
+    <row r="137" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F137"/>
+      <c r="G137"/>
+      <c r="H137"/>
+      <c r="J137"/>
+      <c r="L137"/>
+    </row>
+    <row r="138" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F138"/>
+      <c r="G138"/>
+      <c r="H138"/>
+      <c r="J138"/>
+      <c r="L138"/>
+    </row>
+    <row r="139" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F139"/>
+      <c r="G139"/>
+      <c r="H139"/>
+      <c r="J139"/>
+      <c r="L139"/>
+    </row>
+    <row r="140" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F140"/>
+      <c r="G140"/>
+      <c r="H140"/>
+      <c r="J140"/>
+      <c r="L140"/>
+    </row>
+    <row r="141" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F141"/>
+      <c r="G141"/>
+      <c r="H141"/>
+      <c r="J141"/>
+      <c r="L141"/>
+    </row>
+    <row r="142" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F142"/>
+      <c r="G142"/>
+      <c r="H142"/>
+      <c r="J142"/>
+      <c r="L142"/>
+    </row>
+    <row r="143" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F143"/>
+      <c r="G143"/>
+      <c r="H143"/>
+      <c r="J143"/>
+      <c r="L143"/>
+    </row>
+    <row r="144" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F144"/>
+      <c r="G144"/>
+      <c r="H144"/>
+      <c r="J144"/>
+      <c r="L144"/>
+    </row>
+    <row r="145" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F145"/>
+      <c r="G145"/>
+      <c r="H145"/>
+      <c r="J145"/>
+      <c r="L145"/>
+    </row>
+    <row r="146" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F146"/>
+      <c r="G146"/>
+      <c r="H146"/>
+      <c r="J146"/>
+      <c r="L146"/>
+    </row>
+    <row r="147" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F147"/>
+      <c r="G147"/>
+      <c r="H147"/>
+      <c r="J147"/>
+      <c r="L147"/>
+    </row>
+    <row r="148" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F148"/>
+      <c r="G148"/>
+      <c r="H148"/>
+      <c r="J148"/>
+      <c r="L148"/>
+    </row>
+    <row r="149" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F149"/>
+      <c r="G149"/>
+      <c r="H149"/>
+      <c r="J149"/>
+      <c r="L149"/>
+    </row>
+    <row r="150" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F150"/>
+      <c r="G150"/>
+      <c r="H150"/>
+      <c r="J150"/>
+      <c r="L150"/>
+    </row>
+    <row r="151" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F151"/>
+      <c r="G151"/>
+      <c r="H151"/>
+      <c r="J151"/>
+      <c r="L151"/>
+    </row>
+    <row r="152" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F152"/>
+      <c r="G152"/>
+      <c r="H152"/>
+      <c r="J152"/>
+      <c r="L152"/>
+    </row>
+    <row r="153" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F153"/>
+      <c r="G153"/>
+      <c r="H153"/>
+      <c r="J153"/>
+      <c r="L153"/>
+    </row>
+    <row r="154" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F154"/>
+      <c r="G154"/>
+      <c r="H154"/>
+      <c r="J154"/>
+      <c r="L154"/>
+    </row>
+    <row r="155" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F155"/>
+      <c r="G155"/>
+      <c r="H155"/>
+      <c r="J155"/>
+      <c r="L155"/>
+    </row>
+    <row r="156" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F156"/>
+      <c r="G156"/>
+      <c r="H156"/>
+      <c r="J156"/>
+      <c r="L156"/>
+    </row>
+    <row r="157" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F157"/>
+      <c r="G157"/>
+      <c r="H157"/>
+      <c r="J157"/>
+      <c r="L157"/>
+    </row>
+    <row r="158" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F158"/>
+      <c r="G158"/>
+      <c r="H158"/>
+      <c r="J158"/>
+      <c r="L158"/>
+    </row>
+    <row r="159" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F159"/>
+      <c r="G159"/>
+      <c r="H159"/>
+      <c r="J159"/>
+      <c r="L159"/>
+    </row>
+    <row r="160" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F160"/>
+      <c r="G160"/>
+      <c r="H160"/>
+      <c r="J160"/>
+      <c r="L160"/>
+    </row>
+    <row r="161" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F161"/>
+      <c r="G161"/>
+      <c r="H161"/>
+      <c r="J161"/>
+      <c r="L161"/>
+    </row>
+    <row r="162" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F162"/>
+      <c r="G162"/>
+      <c r="H162"/>
+      <c r="J162"/>
+      <c r="L162"/>
+    </row>
+    <row r="163" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F163"/>
+      <c r="G163"/>
+      <c r="H163"/>
+      <c r="J163"/>
+      <c r="L163"/>
+    </row>
+    <row r="164" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F164"/>
+      <c r="G164"/>
+      <c r="H164"/>
+      <c r="J164"/>
+      <c r="L164"/>
+    </row>
+    <row r="165" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F165"/>
+      <c r="G165"/>
+      <c r="H165"/>
+      <c r="J165"/>
+      <c r="L165"/>
+    </row>
+    <row r="166" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F166"/>
+      <c r="G166"/>
+      <c r="H166"/>
+      <c r="J166"/>
+      <c r="L166"/>
+    </row>
+    <row r="167" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F167"/>
+      <c r="G167"/>
+      <c r="H167"/>
+      <c r="J167"/>
+      <c r="L167"/>
+    </row>
+    <row r="168" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F168"/>
+      <c r="G168"/>
+      <c r="H168"/>
+      <c r="J168"/>
+      <c r="L168"/>
+    </row>
+    <row r="169" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F169"/>
+      <c r="G169"/>
+      <c r="H169"/>
+      <c r="J169"/>
+      <c r="L169"/>
+    </row>
+    <row r="170" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F170"/>
+      <c r="G170"/>
+      <c r="H170"/>
+      <c r="J170"/>
+      <c r="L170"/>
+    </row>
+    <row r="171" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F171"/>
+      <c r="G171"/>
+      <c r="H171"/>
+      <c r="J171"/>
+      <c r="L171"/>
+    </row>
+    <row r="172" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F172"/>
+      <c r="G172"/>
+      <c r="H172"/>
+      <c r="J172"/>
+      <c r="L172"/>
+    </row>
+    <row r="173" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F173"/>
+      <c r="G173"/>
+      <c r="H173"/>
+      <c r="J173"/>
+      <c r="L173"/>
+    </row>
+    <row r="174" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F174"/>
+      <c r="G174"/>
+      <c r="H174"/>
+      <c r="J174"/>
+      <c r="L174"/>
+    </row>
+    <row r="175" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F175"/>
+      <c r="G175"/>
+      <c r="H175"/>
+      <c r="J175"/>
+      <c r="L175"/>
+    </row>
+    <row r="176" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F176"/>
+      <c r="G176"/>
+      <c r="H176"/>
+      <c r="J176"/>
+      <c r="L176"/>
+    </row>
+    <row r="177" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F177"/>
+      <c r="G177"/>
+      <c r="H177"/>
+      <c r="J177"/>
+      <c r="L177"/>
+    </row>
+    <row r="178" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F178"/>
+      <c r="G178"/>
+      <c r="H178"/>
+      <c r="J178"/>
+      <c r="L178"/>
+    </row>
+    <row r="179" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F179"/>
+      <c r="G179"/>
+      <c r="H179"/>
+      <c r="J179"/>
+      <c r="L179"/>
+    </row>
+    <row r="180" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F180"/>
+      <c r="G180"/>
+      <c r="H180"/>
+      <c r="J180"/>
+      <c r="L180"/>
+    </row>
+    <row r="181" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F181"/>
+      <c r="G181"/>
+      <c r="H181"/>
+      <c r="J181"/>
+      <c r="L181"/>
+    </row>
+    <row r="182" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F182"/>
+      <c r="G182"/>
+      <c r="H182"/>
+      <c r="J182"/>
+      <c r="L182"/>
+    </row>
+    <row r="183" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F183"/>
+      <c r="G183"/>
+      <c r="H183"/>
+      <c r="J183"/>
+      <c r="L183"/>
+    </row>
+    <row r="184" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F184"/>
+      <c r="G184"/>
+      <c r="H184"/>
+      <c r="J184"/>
+      <c r="L184"/>
+    </row>
+    <row r="185" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F185"/>
+      <c r="G185"/>
+      <c r="H185"/>
+      <c r="J185"/>
+      <c r="L185"/>
+    </row>
+    <row r="186" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F186"/>
+      <c r="G186"/>
+      <c r="H186"/>
+      <c r="J186"/>
+      <c r="L186"/>
+    </row>
+    <row r="187" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F187"/>
+      <c r="G187"/>
+      <c r="H187"/>
+      <c r="J187"/>
+      <c r="L187"/>
+    </row>
+    <row r="188" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F188"/>
+      <c r="G188"/>
+      <c r="H188"/>
+      <c r="J188"/>
+      <c r="L188"/>
+    </row>
+    <row r="189" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F189"/>
+      <c r="G189"/>
+      <c r="H189"/>
+      <c r="J189"/>
+      <c r="L189"/>
+    </row>
+    <row r="190" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F190"/>
+      <c r="G190"/>
+      <c r="H190"/>
+      <c r="J190"/>
+      <c r="L190"/>
+    </row>
+    <row r="191" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F191"/>
+      <c r="G191"/>
+      <c r="H191"/>
+      <c r="J191"/>
+      <c r="L191"/>
+    </row>
+    <row r="192" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F192"/>
+      <c r="G192"/>
+      <c r="H192"/>
+      <c r="J192"/>
+      <c r="L192"/>
+    </row>
+    <row r="193" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F193"/>
+      <c r="G193"/>
+      <c r="H193"/>
+      <c r="J193"/>
+      <c r="L193"/>
+    </row>
+    <row r="194" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F194"/>
+      <c r="G194"/>
+      <c r="H194"/>
+      <c r="J194"/>
+      <c r="L194"/>
+    </row>
+    <row r="195" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F195"/>
+      <c r="G195"/>
+      <c r="H195"/>
+      <c r="J195"/>
+      <c r="L195"/>
+    </row>
+    <row r="196" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F196"/>
+      <c r="G196"/>
+      <c r="H196"/>
+      <c r="J196"/>
+      <c r="L196"/>
+    </row>
+    <row r="197" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F197"/>
+      <c r="G197"/>
+      <c r="H197"/>
+      <c r="J197"/>
+      <c r="L197"/>
+    </row>
+    <row r="198" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F198"/>
+      <c r="G198"/>
+      <c r="H198"/>
+      <c r="J198"/>
+      <c r="L198"/>
+    </row>
+    <row r="199" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F199"/>
+      <c r="G199"/>
+      <c r="H199"/>
+      <c r="J199"/>
+      <c r="L199"/>
+    </row>
+    <row r="200" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F200"/>
+      <c r="G200"/>
+      <c r="H200"/>
+      <c r="J200"/>
+      <c r="L200"/>
+    </row>
+    <row r="201" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F201"/>
+      <c r="G201"/>
+      <c r="H201"/>
+      <c r="J201"/>
+      <c r="L201"/>
+    </row>
+    <row r="202" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F202"/>
+      <c r="G202"/>
+      <c r="H202"/>
+      <c r="J202"/>
+      <c r="L202"/>
+    </row>
+    <row r="203" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F203"/>
+      <c r="G203"/>
+      <c r="H203"/>
+      <c r="J203"/>
+      <c r="L203"/>
+    </row>
+    <row r="204" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F204"/>
+      <c r="G204"/>
+      <c r="H204"/>
+      <c r="J204"/>
+      <c r="L204"/>
+    </row>
+    <row r="205" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F205"/>
+      <c r="G205"/>
+      <c r="H205"/>
+      <c r="J205"/>
+      <c r="L205"/>
+    </row>
+    <row r="206" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F206"/>
+      <c r="G206"/>
+      <c r="H206"/>
+      <c r="J206"/>
+      <c r="L206"/>
+    </row>
+    <row r="207" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F207"/>
+      <c r="G207"/>
+      <c r="H207"/>
+      <c r="J207"/>
+      <c r="L207"/>
+    </row>
+    <row r="208" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F208"/>
+      <c r="G208"/>
+      <c r="H208"/>
+      <c r="J208"/>
+      <c r="L208"/>
+    </row>
+    <row r="209" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F209"/>
+      <c r="G209"/>
+      <c r="H209"/>
+      <c r="J209"/>
+      <c r="L209"/>
+    </row>
+    <row r="210" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F210"/>
+      <c r="G210"/>
+      <c r="H210"/>
+      <c r="J210"/>
+      <c r="L210"/>
+    </row>
+    <row r="211" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F211"/>
+      <c r="G211"/>
+      <c r="H211"/>
+      <c r="J211"/>
+      <c r="L211"/>
+    </row>
+    <row r="212" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F212"/>
+      <c r="G212"/>
+      <c r="H212"/>
+      <c r="J212"/>
+      <c r="L212"/>
+    </row>
+    <row r="213" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F213"/>
+      <c r="G213"/>
+      <c r="H213"/>
+      <c r="J213"/>
+      <c r="L213"/>
+    </row>
+    <row r="214" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F214"/>
+      <c r="G214"/>
+      <c r="H214"/>
+      <c r="J214"/>
+      <c r="L214"/>
+    </row>
+    <row r="215" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F215"/>
+      <c r="G215"/>
+      <c r="H215"/>
+      <c r="J215"/>
+      <c r="L215"/>
+    </row>
+    <row r="216" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F216"/>
+      <c r="G216"/>
+      <c r="H216"/>
+      <c r="J216"/>
+      <c r="L216"/>
+    </row>
+    <row r="217" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F217"/>
+      <c r="G217"/>
+      <c r="H217"/>
+      <c r="J217"/>
+      <c r="L217"/>
+    </row>
+    <row r="218" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F218"/>
+      <c r="G218"/>
+      <c r="H218"/>
+      <c r="J218"/>
+      <c r="L218"/>
+    </row>
+    <row r="219" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F219"/>
+      <c r="G219"/>
+      <c r="H219"/>
+      <c r="J219"/>
+      <c r="L219"/>
+    </row>
+    <row r="220" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F220"/>
+      <c r="G220"/>
+      <c r="H220"/>
+      <c r="J220"/>
+      <c r="L220"/>
+    </row>
+    <row r="221" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F221"/>
+      <c r="G221"/>
+      <c r="H221"/>
+      <c r="J221"/>
+      <c r="L221"/>
+    </row>
+    <row r="222" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F222"/>
+      <c r="G222"/>
+      <c r="H222"/>
+      <c r="J222"/>
+      <c r="L222"/>
+    </row>
+    <row r="223" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F223"/>
+      <c r="G223"/>
+      <c r="H223"/>
+      <c r="J223"/>
+      <c r="L223"/>
+    </row>
+    <row r="224" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F224"/>
+      <c r="G224"/>
+      <c r="H224"/>
+      <c r="J224"/>
+      <c r="L224"/>
+    </row>
+    <row r="225" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F225"/>
+      <c r="G225"/>
+      <c r="H225"/>
+      <c r="J225"/>
+      <c r="L225"/>
+    </row>
+    <row r="226" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F226"/>
+      <c r="G226"/>
+      <c r="H226"/>
+      <c r="J226"/>
+      <c r="L226"/>
+    </row>
+    <row r="227" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F227"/>
+      <c r="G227"/>
+      <c r="H227"/>
+      <c r="J227"/>
+      <c r="L227"/>
+    </row>
+    <row r="228" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F228"/>
+      <c r="G228"/>
+      <c r="H228"/>
+      <c r="J228"/>
+      <c r="L228"/>
+    </row>
+    <row r="229" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F229"/>
+      <c r="G229"/>
+      <c r="H229"/>
+      <c r="J229"/>
+      <c r="L229"/>
+    </row>
+    <row r="230" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F230"/>
+      <c r="G230"/>
+      <c r="H230"/>
+      <c r="J230"/>
+      <c r="L230"/>
+    </row>
+    <row r="231" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F231"/>
+      <c r="G231"/>
+      <c r="H231"/>
+      <c r="J231"/>
+      <c r="L231"/>
+    </row>
+    <row r="232" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F232"/>
+      <c r="G232"/>
+      <c r="H232"/>
+      <c r="J232"/>
+      <c r="L232"/>
+    </row>
+    <row r="233" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F233"/>
+      <c r="G233"/>
+      <c r="H233"/>
+      <c r="J233"/>
+      <c r="L233"/>
+    </row>
+    <row r="234" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F234"/>
+      <c r="G234"/>
+      <c r="H234"/>
+      <c r="J234"/>
+      <c r="L234"/>
+    </row>
+    <row r="235" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F235"/>
+      <c r="G235"/>
+      <c r="H235"/>
+      <c r="J235"/>
+      <c r="L235"/>
+    </row>
+    <row r="236" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F236"/>
+      <c r="G236"/>
+      <c r="H236"/>
+      <c r="J236"/>
+      <c r="L236"/>
+    </row>
+    <row r="237" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F237"/>
+      <c r="G237"/>
+      <c r="H237"/>
+      <c r="J237"/>
+      <c r="L237"/>
+    </row>
+    <row r="238" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F238"/>
+      <c r="G238"/>
+      <c r="H238"/>
+      <c r="J238"/>
+      <c r="L238"/>
+    </row>
+    <row r="239" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F239"/>
+      <c r="G239"/>
+      <c r="H239"/>
+      <c r="J239"/>
+      <c r="L239"/>
+    </row>
+    <row r="240" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F240"/>
+      <c r="G240"/>
+      <c r="H240"/>
+      <c r="J240"/>
+      <c r="L240"/>
+    </row>
+    <row r="241" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F241"/>
+      <c r="G241"/>
+      <c r="H241"/>
+      <c r="J241"/>
+      <c r="L241"/>
+    </row>
+    <row r="242" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F242"/>
+      <c r="G242"/>
+      <c r="H242"/>
+      <c r="J242"/>
+      <c r="L242"/>
+    </row>
+    <row r="243" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F243"/>
+      <c r="G243"/>
+      <c r="H243"/>
+      <c r="J243"/>
+      <c r="L243"/>
+    </row>
+    <row r="244" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F244"/>
+      <c r="G244"/>
+      <c r="H244"/>
+      <c r="J244"/>
+      <c r="L244"/>
+    </row>
+    <row r="245" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F245"/>
+      <c r="G245"/>
+      <c r="H245"/>
+      <c r="J245"/>
+      <c r="L245"/>
+    </row>
+    <row r="246" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F246"/>
+      <c r="G246"/>
+      <c r="H246"/>
+      <c r="J246"/>
+      <c r="L246"/>
+    </row>
+    <row r="247" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F247"/>
+      <c r="G247"/>
+      <c r="H247"/>
+      <c r="J247"/>
+      <c r="L247"/>
+    </row>
+    <row r="248" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F248"/>
+      <c r="G248"/>
+      <c r="H248"/>
+      <c r="J248"/>
+      <c r="L248"/>
+    </row>
+    <row r="249" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F249"/>
+      <c r="G249"/>
+      <c r="H249"/>
+      <c r="J249"/>
+      <c r="L249"/>
+    </row>
+    <row r="250" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F250"/>
+      <c r="G250"/>
+      <c r="H250"/>
+      <c r="J250"/>
+      <c r="L250"/>
+    </row>
+    <row r="251" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F251"/>
+      <c r="G251"/>
+      <c r="H251"/>
+      <c r="J251"/>
+      <c r="L251"/>
+    </row>
+    <row r="252" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F252"/>
+      <c r="G252"/>
+      <c r="H252"/>
+      <c r="J252"/>
+      <c r="L252"/>
+    </row>
+    <row r="253" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F253"/>
+      <c r="G253"/>
+      <c r="H253"/>
+      <c r="J253"/>
+      <c r="L253"/>
+    </row>
+    <row r="254" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F254"/>
+      <c r="G254"/>
+      <c r="H254"/>
+      <c r="J254"/>
+      <c r="L254"/>
+    </row>
+    <row r="255" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F255"/>
+      <c r="G255"/>
+      <c r="H255"/>
+      <c r="J255"/>
+      <c r="L255"/>
+    </row>
+    <row r="256" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F256"/>
+      <c r="G256"/>
+      <c r="H256"/>
+      <c r="J256"/>
+      <c r="L256"/>
+    </row>
+    <row r="257" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F257"/>
+      <c r="G257"/>
+      <c r="H257"/>
+      <c r="J257"/>
+      <c r="L257"/>
+    </row>
+    <row r="258" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F258"/>
+      <c r="G258"/>
+      <c r="H258"/>
+      <c r="J258"/>
+      <c r="L258"/>
+    </row>
+    <row r="259" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F259"/>
+      <c r="G259"/>
+      <c r="H259"/>
+      <c r="J259"/>
+      <c r="L259"/>
+    </row>
+    <row r="260" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F260"/>
+      <c r="G260"/>
+      <c r="H260"/>
+      <c r="J260"/>
+      <c r="L260"/>
+    </row>
+    <row r="261" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F261"/>
+      <c r="G261"/>
+      <c r="H261"/>
+      <c r="J261"/>
+      <c r="L261"/>
+    </row>
+    <row r="262" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F262"/>
+      <c r="G262"/>
+      <c r="H262"/>
+      <c r="J262"/>
+      <c r="L262"/>
+    </row>
+    <row r="263" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F263"/>
+      <c r="G263"/>
+      <c r="H263"/>
+      <c r="J263"/>
+      <c r="L263"/>
+    </row>
+    <row r="264" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F264"/>
+      <c r="G264"/>
+      <c r="H264"/>
+      <c r="J264"/>
+      <c r="L264"/>
+    </row>
+    <row r="265" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F265"/>
+      <c r="G265"/>
+      <c r="H265"/>
+      <c r="J265"/>
+      <c r="L265"/>
+    </row>
+    <row r="266" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F266"/>
+      <c r="G266"/>
+      <c r="H266"/>
+      <c r="J266"/>
+      <c r="L266"/>
+    </row>
+    <row r="267" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F267"/>
+      <c r="G267"/>
+      <c r="H267"/>
+      <c r="J267"/>
+      <c r="L267"/>
+    </row>
+    <row r="268" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F268"/>
+      <c r="G268"/>
+      <c r="H268"/>
+      <c r="J268"/>
+      <c r="L268"/>
+    </row>
+    <row r="269" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F269"/>
+      <c r="G269"/>
+      <c r="H269"/>
+      <c r="J269"/>
+      <c r="L269"/>
+    </row>
+    <row r="270" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F270"/>
+      <c r="G270"/>
+      <c r="H270"/>
+      <c r="J270"/>
+      <c r="L270"/>
+    </row>
+    <row r="271" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F271"/>
+      <c r="G271"/>
+      <c r="H271"/>
+      <c r="J271"/>
+      <c r="L271"/>
+    </row>
+    <row r="272" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F272"/>
+      <c r="G272"/>
+      <c r="H272"/>
+      <c r="J272"/>
+      <c r="L272"/>
+    </row>
+    <row r="273" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F273"/>
+      <c r="G273"/>
+      <c r="H273"/>
+      <c r="J273"/>
+      <c r="L273"/>
+    </row>
+    <row r="274" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F274"/>
+      <c r="G274"/>
+      <c r="H274"/>
+      <c r="J274"/>
+      <c r="L274"/>
+    </row>
+    <row r="275" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F275"/>
+      <c r="G275"/>
+      <c r="H275"/>
+      <c r="J275"/>
+      <c r="L275"/>
+    </row>
+    <row r="276" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F276"/>
+      <c r="G276"/>
+      <c r="H276"/>
+      <c r="J276"/>
+      <c r="L276"/>
+    </row>
+    <row r="277" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F277"/>
+      <c r="G277"/>
+      <c r="H277"/>
+      <c r="J277"/>
+      <c r="L277"/>
+    </row>
+    <row r="278" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F278"/>
+      <c r="G278"/>
+      <c r="H278"/>
+      <c r="J278"/>
+      <c r="L278"/>
+    </row>
+    <row r="279" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F279"/>
+      <c r="G279"/>
+      <c r="H279"/>
+      <c r="J279"/>
+      <c r="L279"/>
+    </row>
+    <row r="280" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F280"/>
+      <c r="G280"/>
+      <c r="H280"/>
+      <c r="J280"/>
+      <c r="L280"/>
+    </row>
+    <row r="281" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F281"/>
+      <c r="G281"/>
+      <c r="H281"/>
+      <c r="J281"/>
+      <c r="L281"/>
+    </row>
+    <row r="282" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F282"/>
+      <c r="G282"/>
+      <c r="H282"/>
+      <c r="J282"/>
+      <c r="L282"/>
+    </row>
+    <row r="283" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F283"/>
+      <c r="G283"/>
+      <c r="H283"/>
+      <c r="J283"/>
+      <c r="L283"/>
+    </row>
+    <row r="284" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F284"/>
+      <c r="G284"/>
+      <c r="H284"/>
+      <c r="J284"/>
+      <c r="L284"/>
+    </row>
+    <row r="285" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F285"/>
+      <c r="G285"/>
+      <c r="H285"/>
+      <c r="J285"/>
+      <c r="L285"/>
+    </row>
+    <row r="286" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F286"/>
+      <c r="G286"/>
+      <c r="H286"/>
+      <c r="J286"/>
+      <c r="L286"/>
+    </row>
+    <row r="287" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F287"/>
+      <c r="G287"/>
+      <c r="H287"/>
+      <c r="J287"/>
+      <c r="L287"/>
+    </row>
+    <row r="288" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F288"/>
+      <c r="G288"/>
+      <c r="H288"/>
+      <c r="J288"/>
+      <c r="L288"/>
+    </row>
+    <row r="289" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F289"/>
+      <c r="G289"/>
+      <c r="H289"/>
+      <c r="J289"/>
+      <c r="L289"/>
+    </row>
+    <row r="290" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F290"/>
+      <c r="G290"/>
+      <c r="H290"/>
+      <c r="J290"/>
+      <c r="L290"/>
+    </row>
+    <row r="291" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F291"/>
+      <c r="G291"/>
+      <c r="H291"/>
+      <c r="J291"/>
+      <c r="L291"/>
+    </row>
+    <row r="292" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F292"/>
+      <c r="G292"/>
+      <c r="H292"/>
+      <c r="J292"/>
+      <c r="L292"/>
+    </row>
+    <row r="293" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F293"/>
+      <c r="G293"/>
+      <c r="H293"/>
+      <c r="J293"/>
+      <c r="L293"/>
+    </row>
+    <row r="294" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F294"/>
+      <c r="G294"/>
+      <c r="H294"/>
+      <c r="J294"/>
+      <c r="L294"/>
+    </row>
+    <row r="295" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F295"/>
+      <c r="G295"/>
+      <c r="H295"/>
+      <c r="J295"/>
+      <c r="L295"/>
+    </row>
+    <row r="296" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F296"/>
+      <c r="G296"/>
+      <c r="H296"/>
+      <c r="J296"/>
+      <c r="L296"/>
+    </row>
+    <row r="297" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F297"/>
+      <c r="G297"/>
+      <c r="H297"/>
+      <c r="J297"/>
+      <c r="L297"/>
+    </row>
+    <row r="298" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F298"/>
+      <c r="G298"/>
+      <c r="H298"/>
+      <c r="J298"/>
+      <c r="L298"/>
+    </row>
+    <row r="299" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F299"/>
+      <c r="G299"/>
+      <c r="H299"/>
+      <c r="J299"/>
+      <c r="L299"/>
+    </row>
+    <row r="300" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F300"/>
+      <c r="G300"/>
+      <c r="H300"/>
+      <c r="J300"/>
+      <c r="L300"/>
+    </row>
+    <row r="301" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F301"/>
+      <c r="G301"/>
+      <c r="H301"/>
+      <c r="J301"/>
+      <c r="L301"/>
+    </row>
+    <row r="302" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F302"/>
+      <c r="G302"/>
+      <c r="H302"/>
+      <c r="J302"/>
+      <c r="L302"/>
+    </row>
+    <row r="303" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F303"/>
+      <c r="G303"/>
+      <c r="H303"/>
+      <c r="J303"/>
+      <c r="L303"/>
+    </row>
+    <row r="304" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F304"/>
+      <c r="G304"/>
+      <c r="H304"/>
+      <c r="J304"/>
+      <c r="L304"/>
+    </row>
+    <row r="305" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F305"/>
+      <c r="G305"/>
+      <c r="H305"/>
+      <c r="J305"/>
+      <c r="L305"/>
+    </row>
+    <row r="306" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F306"/>
+      <c r="G306"/>
+      <c r="H306"/>
+      <c r="J306"/>
+      <c r="L306"/>
+    </row>
+    <row r="307" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F307"/>
+      <c r="G307"/>
+      <c r="H307"/>
+      <c r="J307"/>
+      <c r="L307"/>
+    </row>
+    <row r="308" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F308"/>
+      <c r="G308"/>
+      <c r="H308"/>
+      <c r="J308"/>
+      <c r="L308"/>
+    </row>
+    <row r="309" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F309"/>
+      <c r="G309"/>
+      <c r="H309"/>
+      <c r="J309"/>
+      <c r="L309"/>
+    </row>
+    <row r="310" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F310"/>
+      <c r="G310"/>
+      <c r="H310"/>
+      <c r="J310"/>
+      <c r="L310"/>
+    </row>
+    <row r="311" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F311"/>
+      <c r="G311"/>
+      <c r="H311"/>
+      <c r="J311"/>
+      <c r="L311"/>
+    </row>
+    <row r="312" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F312"/>
+      <c r="G312"/>
+      <c r="H312"/>
+      <c r="J312"/>
+      <c r="L312"/>
+    </row>
+    <row r="313" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F313"/>
+      <c r="G313"/>
+      <c r="H313"/>
+      <c r="J313"/>
+      <c r="L313"/>
+    </row>
+    <row r="314" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F314"/>
+      <c r="G314"/>
+      <c r="H314"/>
+      <c r="J314"/>
+      <c r="L314"/>
+    </row>
+    <row r="315" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F315"/>
+      <c r="G315"/>
+      <c r="H315"/>
+      <c r="J315"/>
+      <c r="L315"/>
+    </row>
+    <row r="316" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F316"/>
+      <c r="G316"/>
+      <c r="H316"/>
+      <c r="J316"/>
+      <c r="L316"/>
+    </row>
+    <row r="317" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F317"/>
+      <c r="G317"/>
+      <c r="H317"/>
+      <c r="J317"/>
+      <c r="L317"/>
+    </row>
+    <row r="318" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F318"/>
+      <c r="G318"/>
+      <c r="H318"/>
+      <c r="J318"/>
+      <c r="L318"/>
+    </row>
+    <row r="319" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F319"/>
+      <c r="G319"/>
+      <c r="H319"/>
+      <c r="J319"/>
+      <c r="L319"/>
+    </row>
+    <row r="320" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F320"/>
+      <c r="G320"/>
+      <c r="H320"/>
+      <c r="J320"/>
+      <c r="L320"/>
+    </row>
+    <row r="321" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F321"/>
+      <c r="G321"/>
+      <c r="H321"/>
+      <c r="J321"/>
+      <c r="L321"/>
+    </row>
+    <row r="322" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F322"/>
+      <c r="G322"/>
+      <c r="H322"/>
+      <c r="J322"/>
+      <c r="L322"/>
+    </row>
+    <row r="323" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F323"/>
+      <c r="G323"/>
+      <c r="H323"/>
+      <c r="J323"/>
+      <c r="L323"/>
+    </row>
+    <row r="324" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F324"/>
+      <c r="G324"/>
+      <c r="H324"/>
+      <c r="J324"/>
+      <c r="L324"/>
+    </row>
+    <row r="325" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F325"/>
+      <c r="G325"/>
+      <c r="H325"/>
+      <c r="J325"/>
+      <c r="L325"/>
+    </row>
+    <row r="326" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F326"/>
+      <c r="G326"/>
+      <c r="H326"/>
+      <c r="J326"/>
+      <c r="L326"/>
+    </row>
+    <row r="327" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F327"/>
+      <c r="G327"/>
+      <c r="H327"/>
+      <c r="J327"/>
+      <c r="L327"/>
+    </row>
+    <row r="328" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F328"/>
+      <c r="G328"/>
+      <c r="H328"/>
+      <c r="J328"/>
+      <c r="L328"/>
+    </row>
+    <row r="329" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F329"/>
+      <c r="G329"/>
+      <c r="H329"/>
+      <c r="J329"/>
+      <c r="L329"/>
+    </row>
+    <row r="330" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F330"/>
+      <c r="G330"/>
+      <c r="H330"/>
+      <c r="J330"/>
+      <c r="L330"/>
+    </row>
+    <row r="331" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F331"/>
+      <c r="G331"/>
+      <c r="H331"/>
+      <c r="J331"/>
+      <c r="L331"/>
+    </row>
+    <row r="332" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F332"/>
+      <c r="G332"/>
+      <c r="H332"/>
+      <c r="J332"/>
+      <c r="L332"/>
+    </row>
+    <row r="333" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F333"/>
+      <c r="G333"/>
+      <c r="H333"/>
+      <c r="J333"/>
+      <c r="L333"/>
+    </row>
+    <row r="334" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F334"/>
+      <c r="G334"/>
+      <c r="H334"/>
+      <c r="J334"/>
+      <c r="L334"/>
+    </row>
+    <row r="335" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F335"/>
+      <c r="G335"/>
+      <c r="H335"/>
+      <c r="J335"/>
+      <c r="L335"/>
+    </row>
+    <row r="336" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F336"/>
+      <c r="G336"/>
+      <c r="H336"/>
+      <c r="J336"/>
+      <c r="L336"/>
+    </row>
+    <row r="337" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F337"/>
+      <c r="G337"/>
+      <c r="H337"/>
+      <c r="J337"/>
+      <c r="L337"/>
+    </row>
+    <row r="338" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F338"/>
+      <c r="G338"/>
+      <c r="H338"/>
+      <c r="J338"/>
+      <c r="L338"/>
+    </row>
+    <row r="339" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F339"/>
+      <c r="G339"/>
+      <c r="H339"/>
+      <c r="J339"/>
+      <c r="L339"/>
+    </row>
+    <row r="340" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F340"/>
+      <c r="G340"/>
+      <c r="H340"/>
+      <c r="J340"/>
+      <c r="L340"/>
+    </row>
+    <row r="341" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F341"/>
+      <c r="G341"/>
+      <c r="H341"/>
+      <c r="J341"/>
+      <c r="L341"/>
+    </row>
+    <row r="342" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F342"/>
+      <c r="G342"/>
+      <c r="H342"/>
+      <c r="J342"/>
+      <c r="L342"/>
+    </row>
+    <row r="343" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F343"/>
+      <c r="G343"/>
+      <c r="H343"/>
+      <c r="J343"/>
+      <c r="L343"/>
+    </row>
+    <row r="344" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F344"/>
+      <c r="G344"/>
+      <c r="H344"/>
+      <c r="J344"/>
+      <c r="L344"/>
+    </row>
+    <row r="345" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F345"/>
+      <c r="G345"/>
+      <c r="H345"/>
+      <c r="J345"/>
+      <c r="L345"/>
+    </row>
+    <row r="346" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F346"/>
+      <c r="G346"/>
+      <c r="H346"/>
+      <c r="J346"/>
+      <c r="L346"/>
+    </row>
+    <row r="347" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F347"/>
+      <c r="G347"/>
+      <c r="H347"/>
+      <c r="J347"/>
+      <c r="L347"/>
+    </row>
+    <row r="348" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F348"/>
+      <c r="G348"/>
+      <c r="H348"/>
+      <c r="J348"/>
+      <c r="L348"/>
+    </row>
+    <row r="349" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F349"/>
+      <c r="G349"/>
+      <c r="H349"/>
+      <c r="J349"/>
+      <c r="L349"/>
+    </row>
+    <row r="350" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F350"/>
+      <c r="G350"/>
+      <c r="H350"/>
+      <c r="J350"/>
+      <c r="L350"/>
+    </row>
+    <row r="351" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F351"/>
+      <c r="G351"/>
+      <c r="H351"/>
+      <c r="J351"/>
+      <c r="L351"/>
+    </row>
+    <row r="352" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F352"/>
+      <c r="G352"/>
+      <c r="H352"/>
+      <c r="J352"/>
+      <c r="L352"/>
+    </row>
+    <row r="353" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F353"/>
+      <c r="G353"/>
+      <c r="H353"/>
+      <c r="J353"/>
+      <c r="L353"/>
+    </row>
+    <row r="354" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F354"/>
+      <c r="G354"/>
+      <c r="H354"/>
+      <c r="J354"/>
+      <c r="L354"/>
+    </row>
+    <row r="355" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F355"/>
+      <c r="G355"/>
+      <c r="H355"/>
+      <c r="J355"/>
+      <c r="L355"/>
+    </row>
+    <row r="356" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F356"/>
+      <c r="G356"/>
+      <c r="H356"/>
+      <c r="J356"/>
+      <c r="L356"/>
+    </row>
+    <row r="357" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F357"/>
+      <c r="G357"/>
+      <c r="H357"/>
+      <c r="J357"/>
+      <c r="L357"/>
+    </row>
+    <row r="358" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F358"/>
+      <c r="G358"/>
+      <c r="H358"/>
+      <c r="J358"/>
+      <c r="L358"/>
+    </row>
+    <row r="359" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F359"/>
+      <c r="G359"/>
+      <c r="H359"/>
+      <c r="J359"/>
+      <c r="L359"/>
+    </row>
+    <row r="360" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F360"/>
+      <c r="G360"/>
+      <c r="H360"/>
+      <c r="J360"/>
+      <c r="L360"/>
+    </row>
+    <row r="361" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F361"/>
+      <c r="G361"/>
+      <c r="H361"/>
+      <c r="J361"/>
+      <c r="L361"/>
+    </row>
+    <row r="362" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F362"/>
+      <c r="G362"/>
+      <c r="H362"/>
+      <c r="J362"/>
+      <c r="L362"/>
+    </row>
+    <row r="363" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F363"/>
+      <c r="G363"/>
+      <c r="H363"/>
+      <c r="J363"/>
+      <c r="L363"/>
+    </row>
+    <row r="364" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F364"/>
+      <c r="G364"/>
+      <c r="H364"/>
+      <c r="J364"/>
+      <c r="L364"/>
+    </row>
+    <row r="365" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F365"/>
+      <c r="G365"/>
+      <c r="H365"/>
+      <c r="J365"/>
+      <c r="L365"/>
+    </row>
+    <row r="366" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F366"/>
+      <c r="G366"/>
+      <c r="H366"/>
+      <c r="J366"/>
+      <c r="L366"/>
+    </row>
+    <row r="367" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F367"/>
+      <c r="G367"/>
+      <c r="H367"/>
+      <c r="J367"/>
+      <c r="L367"/>
+    </row>
+    <row r="368" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F368"/>
+      <c r="G368"/>
+      <c r="H368"/>
+      <c r="J368"/>
+      <c r="L368"/>
+    </row>
+    <row r="369" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F369"/>
+      <c r="G369"/>
+      <c r="H369"/>
+      <c r="J369"/>
+      <c r="L369"/>
+    </row>
+    <row r="370" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F370"/>
+      <c r="G370"/>
+      <c r="H370"/>
+      <c r="J370"/>
+      <c r="L370"/>
+    </row>
+    <row r="371" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F371"/>
+      <c r="G371"/>
+      <c r="H371"/>
+      <c r="J371"/>
+      <c r="L371"/>
+    </row>
+    <row r="372" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F372"/>
+      <c r="G372"/>
+      <c r="H372"/>
+      <c r="J372"/>
+      <c r="L372"/>
+    </row>
+    <row r="373" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F373"/>
+      <c r="G373"/>
+      <c r="H373"/>
+      <c r="J373"/>
+      <c r="L373"/>
+    </row>
+    <row r="374" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F374"/>
+      <c r="G374"/>
+      <c r="H374"/>
+      <c r="J374"/>
+      <c r="L374"/>
+    </row>
+    <row r="375" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F375"/>
+      <c r="G375"/>
+      <c r="H375"/>
+      <c r="J375"/>
+      <c r="L375"/>
+    </row>
+    <row r="376" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F376"/>
+      <c r="G376"/>
+      <c r="H376"/>
+      <c r="J376"/>
+      <c r="L376"/>
+    </row>
+    <row r="377" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F377"/>
+      <c r="G377"/>
+      <c r="H377"/>
+      <c r="J377"/>
+      <c r="L377"/>
+    </row>
+    <row r="378" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F378"/>
+      <c r="G378"/>
+      <c r="H378"/>
+      <c r="J378"/>
+      <c r="L378"/>
+    </row>
+    <row r="379" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F379"/>
+      <c r="G379"/>
+      <c r="H379"/>
+      <c r="J379"/>
+      <c r="L379"/>
+    </row>
+    <row r="380" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F380"/>
+      <c r="G380"/>
+      <c r="H380"/>
+      <c r="J380"/>
+      <c r="L380"/>
+    </row>
+    <row r="381" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F381"/>
+      <c r="G381"/>
+      <c r="H381"/>
+      <c r="J381"/>
+      <c r="L381"/>
+    </row>
+    <row r="382" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F382"/>
+      <c r="G382"/>
+      <c r="H382"/>
+      <c r="J382"/>
+      <c r="L382"/>
+    </row>
+    <row r="383" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F383"/>
+      <c r="G383"/>
+      <c r="H383"/>
+      <c r="J383"/>
+      <c r="L383"/>
+    </row>
+    <row r="384" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F384"/>
+      <c r="G384"/>
+      <c r="H384"/>
+      <c r="J384"/>
+      <c r="L384"/>
+    </row>
+    <row r="385" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F385"/>
+      <c r="G385"/>
+      <c r="H385"/>
+      <c r="J385"/>
+      <c r="L385"/>
+    </row>
+    <row r="386" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F386"/>
+      <c r="G386"/>
+      <c r="H386"/>
+      <c r="J386"/>
+      <c r="L386"/>
+    </row>
+    <row r="387" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F387"/>
+      <c r="G387"/>
+      <c r="H387"/>
+      <c r="J387"/>
+      <c r="L387"/>
+    </row>
+    <row r="388" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F388"/>
+      <c r="G388"/>
+      <c r="H388"/>
+      <c r="J388"/>
+      <c r="L388"/>
+    </row>
+    <row r="389" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F389"/>
+      <c r="G389"/>
+      <c r="H389"/>
+      <c r="J389"/>
+      <c r="L389"/>
+    </row>
+    <row r="390" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F390"/>
+      <c r="G390"/>
+      <c r="H390"/>
+      <c r="J390"/>
+      <c r="L390"/>
+    </row>
+    <row r="391" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F391"/>
+      <c r="G391"/>
+      <c r="H391"/>
+      <c r="J391"/>
+      <c r="L391"/>
+    </row>
+    <row r="392" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F392"/>
+      <c r="G392"/>
+      <c r="H392"/>
+      <c r="J392"/>
+      <c r="L392"/>
+    </row>
+    <row r="393" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F393"/>
+      <c r="G393"/>
+      <c r="H393"/>
+      <c r="J393"/>
+      <c r="L393"/>
+    </row>
+    <row r="394" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F394"/>
+      <c r="G394"/>
+      <c r="H394"/>
+      <c r="J394"/>
+      <c r="L394"/>
+    </row>
+    <row r="395" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F395"/>
+      <c r="G395"/>
+      <c r="H395"/>
+      <c r="J395"/>
+      <c r="L395"/>
+    </row>
+    <row r="396" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F396"/>
+      <c r="G396"/>
+      <c r="H396"/>
+      <c r="J396"/>
+      <c r="L396"/>
+    </row>
+    <row r="397" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F397"/>
+      <c r="G397"/>
+      <c r="H397"/>
+      <c r="J397"/>
+      <c r="L397"/>
+    </row>
+    <row r="398" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F398"/>
+      <c r="G398"/>
+      <c r="H398"/>
+      <c r="J398"/>
+      <c r="L398"/>
+    </row>
+    <row r="399" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F399"/>
+      <c r="G399"/>
+      <c r="H399"/>
+      <c r="J399"/>
+      <c r="L399"/>
+    </row>
+    <row r="400" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F400"/>
+      <c r="G400"/>
+      <c r="H400"/>
+      <c r="J400"/>
+      <c r="L400"/>
+    </row>
+    <row r="401" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F401"/>
+      <c r="G401"/>
+      <c r="H401"/>
+      <c r="J401"/>
+      <c r="L401"/>
+    </row>
+    <row r="402" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F402"/>
+      <c r="G402"/>
+      <c r="H402"/>
+      <c r="J402"/>
+      <c r="L402"/>
+    </row>
+    <row r="403" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F403"/>
+      <c r="G403"/>
+      <c r="H403"/>
+      <c r="J403"/>
+      <c r="L403"/>
+    </row>
+    <row r="404" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F404"/>
+      <c r="G404"/>
+      <c r="H404"/>
+      <c r="J404"/>
+      <c r="L404"/>
+    </row>
+    <row r="405" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F405"/>
+      <c r="G405"/>
+      <c r="H405"/>
+      <c r="J405"/>
+      <c r="L405"/>
+    </row>
+    <row r="406" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F406"/>
+      <c r="G406"/>
+      <c r="H406"/>
+      <c r="J406"/>
+      <c r="L406"/>
+    </row>
+    <row r="407" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F407"/>
+      <c r="G407"/>
+      <c r="H407"/>
+      <c r="J407"/>
+      <c r="L407"/>
+    </row>
+    <row r="408" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F408"/>
+      <c r="G408"/>
+      <c r="H408"/>
+      <c r="J408"/>
+      <c r="L408"/>
+    </row>
+    <row r="409" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F409"/>
+      <c r="G409"/>
+      <c r="H409"/>
+      <c r="J409"/>
+      <c r="L409"/>
+    </row>
+    <row r="410" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F410"/>
+      <c r="G410"/>
+      <c r="H410"/>
+      <c r="J410"/>
+      <c r="L410"/>
+    </row>
+    <row r="411" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F411"/>
+      <c r="G411"/>
+      <c r="H411"/>
+      <c r="J411"/>
+      <c r="L411"/>
+    </row>
+    <row r="412" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F412"/>
+      <c r="G412"/>
+      <c r="H412"/>
+      <c r="J412"/>
+      <c r="L412"/>
+    </row>
+    <row r="413" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F413"/>
+      <c r="G413"/>
+      <c r="H413"/>
+      <c r="J413"/>
+      <c r="L413"/>
+    </row>
+    <row r="414" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F414"/>
+      <c r="G414"/>
+      <c r="H414"/>
+      <c r="J414"/>
+      <c r="L414"/>
+    </row>
+    <row r="415" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F415"/>
+      <c r="G415"/>
+      <c r="H415"/>
+      <c r="J415"/>
+      <c r="L415"/>
+    </row>
+    <row r="416" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F416"/>
+      <c r="G416"/>
+      <c r="H416"/>
+      <c r="J416"/>
+      <c r="L416"/>
+    </row>
+    <row r="417" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F417"/>
+      <c r="G417"/>
+      <c r="H417"/>
+      <c r="J417"/>
+      <c r="L417"/>
+    </row>
+    <row r="418" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F418"/>
+      <c r="G418"/>
+      <c r="H418"/>
+      <c r="J418"/>
+      <c r="L418"/>
+    </row>
+    <row r="419" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F419"/>
+      <c r="G419"/>
+      <c r="H419"/>
+      <c r="J419"/>
+      <c r="L419"/>
+    </row>
+    <row r="420" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F420"/>
+      <c r="G420"/>
+      <c r="H420"/>
+      <c r="J420"/>
+      <c r="L420"/>
+    </row>
+    <row r="421" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F421"/>
+      <c r="G421"/>
+      <c r="H421"/>
+      <c r="J421"/>
+      <c r="L421"/>
+    </row>
+    <row r="422" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F422"/>
+      <c r="G422"/>
+      <c r="H422"/>
+      <c r="J422"/>
+      <c r="L422"/>
+    </row>
+    <row r="423" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F423"/>
+      <c r="G423"/>
+      <c r="H423"/>
+      <c r="J423"/>
+      <c r="L423"/>
+    </row>
+    <row r="424" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F424"/>
+      <c r="G424"/>
+      <c r="H424"/>
+      <c r="J424"/>
+      <c r="L424"/>
+    </row>
+    <row r="425" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F425"/>
+      <c r="G425"/>
+      <c r="H425"/>
+      <c r="J425"/>
+      <c r="L425"/>
+    </row>
+    <row r="426" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F426"/>
+      <c r="G426"/>
+      <c r="H426"/>
+      <c r="J426"/>
+      <c r="L426"/>
+    </row>
+    <row r="427" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F427"/>
+      <c r="G427"/>
+      <c r="H427"/>
+      <c r="J427"/>
+      <c r="L427"/>
+    </row>
+    <row r="428" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F428"/>
+      <c r="G428"/>
+      <c r="H428"/>
+      <c r="J428"/>
+      <c r="L428"/>
+    </row>
+    <row r="429" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F429"/>
+      <c r="G429"/>
+      <c r="H429"/>
+      <c r="J429"/>
+      <c r="L429"/>
+    </row>
+    <row r="430" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F430"/>
+      <c r="G430"/>
+      <c r="H430"/>
+      <c r="J430"/>
+      <c r="L430"/>
+    </row>
+    <row r="431" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F431"/>
+      <c r="G431"/>
+      <c r="H431"/>
+      <c r="J431"/>
+      <c r="L431"/>
+    </row>
+    <row r="432" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F432"/>
+      <c r="G432"/>
+      <c r="H432"/>
+      <c r="J432"/>
+      <c r="L432"/>
+    </row>
+    <row r="433" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F433"/>
+      <c r="G433"/>
+      <c r="H433"/>
+      <c r="J433"/>
+      <c r="L433"/>
+    </row>
+    <row r="434" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F434"/>
+      <c r="G434"/>
+      <c r="H434"/>
+      <c r="J434"/>
+      <c r="L434"/>
+    </row>
+    <row r="435" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F435"/>
+      <c r="G435"/>
+      <c r="H435"/>
+      <c r="J435"/>
+      <c r="L435"/>
+    </row>
+    <row r="436" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F436"/>
+      <c r="G436"/>
+      <c r="H436"/>
+      <c r="J436"/>
+      <c r="L436"/>
+    </row>
+    <row r="437" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F437"/>
+      <c r="G437"/>
+      <c r="H437"/>
+      <c r="J437"/>
+      <c r="L437"/>
+    </row>
+    <row r="438" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F438"/>
+      <c r="G438"/>
+      <c r="H438"/>
+      <c r="J438"/>
+      <c r="L438"/>
+    </row>
+    <row r="439" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F439"/>
+      <c r="G439"/>
+      <c r="H439"/>
+      <c r="J439"/>
+      <c r="L439"/>
+    </row>
+    <row r="440" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F440"/>
+      <c r="G440"/>
+      <c r="H440"/>
+      <c r="J440"/>
+      <c r="L440"/>
+    </row>
+    <row r="441" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F441"/>
+      <c r="G441"/>
+      <c r="H441"/>
+      <c r="J441"/>
+      <c r="L441"/>
+    </row>
+    <row r="442" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F442"/>
+      <c r="G442"/>
+      <c r="H442"/>
+      <c r="J442"/>
+      <c r="L442"/>
+    </row>
+    <row r="443" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F443"/>
+      <c r="G443"/>
+      <c r="H443"/>
+      <c r="J443"/>
+      <c r="L443"/>
+    </row>
+    <row r="444" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F444"/>
+      <c r="G444"/>
+      <c r="H444"/>
+      <c r="J444"/>
+      <c r="L444"/>
+    </row>
+    <row r="445" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F445"/>
+      <c r="G445"/>
+      <c r="H445"/>
+      <c r="J445"/>
+      <c r="L445"/>
+    </row>
+    <row r="446" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F446"/>
+      <c r="G446"/>
+      <c r="H446"/>
+      <c r="J446"/>
+      <c r="L446"/>
+    </row>
+    <row r="447" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F447"/>
+      <c r="G447"/>
+      <c r="H447"/>
+      <c r="J447"/>
+      <c r="L447"/>
+    </row>
+    <row r="448" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F448"/>
+      <c r="G448"/>
+      <c r="H448"/>
+      <c r="J448"/>
+      <c r="L448"/>
+    </row>
+    <row r="449" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F449"/>
+      <c r="G449"/>
+      <c r="H449"/>
+      <c r="J449"/>
+      <c r="L449"/>
+    </row>
+    <row r="450" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="F450"/>
+      <c r="G450"/>
+      <c r="H450"/>
+      <c r="J450"/>
+      <c r="L450"/>
     </row>
   </sheetData>
   <mergeCells count="1326">
@@ -1753,194 +4938,582 @@
     <mergeCell ref="K450:L450"/>
   </mergeCells>
   <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="E1:N450"/>
-  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nom</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Prénom</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Date de naissance</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Genre</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Adresse</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Classe</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
-  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nom</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Prénom</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Date de naissance</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Genre</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Adresse</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Classe</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nom</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Prénom</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Date de naissance</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Genre</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Adresse</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Classe</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nom</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Prénom</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Date de naissance</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Genre</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Adresse</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Classe</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nom</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Prénom</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Date de naissance</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Genre</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Adresse</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Classe</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Nom</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Prénom</v>
-      </c>
-      <c r="C1" t="str">
-        <v>Date de naissance</v>
-      </c>
-      <c r="D1" t="str">
-        <v>Genre</v>
-      </c>
-      <c r="E1" t="str">
-        <v>Adresse</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Classe</v>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1"/>
-  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/database/datas.xlsx
+++ b/database/datas.xlsx
@@ -3,34 +3,41 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <bookViews>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+  </bookViews>
   <sheets>
     <sheet sheetId="1" name="model" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="1ème Primaire" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="2ème Primaire" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="3ème Primaire" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="4ème Primaire" state="visible" r:id="rId8"/>
-    <sheet sheetId="6" name="5ème Primaire" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="6ème Primaire" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="1ère Maternelle" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="2ème Maternelle" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="3ème Maternelle" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="7ème E.B" state="visible" r:id="rId14"/>
-    <sheet sheetId="12" name="8ème E.B" state="visible" r:id="rId15"/>
-    <sheet sheetId="13" name="1ère Commerciale et Gestion" state="visible" r:id="rId16"/>
-    <sheet sheetId="14" name="2ème Commerciale et Gestion" state="visible" r:id="rId17"/>
-    <sheet sheetId="15" name="3ème Commerciale et Gestion" state="visible" r:id="rId18"/>
-    <sheet sheetId="16" name="4ème Commerciale et Gestion" state="visible" r:id="rId19"/>
-    <sheet sheetId="17" name="1ère Mécanique Générale" state="visible" r:id="rId20"/>
-    <sheet sheetId="18" name="2ème Mécanique Générale" state="visible" r:id="rId21"/>
-    <sheet sheetId="19" name="3ème Mécanique Générale" state="visible" r:id="rId22"/>
-    <sheet sheetId="20" name="4ème Mécanique Générale" state="visible" r:id="rId23"/>
+    <sheet sheetId="2" name="1ère Maternelle" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="2ème Maternelle" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="3ème Maternelle" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="1ème Primaire" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="2ème Primaire" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="3ème Primaire" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="4ème Primaire" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="5ème Primaire" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="6ème Primaire" state="visible" r:id="rId13"/>
+    <sheet sheetId="15" name="7ème E.B" state="visible" r:id="rId14"/>
+    <sheet sheetId="16" name="8ème E.B" state="visible" r:id="rId15"/>
+    <sheet sheetId="11" name="1ère Technique des Coupes &amp; Cou" state="visible" r:id="rId16"/>
+    <sheet sheetId="12" name="2ème Technique des Coupes &amp; Cou" state="visible" r:id="rId17"/>
+    <sheet sheetId="13" name="3ème Technique des Coupes &amp; Cou" state="visible" r:id="rId18"/>
+    <sheet sheetId="14" name="4ème Technique des Coupes &amp; Cou" state="visible" r:id="rId19"/>
+    <sheet sheetId="17" name="1ère Commerciale et Gestion" state="visible" r:id="rId20"/>
+    <sheet sheetId="18" name="2ème Commerciale et Gestion" state="visible" r:id="rId21"/>
+    <sheet sheetId="19" name="3ème Commerciale et Gestion" state="visible" r:id="rId22"/>
+    <sheet sheetId="20" name="4ème Commerciale et Gestion" state="visible" r:id="rId23"/>
+    <sheet sheetId="21" name="1ère Mécanique Générale" state="visible" r:id="rId24"/>
+    <sheet sheetId="22" name="2ème Mécanique Générale" state="visible" r:id="rId25"/>
+    <sheet sheetId="23" name="3ème Mécanique Générale" state="visible" r:id="rId26"/>
+    <sheet sheetId="24" name="4ème Mécanique Générale" state="visible" r:id="rId27"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="6">
   <si>
     <t>Nom</t>
   </si>
@@ -102,7 +109,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -148,13 +155,13 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Angsana New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -177,19 +184,18 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Cordia New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -212,7 +218,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -247,16 +252,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -378,9 +387,226 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+</a:theme>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="1F497D"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="EEECE1"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4F81BD"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="C0504D"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="9BBB59"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8064A2"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4BACC6"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="F79646"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000FF"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="800080"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Arial"/>
+        <a:cs typeface="Arial"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="35000">
+              <a:schemeClr val="phClr">
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="1"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="16200000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="40000">
+              <a:schemeClr val="phClr">
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
   <a:objectDefaults>
     <a:spDef>
-      <a:spPr/>
+      <a:spPr bwMode="auto"/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -399,7 +625,7 @@
       </a:style>
     </a:spDef>
     <a:lnDef>
-      <a:spPr/>
+      <a:spPr bwMode="auto"/>
       <a:bodyPr/>
       <a:lstStyle/>
       <a:style>
@@ -418,14 +644,13 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="E1:N450"/>
-  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0"/>
   <sheetData>
     <row r="1" spans="5:14" x14ac:dyDescent="0.25">
       <c r="F1"/>
@@ -4938,6 +5163,7 @@
     <mergeCell ref="K450:L450"/>
   </mergeCells>
   <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600" verticalDpi="600" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -5254,7 +5480,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -5277,6 +5503,8 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -5311,10 +5539,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -5337,13 +5565,139 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -5366,13 +5720,15 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -5395,13 +5751,15 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -5424,13 +5782,15 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="0" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -5453,6 +5813,8 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 

--- a/database/datas.xlsx
+++ b/database/datas.xlsx
@@ -1,33 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="model" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet sheetId="1" name="model" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t xml:space="preserve">LISTE D'ELEVES</t>
+    <t>LISTE D'ELEVES</t>
   </si>
   <si>
-    <t xml:space="preserve">NOM ET POSTNOM</t>
+    <t>NOM ET POSTNOM</t>
   </si>
   <si>
     <t>PRENOM</t>
   </si>
   <si>
-    <t xml:space="preserve">DATE DE NAISSANCE</t>
+    <t>DATE DE NAISSANCE</t>
   </si>
   <si>
     <t>GENRE</t>
@@ -42,7 +40,7 @@
     <t>OPTION</t>
   </si>
   <si>
-    <t xml:space="preserve">TSHIKAKU TSHITOMBENU</t>
+    <t>TSHIKAKU TSHITOMBENU</t>
   </si>
   <si>
     <t>JEAN</t>
@@ -51,31 +49,38 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
       <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="20.000000"/>
       <color theme="1"/>
+      <sz val="20"/>
       <name val="Fira Code Medium"/>
     </font>
     <font>
-      <sz val="12.000000"/>
       <color theme="1"/>
+      <sz val="12"/>
       <name val="Fira Code Retina"/>
     </font>
     <font>
-      <sz val="12.000000"/>
       <color theme="1"/>
+      <sz val="12"/>
       <name val="Fira Code Light"/>
     </font>
   </fonts>
@@ -93,7 +98,14 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -156,66 +168,66 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="21">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -774,13 +786,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:S1020"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
-    <col min="1" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="16384" width="9.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="14.25">
+    <row r="2" ht="14.25" customHeight="1" spans="6:12" x14ac:dyDescent="0.25">
       <c r="F2" s="2" t="s">
         <v>0</v>
       </c>
@@ -791,7 +804,7 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
-    <row r="3" ht="14.25">
+    <row r="3" ht="14.25" customHeight="1" spans="6:12" x14ac:dyDescent="0.25">
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -800,7 +813,7 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
-    <row r="5" ht="14.25">
+    <row r="5" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>1</v>
       </c>
@@ -834,7 +847,7 @@
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
     </row>
-    <row r="6" ht="14.25">
+    <row r="6" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -854,7 +867,7 @@
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
     </row>
-    <row r="7" ht="15.75">
+    <row r="7" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
         <v>8</v>
       </c>
@@ -880,7 +893,7 @@
       <c r="R7" s="11"/>
       <c r="S7" s="11"/>
     </row>
-    <row r="8" ht="15.75">
+    <row r="8" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="17"/>
@@ -900,7 +913,7 @@
       <c r="R8" s="17"/>
       <c r="S8" s="17"/>
     </row>
-    <row r="9" ht="15.75">
+    <row r="9" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
       <c r="D9" s="17"/>
@@ -920,7 +933,7 @@
       <c r="R9" s="17"/>
       <c r="S9" s="17"/>
     </row>
-    <row r="10" ht="15.75">
+    <row r="10" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
       <c r="D10" s="17"/>
@@ -940,7 +953,7 @@
       <c r="R10" s="17"/>
       <c r="S10" s="17"/>
     </row>
-    <row r="11" ht="15.75">
+    <row r="11" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B11" s="17"/>
       <c r="C11" s="17"/>
       <c r="D11" s="17"/>
@@ -960,7 +973,7 @@
       <c r="R11" s="17"/>
       <c r="S11" s="17"/>
     </row>
-    <row r="12" ht="15.75">
+    <row r="12" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B12" s="17"/>
       <c r="C12" s="17"/>
       <c r="D12" s="17"/>
@@ -980,7 +993,7 @@
       <c r="R12" s="17"/>
       <c r="S12" s="17"/>
     </row>
-    <row r="13" ht="15.75">
+    <row r="13" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B13" s="17"/>
       <c r="C13" s="17"/>
       <c r="D13" s="17"/>
@@ -1000,7 +1013,7 @@
       <c r="R13" s="17"/>
       <c r="S13" s="17"/>
     </row>
-    <row r="14" ht="15.75">
+    <row r="14" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B14" s="17"/>
       <c r="C14" s="17"/>
       <c r="D14" s="17"/>
@@ -1020,7 +1033,7 @@
       <c r="R14" s="17"/>
       <c r="S14" s="17"/>
     </row>
-    <row r="15" ht="15.75">
+    <row r="15" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B15" s="17"/>
       <c r="C15" s="17"/>
       <c r="D15" s="17"/>
@@ -1040,7 +1053,7 @@
       <c r="R15" s="17"/>
       <c r="S15" s="17"/>
     </row>
-    <row r="16" ht="15.75">
+    <row r="16" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B16" s="17"/>
       <c r="C16" s="17"/>
       <c r="D16" s="17"/>
@@ -1060,7 +1073,7 @@
       <c r="R16" s="17"/>
       <c r="S16" s="17"/>
     </row>
-    <row r="17" ht="15.75">
+    <row r="17" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -1080,7 +1093,7 @@
       <c r="R17" s="17"/>
       <c r="S17" s="17"/>
     </row>
-    <row r="18" ht="15.75">
+    <row r="18" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B18" s="17"/>
       <c r="C18" s="17"/>
       <c r="D18" s="17"/>
@@ -1100,7 +1113,7 @@
       <c r="R18" s="17"/>
       <c r="S18" s="17"/>
     </row>
-    <row r="19" ht="15.75">
+    <row r="19" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B19" s="17"/>
       <c r="C19" s="17"/>
       <c r="D19" s="17"/>
@@ -1120,7 +1133,7 @@
       <c r="R19" s="17"/>
       <c r="S19" s="17"/>
     </row>
-    <row r="20" ht="15.75">
+    <row r="20" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B20" s="17"/>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -1140,7 +1153,7 @@
       <c r="R20" s="17"/>
       <c r="S20" s="17"/>
     </row>
-    <row r="21" ht="15.75">
+    <row r="21" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
       <c r="D21" s="17"/>
@@ -1160,7 +1173,7 @@
       <c r="R21" s="17"/>
       <c r="S21" s="17"/>
     </row>
-    <row r="22" ht="15.75">
+    <row r="22" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B22" s="17"/>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
@@ -1180,7 +1193,7 @@
       <c r="R22" s="17"/>
       <c r="S22" s="17"/>
     </row>
-    <row r="23" ht="15.75">
+    <row r="23" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B23" s="17"/>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
@@ -1200,7 +1213,7 @@
       <c r="R23" s="17"/>
       <c r="S23" s="17"/>
     </row>
-    <row r="24" ht="15.75">
+    <row r="24" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
@@ -1220,7 +1233,7 @@
       <c r="R24" s="17"/>
       <c r="S24" s="17"/>
     </row>
-    <row r="25" ht="15.75">
+    <row r="25" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B25" s="17"/>
       <c r="C25" s="17"/>
       <c r="D25" s="17"/>
@@ -1240,7 +1253,7 @@
       <c r="R25" s="17"/>
       <c r="S25" s="17"/>
     </row>
-    <row r="26" ht="15.75">
+    <row r="26" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
       <c r="D26" s="17"/>
@@ -1260,7 +1273,7 @@
       <c r="R26" s="17"/>
       <c r="S26" s="17"/>
     </row>
-    <row r="27" ht="15.75">
+    <row r="27" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B27" s="17"/>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
@@ -1280,7 +1293,7 @@
       <c r="R27" s="17"/>
       <c r="S27" s="17"/>
     </row>
-    <row r="28" ht="15.75">
+    <row r="28" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
       <c r="D28" s="17"/>
@@ -1300,7 +1313,7 @@
       <c r="R28" s="17"/>
       <c r="S28" s="17"/>
     </row>
-    <row r="29" ht="15.75">
+    <row r="29" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B29" s="17"/>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
@@ -1320,7 +1333,7 @@
       <c r="R29" s="17"/>
       <c r="S29" s="17"/>
     </row>
-    <row r="30" ht="15.75">
+    <row r="30" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B30" s="17"/>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -1340,7 +1353,7 @@
       <c r="R30" s="17"/>
       <c r="S30" s="17"/>
     </row>
-    <row r="31" ht="15.75">
+    <row r="31" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B31" s="17"/>
       <c r="C31" s="17"/>
       <c r="D31" s="17"/>
@@ -1360,7 +1373,7 @@
       <c r="R31" s="17"/>
       <c r="S31" s="17"/>
     </row>
-    <row r="32" ht="15.75">
+    <row r="32" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B32" s="17"/>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
@@ -1380,7 +1393,7 @@
       <c r="R32" s="17"/>
       <c r="S32" s="17"/>
     </row>
-    <row r="33" ht="15.75">
+    <row r="33" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B33" s="17"/>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
@@ -1400,7 +1413,7 @@
       <c r="R33" s="17"/>
       <c r="S33" s="17"/>
     </row>
-    <row r="34" ht="15.75">
+    <row r="34" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B34" s="17"/>
       <c r="C34" s="17"/>
       <c r="D34" s="17"/>
@@ -1420,7 +1433,7 @@
       <c r="R34" s="17"/>
       <c r="S34" s="17"/>
     </row>
-    <row r="35" ht="15.75">
+    <row r="35" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B35" s="17"/>
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
@@ -1440,7 +1453,7 @@
       <c r="R35" s="17"/>
       <c r="S35" s="17"/>
     </row>
-    <row r="36" ht="15.75">
+    <row r="36" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B36" s="17"/>
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>
@@ -1460,7 +1473,7 @@
       <c r="R36" s="17"/>
       <c r="S36" s="17"/>
     </row>
-    <row r="37" ht="15.75">
+    <row r="37" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B37" s="17"/>
       <c r="C37" s="17"/>
       <c r="D37" s="17"/>
@@ -1480,7 +1493,7 @@
       <c r="R37" s="17"/>
       <c r="S37" s="17"/>
     </row>
-    <row r="38" ht="15.75">
+    <row r="38" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B38" s="17"/>
       <c r="C38" s="17"/>
       <c r="D38" s="17"/>
@@ -1500,7 +1513,7 @@
       <c r="R38" s="17"/>
       <c r="S38" s="17"/>
     </row>
-    <row r="39" ht="15.75">
+    <row r="39" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B39" s="17"/>
       <c r="C39" s="17"/>
       <c r="D39" s="17"/>
@@ -1520,7 +1533,7 @@
       <c r="R39" s="17"/>
       <c r="S39" s="17"/>
     </row>
-    <row r="40" ht="15.75">
+    <row r="40" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B40" s="17"/>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
@@ -1540,7 +1553,7 @@
       <c r="R40" s="17"/>
       <c r="S40" s="17"/>
     </row>
-    <row r="41" ht="15.75">
+    <row r="41" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B41" s="17"/>
       <c r="C41" s="17"/>
       <c r="D41" s="17"/>
@@ -1560,7 +1573,7 @@
       <c r="R41" s="17"/>
       <c r="S41" s="17"/>
     </row>
-    <row r="42" ht="15.75">
+    <row r="42" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B42" s="17"/>
       <c r="C42" s="17"/>
       <c r="D42" s="17"/>
@@ -1580,7 +1593,7 @@
       <c r="R42" s="17"/>
       <c r="S42" s="17"/>
     </row>
-    <row r="43" ht="15.75">
+    <row r="43" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B43" s="17"/>
       <c r="C43" s="17"/>
       <c r="D43" s="17"/>
@@ -1600,7 +1613,7 @@
       <c r="R43" s="17"/>
       <c r="S43" s="17"/>
     </row>
-    <row r="44" ht="15.75">
+    <row r="44" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B44" s="17"/>
       <c r="C44" s="17"/>
       <c r="D44" s="17"/>
@@ -1620,7 +1633,7 @@
       <c r="R44" s="17"/>
       <c r="S44" s="17"/>
     </row>
-    <row r="45" ht="15.75">
+    <row r="45" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B45" s="17"/>
       <c r="C45" s="17"/>
       <c r="D45" s="17"/>
@@ -1640,7 +1653,7 @@
       <c r="R45" s="17"/>
       <c r="S45" s="17"/>
     </row>
-    <row r="46" ht="15.75">
+    <row r="46" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B46" s="17"/>
       <c r="C46" s="17"/>
       <c r="D46" s="17"/>
@@ -1660,7 +1673,7 @@
       <c r="R46" s="17"/>
       <c r="S46" s="17"/>
     </row>
-    <row r="47" ht="15.75">
+    <row r="47" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B47" s="17"/>
       <c r="C47" s="17"/>
       <c r="D47" s="17"/>
@@ -1680,7 +1693,7 @@
       <c r="R47" s="17"/>
       <c r="S47" s="17"/>
     </row>
-    <row r="48" ht="15.75">
+    <row r="48" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B48" s="17"/>
       <c r="C48" s="17"/>
       <c r="D48" s="17"/>
@@ -1700,7 +1713,7 @@
       <c r="R48" s="17"/>
       <c r="S48" s="17"/>
     </row>
-    <row r="49" ht="15.75">
+    <row r="49" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B49" s="17"/>
       <c r="C49" s="17"/>
       <c r="D49" s="17"/>
@@ -1720,7 +1733,7 @@
       <c r="R49" s="17"/>
       <c r="S49" s="17"/>
     </row>
-    <row r="50" ht="15.75">
+    <row r="50" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B50" s="17"/>
       <c r="C50" s="17"/>
       <c r="D50" s="17"/>
@@ -1740,7 +1753,7 @@
       <c r="R50" s="17"/>
       <c r="S50" s="17"/>
     </row>
-    <row r="51" ht="15.75">
+    <row r="51" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B51" s="17"/>
       <c r="C51" s="17"/>
       <c r="D51" s="17"/>
@@ -1760,7 +1773,7 @@
       <c r="R51" s="17"/>
       <c r="S51" s="17"/>
     </row>
-    <row r="52" ht="15.75">
+    <row r="52" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B52" s="17"/>
       <c r="C52" s="17"/>
       <c r="D52" s="17"/>
@@ -1780,7 +1793,7 @@
       <c r="R52" s="17"/>
       <c r="S52" s="17"/>
     </row>
-    <row r="53" ht="15.75">
+    <row r="53" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B53" s="17"/>
       <c r="C53" s="17"/>
       <c r="D53" s="17"/>
@@ -1800,7 +1813,7 @@
       <c r="R53" s="17"/>
       <c r="S53" s="17"/>
     </row>
-    <row r="54" ht="15.75">
+    <row r="54" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B54" s="17"/>
       <c r="C54" s="17"/>
       <c r="D54" s="17"/>
@@ -1820,7 +1833,7 @@
       <c r="R54" s="17"/>
       <c r="S54" s="17"/>
     </row>
-    <row r="55" ht="15.75">
+    <row r="55" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B55" s="17"/>
       <c r="C55" s="17"/>
       <c r="D55" s="17"/>
@@ -1840,7 +1853,7 @@
       <c r="R55" s="17"/>
       <c r="S55" s="17"/>
     </row>
-    <row r="56" ht="15.75">
+    <row r="56" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B56" s="17"/>
       <c r="C56" s="17"/>
       <c r="D56" s="17"/>
@@ -1860,7 +1873,7 @@
       <c r="R56" s="17"/>
       <c r="S56" s="17"/>
     </row>
-    <row r="57" ht="15.75">
+    <row r="57" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B57" s="17"/>
       <c r="C57" s="17"/>
       <c r="D57" s="17"/>
@@ -1880,7 +1893,7 @@
       <c r="R57" s="17"/>
       <c r="S57" s="17"/>
     </row>
-    <row r="58" ht="15.75">
+    <row r="58" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B58" s="17"/>
       <c r="C58" s="17"/>
       <c r="D58" s="17"/>
@@ -1900,7 +1913,7 @@
       <c r="R58" s="17"/>
       <c r="S58" s="17"/>
     </row>
-    <row r="59" ht="15.75">
+    <row r="59" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B59" s="17"/>
       <c r="C59" s="17"/>
       <c r="D59" s="17"/>
@@ -1920,7 +1933,7 @@
       <c r="R59" s="17"/>
       <c r="S59" s="17"/>
     </row>
-    <row r="60" ht="15.75">
+    <row r="60" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B60" s="17"/>
       <c r="C60" s="17"/>
       <c r="D60" s="17"/>
@@ -1940,7 +1953,7 @@
       <c r="R60" s="17"/>
       <c r="S60" s="17"/>
     </row>
-    <row r="61" ht="15.75">
+    <row r="61" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B61" s="17"/>
       <c r="C61" s="17"/>
       <c r="D61" s="17"/>
@@ -1960,7 +1973,7 @@
       <c r="R61" s="17"/>
       <c r="S61" s="17"/>
     </row>
-    <row r="62" ht="15.75">
+    <row r="62" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B62" s="17"/>
       <c r="C62" s="17"/>
       <c r="D62" s="17"/>
@@ -1980,7 +1993,7 @@
       <c r="R62" s="17"/>
       <c r="S62" s="17"/>
     </row>
-    <row r="63" ht="15.75">
+    <row r="63" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B63" s="17"/>
       <c r="C63" s="17"/>
       <c r="D63" s="17"/>
@@ -2000,7 +2013,7 @@
       <c r="R63" s="17"/>
       <c r="S63" s="17"/>
     </row>
-    <row r="64" ht="15.75">
+    <row r="64" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B64" s="17"/>
       <c r="C64" s="17"/>
       <c r="D64" s="17"/>
@@ -2020,7 +2033,7 @@
       <c r="R64" s="17"/>
       <c r="S64" s="17"/>
     </row>
-    <row r="65" ht="14.25">
+    <row r="65" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B65" s="17"/>
       <c r="C65" s="17"/>
       <c r="D65" s="17"/>
@@ -2040,7 +2053,7 @@
       <c r="R65" s="17"/>
       <c r="S65" s="17"/>
     </row>
-    <row r="66" ht="14.25">
+    <row r="66" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B66" s="17"/>
       <c r="C66" s="17"/>
       <c r="D66" s="17"/>
@@ -2060,7 +2073,7 @@
       <c r="R66" s="17"/>
       <c r="S66" s="17"/>
     </row>
-    <row r="67" ht="14.25">
+    <row r="67" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B67" s="17"/>
       <c r="C67" s="17"/>
       <c r="D67" s="17"/>
@@ -2080,7 +2093,7 @@
       <c r="R67" s="17"/>
       <c r="S67" s="17"/>
     </row>
-    <row r="68" ht="14.25">
+    <row r="68" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B68" s="17"/>
       <c r="C68" s="17"/>
       <c r="D68" s="17"/>
@@ -2100,7 +2113,7 @@
       <c r="R68" s="17"/>
       <c r="S68" s="17"/>
     </row>
-    <row r="69" ht="14.25">
+    <row r="69" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B69" s="17"/>
       <c r="C69" s="17"/>
       <c r="D69" s="17"/>
@@ -2120,7 +2133,7 @@
       <c r="R69" s="17"/>
       <c r="S69" s="17"/>
     </row>
-    <row r="70" ht="14.25">
+    <row r="70" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B70" s="17"/>
       <c r="C70" s="17"/>
       <c r="D70" s="17"/>
@@ -2140,7 +2153,7 @@
       <c r="R70" s="17"/>
       <c r="S70" s="17"/>
     </row>
-    <row r="71" ht="14.25">
+    <row r="71" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B71" s="17"/>
       <c r="C71" s="17"/>
       <c r="D71" s="17"/>
@@ -2160,7 +2173,7 @@
       <c r="R71" s="17"/>
       <c r="S71" s="17"/>
     </row>
-    <row r="72" ht="14.25">
+    <row r="72" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B72" s="17"/>
       <c r="C72" s="17"/>
       <c r="D72" s="17"/>
@@ -2180,7 +2193,7 @@
       <c r="R72" s="17"/>
       <c r="S72" s="17"/>
     </row>
-    <row r="73" ht="14.25">
+    <row r="73" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B73" s="17"/>
       <c r="C73" s="17"/>
       <c r="D73" s="17"/>
@@ -2200,7 +2213,7 @@
       <c r="R73" s="17"/>
       <c r="S73" s="17"/>
     </row>
-    <row r="74" ht="14.25">
+    <row r="74" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B74" s="17"/>
       <c r="C74" s="17"/>
       <c r="D74" s="17"/>
@@ -2220,7 +2233,7 @@
       <c r="R74" s="17"/>
       <c r="S74" s="17"/>
     </row>
-    <row r="75" ht="14.25">
+    <row r="75" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B75" s="17"/>
       <c r="C75" s="17"/>
       <c r="D75" s="17"/>
@@ -2240,7 +2253,7 @@
       <c r="R75" s="17"/>
       <c r="S75" s="17"/>
     </row>
-    <row r="76" ht="14.25">
+    <row r="76" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B76" s="17"/>
       <c r="C76" s="17"/>
       <c r="D76" s="17"/>
@@ -2260,7 +2273,7 @@
       <c r="R76" s="17"/>
       <c r="S76" s="17"/>
     </row>
-    <row r="77" ht="14.25">
+    <row r="77" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B77" s="17"/>
       <c r="C77" s="17"/>
       <c r="D77" s="17"/>
@@ -2280,7 +2293,7 @@
       <c r="R77" s="17"/>
       <c r="S77" s="17"/>
     </row>
-    <row r="78" ht="14.25">
+    <row r="78" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B78" s="17"/>
       <c r="C78" s="17"/>
       <c r="D78" s="17"/>
@@ -2300,7 +2313,7 @@
       <c r="R78" s="17"/>
       <c r="S78" s="17"/>
     </row>
-    <row r="79" ht="14.25">
+    <row r="79" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B79" s="17"/>
       <c r="C79" s="17"/>
       <c r="D79" s="17"/>
@@ -2320,7 +2333,7 @@
       <c r="R79" s="17"/>
       <c r="S79" s="17"/>
     </row>
-    <row r="80" ht="14.25">
+    <row r="80" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B80" s="17"/>
       <c r="C80" s="17"/>
       <c r="D80" s="17"/>
@@ -2340,7 +2353,7 @@
       <c r="R80" s="17"/>
       <c r="S80" s="17"/>
     </row>
-    <row r="81" ht="14.25">
+    <row r="81" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B81" s="17"/>
       <c r="C81" s="17"/>
       <c r="D81" s="17"/>
@@ -2360,7 +2373,7 @@
       <c r="R81" s="17"/>
       <c r="S81" s="17"/>
     </row>
-    <row r="82" ht="14.25">
+    <row r="82" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B82" s="17"/>
       <c r="C82" s="17"/>
       <c r="D82" s="17"/>
@@ -2380,7 +2393,7 @@
       <c r="R82" s="17"/>
       <c r="S82" s="17"/>
     </row>
-    <row r="83" ht="14.25">
+    <row r="83" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B83" s="17"/>
       <c r="C83" s="17"/>
       <c r="D83" s="17"/>
@@ -2400,7 +2413,7 @@
       <c r="R83" s="17"/>
       <c r="S83" s="17"/>
     </row>
-    <row r="84" ht="14.25">
+    <row r="84" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B84" s="17"/>
       <c r="C84" s="17"/>
       <c r="D84" s="17"/>
@@ -2420,7 +2433,7 @@
       <c r="R84" s="17"/>
       <c r="S84" s="17"/>
     </row>
-    <row r="85" ht="14.25">
+    <row r="85" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B85" s="17"/>
       <c r="C85" s="17"/>
       <c r="D85" s="17"/>
@@ -2440,7 +2453,7 @@
       <c r="R85" s="17"/>
       <c r="S85" s="17"/>
     </row>
-    <row r="86" ht="14.25">
+    <row r="86" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B86" s="17"/>
       <c r="C86" s="17"/>
       <c r="D86" s="17"/>
@@ -2460,7 +2473,7 @@
       <c r="R86" s="17"/>
       <c r="S86" s="17"/>
     </row>
-    <row r="87" ht="14.25">
+    <row r="87" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B87" s="17"/>
       <c r="C87" s="17"/>
       <c r="D87" s="17"/>
@@ -2480,7 +2493,7 @@
       <c r="R87" s="17"/>
       <c r="S87" s="17"/>
     </row>
-    <row r="88" ht="14.25">
+    <row r="88" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B88" s="17"/>
       <c r="C88" s="17"/>
       <c r="D88" s="17"/>
@@ -2500,7 +2513,7 @@
       <c r="R88" s="17"/>
       <c r="S88" s="17"/>
     </row>
-    <row r="89" ht="14.25">
+    <row r="89" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B89" s="17"/>
       <c r="C89" s="17"/>
       <c r="D89" s="17"/>
@@ -2520,7 +2533,7 @@
       <c r="R89" s="17"/>
       <c r="S89" s="17"/>
     </row>
-    <row r="90" ht="14.25">
+    <row r="90" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B90" s="17"/>
       <c r="C90" s="17"/>
       <c r="D90" s="17"/>
@@ -2540,7 +2553,7 @@
       <c r="R90" s="17"/>
       <c r="S90" s="17"/>
     </row>
-    <row r="91" ht="14.25">
+    <row r="91" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B91" s="17"/>
       <c r="C91" s="17"/>
       <c r="D91" s="17"/>
@@ -2560,7 +2573,7 @@
       <c r="R91" s="17"/>
       <c r="S91" s="17"/>
     </row>
-    <row r="92" ht="14.25">
+    <row r="92" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B92" s="17"/>
       <c r="C92" s="17"/>
       <c r="D92" s="17"/>
@@ -2580,7 +2593,7 @@
       <c r="R92" s="17"/>
       <c r="S92" s="17"/>
     </row>
-    <row r="93" ht="14.25">
+    <row r="93" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B93" s="17"/>
       <c r="C93" s="17"/>
       <c r="D93" s="17"/>
@@ -2600,7 +2613,7 @@
       <c r="R93" s="17"/>
       <c r="S93" s="17"/>
     </row>
-    <row r="94" ht="14.25">
+    <row r="94" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B94" s="17"/>
       <c r="C94" s="17"/>
       <c r="D94" s="17"/>
@@ -2620,7 +2633,7 @@
       <c r="R94" s="17"/>
       <c r="S94" s="17"/>
     </row>
-    <row r="95" ht="14.25">
+    <row r="95" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B95" s="17"/>
       <c r="C95" s="17"/>
       <c r="D95" s="17"/>
@@ -2640,7 +2653,7 @@
       <c r="R95" s="17"/>
       <c r="S95" s="17"/>
     </row>
-    <row r="96" ht="14.25">
+    <row r="96" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B96" s="17"/>
       <c r="C96" s="17"/>
       <c r="D96" s="17"/>
@@ -2660,7 +2673,7 @@
       <c r="R96" s="17"/>
       <c r="S96" s="17"/>
     </row>
-    <row r="97" ht="14.25">
+    <row r="97" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B97" s="17"/>
       <c r="C97" s="17"/>
       <c r="D97" s="17"/>
@@ -2680,7 +2693,7 @@
       <c r="R97" s="17"/>
       <c r="S97" s="17"/>
     </row>
-    <row r="98" ht="14.25">
+    <row r="98" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B98" s="17"/>
       <c r="C98" s="17"/>
       <c r="D98" s="17"/>
@@ -2700,7 +2713,7 @@
       <c r="R98" s="17"/>
       <c r="S98" s="17"/>
     </row>
-    <row r="99" ht="14.25">
+    <row r="99" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B99" s="17"/>
       <c r="C99" s="17"/>
       <c r="D99" s="17"/>
@@ -2720,7 +2733,7 @@
       <c r="R99" s="17"/>
       <c r="S99" s="17"/>
     </row>
-    <row r="100" ht="14.25">
+    <row r="100" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B100" s="17"/>
       <c r="C100" s="17"/>
       <c r="D100" s="17"/>
@@ -2740,7 +2753,7 @@
       <c r="R100" s="17"/>
       <c r="S100" s="17"/>
     </row>
-    <row r="101" ht="14.25">
+    <row r="101" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B101" s="17"/>
       <c r="C101" s="17"/>
       <c r="D101" s="17"/>
@@ -2760,7 +2773,7 @@
       <c r="R101" s="17"/>
       <c r="S101" s="17"/>
     </row>
-    <row r="102" ht="14.25">
+    <row r="102" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B102" s="17"/>
       <c r="C102" s="17"/>
       <c r="D102" s="17"/>
@@ -2780,7 +2793,7 @@
       <c r="R102" s="17"/>
       <c r="S102" s="17"/>
     </row>
-    <row r="103" ht="14.25">
+    <row r="103" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B103" s="17"/>
       <c r="C103" s="17"/>
       <c r="D103" s="17"/>
@@ -2800,7 +2813,7 @@
       <c r="R103" s="17"/>
       <c r="S103" s="17"/>
     </row>
-    <row r="104" ht="14.25">
+    <row r="104" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B104" s="17"/>
       <c r="C104" s="17"/>
       <c r="D104" s="17"/>
@@ -2820,7 +2833,7 @@
       <c r="R104" s="17"/>
       <c r="S104" s="17"/>
     </row>
-    <row r="105" ht="14.25">
+    <row r="105" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B105" s="17"/>
       <c r="C105" s="17"/>
       <c r="D105" s="17"/>
@@ -2840,7 +2853,7 @@
       <c r="R105" s="17"/>
       <c r="S105" s="17"/>
     </row>
-    <row r="106" ht="14.25">
+    <row r="106" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B106" s="17"/>
       <c r="C106" s="17"/>
       <c r="D106" s="17"/>
@@ -2860,7 +2873,7 @@
       <c r="R106" s="17"/>
       <c r="S106" s="17"/>
     </row>
-    <row r="107" ht="14.25">
+    <row r="107" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B107" s="17"/>
       <c r="C107" s="17"/>
       <c r="D107" s="17"/>
@@ -2880,7 +2893,7 @@
       <c r="R107" s="17"/>
       <c r="S107" s="17"/>
     </row>
-    <row r="108" ht="14.25">
+    <row r="108" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B108" s="17"/>
       <c r="C108" s="17"/>
       <c r="D108" s="17"/>
@@ -2900,7 +2913,7 @@
       <c r="R108" s="17"/>
       <c r="S108" s="17"/>
     </row>
-    <row r="109" ht="14.25">
+    <row r="109" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B109" s="17"/>
       <c r="C109" s="17"/>
       <c r="D109" s="17"/>
@@ -2920,7 +2933,7 @@
       <c r="R109" s="17"/>
       <c r="S109" s="17"/>
     </row>
-    <row r="110" ht="14.25">
+    <row r="110" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B110" s="17"/>
       <c r="C110" s="17"/>
       <c r="D110" s="17"/>
@@ -2940,7 +2953,7 @@
       <c r="R110" s="17"/>
       <c r="S110" s="17"/>
     </row>
-    <row r="111" ht="14.25">
+    <row r="111" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B111" s="17"/>
       <c r="C111" s="17"/>
       <c r="D111" s="17"/>
@@ -2960,7 +2973,7 @@
       <c r="R111" s="17"/>
       <c r="S111" s="17"/>
     </row>
-    <row r="112" ht="14.25">
+    <row r="112" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B112" s="17"/>
       <c r="C112" s="17"/>
       <c r="D112" s="17"/>
@@ -2980,7 +2993,7 @@
       <c r="R112" s="17"/>
       <c r="S112" s="17"/>
     </row>
-    <row r="113" ht="14.25">
+    <row r="113" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B113" s="17"/>
       <c r="C113" s="17"/>
       <c r="D113" s="17"/>
@@ -3000,7 +3013,7 @@
       <c r="R113" s="17"/>
       <c r="S113" s="17"/>
     </row>
-    <row r="114" ht="14.25">
+    <row r="114" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B114" s="17"/>
       <c r="C114" s="17"/>
       <c r="D114" s="17"/>
@@ -3020,7 +3033,7 @@
       <c r="R114" s="17"/>
       <c r="S114" s="17"/>
     </row>
-    <row r="115" ht="14.25">
+    <row r="115" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B115" s="17"/>
       <c r="C115" s="17"/>
       <c r="D115" s="17"/>
@@ -3040,7 +3053,7 @@
       <c r="R115" s="17"/>
       <c r="S115" s="17"/>
     </row>
-    <row r="116" ht="14.25">
+    <row r="116" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B116" s="17"/>
       <c r="C116" s="17"/>
       <c r="D116" s="17"/>
@@ -3060,7 +3073,7 @@
       <c r="R116" s="17"/>
       <c r="S116" s="17"/>
     </row>
-    <row r="117" ht="14.25">
+    <row r="117" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B117" s="17"/>
       <c r="C117" s="17"/>
       <c r="D117" s="17"/>
@@ -3080,7 +3093,7 @@
       <c r="R117" s="17"/>
       <c r="S117" s="17"/>
     </row>
-    <row r="118" ht="14.25">
+    <row r="118" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B118" s="17"/>
       <c r="C118" s="17"/>
       <c r="D118" s="17"/>
@@ -3100,7 +3113,7 @@
       <c r="R118" s="17"/>
       <c r="S118" s="17"/>
     </row>
-    <row r="119" ht="14.25">
+    <row r="119" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B119" s="17"/>
       <c r="C119" s="17"/>
       <c r="D119" s="17"/>
@@ -3120,7 +3133,7 @@
       <c r="R119" s="17"/>
       <c r="S119" s="17"/>
     </row>
-    <row r="120" ht="14.25">
+    <row r="120" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B120" s="17"/>
       <c r="C120" s="17"/>
       <c r="D120" s="17"/>
@@ -3140,7 +3153,7 @@
       <c r="R120" s="17"/>
       <c r="S120" s="17"/>
     </row>
-    <row r="121" ht="14.25">
+    <row r="121" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B121" s="17"/>
       <c r="C121" s="17"/>
       <c r="D121" s="17"/>
@@ -3160,7 +3173,7 @@
       <c r="R121" s="17"/>
       <c r="S121" s="17"/>
     </row>
-    <row r="122" ht="14.25">
+    <row r="122" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B122" s="17"/>
       <c r="C122" s="17"/>
       <c r="D122" s="17"/>
@@ -3180,7 +3193,7 @@
       <c r="R122" s="17"/>
       <c r="S122" s="17"/>
     </row>
-    <row r="123" ht="14.25">
+    <row r="123" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B123" s="17"/>
       <c r="C123" s="17"/>
       <c r="D123" s="17"/>
@@ -3200,7 +3213,7 @@
       <c r="R123" s="17"/>
       <c r="S123" s="17"/>
     </row>
-    <row r="124" ht="14.25">
+    <row r="124" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B124" s="17"/>
       <c r="C124" s="17"/>
       <c r="D124" s="17"/>
@@ -3220,7 +3233,7 @@
       <c r="R124" s="17"/>
       <c r="S124" s="17"/>
     </row>
-    <row r="125" ht="14.25">
+    <row r="125" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B125" s="17"/>
       <c r="C125" s="17"/>
       <c r="D125" s="17"/>
@@ -3240,7 +3253,7 @@
       <c r="R125" s="17"/>
       <c r="S125" s="17"/>
     </row>
-    <row r="126" ht="14.25">
+    <row r="126" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B126" s="17"/>
       <c r="C126" s="17"/>
       <c r="D126" s="17"/>
@@ -3260,7 +3273,7 @@
       <c r="R126" s="17"/>
       <c r="S126" s="17"/>
     </row>
-    <row r="127" ht="14.25">
+    <row r="127" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B127" s="17"/>
       <c r="C127" s="17"/>
       <c r="D127" s="17"/>
@@ -3280,7 +3293,7 @@
       <c r="R127" s="17"/>
       <c r="S127" s="17"/>
     </row>
-    <row r="128" ht="14.25">
+    <row r="128" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B128" s="17"/>
       <c r="C128" s="17"/>
       <c r="D128" s="17"/>
@@ -3300,7 +3313,7 @@
       <c r="R128" s="17"/>
       <c r="S128" s="17"/>
     </row>
-    <row r="129" ht="14.25">
+    <row r="129" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B129" s="17"/>
       <c r="C129" s="17"/>
       <c r="D129" s="17"/>
@@ -3320,7 +3333,7 @@
       <c r="R129" s="17"/>
       <c r="S129" s="17"/>
     </row>
-    <row r="130" ht="14.25">
+    <row r="130" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B130" s="17"/>
       <c r="C130" s="17"/>
       <c r="D130" s="17"/>
@@ -3340,7 +3353,7 @@
       <c r="R130" s="17"/>
       <c r="S130" s="17"/>
     </row>
-    <row r="131" ht="14.25">
+    <row r="131" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B131" s="17"/>
       <c r="C131" s="17"/>
       <c r="D131" s="17"/>
@@ -3360,7 +3373,7 @@
       <c r="R131" s="17"/>
       <c r="S131" s="17"/>
     </row>
-    <row r="132" ht="14.25">
+    <row r="132" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B132" s="17"/>
       <c r="C132" s="17"/>
       <c r="D132" s="17"/>
@@ -3380,7 +3393,7 @@
       <c r="R132" s="17"/>
       <c r="S132" s="17"/>
     </row>
-    <row r="133" ht="14.25">
+    <row r="133" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B133" s="17"/>
       <c r="C133" s="17"/>
       <c r="D133" s="17"/>
@@ -3400,7 +3413,7 @@
       <c r="R133" s="17"/>
       <c r="S133" s="17"/>
     </row>
-    <row r="134" ht="14.25">
+    <row r="134" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B134" s="17"/>
       <c r="C134" s="17"/>
       <c r="D134" s="17"/>
@@ -3420,7 +3433,7 @@
       <c r="R134" s="17"/>
       <c r="S134" s="17"/>
     </row>
-    <row r="135" ht="14.25">
+    <row r="135" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B135" s="17"/>
       <c r="C135" s="17"/>
       <c r="D135" s="17"/>
@@ -3440,7 +3453,7 @@
       <c r="R135" s="17"/>
       <c r="S135" s="17"/>
     </row>
-    <row r="136" ht="14.25">
+    <row r="136" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B136" s="17"/>
       <c r="C136" s="17"/>
       <c r="D136" s="17"/>
@@ -3460,7 +3473,7 @@
       <c r="R136" s="17"/>
       <c r="S136" s="17"/>
     </row>
-    <row r="137" ht="14.25">
+    <row r="137" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B137" s="17"/>
       <c r="C137" s="17"/>
       <c r="D137" s="17"/>
@@ -3480,7 +3493,7 @@
       <c r="R137" s="17"/>
       <c r="S137" s="17"/>
     </row>
-    <row r="138" ht="14.25">
+    <row r="138" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B138" s="17"/>
       <c r="C138" s="17"/>
       <c r="D138" s="17"/>
@@ -3500,7 +3513,7 @@
       <c r="R138" s="17"/>
       <c r="S138" s="17"/>
     </row>
-    <row r="139" ht="14.25">
+    <row r="139" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B139" s="17"/>
       <c r="C139" s="17"/>
       <c r="D139" s="17"/>
@@ -3520,7 +3533,7 @@
       <c r="R139" s="17"/>
       <c r="S139" s="17"/>
     </row>
-    <row r="140" ht="14.25">
+    <row r="140" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B140" s="17"/>
       <c r="C140" s="17"/>
       <c r="D140" s="17"/>
@@ -3540,7 +3553,7 @@
       <c r="R140" s="17"/>
       <c r="S140" s="17"/>
     </row>
-    <row r="141" ht="14.25">
+    <row r="141" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B141" s="17"/>
       <c r="C141" s="17"/>
       <c r="D141" s="17"/>
@@ -3560,7 +3573,7 @@
       <c r="R141" s="17"/>
       <c r="S141" s="17"/>
     </row>
-    <row r="142" ht="14.25">
+    <row r="142" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B142" s="17"/>
       <c r="C142" s="17"/>
       <c r="D142" s="17"/>
@@ -3580,7 +3593,7 @@
       <c r="R142" s="17"/>
       <c r="S142" s="17"/>
     </row>
-    <row r="143" ht="14.25">
+    <row r="143" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B143" s="17"/>
       <c r="C143" s="17"/>
       <c r="D143" s="17"/>
@@ -3600,7 +3613,7 @@
       <c r="R143" s="17"/>
       <c r="S143" s="17"/>
     </row>
-    <row r="144" ht="14.25">
+    <row r="144" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B144" s="17"/>
       <c r="C144" s="17"/>
       <c r="D144" s="17"/>
@@ -3620,7 +3633,7 @@
       <c r="R144" s="17"/>
       <c r="S144" s="17"/>
     </row>
-    <row r="145" ht="14.25">
+    <row r="145" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B145" s="17"/>
       <c r="C145" s="17"/>
       <c r="D145" s="17"/>
@@ -3640,7 +3653,7 @@
       <c r="R145" s="17"/>
       <c r="S145" s="17"/>
     </row>
-    <row r="146" ht="14.25">
+    <row r="146" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B146" s="17"/>
       <c r="C146" s="17"/>
       <c r="D146" s="17"/>
@@ -3660,7 +3673,7 @@
       <c r="R146" s="17"/>
       <c r="S146" s="17"/>
     </row>
-    <row r="147" ht="14.25">
+    <row r="147" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B147" s="17"/>
       <c r="C147" s="17"/>
       <c r="D147" s="17"/>
@@ -3680,7 +3693,7 @@
       <c r="R147" s="17"/>
       <c r="S147" s="17"/>
     </row>
-    <row r="148" ht="14.25">
+    <row r="148" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B148" s="17"/>
       <c r="C148" s="17"/>
       <c r="D148" s="17"/>
@@ -3700,7 +3713,7 @@
       <c r="R148" s="17"/>
       <c r="S148" s="17"/>
     </row>
-    <row r="149" ht="14.25">
+    <row r="149" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B149" s="17"/>
       <c r="C149" s="17"/>
       <c r="D149" s="17"/>
@@ -3720,7 +3733,7 @@
       <c r="R149" s="17"/>
       <c r="S149" s="17"/>
     </row>
-    <row r="150" ht="14.25">
+    <row r="150" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B150" s="17"/>
       <c r="C150" s="17"/>
       <c r="D150" s="17"/>
@@ -3740,7 +3753,7 @@
       <c r="R150" s="17"/>
       <c r="S150" s="17"/>
     </row>
-    <row r="151" ht="14.25">
+    <row r="151" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B151" s="17"/>
       <c r="C151" s="17"/>
       <c r="D151" s="17"/>
@@ -3760,7 +3773,7 @@
       <c r="R151" s="17"/>
       <c r="S151" s="17"/>
     </row>
-    <row r="152" ht="14.25">
+    <row r="152" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B152" s="17"/>
       <c r="C152" s="17"/>
       <c r="D152" s="17"/>
@@ -3780,7 +3793,7 @@
       <c r="R152" s="17"/>
       <c r="S152" s="17"/>
     </row>
-    <row r="153" ht="14.25">
+    <row r="153" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B153" s="17"/>
       <c r="C153" s="17"/>
       <c r="D153" s="17"/>
@@ -3800,7 +3813,7 @@
       <c r="R153" s="17"/>
       <c r="S153" s="17"/>
     </row>
-    <row r="154" ht="14.25">
+    <row r="154" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B154" s="17"/>
       <c r="C154" s="17"/>
       <c r="D154" s="17"/>
@@ -3820,7 +3833,7 @@
       <c r="R154" s="17"/>
       <c r="S154" s="17"/>
     </row>
-    <row r="155" ht="14.25">
+    <row r="155" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B155" s="17"/>
       <c r="C155" s="17"/>
       <c r="D155" s="17"/>
@@ -3840,7 +3853,7 @@
       <c r="R155" s="17"/>
       <c r="S155" s="17"/>
     </row>
-    <row r="156" ht="14.25">
+    <row r="156" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B156" s="17"/>
       <c r="C156" s="17"/>
       <c r="D156" s="17"/>
@@ -3860,7 +3873,7 @@
       <c r="R156" s="17"/>
       <c r="S156" s="17"/>
     </row>
-    <row r="157" ht="14.25">
+    <row r="157" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B157" s="17"/>
       <c r="C157" s="17"/>
       <c r="D157" s="17"/>
@@ -3880,7 +3893,7 @@
       <c r="R157" s="17"/>
       <c r="S157" s="17"/>
     </row>
-    <row r="158" ht="14.25">
+    <row r="158" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B158" s="17"/>
       <c r="C158" s="17"/>
       <c r="D158" s="17"/>
@@ -3900,7 +3913,7 @@
       <c r="R158" s="17"/>
       <c r="S158" s="17"/>
     </row>
-    <row r="159" ht="14.25">
+    <row r="159" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B159" s="17"/>
       <c r="C159" s="17"/>
       <c r="D159" s="17"/>
@@ -3920,7 +3933,7 @@
       <c r="R159" s="17"/>
       <c r="S159" s="17"/>
     </row>
-    <row r="160" ht="14.25">
+    <row r="160" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B160" s="17"/>
       <c r="C160" s="17"/>
       <c r="D160" s="17"/>
@@ -3940,7 +3953,7 @@
       <c r="R160" s="17"/>
       <c r="S160" s="17"/>
     </row>
-    <row r="161" ht="14.25">
+    <row r="161" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B161" s="17"/>
       <c r="C161" s="17"/>
       <c r="D161" s="17"/>
@@ -3960,7 +3973,7 @@
       <c r="R161" s="17"/>
       <c r="S161" s="17"/>
     </row>
-    <row r="162" ht="14.25">
+    <row r="162" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B162" s="17"/>
       <c r="C162" s="17"/>
       <c r="D162" s="17"/>
@@ -3980,7 +3993,7 @@
       <c r="R162" s="17"/>
       <c r="S162" s="17"/>
     </row>
-    <row r="163" ht="14.25">
+    <row r="163" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B163" s="17"/>
       <c r="C163" s="17"/>
       <c r="D163" s="17"/>
@@ -4000,7 +4013,7 @@
       <c r="R163" s="17"/>
       <c r="S163" s="17"/>
     </row>
-    <row r="164" ht="14.25">
+    <row r="164" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B164" s="17"/>
       <c r="C164" s="17"/>
       <c r="D164" s="17"/>
@@ -4020,7 +4033,7 @@
       <c r="R164" s="17"/>
       <c r="S164" s="17"/>
     </row>
-    <row r="165" ht="14.25">
+    <row r="165" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B165" s="17"/>
       <c r="C165" s="17"/>
       <c r="D165" s="17"/>
@@ -4040,7 +4053,7 @@
       <c r="R165" s="17"/>
       <c r="S165" s="17"/>
     </row>
-    <row r="166" ht="14.25">
+    <row r="166" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B166" s="17"/>
       <c r="C166" s="17"/>
       <c r="D166" s="17"/>
@@ -4060,7 +4073,7 @@
       <c r="R166" s="17"/>
       <c r="S166" s="17"/>
     </row>
-    <row r="167" ht="14.25">
+    <row r="167" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B167" s="17"/>
       <c r="C167" s="17"/>
       <c r="D167" s="17"/>
@@ -4080,7 +4093,7 @@
       <c r="R167" s="17"/>
       <c r="S167" s="17"/>
     </row>
-    <row r="168" ht="14.25">
+    <row r="168" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B168" s="17"/>
       <c r="C168" s="17"/>
       <c r="D168" s="17"/>
@@ -4100,7 +4113,7 @@
       <c r="R168" s="17"/>
       <c r="S168" s="17"/>
     </row>
-    <row r="169" ht="14.25">
+    <row r="169" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B169" s="17"/>
       <c r="C169" s="17"/>
       <c r="D169" s="17"/>
@@ -4120,7 +4133,7 @@
       <c r="R169" s="17"/>
       <c r="S169" s="17"/>
     </row>
-    <row r="170" ht="14.25">
+    <row r="170" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B170" s="17"/>
       <c r="C170" s="17"/>
       <c r="D170" s="17"/>
@@ -4140,7 +4153,7 @@
       <c r="R170" s="17"/>
       <c r="S170" s="17"/>
     </row>
-    <row r="171" ht="14.25">
+    <row r="171" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B171" s="17"/>
       <c r="C171" s="17"/>
       <c r="D171" s="17"/>
@@ -4160,7 +4173,7 @@
       <c r="R171" s="17"/>
       <c r="S171" s="17"/>
     </row>
-    <row r="172" ht="14.25">
+    <row r="172" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B172" s="17"/>
       <c r="C172" s="17"/>
       <c r="D172" s="17"/>
@@ -4180,7 +4193,7 @@
       <c r="R172" s="17"/>
       <c r="S172" s="17"/>
     </row>
-    <row r="173" ht="14.25">
+    <row r="173" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B173" s="17"/>
       <c r="C173" s="17"/>
       <c r="D173" s="17"/>
@@ -4200,7 +4213,7 @@
       <c r="R173" s="17"/>
       <c r="S173" s="17"/>
     </row>
-    <row r="174" ht="14.25">
+    <row r="174" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B174" s="17"/>
       <c r="C174" s="17"/>
       <c r="D174" s="17"/>
@@ -4220,7 +4233,7 @@
       <c r="R174" s="17"/>
       <c r="S174" s="17"/>
     </row>
-    <row r="175" ht="14.25">
+    <row r="175" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B175" s="17"/>
       <c r="C175" s="17"/>
       <c r="D175" s="17"/>
@@ -4240,7 +4253,7 @@
       <c r="R175" s="17"/>
       <c r="S175" s="17"/>
     </row>
-    <row r="176" ht="14.25">
+    <row r="176" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B176" s="17"/>
       <c r="C176" s="17"/>
       <c r="D176" s="17"/>
@@ -4260,7 +4273,7 @@
       <c r="R176" s="17"/>
       <c r="S176" s="17"/>
     </row>
-    <row r="177" ht="14.25">
+    <row r="177" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B177" s="17"/>
       <c r="C177" s="17"/>
       <c r="D177" s="17"/>
@@ -4280,7 +4293,7 @@
       <c r="R177" s="17"/>
       <c r="S177" s="17"/>
     </row>
-    <row r="178" ht="14.25">
+    <row r="178" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B178" s="17"/>
       <c r="C178" s="17"/>
       <c r="D178" s="17"/>
@@ -4300,7 +4313,7 @@
       <c r="R178" s="17"/>
       <c r="S178" s="17"/>
     </row>
-    <row r="179" ht="14.25">
+    <row r="179" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B179" s="17"/>
       <c r="C179" s="17"/>
       <c r="D179" s="17"/>
@@ -4320,7 +4333,7 @@
       <c r="R179" s="17"/>
       <c r="S179" s="17"/>
     </row>
-    <row r="180" ht="14.25">
+    <row r="180" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B180" s="17"/>
       <c r="C180" s="17"/>
       <c r="D180" s="17"/>
@@ -4340,7 +4353,7 @@
       <c r="R180" s="17"/>
       <c r="S180" s="17"/>
     </row>
-    <row r="181" ht="14.25">
+    <row r="181" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B181" s="17"/>
       <c r="C181" s="17"/>
       <c r="D181" s="17"/>
@@ -4360,7 +4373,7 @@
       <c r="R181" s="17"/>
       <c r="S181" s="17"/>
     </row>
-    <row r="182" ht="14.25">
+    <row r="182" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B182" s="17"/>
       <c r="C182" s="17"/>
       <c r="D182" s="17"/>
@@ -4380,7 +4393,7 @@
       <c r="R182" s="17"/>
       <c r="S182" s="17"/>
     </row>
-    <row r="183" ht="14.25">
+    <row r="183" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B183" s="17"/>
       <c r="C183" s="17"/>
       <c r="D183" s="17"/>
@@ -4400,7 +4413,7 @@
       <c r="R183" s="17"/>
       <c r="S183" s="17"/>
     </row>
-    <row r="184" ht="14.25">
+    <row r="184" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B184" s="17"/>
       <c r="C184" s="17"/>
       <c r="D184" s="17"/>
@@ -4420,7 +4433,7 @@
       <c r="R184" s="17"/>
       <c r="S184" s="17"/>
     </row>
-    <row r="185" ht="14.25">
+    <row r="185" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B185" s="17"/>
       <c r="C185" s="17"/>
       <c r="D185" s="17"/>
@@ -4440,7 +4453,7 @@
       <c r="R185" s="17"/>
       <c r="S185" s="17"/>
     </row>
-    <row r="186" ht="14.25">
+    <row r="186" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B186" s="17"/>
       <c r="C186" s="17"/>
       <c r="D186" s="17"/>
@@ -4460,7 +4473,7 @@
       <c r="R186" s="17"/>
       <c r="S186" s="17"/>
     </row>
-    <row r="187" ht="14.25">
+    <row r="187" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B187" s="17"/>
       <c r="C187" s="17"/>
       <c r="D187" s="17"/>
@@ -4480,7 +4493,7 @@
       <c r="R187" s="17"/>
       <c r="S187" s="17"/>
     </row>
-    <row r="188" ht="14.25">
+    <row r="188" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B188" s="17"/>
       <c r="C188" s="17"/>
       <c r="D188" s="17"/>
@@ -4500,7 +4513,7 @@
       <c r="R188" s="17"/>
       <c r="S188" s="17"/>
     </row>
-    <row r="189" ht="14.25">
+    <row r="189" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B189" s="17"/>
       <c r="C189" s="17"/>
       <c r="D189" s="17"/>
@@ -4520,7 +4533,7 @@
       <c r="R189" s="17"/>
       <c r="S189" s="17"/>
     </row>
-    <row r="190" ht="14.25">
+    <row r="190" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B190" s="17"/>
       <c r="C190" s="17"/>
       <c r="D190" s="17"/>
@@ -4540,7 +4553,7 @@
       <c r="R190" s="17"/>
       <c r="S190" s="17"/>
     </row>
-    <row r="191" ht="14.25">
+    <row r="191" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B191" s="17"/>
       <c r="C191" s="17"/>
       <c r="D191" s="17"/>
@@ -4560,7 +4573,7 @@
       <c r="R191" s="17"/>
       <c r="S191" s="17"/>
     </row>
-    <row r="192" ht="14.25">
+    <row r="192" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B192" s="17"/>
       <c r="C192" s="17"/>
       <c r="D192" s="17"/>
@@ -4580,7 +4593,7 @@
       <c r="R192" s="17"/>
       <c r="S192" s="17"/>
     </row>
-    <row r="193" ht="14.25">
+    <row r="193" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B193" s="17"/>
       <c r="C193" s="17"/>
       <c r="D193" s="17"/>
@@ -4600,7 +4613,7 @@
       <c r="R193" s="17"/>
       <c r="S193" s="17"/>
     </row>
-    <row r="194" ht="14.25">
+    <row r="194" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B194" s="17"/>
       <c r="C194" s="17"/>
       <c r="D194" s="17"/>
@@ -4620,7 +4633,7 @@
       <c r="R194" s="17"/>
       <c r="S194" s="17"/>
     </row>
-    <row r="195" ht="14.25">
+    <row r="195" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B195" s="17"/>
       <c r="C195" s="17"/>
       <c r="D195" s="17"/>
@@ -4640,7 +4653,7 @@
       <c r="R195" s="17"/>
       <c r="S195" s="17"/>
     </row>
-    <row r="196" ht="14.25">
+    <row r="196" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B196" s="17"/>
       <c r="C196" s="17"/>
       <c r="D196" s="17"/>
@@ -4660,7 +4673,7 @@
       <c r="R196" s="17"/>
       <c r="S196" s="17"/>
     </row>
-    <row r="197" ht="14.25">
+    <row r="197" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B197" s="17"/>
       <c r="C197" s="17"/>
       <c r="D197" s="17"/>
@@ -4680,7 +4693,7 @@
       <c r="R197" s="17"/>
       <c r="S197" s="17"/>
     </row>
-    <row r="198" ht="14.25">
+    <row r="198" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B198" s="17"/>
       <c r="C198" s="17"/>
       <c r="D198" s="17"/>
@@ -4700,7 +4713,7 @@
       <c r="R198" s="17"/>
       <c r="S198" s="17"/>
     </row>
-    <row r="199" ht="14.25">
+    <row r="199" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B199" s="17"/>
       <c r="C199" s="17"/>
       <c r="D199" s="17"/>
@@ -4720,7 +4733,7 @@
       <c r="R199" s="17"/>
       <c r="S199" s="17"/>
     </row>
-    <row r="200" ht="14.25">
+    <row r="200" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B200" s="17"/>
       <c r="C200" s="17"/>
       <c r="D200" s="17"/>
@@ -4740,7 +4753,7 @@
       <c r="R200" s="17"/>
       <c r="S200" s="17"/>
     </row>
-    <row r="201" ht="14.25">
+    <row r="201" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B201" s="17"/>
       <c r="C201" s="17"/>
       <c r="D201" s="17"/>
@@ -4760,7 +4773,7 @@
       <c r="R201" s="17"/>
       <c r="S201" s="17"/>
     </row>
-    <row r="202" ht="14.25">
+    <row r="202" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B202" s="17"/>
       <c r="C202" s="17"/>
       <c r="D202" s="17"/>
@@ -4780,7 +4793,7 @@
       <c r="R202" s="17"/>
       <c r="S202" s="17"/>
     </row>
-    <row r="203" ht="14.25">
+    <row r="203" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B203" s="17"/>
       <c r="C203" s="17"/>
       <c r="D203" s="17"/>
@@ -4800,7 +4813,7 @@
       <c r="R203" s="17"/>
       <c r="S203" s="17"/>
     </row>
-    <row r="204" ht="14.25">
+    <row r="204" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B204" s="17"/>
       <c r="C204" s="17"/>
       <c r="D204" s="17"/>
@@ -4820,7 +4833,7 @@
       <c r="R204" s="17"/>
       <c r="S204" s="17"/>
     </row>
-    <row r="205" ht="14.25">
+    <row r="205" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B205" s="17"/>
       <c r="C205" s="17"/>
       <c r="D205" s="17"/>
@@ -4840,7 +4853,7 @@
       <c r="R205" s="17"/>
       <c r="S205" s="17"/>
     </row>
-    <row r="206" ht="14.25">
+    <row r="206" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B206" s="17"/>
       <c r="C206" s="17"/>
       <c r="D206" s="17"/>
@@ -4860,7 +4873,7 @@
       <c r="R206" s="17"/>
       <c r="S206" s="17"/>
     </row>
-    <row r="207" ht="14.25">
+    <row r="207" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B207" s="17"/>
       <c r="C207" s="17"/>
       <c r="D207" s="17"/>
@@ -4880,7 +4893,7 @@
       <c r="R207" s="17"/>
       <c r="S207" s="17"/>
     </row>
-    <row r="208" ht="14.25">
+    <row r="208" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B208" s="17"/>
       <c r="C208" s="17"/>
       <c r="D208" s="17"/>
@@ -4900,7 +4913,7 @@
       <c r="R208" s="17"/>
       <c r="S208" s="17"/>
     </row>
-    <row r="209" ht="14.25">
+    <row r="209" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B209" s="17"/>
       <c r="C209" s="17"/>
       <c r="D209" s="17"/>
@@ -4920,7 +4933,7 @@
       <c r="R209" s="17"/>
       <c r="S209" s="17"/>
     </row>
-    <row r="210" ht="14.25">
+    <row r="210" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B210" s="17"/>
       <c r="C210" s="17"/>
       <c r="D210" s="17"/>
@@ -4940,7 +4953,7 @@
       <c r="R210" s="17"/>
       <c r="S210" s="17"/>
     </row>
-    <row r="211" ht="14.25">
+    <row r="211" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B211" s="17"/>
       <c r="C211" s="17"/>
       <c r="D211" s="17"/>
@@ -4960,7 +4973,7 @@
       <c r="R211" s="17"/>
       <c r="S211" s="17"/>
     </row>
-    <row r="212" ht="14.25">
+    <row r="212" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B212" s="17"/>
       <c r="C212" s="17"/>
       <c r="D212" s="17"/>
@@ -4980,7 +4993,7 @@
       <c r="R212" s="17"/>
       <c r="S212" s="17"/>
     </row>
-    <row r="213" ht="14.25">
+    <row r="213" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B213" s="17"/>
       <c r="C213" s="17"/>
       <c r="D213" s="17"/>
@@ -5000,7 +5013,7 @@
       <c r="R213" s="17"/>
       <c r="S213" s="17"/>
     </row>
-    <row r="214" ht="14.25">
+    <row r="214" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B214" s="17"/>
       <c r="C214" s="17"/>
       <c r="D214" s="17"/>
@@ -5020,7 +5033,7 @@
       <c r="R214" s="17"/>
       <c r="S214" s="17"/>
     </row>
-    <row r="215" ht="14.25">
+    <row r="215" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B215" s="17"/>
       <c r="C215" s="17"/>
       <c r="D215" s="17"/>
@@ -5040,7 +5053,7 @@
       <c r="R215" s="17"/>
       <c r="S215" s="17"/>
     </row>
-    <row r="216" ht="14.25">
+    <row r="216" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B216" s="17"/>
       <c r="C216" s="17"/>
       <c r="D216" s="17"/>
@@ -5060,7 +5073,7 @@
       <c r="R216" s="17"/>
       <c r="S216" s="17"/>
     </row>
-    <row r="217" ht="14.25">
+    <row r="217" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B217" s="17"/>
       <c r="C217" s="17"/>
       <c r="D217" s="17"/>
@@ -5080,7 +5093,7 @@
       <c r="R217" s="17"/>
       <c r="S217" s="17"/>
     </row>
-    <row r="218" ht="14.25">
+    <row r="218" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B218" s="17"/>
       <c r="C218" s="17"/>
       <c r="D218" s="17"/>
@@ -5100,7 +5113,7 @@
       <c r="R218" s="17"/>
       <c r="S218" s="17"/>
     </row>
-    <row r="219" ht="14.25">
+    <row r="219" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B219" s="17"/>
       <c r="C219" s="17"/>
       <c r="D219" s="17"/>
@@ -5120,7 +5133,7 @@
       <c r="R219" s="17"/>
       <c r="S219" s="17"/>
     </row>
-    <row r="220" ht="14.25">
+    <row r="220" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B220" s="17"/>
       <c r="C220" s="17"/>
       <c r="D220" s="17"/>
@@ -5140,7 +5153,7 @@
       <c r="R220" s="17"/>
       <c r="S220" s="17"/>
     </row>
-    <row r="221" ht="14.25">
+    <row r="221" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B221" s="17"/>
       <c r="C221" s="17"/>
       <c r="D221" s="17"/>
@@ -5160,7 +5173,7 @@
       <c r="R221" s="17"/>
       <c r="S221" s="17"/>
     </row>
-    <row r="222" ht="14.25">
+    <row r="222" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B222" s="17"/>
       <c r="C222" s="17"/>
       <c r="D222" s="17"/>
@@ -5180,7 +5193,7 @@
       <c r="R222" s="17"/>
       <c r="S222" s="17"/>
     </row>
-    <row r="223" ht="14.25">
+    <row r="223" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B223" s="17"/>
       <c r="C223" s="17"/>
       <c r="D223" s="17"/>
@@ -5200,7 +5213,7 @@
       <c r="R223" s="17"/>
       <c r="S223" s="17"/>
     </row>
-    <row r="224" ht="14.25">
+    <row r="224" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B224" s="17"/>
       <c r="C224" s="17"/>
       <c r="D224" s="17"/>
@@ -5220,7 +5233,7 @@
       <c r="R224" s="17"/>
       <c r="S224" s="17"/>
     </row>
-    <row r="225" ht="14.25">
+    <row r="225" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B225" s="17"/>
       <c r="C225" s="17"/>
       <c r="D225" s="17"/>
@@ -5240,7 +5253,7 @@
       <c r="R225" s="17"/>
       <c r="S225" s="17"/>
     </row>
-    <row r="226" ht="14.25">
+    <row r="226" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B226" s="17"/>
       <c r="C226" s="17"/>
       <c r="D226" s="17"/>
@@ -5260,7 +5273,7 @@
       <c r="R226" s="17"/>
       <c r="S226" s="17"/>
     </row>
-    <row r="227" ht="14.25">
+    <row r="227" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B227" s="17"/>
       <c r="C227" s="17"/>
       <c r="D227" s="17"/>
@@ -5280,7 +5293,7 @@
       <c r="R227" s="17"/>
       <c r="S227" s="17"/>
     </row>
-    <row r="228" ht="14.25">
+    <row r="228" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B228" s="17"/>
       <c r="C228" s="17"/>
       <c r="D228" s="17"/>
@@ -5300,7 +5313,7 @@
       <c r="R228" s="17"/>
       <c r="S228" s="17"/>
     </row>
-    <row r="229" ht="14.25">
+    <row r="229" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B229" s="17"/>
       <c r="C229" s="17"/>
       <c r="D229" s="17"/>
@@ -5320,7 +5333,7 @@
       <c r="R229" s="17"/>
       <c r="S229" s="17"/>
     </row>
-    <row r="230" ht="14.25">
+    <row r="230" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B230" s="17"/>
       <c r="C230" s="17"/>
       <c r="D230" s="17"/>
@@ -5340,7 +5353,7 @@
       <c r="R230" s="17"/>
       <c r="S230" s="17"/>
     </row>
-    <row r="231" ht="14.25">
+    <row r="231" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B231" s="17"/>
       <c r="C231" s="17"/>
       <c r="D231" s="17"/>
@@ -5360,7 +5373,7 @@
       <c r="R231" s="17"/>
       <c r="S231" s="17"/>
     </row>
-    <row r="232" ht="14.25">
+    <row r="232" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B232" s="17"/>
       <c r="C232" s="17"/>
       <c r="D232" s="17"/>
@@ -5380,7 +5393,7 @@
       <c r="R232" s="17"/>
       <c r="S232" s="17"/>
     </row>
-    <row r="233" ht="14.25">
+    <row r="233" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B233" s="17"/>
       <c r="C233" s="17"/>
       <c r="D233" s="17"/>
@@ -5400,7 +5413,7 @@
       <c r="R233" s="17"/>
       <c r="S233" s="17"/>
     </row>
-    <row r="234" ht="14.25">
+    <row r="234" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B234" s="17"/>
       <c r="C234" s="17"/>
       <c r="D234" s="17"/>
@@ -5420,7 +5433,7 @@
       <c r="R234" s="17"/>
       <c r="S234" s="17"/>
     </row>
-    <row r="235" ht="14.25">
+    <row r="235" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B235" s="17"/>
       <c r="C235" s="17"/>
       <c r="D235" s="17"/>
@@ -5440,7 +5453,7 @@
       <c r="R235" s="17"/>
       <c r="S235" s="17"/>
     </row>
-    <row r="236" ht="14.25">
+    <row r="236" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B236" s="17"/>
       <c r="C236" s="17"/>
       <c r="D236" s="17"/>
@@ -5460,7 +5473,7 @@
       <c r="R236" s="17"/>
       <c r="S236" s="17"/>
     </row>
-    <row r="237" ht="14.25">
+    <row r="237" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B237" s="17"/>
       <c r="C237" s="17"/>
       <c r="D237" s="17"/>
@@ -5480,7 +5493,7 @@
       <c r="R237" s="17"/>
       <c r="S237" s="17"/>
     </row>
-    <row r="238" ht="14.25">
+    <row r="238" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B238" s="17"/>
       <c r="C238" s="17"/>
       <c r="D238" s="17"/>
@@ -5500,7 +5513,7 @@
       <c r="R238" s="17"/>
       <c r="S238" s="17"/>
     </row>
-    <row r="239" ht="14.25">
+    <row r="239" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B239" s="17"/>
       <c r="C239" s="17"/>
       <c r="D239" s="17"/>
@@ -5520,7 +5533,7 @@
       <c r="R239" s="17"/>
       <c r="S239" s="17"/>
     </row>
-    <row r="240" ht="14.25">
+    <row r="240" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B240" s="17"/>
       <c r="C240" s="17"/>
       <c r="D240" s="17"/>
@@ -5540,7 +5553,7 @@
       <c r="R240" s="17"/>
       <c r="S240" s="17"/>
     </row>
-    <row r="241" ht="14.25">
+    <row r="241" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B241" s="17"/>
       <c r="C241" s="17"/>
       <c r="D241" s="17"/>
@@ -5560,7 +5573,7 @@
       <c r="R241" s="17"/>
       <c r="S241" s="17"/>
     </row>
-    <row r="242" ht="14.25">
+    <row r="242" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B242" s="17"/>
       <c r="C242" s="17"/>
       <c r="D242" s="17"/>
@@ -5580,7 +5593,7 @@
       <c r="R242" s="17"/>
       <c r="S242" s="17"/>
     </row>
-    <row r="243" ht="14.25">
+    <row r="243" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B243" s="17"/>
       <c r="C243" s="17"/>
       <c r="D243" s="17"/>
@@ -5600,7 +5613,7 @@
       <c r="R243" s="17"/>
       <c r="S243" s="17"/>
     </row>
-    <row r="244" ht="14.25">
+    <row r="244" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B244" s="17"/>
       <c r="C244" s="17"/>
       <c r="D244" s="17"/>
@@ -5620,7 +5633,7 @@
       <c r="R244" s="17"/>
       <c r="S244" s="17"/>
     </row>
-    <row r="245" ht="14.25">
+    <row r="245" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B245" s="17"/>
       <c r="C245" s="17"/>
       <c r="D245" s="17"/>
@@ -5640,7 +5653,7 @@
       <c r="R245" s="17"/>
       <c r="S245" s="17"/>
     </row>
-    <row r="246" ht="14.25">
+    <row r="246" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B246" s="17"/>
       <c r="C246" s="17"/>
       <c r="D246" s="17"/>
@@ -5660,7 +5673,7 @@
       <c r="R246" s="17"/>
       <c r="S246" s="17"/>
     </row>
-    <row r="247" ht="14.25">
+    <row r="247" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B247" s="17"/>
       <c r="C247" s="17"/>
       <c r="D247" s="17"/>
@@ -5680,7 +5693,7 @@
       <c r="R247" s="17"/>
       <c r="S247" s="17"/>
     </row>
-    <row r="248" ht="14.25">
+    <row r="248" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B248" s="17"/>
       <c r="C248" s="17"/>
       <c r="D248" s="17"/>
@@ -5700,7 +5713,7 @@
       <c r="R248" s="17"/>
       <c r="S248" s="17"/>
     </row>
-    <row r="249" ht="14.25">
+    <row r="249" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B249" s="17"/>
       <c r="C249" s="17"/>
       <c r="D249" s="17"/>
@@ -5720,7 +5733,7 @@
       <c r="R249" s="17"/>
       <c r="S249" s="17"/>
     </row>
-    <row r="250" ht="14.25">
+    <row r="250" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B250" s="17"/>
       <c r="C250" s="17"/>
       <c r="D250" s="17"/>
@@ -5740,7 +5753,7 @@
       <c r="R250" s="17"/>
       <c r="S250" s="17"/>
     </row>
-    <row r="251" ht="14.25">
+    <row r="251" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B251" s="17"/>
       <c r="C251" s="17"/>
       <c r="D251" s="17"/>
@@ -5760,7 +5773,7 @@
       <c r="R251" s="17"/>
       <c r="S251" s="17"/>
     </row>
-    <row r="252" ht="14.25">
+    <row r="252" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B252" s="17"/>
       <c r="C252" s="17"/>
       <c r="D252" s="17"/>
@@ -5780,7 +5793,7 @@
       <c r="R252" s="17"/>
       <c r="S252" s="17"/>
     </row>
-    <row r="253" ht="14.25">
+    <row r="253" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B253" s="17"/>
       <c r="C253" s="17"/>
       <c r="D253" s="17"/>
@@ -5800,7 +5813,7 @@
       <c r="R253" s="17"/>
       <c r="S253" s="17"/>
     </row>
-    <row r="254" ht="14.25">
+    <row r="254" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B254" s="17"/>
       <c r="C254" s="17"/>
       <c r="D254" s="17"/>
@@ -5820,7 +5833,7 @@
       <c r="R254" s="17"/>
       <c r="S254" s="17"/>
     </row>
-    <row r="255" ht="14.25">
+    <row r="255" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B255" s="17"/>
       <c r="C255" s="17"/>
       <c r="D255" s="17"/>
@@ -5840,7 +5853,7 @@
       <c r="R255" s="17"/>
       <c r="S255" s="17"/>
     </row>
-    <row r="256" ht="14.25">
+    <row r="256" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B256" s="17"/>
       <c r="C256" s="17"/>
       <c r="D256" s="17"/>
@@ -5860,7 +5873,7 @@
       <c r="R256" s="17"/>
       <c r="S256" s="17"/>
     </row>
-    <row r="257" ht="14.25">
+    <row r="257" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B257" s="17"/>
       <c r="C257" s="17"/>
       <c r="D257" s="17"/>
@@ -5880,7 +5893,7 @@
       <c r="R257" s="17"/>
       <c r="S257" s="17"/>
     </row>
-    <row r="258" ht="14.25">
+    <row r="258" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B258" s="17"/>
       <c r="C258" s="17"/>
       <c r="D258" s="17"/>
@@ -5900,7 +5913,7 @@
       <c r="R258" s="17"/>
       <c r="S258" s="17"/>
     </row>
-    <row r="259" ht="14.25">
+    <row r="259" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B259" s="17"/>
       <c r="C259" s="17"/>
       <c r="D259" s="17"/>
@@ -5920,7 +5933,7 @@
       <c r="R259" s="17"/>
       <c r="S259" s="17"/>
     </row>
-    <row r="260" ht="14.25">
+    <row r="260" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B260" s="17"/>
       <c r="C260" s="17"/>
       <c r="D260" s="17"/>
@@ -5940,7 +5953,7 @@
       <c r="R260" s="17"/>
       <c r="S260" s="17"/>
     </row>
-    <row r="261" ht="14.25">
+    <row r="261" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B261" s="17"/>
       <c r="C261" s="17"/>
       <c r="D261" s="17"/>
@@ -5960,7 +5973,7 @@
       <c r="R261" s="17"/>
       <c r="S261" s="17"/>
     </row>
-    <row r="262" ht="14.25">
+    <row r="262" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B262" s="17"/>
       <c r="C262" s="17"/>
       <c r="D262" s="17"/>
@@ -5980,7 +5993,7 @@
       <c r="R262" s="17"/>
       <c r="S262" s="17"/>
     </row>
-    <row r="263" ht="14.25">
+    <row r="263" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B263" s="17"/>
       <c r="C263" s="17"/>
       <c r="D263" s="17"/>
@@ -6000,7 +6013,7 @@
       <c r="R263" s="17"/>
       <c r="S263" s="17"/>
     </row>
-    <row r="264" ht="14.25">
+    <row r="264" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B264" s="17"/>
       <c r="C264" s="17"/>
       <c r="D264" s="17"/>
@@ -6020,7 +6033,7 @@
       <c r="R264" s="17"/>
       <c r="S264" s="17"/>
     </row>
-    <row r="265" ht="14.25">
+    <row r="265" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B265" s="17"/>
       <c r="C265" s="17"/>
       <c r="D265" s="17"/>
@@ -6040,7 +6053,7 @@
       <c r="R265" s="17"/>
       <c r="S265" s="17"/>
     </row>
-    <row r="266" ht="14.25">
+    <row r="266" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B266" s="17"/>
       <c r="C266" s="17"/>
       <c r="D266" s="17"/>
@@ -6060,7 +6073,7 @@
       <c r="R266" s="17"/>
       <c r="S266" s="17"/>
     </row>
-    <row r="267" ht="14.25">
+    <row r="267" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B267" s="17"/>
       <c r="C267" s="17"/>
       <c r="D267" s="17"/>
@@ -6080,7 +6093,7 @@
       <c r="R267" s="17"/>
       <c r="S267" s="17"/>
     </row>
-    <row r="268" ht="14.25">
+    <row r="268" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B268" s="17"/>
       <c r="C268" s="17"/>
       <c r="D268" s="17"/>
@@ -6100,7 +6113,7 @@
       <c r="R268" s="17"/>
       <c r="S268" s="17"/>
     </row>
-    <row r="269" ht="14.25">
+    <row r="269" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B269" s="17"/>
       <c r="C269" s="17"/>
       <c r="D269" s="17"/>
@@ -6120,7 +6133,7 @@
       <c r="R269" s="17"/>
       <c r="S269" s="17"/>
     </row>
-    <row r="270" ht="14.25">
+    <row r="270" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B270" s="17"/>
       <c r="C270" s="17"/>
       <c r="D270" s="17"/>
@@ -6140,7 +6153,7 @@
       <c r="R270" s="17"/>
       <c r="S270" s="17"/>
     </row>
-    <row r="271" ht="14.25">
+    <row r="271" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B271" s="17"/>
       <c r="C271" s="17"/>
       <c r="D271" s="17"/>
@@ -6160,7 +6173,7 @@
       <c r="R271" s="17"/>
       <c r="S271" s="17"/>
     </row>
-    <row r="272" ht="14.25">
+    <row r="272" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B272" s="17"/>
       <c r="C272" s="17"/>
       <c r="D272" s="17"/>
@@ -6180,7 +6193,7 @@
       <c r="R272" s="17"/>
       <c r="S272" s="17"/>
     </row>
-    <row r="273" ht="14.25">
+    <row r="273" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B273" s="17"/>
       <c r="C273" s="17"/>
       <c r="D273" s="17"/>
@@ -6200,7 +6213,7 @@
       <c r="R273" s="17"/>
       <c r="S273" s="17"/>
     </row>
-    <row r="274" ht="14.25">
+    <row r="274" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B274" s="17"/>
       <c r="C274" s="17"/>
       <c r="D274" s="17"/>
@@ -6220,7 +6233,7 @@
       <c r="R274" s="17"/>
       <c r="S274" s="17"/>
     </row>
-    <row r="275" ht="14.25">
+    <row r="275" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B275" s="17"/>
       <c r="C275" s="17"/>
       <c r="D275" s="17"/>
@@ -6240,7 +6253,7 @@
       <c r="R275" s="17"/>
       <c r="S275" s="17"/>
     </row>
-    <row r="276" ht="14.25">
+    <row r="276" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B276" s="17"/>
       <c r="C276" s="17"/>
       <c r="D276" s="17"/>
@@ -6260,7 +6273,7 @@
       <c r="R276" s="17"/>
       <c r="S276" s="17"/>
     </row>
-    <row r="277" ht="14.25">
+    <row r="277" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B277" s="17"/>
       <c r="C277" s="17"/>
       <c r="D277" s="17"/>
@@ -6280,7 +6293,7 @@
       <c r="R277" s="17"/>
       <c r="S277" s="17"/>
     </row>
-    <row r="278" ht="14.25">
+    <row r="278" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B278" s="17"/>
       <c r="C278" s="17"/>
       <c r="D278" s="17"/>
@@ -6300,7 +6313,7 @@
       <c r="R278" s="17"/>
       <c r="S278" s="17"/>
     </row>
-    <row r="279" ht="14.25">
+    <row r="279" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B279" s="17"/>
       <c r="C279" s="17"/>
       <c r="D279" s="17"/>
@@ -6320,7 +6333,7 @@
       <c r="R279" s="17"/>
       <c r="S279" s="17"/>
     </row>
-    <row r="280" ht="14.25">
+    <row r="280" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B280" s="17"/>
       <c r="C280" s="17"/>
       <c r="D280" s="17"/>
@@ -6340,7 +6353,7 @@
       <c r="R280" s="17"/>
       <c r="S280" s="17"/>
     </row>
-    <row r="281" ht="14.25">
+    <row r="281" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B281" s="17"/>
       <c r="C281" s="17"/>
       <c r="D281" s="17"/>
@@ -6360,7 +6373,7 @@
       <c r="R281" s="17"/>
       <c r="S281" s="17"/>
     </row>
-    <row r="282" ht="14.25">
+    <row r="282" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B282" s="17"/>
       <c r="C282" s="17"/>
       <c r="D282" s="17"/>
@@ -6380,7 +6393,7 @@
       <c r="R282" s="17"/>
       <c r="S282" s="17"/>
     </row>
-    <row r="283" ht="14.25">
+    <row r="283" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B283" s="17"/>
       <c r="C283" s="17"/>
       <c r="D283" s="17"/>
@@ -6400,7 +6413,7 @@
       <c r="R283" s="17"/>
       <c r="S283" s="17"/>
     </row>
-    <row r="284" ht="14.25">
+    <row r="284" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B284" s="17"/>
       <c r="C284" s="17"/>
       <c r="D284" s="17"/>
@@ -6420,7 +6433,7 @@
       <c r="R284" s="17"/>
       <c r="S284" s="17"/>
     </row>
-    <row r="285" ht="14.25">
+    <row r="285" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B285" s="17"/>
       <c r="C285" s="17"/>
       <c r="D285" s="17"/>
@@ -6440,7 +6453,7 @@
       <c r="R285" s="17"/>
       <c r="S285" s="17"/>
     </row>
-    <row r="286" ht="14.25">
+    <row r="286" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B286" s="17"/>
       <c r="C286" s="17"/>
       <c r="D286" s="17"/>
@@ -6460,7 +6473,7 @@
       <c r="R286" s="17"/>
       <c r="S286" s="17"/>
     </row>
-    <row r="287" ht="14.25">
+    <row r="287" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B287" s="17"/>
       <c r="C287" s="17"/>
       <c r="D287" s="17"/>
@@ -6480,7 +6493,7 @@
       <c r="R287" s="17"/>
       <c r="S287" s="17"/>
     </row>
-    <row r="288" ht="14.25">
+    <row r="288" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B288" s="17"/>
       <c r="C288" s="17"/>
       <c r="D288" s="17"/>
@@ -6500,7 +6513,7 @@
       <c r="R288" s="17"/>
       <c r="S288" s="17"/>
     </row>
-    <row r="289" ht="14.25">
+    <row r="289" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B289" s="17"/>
       <c r="C289" s="17"/>
       <c r="D289" s="17"/>
@@ -6520,7 +6533,7 @@
       <c r="R289" s="17"/>
       <c r="S289" s="17"/>
     </row>
-    <row r="290" ht="14.25">
+    <row r="290" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B290" s="17"/>
       <c r="C290" s="17"/>
       <c r="D290" s="17"/>
@@ -6540,7 +6553,7 @@
       <c r="R290" s="17"/>
       <c r="S290" s="17"/>
     </row>
-    <row r="291" ht="14.25">
+    <row r="291" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B291" s="17"/>
       <c r="C291" s="17"/>
       <c r="D291" s="17"/>
@@ -6560,7 +6573,7 @@
       <c r="R291" s="17"/>
       <c r="S291" s="17"/>
     </row>
-    <row r="292" ht="14.25">
+    <row r="292" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B292" s="17"/>
       <c r="C292" s="17"/>
       <c r="D292" s="17"/>
@@ -6580,7 +6593,7 @@
       <c r="R292" s="17"/>
       <c r="S292" s="17"/>
     </row>
-    <row r="293" ht="14.25">
+    <row r="293" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B293" s="17"/>
       <c r="C293" s="17"/>
       <c r="D293" s="17"/>
@@ -6600,7 +6613,7 @@
       <c r="R293" s="17"/>
       <c r="S293" s="17"/>
     </row>
-    <row r="294" ht="14.25">
+    <row r="294" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B294" s="17"/>
       <c r="C294" s="17"/>
       <c r="D294" s="17"/>
@@ -6620,7 +6633,7 @@
       <c r="R294" s="17"/>
       <c r="S294" s="17"/>
     </row>
-    <row r="295" ht="14.25">
+    <row r="295" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B295" s="17"/>
       <c r="C295" s="17"/>
       <c r="D295" s="17"/>
@@ -6640,7 +6653,7 @@
       <c r="R295" s="17"/>
       <c r="S295" s="17"/>
     </row>
-    <row r="296" ht="14.25">
+    <row r="296" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B296" s="17"/>
       <c r="C296" s="17"/>
       <c r="D296" s="17"/>
@@ -6660,7 +6673,7 @@
       <c r="R296" s="17"/>
       <c r="S296" s="17"/>
     </row>
-    <row r="297" ht="14.25">
+    <row r="297" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B297" s="17"/>
       <c r="C297" s="17"/>
       <c r="D297" s="17"/>
@@ -6680,7 +6693,7 @@
       <c r="R297" s="17"/>
       <c r="S297" s="17"/>
     </row>
-    <row r="298" ht="14.25">
+    <row r="298" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B298" s="17"/>
       <c r="C298" s="17"/>
       <c r="D298" s="17"/>
@@ -6700,7 +6713,7 @@
       <c r="R298" s="17"/>
       <c r="S298" s="17"/>
     </row>
-    <row r="299" ht="14.25">
+    <row r="299" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B299" s="17"/>
       <c r="C299" s="17"/>
       <c r="D299" s="17"/>
@@ -6720,7 +6733,7 @@
       <c r="R299" s="17"/>
       <c r="S299" s="17"/>
     </row>
-    <row r="300" ht="14.25">
+    <row r="300" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B300" s="17"/>
       <c r="C300" s="17"/>
       <c r="D300" s="17"/>
@@ -6740,7 +6753,7 @@
       <c r="R300" s="17"/>
       <c r="S300" s="17"/>
     </row>
-    <row r="301" ht="14.25">
+    <row r="301" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B301" s="17"/>
       <c r="C301" s="17"/>
       <c r="D301" s="17"/>
@@ -6760,7 +6773,7 @@
       <c r="R301" s="17"/>
       <c r="S301" s="17"/>
     </row>
-    <row r="302" ht="14.25">
+    <row r="302" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B302" s="17"/>
       <c r="C302" s="17"/>
       <c r="D302" s="17"/>
@@ -6780,7 +6793,7 @@
       <c r="R302" s="17"/>
       <c r="S302" s="17"/>
     </row>
-    <row r="303" ht="14.25">
+    <row r="303" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B303" s="17"/>
       <c r="C303" s="17"/>
       <c r="D303" s="17"/>
@@ -6800,7 +6813,7 @@
       <c r="R303" s="17"/>
       <c r="S303" s="17"/>
     </row>
-    <row r="304" ht="14.25">
+    <row r="304" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B304" s="17"/>
       <c r="C304" s="17"/>
       <c r="D304" s="17"/>
@@ -6820,7 +6833,7 @@
       <c r="R304" s="17"/>
       <c r="S304" s="17"/>
     </row>
-    <row r="305" ht="14.25">
+    <row r="305" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B305" s="17"/>
       <c r="C305" s="17"/>
       <c r="D305" s="17"/>
@@ -6840,7 +6853,7 @@
       <c r="R305" s="17"/>
       <c r="S305" s="17"/>
     </row>
-    <row r="306" ht="14.25">
+    <row r="306" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B306" s="17"/>
       <c r="C306" s="17"/>
       <c r="D306" s="17"/>
@@ -6860,7 +6873,7 @@
       <c r="R306" s="17"/>
       <c r="S306" s="17"/>
     </row>
-    <row r="307" ht="14.25">
+    <row r="307" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B307" s="17"/>
       <c r="C307" s="17"/>
       <c r="D307" s="17"/>
@@ -6880,7 +6893,7 @@
       <c r="R307" s="17"/>
       <c r="S307" s="17"/>
     </row>
-    <row r="308" ht="14.25">
+    <row r="308" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B308" s="17"/>
       <c r="C308" s="17"/>
       <c r="D308" s="17"/>
@@ -6900,7 +6913,7 @@
       <c r="R308" s="17"/>
       <c r="S308" s="17"/>
     </row>
-    <row r="309" ht="14.25">
+    <row r="309" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B309" s="17"/>
       <c r="C309" s="17"/>
       <c r="D309" s="17"/>
@@ -6920,7 +6933,7 @@
       <c r="R309" s="17"/>
       <c r="S309" s="17"/>
     </row>
-    <row r="310" ht="14.25">
+    <row r="310" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B310" s="17"/>
       <c r="C310" s="17"/>
       <c r="D310" s="17"/>
@@ -6940,7 +6953,7 @@
       <c r="R310" s="17"/>
       <c r="S310" s="17"/>
     </row>
-    <row r="311" ht="14.25">
+    <row r="311" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B311" s="17"/>
       <c r="C311" s="17"/>
       <c r="D311" s="17"/>
@@ -6960,7 +6973,7 @@
       <c r="R311" s="17"/>
       <c r="S311" s="17"/>
     </row>
-    <row r="312" ht="14.25">
+    <row r="312" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B312" s="17"/>
       <c r="C312" s="17"/>
       <c r="D312" s="17"/>
@@ -6980,7 +6993,7 @@
       <c r="R312" s="17"/>
       <c r="S312" s="17"/>
     </row>
-    <row r="313" ht="14.25">
+    <row r="313" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B313" s="17"/>
       <c r="C313" s="17"/>
       <c r="D313" s="17"/>
@@ -7000,7 +7013,7 @@
       <c r="R313" s="17"/>
       <c r="S313" s="17"/>
     </row>
-    <row r="314" ht="14.25">
+    <row r="314" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B314" s="17"/>
       <c r="C314" s="17"/>
       <c r="D314" s="17"/>
@@ -7020,7 +7033,7 @@
       <c r="R314" s="17"/>
       <c r="S314" s="17"/>
     </row>
-    <row r="315" ht="14.25">
+    <row r="315" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B315" s="17"/>
       <c r="C315" s="17"/>
       <c r="D315" s="17"/>
@@ -7040,7 +7053,7 @@
       <c r="R315" s="17"/>
       <c r="S315" s="17"/>
     </row>
-    <row r="316" ht="14.25">
+    <row r="316" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B316" s="17"/>
       <c r="C316" s="17"/>
       <c r="D316" s="17"/>
@@ -7060,7 +7073,7 @@
       <c r="R316" s="17"/>
       <c r="S316" s="17"/>
     </row>
-    <row r="317" ht="14.25">
+    <row r="317" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B317" s="17"/>
       <c r="C317" s="17"/>
       <c r="D317" s="17"/>
@@ -7080,7 +7093,7 @@
       <c r="R317" s="17"/>
       <c r="S317" s="17"/>
     </row>
-    <row r="318" ht="14.25">
+    <row r="318" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B318" s="17"/>
       <c r="C318" s="17"/>
       <c r="D318" s="17"/>
@@ -7100,7 +7113,7 @@
       <c r="R318" s="17"/>
       <c r="S318" s="17"/>
     </row>
-    <row r="319" ht="14.25">
+    <row r="319" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B319" s="17"/>
       <c r="C319" s="17"/>
       <c r="D319" s="17"/>
@@ -7120,7 +7133,7 @@
       <c r="R319" s="17"/>
       <c r="S319" s="17"/>
     </row>
-    <row r="320" ht="14.25">
+    <row r="320" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B320" s="17"/>
       <c r="C320" s="17"/>
       <c r="D320" s="17"/>
@@ -7140,7 +7153,7 @@
       <c r="R320" s="17"/>
       <c r="S320" s="17"/>
     </row>
-    <row r="321" ht="14.25">
+    <row r="321" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B321" s="17"/>
       <c r="C321" s="17"/>
       <c r="D321" s="17"/>
@@ -7160,7 +7173,7 @@
       <c r="R321" s="17"/>
       <c r="S321" s="17"/>
     </row>
-    <row r="322" ht="14.25">
+    <row r="322" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B322" s="17"/>
       <c r="C322" s="17"/>
       <c r="D322" s="17"/>
@@ -7180,7 +7193,7 @@
       <c r="R322" s="17"/>
       <c r="S322" s="17"/>
     </row>
-    <row r="323" ht="14.25">
+    <row r="323" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B323" s="17"/>
       <c r="C323" s="17"/>
       <c r="D323" s="17"/>
@@ -7200,7 +7213,7 @@
       <c r="R323" s="17"/>
       <c r="S323" s="17"/>
     </row>
-    <row r="324" ht="14.25">
+    <row r="324" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B324" s="17"/>
       <c r="C324" s="17"/>
       <c r="D324" s="17"/>
@@ -7220,7 +7233,7 @@
       <c r="R324" s="17"/>
       <c r="S324" s="17"/>
     </row>
-    <row r="325" ht="14.25">
+    <row r="325" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B325" s="17"/>
       <c r="C325" s="17"/>
       <c r="D325" s="17"/>
@@ -7240,7 +7253,7 @@
       <c r="R325" s="17"/>
       <c r="S325" s="17"/>
     </row>
-    <row r="326" ht="14.25">
+    <row r="326" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B326" s="17"/>
       <c r="C326" s="17"/>
       <c r="D326" s="17"/>
@@ -7260,7 +7273,7 @@
       <c r="R326" s="17"/>
       <c r="S326" s="17"/>
     </row>
-    <row r="327" ht="14.25">
+    <row r="327" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B327" s="17"/>
       <c r="C327" s="17"/>
       <c r="D327" s="17"/>
@@ -7280,7 +7293,7 @@
       <c r="R327" s="17"/>
       <c r="S327" s="17"/>
     </row>
-    <row r="328" ht="14.25">
+    <row r="328" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B328" s="17"/>
       <c r="C328" s="17"/>
       <c r="D328" s="17"/>
@@ -7300,7 +7313,7 @@
       <c r="R328" s="17"/>
       <c r="S328" s="17"/>
     </row>
-    <row r="329" ht="14.25">
+    <row r="329" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B329" s="17"/>
       <c r="C329" s="17"/>
       <c r="D329" s="17"/>
@@ -7320,7 +7333,7 @@
       <c r="R329" s="17"/>
       <c r="S329" s="17"/>
     </row>
-    <row r="330" ht="14.25">
+    <row r="330" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B330" s="17"/>
       <c r="C330" s="17"/>
       <c r="D330" s="17"/>
@@ -7340,7 +7353,7 @@
       <c r="R330" s="17"/>
       <c r="S330" s="17"/>
     </row>
-    <row r="331" ht="14.25">
+    <row r="331" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B331" s="17"/>
       <c r="C331" s="17"/>
       <c r="D331" s="17"/>
@@ -7360,7 +7373,7 @@
       <c r="R331" s="17"/>
       <c r="S331" s="17"/>
     </row>
-    <row r="332" ht="14.25">
+    <row r="332" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B332" s="17"/>
       <c r="C332" s="17"/>
       <c r="D332" s="17"/>
@@ -7380,7 +7393,7 @@
       <c r="R332" s="17"/>
       <c r="S332" s="17"/>
     </row>
-    <row r="333" ht="14.25">
+    <row r="333" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B333" s="17"/>
       <c r="C333" s="17"/>
       <c r="D333" s="17"/>
@@ -7400,7 +7413,7 @@
       <c r="R333" s="17"/>
       <c r="S333" s="17"/>
     </row>
-    <row r="334" ht="14.25">
+    <row r="334" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B334" s="17"/>
       <c r="C334" s="17"/>
       <c r="D334" s="17"/>
@@ -7420,7 +7433,7 @@
       <c r="R334" s="17"/>
       <c r="S334" s="17"/>
     </row>
-    <row r="335" ht="14.25">
+    <row r="335" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B335" s="17"/>
       <c r="C335" s="17"/>
       <c r="D335" s="17"/>
@@ -7440,7 +7453,7 @@
       <c r="R335" s="17"/>
       <c r="S335" s="17"/>
     </row>
-    <row r="336" ht="14.25">
+    <row r="336" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B336" s="17"/>
       <c r="C336" s="17"/>
       <c r="D336" s="17"/>
@@ -7460,7 +7473,7 @@
       <c r="R336" s="17"/>
       <c r="S336" s="17"/>
     </row>
-    <row r="337" ht="14.25">
+    <row r="337" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B337" s="17"/>
       <c r="C337" s="17"/>
       <c r="D337" s="17"/>
@@ -7480,7 +7493,7 @@
       <c r="R337" s="17"/>
       <c r="S337" s="17"/>
     </row>
-    <row r="338" ht="14.25">
+    <row r="338" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B338" s="17"/>
       <c r="C338" s="17"/>
       <c r="D338" s="17"/>
@@ -7500,7 +7513,7 @@
       <c r="R338" s="17"/>
       <c r="S338" s="17"/>
     </row>
-    <row r="339" ht="14.25">
+    <row r="339" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B339" s="17"/>
       <c r="C339" s="17"/>
       <c r="D339" s="17"/>
@@ -7520,7 +7533,7 @@
       <c r="R339" s="17"/>
       <c r="S339" s="17"/>
     </row>
-    <row r="340" ht="14.25">
+    <row r="340" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B340" s="17"/>
       <c r="C340" s="17"/>
       <c r="D340" s="17"/>
@@ -7540,7 +7553,7 @@
       <c r="R340" s="17"/>
       <c r="S340" s="17"/>
     </row>
-    <row r="341" ht="14.25">
+    <row r="341" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B341" s="17"/>
       <c r="C341" s="17"/>
       <c r="D341" s="17"/>
@@ -7560,7 +7573,7 @@
       <c r="R341" s="17"/>
       <c r="S341" s="17"/>
     </row>
-    <row r="342" ht="14.25">
+    <row r="342" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B342" s="17"/>
       <c r="C342" s="17"/>
       <c r="D342" s="17"/>
@@ -7580,7 +7593,7 @@
       <c r="R342" s="17"/>
       <c r="S342" s="17"/>
     </row>
-    <row r="343" ht="14.25">
+    <row r="343" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B343" s="17"/>
       <c r="C343" s="17"/>
       <c r="D343" s="17"/>
@@ -7600,7 +7613,7 @@
       <c r="R343" s="17"/>
       <c r="S343" s="17"/>
     </row>
-    <row r="344" ht="14.25">
+    <row r="344" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B344" s="17"/>
       <c r="C344" s="17"/>
       <c r="D344" s="17"/>
@@ -7620,7 +7633,7 @@
       <c r="R344" s="17"/>
       <c r="S344" s="17"/>
     </row>
-    <row r="345" ht="14.25">
+    <row r="345" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B345" s="17"/>
       <c r="C345" s="17"/>
       <c r="D345" s="17"/>
@@ -7640,7 +7653,7 @@
       <c r="R345" s="17"/>
       <c r="S345" s="17"/>
     </row>
-    <row r="346" ht="14.25">
+    <row r="346" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B346" s="17"/>
       <c r="C346" s="17"/>
       <c r="D346" s="17"/>
@@ -7660,7 +7673,7 @@
       <c r="R346" s="17"/>
       <c r="S346" s="17"/>
     </row>
-    <row r="347" ht="14.25">
+    <row r="347" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B347" s="17"/>
       <c r="C347" s="17"/>
       <c r="D347" s="17"/>
@@ -7680,7 +7693,7 @@
       <c r="R347" s="17"/>
       <c r="S347" s="17"/>
     </row>
-    <row r="348" ht="14.25">
+    <row r="348" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B348" s="17"/>
       <c r="C348" s="17"/>
       <c r="D348" s="17"/>
@@ -7700,7 +7713,7 @@
       <c r="R348" s="17"/>
       <c r="S348" s="17"/>
     </row>
-    <row r="349" ht="14.25">
+    <row r="349" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B349" s="17"/>
       <c r="C349" s="17"/>
       <c r="D349" s="17"/>
@@ -7720,7 +7733,7 @@
       <c r="R349" s="17"/>
       <c r="S349" s="17"/>
     </row>
-    <row r="350" ht="14.25">
+    <row r="350" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B350" s="17"/>
       <c r="C350" s="17"/>
       <c r="D350" s="17"/>
@@ -7740,7 +7753,7 @@
       <c r="R350" s="17"/>
       <c r="S350" s="17"/>
     </row>
-    <row r="351" ht="14.25">
+    <row r="351" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B351" s="17"/>
       <c r="C351" s="17"/>
       <c r="D351" s="17"/>
@@ -7760,7 +7773,7 @@
       <c r="R351" s="17"/>
       <c r="S351" s="17"/>
     </row>
-    <row r="352" ht="14.25">
+    <row r="352" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B352" s="17"/>
       <c r="C352" s="17"/>
       <c r="D352" s="17"/>
@@ -7780,7 +7793,7 @@
       <c r="R352" s="17"/>
       <c r="S352" s="17"/>
     </row>
-    <row r="353" ht="14.25">
+    <row r="353" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B353" s="17"/>
       <c r="C353" s="17"/>
       <c r="D353" s="17"/>
@@ -7800,7 +7813,7 @@
       <c r="R353" s="17"/>
       <c r="S353" s="17"/>
     </row>
-    <row r="354" ht="14.25">
+    <row r="354" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B354" s="17"/>
       <c r="C354" s="17"/>
       <c r="D354" s="17"/>
@@ -7820,7 +7833,7 @@
       <c r="R354" s="17"/>
       <c r="S354" s="17"/>
     </row>
-    <row r="355" ht="14.25">
+    <row r="355" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B355" s="17"/>
       <c r="C355" s="17"/>
       <c r="D355" s="17"/>
@@ -7840,7 +7853,7 @@
       <c r="R355" s="17"/>
       <c r="S355" s="17"/>
     </row>
-    <row r="356" ht="14.25">
+    <row r="356" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B356" s="17"/>
       <c r="C356" s="17"/>
       <c r="D356" s="17"/>
@@ -7860,7 +7873,7 @@
       <c r="R356" s="17"/>
       <c r="S356" s="17"/>
     </row>
-    <row r="357" ht="14.25">
+    <row r="357" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B357" s="17"/>
       <c r="C357" s="17"/>
       <c r="D357" s="17"/>
@@ -7880,7 +7893,7 @@
       <c r="R357" s="17"/>
       <c r="S357" s="17"/>
     </row>
-    <row r="358" ht="14.25">
+    <row r="358" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B358" s="17"/>
       <c r="C358" s="17"/>
       <c r="D358" s="17"/>
@@ -7900,7 +7913,7 @@
       <c r="R358" s="17"/>
       <c r="S358" s="17"/>
     </row>
-    <row r="359" ht="14.25">
+    <row r="359" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B359" s="17"/>
       <c r="C359" s="17"/>
       <c r="D359" s="17"/>
@@ -7920,7 +7933,7 @@
       <c r="R359" s="17"/>
       <c r="S359" s="17"/>
     </row>
-    <row r="360" ht="14.25">
+    <row r="360" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B360" s="17"/>
       <c r="C360" s="17"/>
       <c r="D360" s="17"/>
@@ -7940,7 +7953,7 @@
       <c r="R360" s="17"/>
       <c r="S360" s="17"/>
     </row>
-    <row r="361" ht="14.25">
+    <row r="361" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B361" s="17"/>
       <c r="C361" s="17"/>
       <c r="D361" s="17"/>
@@ -7960,7 +7973,7 @@
       <c r="R361" s="17"/>
       <c r="S361" s="17"/>
     </row>
-    <row r="362" ht="14.25">
+    <row r="362" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B362" s="17"/>
       <c r="C362" s="17"/>
       <c r="D362" s="17"/>
@@ -7980,7 +7993,7 @@
       <c r="R362" s="17"/>
       <c r="S362" s="17"/>
     </row>
-    <row r="363" ht="14.25">
+    <row r="363" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B363" s="17"/>
       <c r="C363" s="17"/>
       <c r="D363" s="17"/>
@@ -8000,7 +8013,7 @@
       <c r="R363" s="17"/>
       <c r="S363" s="17"/>
     </row>
-    <row r="364" ht="14.25">
+    <row r="364" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B364" s="17"/>
       <c r="C364" s="17"/>
       <c r="D364" s="17"/>
@@ -8020,7 +8033,7 @@
       <c r="R364" s="17"/>
       <c r="S364" s="17"/>
     </row>
-    <row r="365" ht="14.25">
+    <row r="365" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B365" s="17"/>
       <c r="C365" s="17"/>
       <c r="D365" s="17"/>
@@ -8040,7 +8053,7 @@
       <c r="R365" s="17"/>
       <c r="S365" s="17"/>
     </row>
-    <row r="366" ht="14.25">
+    <row r="366" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B366" s="17"/>
       <c r="C366" s="17"/>
       <c r="D366" s="17"/>
@@ -8060,7 +8073,7 @@
       <c r="R366" s="17"/>
       <c r="S366" s="17"/>
     </row>
-    <row r="367" ht="14.25">
+    <row r="367" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B367" s="17"/>
       <c r="C367" s="17"/>
       <c r="D367" s="17"/>
@@ -8080,7 +8093,7 @@
       <c r="R367" s="17"/>
       <c r="S367" s="17"/>
     </row>
-    <row r="368" ht="14.25">
+    <row r="368" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B368" s="17"/>
       <c r="C368" s="17"/>
       <c r="D368" s="17"/>
@@ -8100,7 +8113,7 @@
       <c r="R368" s="17"/>
       <c r="S368" s="17"/>
     </row>
-    <row r="369" ht="14.25">
+    <row r="369" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B369" s="17"/>
       <c r="C369" s="17"/>
       <c r="D369" s="17"/>
@@ -8120,7 +8133,7 @@
       <c r="R369" s="17"/>
       <c r="S369" s="17"/>
     </row>
-    <row r="370" ht="14.25">
+    <row r="370" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B370" s="17"/>
       <c r="C370" s="17"/>
       <c r="D370" s="17"/>
@@ -8140,7 +8153,7 @@
       <c r="R370" s="17"/>
       <c r="S370" s="17"/>
     </row>
-    <row r="371" ht="14.25">
+    <row r="371" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B371" s="17"/>
       <c r="C371" s="17"/>
       <c r="D371" s="17"/>
@@ -8160,7 +8173,7 @@
       <c r="R371" s="17"/>
       <c r="S371" s="17"/>
     </row>
-    <row r="372" ht="14.25">
+    <row r="372" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B372" s="17"/>
       <c r="C372" s="17"/>
       <c r="D372" s="17"/>
@@ -8180,7 +8193,7 @@
       <c r="R372" s="17"/>
       <c r="S372" s="17"/>
     </row>
-    <row r="373" ht="14.25">
+    <row r="373" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B373" s="17"/>
       <c r="C373" s="17"/>
       <c r="D373" s="17"/>
@@ -8200,7 +8213,7 @@
       <c r="R373" s="17"/>
       <c r="S373" s="17"/>
     </row>
-    <row r="374" ht="14.25">
+    <row r="374" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B374" s="17"/>
       <c r="C374" s="17"/>
       <c r="D374" s="17"/>
@@ -8220,7 +8233,7 @@
       <c r="R374" s="17"/>
       <c r="S374" s="17"/>
     </row>
-    <row r="375" ht="14.25">
+    <row r="375" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B375" s="17"/>
       <c r="C375" s="17"/>
       <c r="D375" s="17"/>
@@ -8240,7 +8253,7 @@
       <c r="R375" s="17"/>
       <c r="S375" s="17"/>
     </row>
-    <row r="376" ht="14.25">
+    <row r="376" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B376" s="17"/>
       <c r="C376" s="17"/>
       <c r="D376" s="17"/>
@@ -8260,7 +8273,7 @@
       <c r="R376" s="17"/>
       <c r="S376" s="17"/>
     </row>
-    <row r="377" ht="14.25">
+    <row r="377" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B377" s="17"/>
       <c r="C377" s="17"/>
       <c r="D377" s="17"/>
@@ -8280,7 +8293,7 @@
       <c r="R377" s="17"/>
       <c r="S377" s="17"/>
     </row>
-    <row r="378" ht="14.25">
+    <row r="378" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B378" s="17"/>
       <c r="C378" s="17"/>
       <c r="D378" s="17"/>
@@ -8300,7 +8313,7 @@
       <c r="R378" s="17"/>
       <c r="S378" s="17"/>
     </row>
-    <row r="379" ht="14.25">
+    <row r="379" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B379" s="17"/>
       <c r="C379" s="17"/>
       <c r="D379" s="17"/>
@@ -8320,7 +8333,7 @@
       <c r="R379" s="17"/>
       <c r="S379" s="17"/>
     </row>
-    <row r="380" ht="14.25">
+    <row r="380" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B380" s="17"/>
       <c r="C380" s="17"/>
       <c r="D380" s="17"/>
@@ -8340,7 +8353,7 @@
       <c r="R380" s="17"/>
       <c r="S380" s="17"/>
     </row>
-    <row r="381" ht="14.25">
+    <row r="381" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B381" s="17"/>
       <c r="C381" s="17"/>
       <c r="D381" s="17"/>
@@ -8360,7 +8373,7 @@
       <c r="R381" s="17"/>
       <c r="S381" s="17"/>
     </row>
-    <row r="382" ht="14.25">
+    <row r="382" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B382" s="17"/>
       <c r="C382" s="17"/>
       <c r="D382" s="17"/>
@@ -8380,7 +8393,7 @@
       <c r="R382" s="17"/>
       <c r="S382" s="17"/>
     </row>
-    <row r="383" ht="14.25">
+    <row r="383" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B383" s="17"/>
       <c r="C383" s="17"/>
       <c r="D383" s="17"/>
@@ -8400,7 +8413,7 @@
       <c r="R383" s="17"/>
       <c r="S383" s="17"/>
     </row>
-    <row r="384" ht="14.25">
+    <row r="384" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B384" s="17"/>
       <c r="C384" s="17"/>
       <c r="D384" s="17"/>
@@ -8420,7 +8433,7 @@
       <c r="R384" s="17"/>
       <c r="S384" s="17"/>
     </row>
-    <row r="385" ht="14.25">
+    <row r="385" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B385" s="17"/>
       <c r="C385" s="17"/>
       <c r="D385" s="17"/>
@@ -8440,7 +8453,7 @@
       <c r="R385" s="17"/>
       <c r="S385" s="17"/>
     </row>
-    <row r="386" ht="14.25">
+    <row r="386" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B386" s="17"/>
       <c r="C386" s="17"/>
       <c r="D386" s="17"/>
@@ -8460,7 +8473,7 @@
       <c r="R386" s="17"/>
       <c r="S386" s="17"/>
     </row>
-    <row r="387" ht="14.25">
+    <row r="387" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B387" s="17"/>
       <c r="C387" s="17"/>
       <c r="D387" s="17"/>
@@ -8480,7 +8493,7 @@
       <c r="R387" s="17"/>
       <c r="S387" s="17"/>
     </row>
-    <row r="388" ht="14.25">
+    <row r="388" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B388" s="17"/>
       <c r="C388" s="17"/>
       <c r="D388" s="17"/>
@@ -8500,7 +8513,7 @@
       <c r="R388" s="17"/>
       <c r="S388" s="17"/>
     </row>
-    <row r="389" ht="14.25">
+    <row r="389" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B389" s="17"/>
       <c r="C389" s="17"/>
       <c r="D389" s="17"/>
@@ -8520,7 +8533,7 @@
       <c r="R389" s="17"/>
       <c r="S389" s="17"/>
     </row>
-    <row r="390" ht="14.25">
+    <row r="390" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B390" s="17"/>
       <c r="C390" s="17"/>
       <c r="D390" s="17"/>
@@ -8540,7 +8553,7 @@
       <c r="R390" s="17"/>
       <c r="S390" s="17"/>
     </row>
-    <row r="391" ht="14.25">
+    <row r="391" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B391" s="17"/>
       <c r="C391" s="17"/>
       <c r="D391" s="17"/>
@@ -8560,7 +8573,7 @@
       <c r="R391" s="17"/>
       <c r="S391" s="17"/>
     </row>
-    <row r="392" ht="14.25">
+    <row r="392" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B392" s="17"/>
       <c r="C392" s="17"/>
       <c r="D392" s="17"/>
@@ -8580,7 +8593,7 @@
       <c r="R392" s="17"/>
       <c r="S392" s="17"/>
     </row>
-    <row r="393" ht="14.25">
+    <row r="393" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B393" s="17"/>
       <c r="C393" s="17"/>
       <c r="D393" s="17"/>
@@ -8600,7 +8613,7 @@
       <c r="R393" s="17"/>
       <c r="S393" s="17"/>
     </row>
-    <row r="394" ht="14.25">
+    <row r="394" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B394" s="17"/>
       <c r="C394" s="17"/>
       <c r="D394" s="17"/>
@@ -8620,7 +8633,7 @@
       <c r="R394" s="17"/>
       <c r="S394" s="17"/>
     </row>
-    <row r="395" ht="14.25">
+    <row r="395" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B395" s="17"/>
       <c r="C395" s="17"/>
       <c r="D395" s="17"/>
@@ -8640,7 +8653,7 @@
       <c r="R395" s="17"/>
       <c r="S395" s="17"/>
     </row>
-    <row r="396" ht="14.25">
+    <row r="396" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B396" s="17"/>
       <c r="C396" s="17"/>
       <c r="D396" s="17"/>
@@ -8660,7 +8673,7 @@
       <c r="R396" s="17"/>
       <c r="S396" s="17"/>
     </row>
-    <row r="397" ht="14.25">
+    <row r="397" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B397" s="17"/>
       <c r="C397" s="17"/>
       <c r="D397" s="17"/>
@@ -8680,7 +8693,7 @@
       <c r="R397" s="17"/>
       <c r="S397" s="17"/>
     </row>
-    <row r="398" ht="14.25">
+    <row r="398" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B398" s="17"/>
       <c r="C398" s="17"/>
       <c r="D398" s="17"/>
@@ -8700,7 +8713,7 @@
       <c r="R398" s="17"/>
       <c r="S398" s="17"/>
     </row>
-    <row r="399" ht="14.25">
+    <row r="399" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B399" s="17"/>
       <c r="C399" s="17"/>
       <c r="D399" s="17"/>
@@ -8720,7 +8733,7 @@
       <c r="R399" s="17"/>
       <c r="S399" s="17"/>
     </row>
-    <row r="400" ht="14.25">
+    <row r="400" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B400" s="17"/>
       <c r="C400" s="17"/>
       <c r="D400" s="17"/>
@@ -8740,7 +8753,7 @@
       <c r="R400" s="17"/>
       <c r="S400" s="17"/>
     </row>
-    <row r="401" ht="14.25">
+    <row r="401" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B401" s="17"/>
       <c r="C401" s="17"/>
       <c r="D401" s="17"/>
@@ -8760,7 +8773,7 @@
       <c r="R401" s="17"/>
       <c r="S401" s="17"/>
     </row>
-    <row r="402" ht="14.25">
+    <row r="402" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B402" s="17"/>
       <c r="C402" s="17"/>
       <c r="D402" s="17"/>
@@ -8780,7 +8793,7 @@
       <c r="R402" s="17"/>
       <c r="S402" s="17"/>
     </row>
-    <row r="403" ht="14.25">
+    <row r="403" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B403" s="17"/>
       <c r="C403" s="17"/>
       <c r="D403" s="17"/>
@@ -8800,7 +8813,7 @@
       <c r="R403" s="17"/>
       <c r="S403" s="17"/>
     </row>
-    <row r="404" ht="14.25">
+    <row r="404" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B404" s="17"/>
       <c r="C404" s="17"/>
       <c r="D404" s="17"/>
@@ -8820,7 +8833,7 @@
       <c r="R404" s="17"/>
       <c r="S404" s="17"/>
     </row>
-    <row r="405" ht="14.25">
+    <row r="405" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B405" s="17"/>
       <c r="C405" s="17"/>
       <c r="D405" s="17"/>
@@ -8840,7 +8853,7 @@
       <c r="R405" s="17"/>
       <c r="S405" s="17"/>
     </row>
-    <row r="406" ht="14.25">
+    <row r="406" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B406" s="17"/>
       <c r="C406" s="17"/>
       <c r="D406" s="17"/>
@@ -8860,7 +8873,7 @@
       <c r="R406" s="17"/>
       <c r="S406" s="17"/>
     </row>
-    <row r="407" ht="14.25">
+    <row r="407" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B407" s="17"/>
       <c r="C407" s="17"/>
       <c r="D407" s="17"/>
@@ -8880,7 +8893,7 @@
       <c r="R407" s="17"/>
       <c r="S407" s="17"/>
     </row>
-    <row r="408" ht="14.25">
+    <row r="408" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B408" s="17"/>
       <c r="C408" s="17"/>
       <c r="D408" s="17"/>
@@ -8900,7 +8913,7 @@
       <c r="R408" s="17"/>
       <c r="S408" s="17"/>
     </row>
-    <row r="409" ht="14.25">
+    <row r="409" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B409" s="17"/>
       <c r="C409" s="17"/>
       <c r="D409" s="17"/>
@@ -8920,7 +8933,7 @@
       <c r="R409" s="17"/>
       <c r="S409" s="17"/>
     </row>
-    <row r="410" ht="14.25">
+    <row r="410" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B410" s="17"/>
       <c r="C410" s="17"/>
       <c r="D410" s="17"/>
@@ -8940,7 +8953,7 @@
       <c r="R410" s="17"/>
       <c r="S410" s="17"/>
     </row>
-    <row r="411" ht="14.25">
+    <row r="411" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B411" s="17"/>
       <c r="C411" s="17"/>
       <c r="D411" s="17"/>
@@ -8960,7 +8973,7 @@
       <c r="R411" s="17"/>
       <c r="S411" s="17"/>
     </row>
-    <row r="412" ht="14.25">
+    <row r="412" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B412" s="17"/>
       <c r="C412" s="17"/>
       <c r="D412" s="17"/>
@@ -8980,7 +8993,7 @@
       <c r="R412" s="17"/>
       <c r="S412" s="17"/>
     </row>
-    <row r="413" ht="14.25">
+    <row r="413" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B413" s="17"/>
       <c r="C413" s="17"/>
       <c r="D413" s="17"/>
@@ -9000,7 +9013,7 @@
       <c r="R413" s="17"/>
       <c r="S413" s="17"/>
     </row>
-    <row r="414" ht="14.25">
+    <row r="414" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B414" s="17"/>
       <c r="C414" s="17"/>
       <c r="D414" s="17"/>
@@ -9020,7 +9033,7 @@
       <c r="R414" s="17"/>
       <c r="S414" s="17"/>
     </row>
-    <row r="415" ht="14.25">
+    <row r="415" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B415" s="17"/>
       <c r="C415" s="17"/>
       <c r="D415" s="17"/>
@@ -9040,7 +9053,7 @@
       <c r="R415" s="17"/>
       <c r="S415" s="17"/>
     </row>
-    <row r="416" ht="14.25">
+    <row r="416" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B416" s="17"/>
       <c r="C416" s="17"/>
       <c r="D416" s="17"/>
@@ -9060,7 +9073,7 @@
       <c r="R416" s="17"/>
       <c r="S416" s="17"/>
     </row>
-    <row r="417" ht="14.25">
+    <row r="417" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B417" s="17"/>
       <c r="C417" s="17"/>
       <c r="D417" s="17"/>
@@ -9080,7 +9093,7 @@
       <c r="R417" s="17"/>
       <c r="S417" s="17"/>
     </row>
-    <row r="418" ht="14.25">
+    <row r="418" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B418" s="17"/>
       <c r="C418" s="17"/>
       <c r="D418" s="17"/>
@@ -9100,7 +9113,7 @@
       <c r="R418" s="17"/>
       <c r="S418" s="17"/>
     </row>
-    <row r="419" ht="14.25">
+    <row r="419" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B419" s="17"/>
       <c r="C419" s="17"/>
       <c r="D419" s="17"/>
@@ -9120,7 +9133,7 @@
       <c r="R419" s="17"/>
       <c r="S419" s="17"/>
     </row>
-    <row r="420" ht="14.25">
+    <row r="420" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B420" s="17"/>
       <c r="C420" s="17"/>
       <c r="D420" s="17"/>
@@ -9140,7 +9153,7 @@
       <c r="R420" s="17"/>
       <c r="S420" s="17"/>
     </row>
-    <row r="421" ht="14.25">
+    <row r="421" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B421" s="17"/>
       <c r="C421" s="17"/>
       <c r="D421" s="17"/>
@@ -9160,7 +9173,7 @@
       <c r="R421" s="17"/>
       <c r="S421" s="17"/>
     </row>
-    <row r="422" ht="14.25">
+    <row r="422" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B422" s="17"/>
       <c r="C422" s="17"/>
       <c r="D422" s="17"/>
@@ -9180,7 +9193,7 @@
       <c r="R422" s="17"/>
       <c r="S422" s="17"/>
     </row>
-    <row r="423" ht="14.25">
+    <row r="423" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B423" s="17"/>
       <c r="C423" s="17"/>
       <c r="D423" s="17"/>
@@ -9200,7 +9213,7 @@
       <c r="R423" s="17"/>
       <c r="S423" s="17"/>
     </row>
-    <row r="424" ht="14.25">
+    <row r="424" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B424" s="17"/>
       <c r="C424" s="17"/>
       <c r="D424" s="17"/>
@@ -9220,7 +9233,7 @@
       <c r="R424" s="17"/>
       <c r="S424" s="17"/>
     </row>
-    <row r="425" ht="14.25">
+    <row r="425" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B425" s="17"/>
       <c r="C425" s="17"/>
       <c r="D425" s="17"/>
@@ -9240,7 +9253,7 @@
       <c r="R425" s="17"/>
       <c r="S425" s="17"/>
     </row>
-    <row r="426" ht="14.25">
+    <row r="426" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B426" s="17"/>
       <c r="C426" s="17"/>
       <c r="D426" s="17"/>
@@ -9260,7 +9273,7 @@
       <c r="R426" s="17"/>
       <c r="S426" s="17"/>
     </row>
-    <row r="427" ht="14.25">
+    <row r="427" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B427" s="17"/>
       <c r="C427" s="17"/>
       <c r="D427" s="17"/>
@@ -9280,7 +9293,7 @@
       <c r="R427" s="17"/>
       <c r="S427" s="17"/>
     </row>
-    <row r="428" ht="14.25">
+    <row r="428" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B428" s="17"/>
       <c r="C428" s="17"/>
       <c r="D428" s="17"/>
@@ -9300,7 +9313,7 @@
       <c r="R428" s="17"/>
       <c r="S428" s="17"/>
     </row>
-    <row r="429" ht="14.25">
+    <row r="429" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B429" s="17"/>
       <c r="C429" s="17"/>
       <c r="D429" s="17"/>
@@ -9320,7 +9333,7 @@
       <c r="R429" s="17"/>
       <c r="S429" s="17"/>
     </row>
-    <row r="430" ht="14.25">
+    <row r="430" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B430" s="17"/>
       <c r="C430" s="17"/>
       <c r="D430" s="17"/>
@@ -9340,7 +9353,7 @@
       <c r="R430" s="17"/>
       <c r="S430" s="17"/>
     </row>
-    <row r="431" ht="14.25">
+    <row r="431" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B431" s="17"/>
       <c r="C431" s="17"/>
       <c r="D431" s="17"/>
@@ -9360,7 +9373,7 @@
       <c r="R431" s="17"/>
       <c r="S431" s="17"/>
     </row>
-    <row r="432" ht="14.25">
+    <row r="432" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B432" s="17"/>
       <c r="C432" s="17"/>
       <c r="D432" s="17"/>
@@ -9380,7 +9393,7 @@
       <c r="R432" s="17"/>
       <c r="S432" s="17"/>
     </row>
-    <row r="433" ht="14.25">
+    <row r="433" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B433" s="17"/>
       <c r="C433" s="17"/>
       <c r="D433" s="17"/>
@@ -9400,7 +9413,7 @@
       <c r="R433" s="17"/>
       <c r="S433" s="17"/>
     </row>
-    <row r="434" ht="14.25">
+    <row r="434" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B434" s="17"/>
       <c r="C434" s="17"/>
       <c r="D434" s="17"/>
@@ -9420,7 +9433,7 @@
       <c r="R434" s="17"/>
       <c r="S434" s="17"/>
     </row>
-    <row r="435" ht="14.25">
+    <row r="435" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B435" s="17"/>
       <c r="C435" s="17"/>
       <c r="D435" s="17"/>
@@ -9440,7 +9453,7 @@
       <c r="R435" s="17"/>
       <c r="S435" s="17"/>
     </row>
-    <row r="436" ht="14.25">
+    <row r="436" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B436" s="17"/>
       <c r="C436" s="17"/>
       <c r="D436" s="17"/>
@@ -9460,7 +9473,7 @@
       <c r="R436" s="17"/>
       <c r="S436" s="17"/>
     </row>
-    <row r="437" ht="14.25">
+    <row r="437" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B437" s="17"/>
       <c r="C437" s="17"/>
       <c r="D437" s="17"/>
@@ -9480,7 +9493,7 @@
       <c r="R437" s="17"/>
       <c r="S437" s="17"/>
     </row>
-    <row r="438" ht="14.25">
+    <row r="438" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B438" s="17"/>
       <c r="C438" s="17"/>
       <c r="D438" s="17"/>
@@ -9500,7 +9513,7 @@
       <c r="R438" s="17"/>
       <c r="S438" s="17"/>
     </row>
-    <row r="439" ht="14.25">
+    <row r="439" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B439" s="17"/>
       <c r="C439" s="17"/>
       <c r="D439" s="17"/>
@@ -9520,7 +9533,7 @@
       <c r="R439" s="17"/>
       <c r="S439" s="17"/>
     </row>
-    <row r="440" ht="14.25">
+    <row r="440" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B440" s="17"/>
       <c r="C440" s="17"/>
       <c r="D440" s="17"/>
@@ -9540,7 +9553,7 @@
       <c r="R440" s="17"/>
       <c r="S440" s="17"/>
     </row>
-    <row r="441" ht="14.25">
+    <row r="441" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B441" s="17"/>
       <c r="C441" s="17"/>
       <c r="D441" s="17"/>
@@ -9560,7 +9573,7 @@
       <c r="R441" s="17"/>
       <c r="S441" s="17"/>
     </row>
-    <row r="442" ht="14.25">
+    <row r="442" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B442" s="17"/>
       <c r="C442" s="17"/>
       <c r="D442" s="17"/>
@@ -9580,7 +9593,7 @@
       <c r="R442" s="17"/>
       <c r="S442" s="17"/>
     </row>
-    <row r="443" ht="14.25">
+    <row r="443" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B443" s="17"/>
       <c r="C443" s="17"/>
       <c r="D443" s="17"/>
@@ -9600,7 +9613,7 @@
       <c r="R443" s="17"/>
       <c r="S443" s="17"/>
     </row>
-    <row r="444" ht="14.25">
+    <row r="444" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B444" s="17"/>
       <c r="C444" s="17"/>
       <c r="D444" s="17"/>
@@ -9620,7 +9633,7 @@
       <c r="R444" s="17"/>
       <c r="S444" s="17"/>
     </row>
-    <row r="445" ht="14.25">
+    <row r="445" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B445" s="17"/>
       <c r="C445" s="17"/>
       <c r="D445" s="17"/>
@@ -9640,7 +9653,7 @@
       <c r="R445" s="17"/>
       <c r="S445" s="17"/>
     </row>
-    <row r="446" ht="14.25">
+    <row r="446" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B446" s="17"/>
       <c r="C446" s="17"/>
       <c r="D446" s="17"/>
@@ -9660,7 +9673,7 @@
       <c r="R446" s="17"/>
       <c r="S446" s="17"/>
     </row>
-    <row r="447" ht="14.25">
+    <row r="447" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B447" s="17"/>
       <c r="C447" s="17"/>
       <c r="D447" s="17"/>
@@ -9680,7 +9693,7 @@
       <c r="R447" s="17"/>
       <c r="S447" s="17"/>
     </row>
-    <row r="448" ht="14.25">
+    <row r="448" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B448" s="17"/>
       <c r="C448" s="17"/>
       <c r="D448" s="17"/>
@@ -9700,7 +9713,7 @@
       <c r="R448" s="17"/>
       <c r="S448" s="17"/>
     </row>
-    <row r="449" ht="14.25">
+    <row r="449" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B449" s="17"/>
       <c r="C449" s="17"/>
       <c r="D449" s="17"/>
@@ -9720,7 +9733,7 @@
       <c r="R449" s="17"/>
       <c r="S449" s="17"/>
     </row>
-    <row r="450" ht="14.25">
+    <row r="450" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B450" s="17"/>
       <c r="C450" s="17"/>
       <c r="D450" s="17"/>
@@ -9740,7 +9753,7 @@
       <c r="R450" s="17"/>
       <c r="S450" s="17"/>
     </row>
-    <row r="451" ht="14.25">
+    <row r="451" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B451" s="17"/>
       <c r="C451" s="17"/>
       <c r="D451" s="17"/>
@@ -9760,7 +9773,7 @@
       <c r="R451" s="17"/>
       <c r="S451" s="17"/>
     </row>
-    <row r="452" ht="14.25">
+    <row r="452" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B452" s="17"/>
       <c r="C452" s="17"/>
       <c r="D452" s="17"/>
@@ -9780,7 +9793,7 @@
       <c r="R452" s="17"/>
       <c r="S452" s="17"/>
     </row>
-    <row r="453" ht="14.25">
+    <row r="453" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B453" s="17"/>
       <c r="C453" s="17"/>
       <c r="D453" s="17"/>
@@ -9800,7 +9813,7 @@
       <c r="R453" s="17"/>
       <c r="S453" s="17"/>
     </row>
-    <row r="454" ht="14.25">
+    <row r="454" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B454" s="17"/>
       <c r="C454" s="17"/>
       <c r="D454" s="17"/>
@@ -9820,7 +9833,7 @@
       <c r="R454" s="17"/>
       <c r="S454" s="17"/>
     </row>
-    <row r="455" ht="14.25">
+    <row r="455" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B455" s="17"/>
       <c r="C455" s="17"/>
       <c r="D455" s="17"/>
@@ -9840,7 +9853,7 @@
       <c r="R455" s="17"/>
       <c r="S455" s="17"/>
     </row>
-    <row r="456" ht="14.25">
+    <row r="456" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B456" s="17"/>
       <c r="C456" s="17"/>
       <c r="D456" s="17"/>
@@ -9860,7 +9873,7 @@
       <c r="R456" s="17"/>
       <c r="S456" s="17"/>
     </row>
-    <row r="457" ht="14.25">
+    <row r="457" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B457" s="17"/>
       <c r="C457" s="17"/>
       <c r="D457" s="17"/>
@@ -9880,7 +9893,7 @@
       <c r="R457" s="17"/>
       <c r="S457" s="17"/>
     </row>
-    <row r="458" ht="14.25">
+    <row r="458" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B458" s="17"/>
       <c r="C458" s="17"/>
       <c r="D458" s="17"/>
@@ -9900,7 +9913,7 @@
       <c r="R458" s="17"/>
       <c r="S458" s="17"/>
     </row>
-    <row r="459" ht="14.25">
+    <row r="459" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B459" s="17"/>
       <c r="C459" s="17"/>
       <c r="D459" s="17"/>
@@ -9920,7 +9933,7 @@
       <c r="R459" s="17"/>
       <c r="S459" s="17"/>
     </row>
-    <row r="460" ht="14.25">
+    <row r="460" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B460" s="17"/>
       <c r="C460" s="17"/>
       <c r="D460" s="17"/>
@@ -9940,7 +9953,7 @@
       <c r="R460" s="17"/>
       <c r="S460" s="17"/>
     </row>
-    <row r="461" ht="14.25">
+    <row r="461" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B461" s="17"/>
       <c r="C461" s="17"/>
       <c r="D461" s="17"/>
@@ -9960,7 +9973,7 @@
       <c r="R461" s="17"/>
       <c r="S461" s="17"/>
     </row>
-    <row r="462" ht="14.25">
+    <row r="462" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B462" s="17"/>
       <c r="C462" s="17"/>
       <c r="D462" s="17"/>
@@ -9980,7 +9993,7 @@
       <c r="R462" s="17"/>
       <c r="S462" s="17"/>
     </row>
-    <row r="463" ht="14.25">
+    <row r="463" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B463" s="17"/>
       <c r="C463" s="17"/>
       <c r="D463" s="17"/>
@@ -10000,7 +10013,7 @@
       <c r="R463" s="17"/>
       <c r="S463" s="17"/>
     </row>
-    <row r="464" ht="14.25">
+    <row r="464" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B464" s="17"/>
       <c r="C464" s="17"/>
       <c r="D464" s="17"/>
@@ -10020,7 +10033,7 @@
       <c r="R464" s="17"/>
       <c r="S464" s="17"/>
     </row>
-    <row r="465" ht="14.25">
+    <row r="465" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B465" s="17"/>
       <c r="C465" s="17"/>
       <c r="D465" s="17"/>
@@ -10040,7 +10053,7 @@
       <c r="R465" s="17"/>
       <c r="S465" s="17"/>
     </row>
-    <row r="466" ht="14.25">
+    <row r="466" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B466" s="17"/>
       <c r="C466" s="17"/>
       <c r="D466" s="17"/>
@@ -10060,7 +10073,7 @@
       <c r="R466" s="17"/>
       <c r="S466" s="17"/>
     </row>
-    <row r="467" ht="14.25">
+    <row r="467" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B467" s="17"/>
       <c r="C467" s="17"/>
       <c r="D467" s="17"/>
@@ -10080,7 +10093,7 @@
       <c r="R467" s="17"/>
       <c r="S467" s="17"/>
     </row>
-    <row r="468" ht="14.25">
+    <row r="468" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B468" s="17"/>
       <c r="C468" s="17"/>
       <c r="D468" s="17"/>
@@ -10100,7 +10113,7 @@
       <c r="R468" s="17"/>
       <c r="S468" s="17"/>
     </row>
-    <row r="469" ht="14.25">
+    <row r="469" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B469" s="17"/>
       <c r="C469" s="17"/>
       <c r="D469" s="17"/>
@@ -10120,7 +10133,7 @@
       <c r="R469" s="17"/>
       <c r="S469" s="17"/>
     </row>
-    <row r="470" ht="14.25">
+    <row r="470" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B470" s="17"/>
       <c r="C470" s="17"/>
       <c r="D470" s="17"/>
@@ -10140,7 +10153,7 @@
       <c r="R470" s="17"/>
       <c r="S470" s="17"/>
     </row>
-    <row r="471" ht="14.25">
+    <row r="471" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B471" s="17"/>
       <c r="C471" s="17"/>
       <c r="D471" s="17"/>
@@ -10160,7 +10173,7 @@
       <c r="R471" s="17"/>
       <c r="S471" s="17"/>
     </row>
-    <row r="472" ht="14.25">
+    <row r="472" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B472" s="17"/>
       <c r="C472" s="17"/>
       <c r="D472" s="17"/>
@@ -10180,7 +10193,7 @@
       <c r="R472" s="17"/>
       <c r="S472" s="17"/>
     </row>
-    <row r="473" ht="14.25">
+    <row r="473" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B473" s="17"/>
       <c r="C473" s="17"/>
       <c r="D473" s="17"/>
@@ -10200,7 +10213,7 @@
       <c r="R473" s="17"/>
       <c r="S473" s="17"/>
     </row>
-    <row r="474" ht="14.25">
+    <row r="474" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B474" s="17"/>
       <c r="C474" s="17"/>
       <c r="D474" s="17"/>
@@ -10220,7 +10233,7 @@
       <c r="R474" s="17"/>
       <c r="S474" s="17"/>
     </row>
-    <row r="475" ht="14.25">
+    <row r="475" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B475" s="17"/>
       <c r="C475" s="17"/>
       <c r="D475" s="17"/>
@@ -10240,7 +10253,7 @@
       <c r="R475" s="17"/>
       <c r="S475" s="17"/>
     </row>
-    <row r="476" ht="14.25">
+    <row r="476" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B476" s="17"/>
       <c r="C476" s="17"/>
       <c r="D476" s="17"/>
@@ -10260,7 +10273,7 @@
       <c r="R476" s="17"/>
       <c r="S476" s="17"/>
     </row>
-    <row r="477" ht="14.25">
+    <row r="477" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B477" s="17"/>
       <c r="C477" s="17"/>
       <c r="D477" s="17"/>
@@ -10280,7 +10293,7 @@
       <c r="R477" s="17"/>
       <c r="S477" s="17"/>
     </row>
-    <row r="478" ht="14.25">
+    <row r="478" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B478" s="17"/>
       <c r="C478" s="17"/>
       <c r="D478" s="17"/>
@@ -10300,7 +10313,7 @@
       <c r="R478" s="17"/>
       <c r="S478" s="17"/>
     </row>
-    <row r="479" ht="14.25">
+    <row r="479" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B479" s="17"/>
       <c r="C479" s="17"/>
       <c r="D479" s="17"/>
@@ -10320,7 +10333,7 @@
       <c r="R479" s="17"/>
       <c r="S479" s="17"/>
     </row>
-    <row r="480" ht="14.25">
+    <row r="480" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B480" s="17"/>
       <c r="C480" s="17"/>
       <c r="D480" s="17"/>
@@ -10340,7 +10353,7 @@
       <c r="R480" s="17"/>
       <c r="S480" s="17"/>
     </row>
-    <row r="481" ht="14.25">
+    <row r="481" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B481" s="17"/>
       <c r="C481" s="17"/>
       <c r="D481" s="17"/>
@@ -10360,7 +10373,7 @@
       <c r="R481" s="17"/>
       <c r="S481" s="17"/>
     </row>
-    <row r="482" ht="14.25">
+    <row r="482" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B482" s="17"/>
       <c r="C482" s="17"/>
       <c r="D482" s="17"/>
@@ -10380,7 +10393,7 @@
       <c r="R482" s="17"/>
       <c r="S482" s="17"/>
     </row>
-    <row r="483" ht="14.25">
+    <row r="483" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B483" s="17"/>
       <c r="C483" s="17"/>
       <c r="D483" s="17"/>
@@ -10400,7 +10413,7 @@
       <c r="R483" s="17"/>
       <c r="S483" s="17"/>
     </row>
-    <row r="484" ht="14.25">
+    <row r="484" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B484" s="17"/>
       <c r="C484" s="17"/>
       <c r="D484" s="17"/>
@@ -10420,7 +10433,7 @@
       <c r="R484" s="17"/>
       <c r="S484" s="17"/>
     </row>
-    <row r="485" ht="14.25">
+    <row r="485" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B485" s="17"/>
       <c r="C485" s="17"/>
       <c r="D485" s="17"/>
@@ -10440,7 +10453,7 @@
       <c r="R485" s="17"/>
       <c r="S485" s="17"/>
     </row>
-    <row r="486" ht="14.25">
+    <row r="486" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B486" s="17"/>
       <c r="C486" s="17"/>
       <c r="D486" s="17"/>
@@ -10460,7 +10473,7 @@
       <c r="R486" s="17"/>
       <c r="S486" s="17"/>
     </row>
-    <row r="487" ht="14.25">
+    <row r="487" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B487" s="17"/>
       <c r="C487" s="17"/>
       <c r="D487" s="17"/>
@@ -10480,7 +10493,7 @@
       <c r="R487" s="17"/>
       <c r="S487" s="17"/>
     </row>
-    <row r="488" ht="14.25">
+    <row r="488" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B488" s="17"/>
       <c r="C488" s="17"/>
       <c r="D488" s="17"/>
@@ -10500,7 +10513,7 @@
       <c r="R488" s="17"/>
       <c r="S488" s="17"/>
     </row>
-    <row r="489" ht="14.25">
+    <row r="489" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B489" s="17"/>
       <c r="C489" s="17"/>
       <c r="D489" s="17"/>
@@ -10520,7 +10533,7 @@
       <c r="R489" s="17"/>
       <c r="S489" s="17"/>
     </row>
-    <row r="490" ht="14.25">
+    <row r="490" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B490" s="17"/>
       <c r="C490" s="17"/>
       <c r="D490" s="17"/>
@@ -10540,7 +10553,7 @@
       <c r="R490" s="17"/>
       <c r="S490" s="17"/>
     </row>
-    <row r="491" ht="14.25">
+    <row r="491" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B491" s="17"/>
       <c r="C491" s="17"/>
       <c r="D491" s="17"/>
@@ -10560,7 +10573,7 @@
       <c r="R491" s="17"/>
       <c r="S491" s="17"/>
     </row>
-    <row r="492" ht="14.25">
+    <row r="492" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B492" s="17"/>
       <c r="C492" s="17"/>
       <c r="D492" s="17"/>
@@ -10580,7 +10593,7 @@
       <c r="R492" s="17"/>
       <c r="S492" s="17"/>
     </row>
-    <row r="493" ht="14.25">
+    <row r="493" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B493" s="17"/>
       <c r="C493" s="17"/>
       <c r="D493" s="17"/>
@@ -10600,7 +10613,7 @@
       <c r="R493" s="17"/>
       <c r="S493" s="17"/>
     </row>
-    <row r="494" ht="14.25">
+    <row r="494" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B494" s="17"/>
       <c r="C494" s="17"/>
       <c r="D494" s="17"/>
@@ -10620,7 +10633,7 @@
       <c r="R494" s="17"/>
       <c r="S494" s="17"/>
     </row>
-    <row r="495" ht="14.25">
+    <row r="495" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B495" s="17"/>
       <c r="C495" s="17"/>
       <c r="D495" s="17"/>
@@ -10640,7 +10653,7 @@
       <c r="R495" s="17"/>
       <c r="S495" s="17"/>
     </row>
-    <row r="496" ht="14.25">
+    <row r="496" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B496" s="17"/>
       <c r="C496" s="17"/>
       <c r="D496" s="17"/>
@@ -10660,7 +10673,7 @@
       <c r="R496" s="17"/>
       <c r="S496" s="17"/>
     </row>
-    <row r="497" ht="14.25">
+    <row r="497" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B497" s="17"/>
       <c r="C497" s="17"/>
       <c r="D497" s="17"/>
@@ -10680,7 +10693,7 @@
       <c r="R497" s="17"/>
       <c r="S497" s="17"/>
     </row>
-    <row r="498" ht="14.25">
+    <row r="498" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B498" s="17"/>
       <c r="C498" s="17"/>
       <c r="D498" s="17"/>
@@ -10700,7 +10713,7 @@
       <c r="R498" s="17"/>
       <c r="S498" s="17"/>
     </row>
-    <row r="499" ht="14.25">
+    <row r="499" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B499" s="17"/>
       <c r="C499" s="17"/>
       <c r="D499" s="17"/>
@@ -10720,7 +10733,7 @@
       <c r="R499" s="17"/>
       <c r="S499" s="17"/>
     </row>
-    <row r="500" ht="14.25">
+    <row r="500" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B500" s="17"/>
       <c r="C500" s="17"/>
       <c r="D500" s="17"/>
@@ -10740,7 +10753,7 @@
       <c r="R500" s="17"/>
       <c r="S500" s="17"/>
     </row>
-    <row r="501" ht="14.25">
+    <row r="501" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B501" s="17"/>
       <c r="C501" s="17"/>
       <c r="D501" s="17"/>
@@ -10760,7 +10773,7 @@
       <c r="R501" s="17"/>
       <c r="S501" s="17"/>
     </row>
-    <row r="502" ht="14.25">
+    <row r="502" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B502" s="17"/>
       <c r="C502" s="17"/>
       <c r="D502" s="17"/>
@@ -10780,7 +10793,7 @@
       <c r="R502" s="17"/>
       <c r="S502" s="17"/>
     </row>
-    <row r="503" ht="14.25">
+    <row r="503" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B503" s="17"/>
       <c r="C503" s="17"/>
       <c r="D503" s="17"/>
@@ -10800,7 +10813,7 @@
       <c r="R503" s="17"/>
       <c r="S503" s="17"/>
     </row>
-    <row r="504" ht="14.25">
+    <row r="504" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B504" s="17"/>
       <c r="C504" s="17"/>
       <c r="D504" s="17"/>
@@ -10820,7 +10833,7 @@
       <c r="R504" s="17"/>
       <c r="S504" s="17"/>
     </row>
-    <row r="505" ht="14.25">
+    <row r="505" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B505" s="17"/>
       <c r="C505" s="17"/>
       <c r="D505" s="17"/>
@@ -10840,7 +10853,7 @@
       <c r="R505" s="17"/>
       <c r="S505" s="17"/>
     </row>
-    <row r="506" ht="14.25">
+    <row r="506" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B506" s="17"/>
       <c r="C506" s="17"/>
       <c r="D506" s="17"/>
@@ -10860,7 +10873,7 @@
       <c r="R506" s="17"/>
       <c r="S506" s="17"/>
     </row>
-    <row r="507" ht="14.25">
+    <row r="507" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B507" s="17"/>
       <c r="C507" s="17"/>
       <c r="D507" s="17"/>
@@ -10880,7 +10893,7 @@
       <c r="R507" s="17"/>
       <c r="S507" s="17"/>
     </row>
-    <row r="508" ht="14.25">
+    <row r="508" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B508" s="17"/>
       <c r="C508" s="17"/>
       <c r="D508" s="17"/>
@@ -10900,7 +10913,7 @@
       <c r="R508" s="17"/>
       <c r="S508" s="17"/>
     </row>
-    <row r="509" ht="14.25">
+    <row r="509" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B509" s="17"/>
       <c r="C509" s="17"/>
       <c r="D509" s="17"/>
@@ -10920,7 +10933,7 @@
       <c r="R509" s="17"/>
       <c r="S509" s="17"/>
     </row>
-    <row r="510" ht="14.25">
+    <row r="510" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B510" s="17"/>
       <c r="C510" s="17"/>
       <c r="D510" s="17"/>
@@ -10940,7 +10953,7 @@
       <c r="R510" s="17"/>
       <c r="S510" s="17"/>
     </row>
-    <row r="511" ht="14.25">
+    <row r="511" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B511" s="17"/>
       <c r="C511" s="17"/>
       <c r="D511" s="17"/>
@@ -10960,7 +10973,7 @@
       <c r="R511" s="17"/>
       <c r="S511" s="17"/>
     </row>
-    <row r="512" ht="14.25">
+    <row r="512" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B512" s="17"/>
       <c r="C512" s="17"/>
       <c r="D512" s="17"/>
@@ -10980,7 +10993,7 @@
       <c r="R512" s="17"/>
       <c r="S512" s="17"/>
     </row>
-    <row r="513" ht="14.25">
+    <row r="513" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B513" s="17"/>
       <c r="C513" s="17"/>
       <c r="D513" s="17"/>
@@ -11000,7 +11013,7 @@
       <c r="R513" s="17"/>
       <c r="S513" s="17"/>
     </row>
-    <row r="514" ht="14.25">
+    <row r="514" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B514" s="17"/>
       <c r="C514" s="17"/>
       <c r="D514" s="17"/>
@@ -11020,7 +11033,7 @@
       <c r="R514" s="17"/>
       <c r="S514" s="17"/>
     </row>
-    <row r="515" ht="14.25">
+    <row r="515" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B515" s="17"/>
       <c r="C515" s="17"/>
       <c r="D515" s="17"/>
@@ -11040,7 +11053,7 @@
       <c r="R515" s="17"/>
       <c r="S515" s="17"/>
     </row>
-    <row r="516" ht="14.25">
+    <row r="516" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B516" s="17"/>
       <c r="C516" s="17"/>
       <c r="D516" s="17"/>
@@ -11060,7 +11073,7 @@
       <c r="R516" s="17"/>
       <c r="S516" s="17"/>
     </row>
-    <row r="517" ht="14.25">
+    <row r="517" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B517" s="17"/>
       <c r="C517" s="17"/>
       <c r="D517" s="17"/>
@@ -11080,7 +11093,7 @@
       <c r="R517" s="17"/>
       <c r="S517" s="17"/>
     </row>
-    <row r="518" ht="14.25">
+    <row r="518" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B518" s="17"/>
       <c r="C518" s="17"/>
       <c r="D518" s="17"/>
@@ -11100,7 +11113,7 @@
       <c r="R518" s="17"/>
       <c r="S518" s="17"/>
     </row>
-    <row r="519" ht="14.25">
+    <row r="519" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B519" s="17"/>
       <c r="C519" s="17"/>
       <c r="D519" s="17"/>
@@ -11120,7 +11133,7 @@
       <c r="R519" s="17"/>
       <c r="S519" s="17"/>
     </row>
-    <row r="520" ht="14.25">
+    <row r="520" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B520" s="17"/>
       <c r="C520" s="17"/>
       <c r="D520" s="17"/>
@@ -11140,7 +11153,7 @@
       <c r="R520" s="17"/>
       <c r="S520" s="17"/>
     </row>
-    <row r="521" ht="14.25">
+    <row r="521" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B521" s="17"/>
       <c r="C521" s="17"/>
       <c r="D521" s="17"/>
@@ -11160,7 +11173,7 @@
       <c r="R521" s="17"/>
       <c r="S521" s="17"/>
     </row>
-    <row r="522" ht="14.25">
+    <row r="522" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B522" s="17"/>
       <c r="C522" s="17"/>
       <c r="D522" s="17"/>
@@ -11180,7 +11193,7 @@
       <c r="R522" s="17"/>
       <c r="S522" s="17"/>
     </row>
-    <row r="523" ht="14.25">
+    <row r="523" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B523" s="17"/>
       <c r="C523" s="17"/>
       <c r="D523" s="17"/>
@@ -11200,7 +11213,7 @@
       <c r="R523" s="17"/>
       <c r="S523" s="17"/>
     </row>
-    <row r="524" ht="14.25">
+    <row r="524" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B524" s="17"/>
       <c r="C524" s="17"/>
       <c r="D524" s="17"/>
@@ -11220,7 +11233,7 @@
       <c r="R524" s="17"/>
       <c r="S524" s="17"/>
     </row>
-    <row r="525" ht="14.25">
+    <row r="525" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B525" s="17"/>
       <c r="C525" s="17"/>
       <c r="D525" s="17"/>
@@ -11240,7 +11253,7 @@
       <c r="R525" s="17"/>
       <c r="S525" s="17"/>
     </row>
-    <row r="526" ht="14.25">
+    <row r="526" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B526" s="17"/>
       <c r="C526" s="17"/>
       <c r="D526" s="17"/>
@@ -11260,7 +11273,7 @@
       <c r="R526" s="17"/>
       <c r="S526" s="17"/>
     </row>
-    <row r="527" ht="14.25">
+    <row r="527" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B527" s="17"/>
       <c r="C527" s="17"/>
       <c r="D527" s="17"/>
@@ -11280,7 +11293,7 @@
       <c r="R527" s="17"/>
       <c r="S527" s="17"/>
     </row>
-    <row r="528" ht="14.25">
+    <row r="528" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B528" s="17"/>
       <c r="C528" s="17"/>
       <c r="D528" s="17"/>
@@ -11300,7 +11313,7 @@
       <c r="R528" s="17"/>
       <c r="S528" s="17"/>
     </row>
-    <row r="529" ht="14.25">
+    <row r="529" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B529" s="17"/>
       <c r="C529" s="17"/>
       <c r="D529" s="17"/>
@@ -11320,7 +11333,7 @@
       <c r="R529" s="17"/>
       <c r="S529" s="17"/>
     </row>
-    <row r="530" ht="14.25">
+    <row r="530" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B530" s="17"/>
       <c r="C530" s="17"/>
       <c r="D530" s="17"/>
@@ -11340,7 +11353,7 @@
       <c r="R530" s="17"/>
       <c r="S530" s="17"/>
     </row>
-    <row r="531" ht="14.25">
+    <row r="531" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B531" s="17"/>
       <c r="C531" s="17"/>
       <c r="D531" s="17"/>
@@ -11360,7 +11373,7 @@
       <c r="R531" s="17"/>
       <c r="S531" s="17"/>
     </row>
-    <row r="532" ht="14.25">
+    <row r="532" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B532" s="17"/>
       <c r="C532" s="17"/>
       <c r="D532" s="17"/>
@@ -11380,7 +11393,7 @@
       <c r="R532" s="17"/>
       <c r="S532" s="17"/>
     </row>
-    <row r="533" ht="14.25">
+    <row r="533" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B533" s="17"/>
       <c r="C533" s="17"/>
       <c r="D533" s="17"/>
@@ -11400,7 +11413,7 @@
       <c r="R533" s="17"/>
       <c r="S533" s="17"/>
     </row>
-    <row r="534" ht="14.25">
+    <row r="534" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B534" s="17"/>
       <c r="C534" s="17"/>
       <c r="D534" s="17"/>
@@ -11420,7 +11433,7 @@
       <c r="R534" s="17"/>
       <c r="S534" s="17"/>
     </row>
-    <row r="535" ht="14.25">
+    <row r="535" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B535" s="17"/>
       <c r="C535" s="17"/>
       <c r="D535" s="17"/>
@@ -11440,7 +11453,7 @@
       <c r="R535" s="17"/>
       <c r="S535" s="17"/>
     </row>
-    <row r="536" ht="14.25">
+    <row r="536" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B536" s="17"/>
       <c r="C536" s="17"/>
       <c r="D536" s="17"/>
@@ -11460,7 +11473,7 @@
       <c r="R536" s="17"/>
       <c r="S536" s="17"/>
     </row>
-    <row r="537" ht="14.25">
+    <row r="537" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B537" s="17"/>
       <c r="C537" s="17"/>
       <c r="D537" s="17"/>
@@ -11480,7 +11493,7 @@
       <c r="R537" s="17"/>
       <c r="S537" s="17"/>
     </row>
-    <row r="538" ht="14.25">
+    <row r="538" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B538" s="17"/>
       <c r="C538" s="17"/>
       <c r="D538" s="17"/>
@@ -11500,7 +11513,7 @@
       <c r="R538" s="17"/>
       <c r="S538" s="17"/>
     </row>
-    <row r="539" ht="14.25">
+    <row r="539" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B539" s="17"/>
       <c r="C539" s="17"/>
       <c r="D539" s="17"/>
@@ -11520,7 +11533,7 @@
       <c r="R539" s="17"/>
       <c r="S539" s="17"/>
     </row>
-    <row r="540" ht="14.25">
+    <row r="540" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B540" s="17"/>
       <c r="C540" s="17"/>
       <c r="D540" s="17"/>
@@ -11540,7 +11553,7 @@
       <c r="R540" s="17"/>
       <c r="S540" s="17"/>
     </row>
-    <row r="541" ht="14.25">
+    <row r="541" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B541" s="17"/>
       <c r="C541" s="17"/>
       <c r="D541" s="17"/>
@@ -11560,7 +11573,7 @@
       <c r="R541" s="17"/>
       <c r="S541" s="17"/>
     </row>
-    <row r="542" ht="14.25">
+    <row r="542" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B542" s="17"/>
       <c r="C542" s="17"/>
       <c r="D542" s="17"/>
@@ -11580,7 +11593,7 @@
       <c r="R542" s="17"/>
       <c r="S542" s="17"/>
     </row>
-    <row r="543" ht="14.25">
+    <row r="543" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B543" s="17"/>
       <c r="C543" s="17"/>
       <c r="D543" s="17"/>
@@ -11600,7 +11613,7 @@
       <c r="R543" s="17"/>
       <c r="S543" s="17"/>
     </row>
-    <row r="544" ht="14.25">
+    <row r="544" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B544" s="17"/>
       <c r="C544" s="17"/>
       <c r="D544" s="17"/>
@@ -11620,7 +11633,7 @@
       <c r="R544" s="17"/>
       <c r="S544" s="17"/>
     </row>
-    <row r="545" ht="14.25">
+    <row r="545" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B545" s="17"/>
       <c r="C545" s="17"/>
       <c r="D545" s="17"/>
@@ -11640,7 +11653,7 @@
       <c r="R545" s="17"/>
       <c r="S545" s="17"/>
     </row>
-    <row r="546" ht="14.25">
+    <row r="546" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B546" s="17"/>
       <c r="C546" s="17"/>
       <c r="D546" s="17"/>
@@ -11660,7 +11673,7 @@
       <c r="R546" s="17"/>
       <c r="S546" s="17"/>
     </row>
-    <row r="547" ht="14.25">
+    <row r="547" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B547" s="17"/>
       <c r="C547" s="17"/>
       <c r="D547" s="17"/>
@@ -11680,7 +11693,7 @@
       <c r="R547" s="17"/>
       <c r="S547" s="17"/>
     </row>
-    <row r="548" ht="14.25">
+    <row r="548" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B548" s="17"/>
       <c r="C548" s="17"/>
       <c r="D548" s="17"/>
@@ -11700,7 +11713,7 @@
       <c r="R548" s="17"/>
       <c r="S548" s="17"/>
     </row>
-    <row r="549" ht="14.25">
+    <row r="549" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B549" s="17"/>
       <c r="C549" s="17"/>
       <c r="D549" s="17"/>
@@ -11720,7 +11733,7 @@
       <c r="R549" s="17"/>
       <c r="S549" s="17"/>
     </row>
-    <row r="550" ht="14.25">
+    <row r="550" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B550" s="17"/>
       <c r="C550" s="17"/>
       <c r="D550" s="17"/>
@@ -11740,7 +11753,7 @@
       <c r="R550" s="17"/>
       <c r="S550" s="17"/>
     </row>
-    <row r="551" ht="14.25">
+    <row r="551" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B551" s="17"/>
       <c r="C551" s="17"/>
       <c r="D551" s="17"/>
@@ -11760,7 +11773,7 @@
       <c r="R551" s="17"/>
       <c r="S551" s="17"/>
     </row>
-    <row r="552" ht="14.25">
+    <row r="552" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B552" s="17"/>
       <c r="C552" s="17"/>
       <c r="D552" s="17"/>
@@ -11780,7 +11793,7 @@
       <c r="R552" s="17"/>
       <c r="S552" s="17"/>
     </row>
-    <row r="553" ht="14.25">
+    <row r="553" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B553" s="17"/>
       <c r="C553" s="17"/>
       <c r="D553" s="17"/>
@@ -11800,7 +11813,7 @@
       <c r="R553" s="17"/>
       <c r="S553" s="17"/>
     </row>
-    <row r="554" ht="14.25">
+    <row r="554" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B554" s="17"/>
       <c r="C554" s="17"/>
       <c r="D554" s="17"/>
@@ -11820,7 +11833,7 @@
       <c r="R554" s="17"/>
       <c r="S554" s="17"/>
     </row>
-    <row r="555" ht="14.25">
+    <row r="555" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B555" s="17"/>
       <c r="C555" s="17"/>
       <c r="D555" s="17"/>
@@ -11840,7 +11853,7 @@
       <c r="R555" s="17"/>
       <c r="S555" s="17"/>
     </row>
-    <row r="556" ht="14.25">
+    <row r="556" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B556" s="17"/>
       <c r="C556" s="17"/>
       <c r="D556" s="17"/>
@@ -11860,7 +11873,7 @@
       <c r="R556" s="17"/>
       <c r="S556" s="17"/>
     </row>
-    <row r="557" ht="14.25">
+    <row r="557" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B557" s="17"/>
       <c r="C557" s="17"/>
       <c r="D557" s="17"/>
@@ -11880,7 +11893,7 @@
       <c r="R557" s="17"/>
       <c r="S557" s="17"/>
     </row>
-    <row r="558" ht="14.25">
+    <row r="558" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B558" s="17"/>
       <c r="C558" s="17"/>
       <c r="D558" s="17"/>
@@ -11900,7 +11913,7 @@
       <c r="R558" s="17"/>
       <c r="S558" s="17"/>
     </row>
-    <row r="559" ht="14.25">
+    <row r="559" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B559" s="17"/>
       <c r="C559" s="17"/>
       <c r="D559" s="17"/>
@@ -11920,7 +11933,7 @@
       <c r="R559" s="17"/>
       <c r="S559" s="17"/>
     </row>
-    <row r="560" ht="14.25">
+    <row r="560" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B560" s="17"/>
       <c r="C560" s="17"/>
       <c r="D560" s="17"/>
@@ -11940,7 +11953,7 @@
       <c r="R560" s="17"/>
       <c r="S560" s="17"/>
     </row>
-    <row r="561" ht="14.25">
+    <row r="561" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B561" s="17"/>
       <c r="C561" s="17"/>
       <c r="D561" s="17"/>
@@ -11960,7 +11973,7 @@
       <c r="R561" s="17"/>
       <c r="S561" s="17"/>
     </row>
-    <row r="562" ht="14.25">
+    <row r="562" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B562" s="17"/>
       <c r="C562" s="17"/>
       <c r="D562" s="17"/>
@@ -11980,7 +11993,7 @@
       <c r="R562" s="17"/>
       <c r="S562" s="17"/>
     </row>
-    <row r="563" ht="14.25">
+    <row r="563" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B563" s="17"/>
       <c r="C563" s="17"/>
       <c r="D563" s="17"/>
@@ -12000,7 +12013,7 @@
       <c r="R563" s="17"/>
       <c r="S563" s="17"/>
     </row>
-    <row r="564" ht="14.25">
+    <row r="564" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B564" s="17"/>
       <c r="C564" s="17"/>
       <c r="D564" s="17"/>
@@ -12020,7 +12033,7 @@
       <c r="R564" s="17"/>
       <c r="S564" s="17"/>
     </row>
-    <row r="565" ht="14.25">
+    <row r="565" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B565" s="17"/>
       <c r="C565" s="17"/>
       <c r="D565" s="17"/>
@@ -12040,7 +12053,7 @@
       <c r="R565" s="17"/>
       <c r="S565" s="17"/>
     </row>
-    <row r="566" ht="14.25">
+    <row r="566" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B566" s="17"/>
       <c r="C566" s="17"/>
       <c r="D566" s="17"/>
@@ -12060,7 +12073,7 @@
       <c r="R566" s="17"/>
       <c r="S566" s="17"/>
     </row>
-    <row r="567" ht="14.25">
+    <row r="567" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B567" s="17"/>
       <c r="C567" s="17"/>
       <c r="D567" s="17"/>
@@ -12080,7 +12093,7 @@
       <c r="R567" s="17"/>
       <c r="S567" s="17"/>
     </row>
-    <row r="568" ht="14.25">
+    <row r="568" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B568" s="17"/>
       <c r="C568" s="17"/>
       <c r="D568" s="17"/>
@@ -12100,7 +12113,7 @@
       <c r="R568" s="17"/>
       <c r="S568" s="17"/>
     </row>
-    <row r="569" ht="14.25">
+    <row r="569" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B569" s="17"/>
       <c r="C569" s="17"/>
       <c r="D569" s="17"/>
@@ -12120,7 +12133,7 @@
       <c r="R569" s="17"/>
       <c r="S569" s="17"/>
     </row>
-    <row r="570" ht="14.25">
+    <row r="570" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B570" s="17"/>
       <c r="C570" s="17"/>
       <c r="D570" s="17"/>
@@ -12140,7 +12153,7 @@
       <c r="R570" s="17"/>
       <c r="S570" s="17"/>
     </row>
-    <row r="571" ht="14.25">
+    <row r="571" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B571" s="17"/>
       <c r="C571" s="17"/>
       <c r="D571" s="17"/>
@@ -12160,7 +12173,7 @@
       <c r="R571" s="17"/>
       <c r="S571" s="17"/>
     </row>
-    <row r="572" ht="14.25">
+    <row r="572" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B572" s="17"/>
       <c r="C572" s="17"/>
       <c r="D572" s="17"/>
@@ -12180,7 +12193,7 @@
       <c r="R572" s="17"/>
       <c r="S572" s="17"/>
     </row>
-    <row r="573" ht="14.25">
+    <row r="573" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B573" s="17"/>
       <c r="C573" s="17"/>
       <c r="D573" s="17"/>
@@ -12200,7 +12213,7 @@
       <c r="R573" s="17"/>
       <c r="S573" s="17"/>
     </row>
-    <row r="574" ht="14.25">
+    <row r="574" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B574" s="17"/>
       <c r="C574" s="17"/>
       <c r="D574" s="17"/>
@@ -12220,7 +12233,7 @@
       <c r="R574" s="17"/>
       <c r="S574" s="17"/>
     </row>
-    <row r="575" ht="14.25">
+    <row r="575" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B575" s="17"/>
       <c r="C575" s="17"/>
       <c r="D575" s="17"/>
@@ -12240,7 +12253,7 @@
       <c r="R575" s="17"/>
       <c r="S575" s="17"/>
     </row>
-    <row r="576" ht="14.25">
+    <row r="576" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B576" s="17"/>
       <c r="C576" s="17"/>
       <c r="D576" s="17"/>
@@ -12260,7 +12273,7 @@
       <c r="R576" s="17"/>
       <c r="S576" s="17"/>
     </row>
-    <row r="577" ht="14.25">
+    <row r="577" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B577" s="17"/>
       <c r="C577" s="17"/>
       <c r="D577" s="17"/>
@@ -12280,7 +12293,7 @@
       <c r="R577" s="17"/>
       <c r="S577" s="17"/>
     </row>
-    <row r="578" ht="14.25">
+    <row r="578" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B578" s="17"/>
       <c r="C578" s="17"/>
       <c r="D578" s="17"/>
@@ -12300,7 +12313,7 @@
       <c r="R578" s="17"/>
       <c r="S578" s="17"/>
     </row>
-    <row r="579" ht="14.25">
+    <row r="579" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B579" s="17"/>
       <c r="C579" s="17"/>
       <c r="D579" s="17"/>
@@ -12320,7 +12333,7 @@
       <c r="R579" s="17"/>
       <c r="S579" s="17"/>
     </row>
-    <row r="580" ht="14.25">
+    <row r="580" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B580" s="17"/>
       <c r="C580" s="17"/>
       <c r="D580" s="17"/>
@@ -12340,7 +12353,7 @@
       <c r="R580" s="17"/>
       <c r="S580" s="17"/>
     </row>
-    <row r="581" ht="14.25">
+    <row r="581" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B581" s="17"/>
       <c r="C581" s="17"/>
       <c r="D581" s="17"/>
@@ -12360,7 +12373,7 @@
       <c r="R581" s="17"/>
       <c r="S581" s="17"/>
     </row>
-    <row r="582" ht="14.25">
+    <row r="582" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B582" s="17"/>
       <c r="C582" s="17"/>
       <c r="D582" s="17"/>
@@ -12380,7 +12393,7 @@
       <c r="R582" s="17"/>
       <c r="S582" s="17"/>
     </row>
-    <row r="583" ht="14.25">
+    <row r="583" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B583" s="17"/>
       <c r="C583" s="17"/>
       <c r="D583" s="17"/>
@@ -12400,7 +12413,7 @@
       <c r="R583" s="17"/>
       <c r="S583" s="17"/>
     </row>
-    <row r="584" ht="14.25">
+    <row r="584" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B584" s="17"/>
       <c r="C584" s="17"/>
       <c r="D584" s="17"/>
@@ -12420,7 +12433,7 @@
       <c r="R584" s="17"/>
       <c r="S584" s="17"/>
     </row>
-    <row r="585" ht="14.25">
+    <row r="585" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B585" s="17"/>
       <c r="C585" s="17"/>
       <c r="D585" s="17"/>
@@ -12440,7 +12453,7 @@
       <c r="R585" s="17"/>
       <c r="S585" s="17"/>
     </row>
-    <row r="586" ht="14.25">
+    <row r="586" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B586" s="17"/>
       <c r="C586" s="17"/>
       <c r="D586" s="17"/>
@@ -12460,7 +12473,7 @@
       <c r="R586" s="17"/>
       <c r="S586" s="17"/>
     </row>
-    <row r="587" ht="14.25">
+    <row r="587" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B587" s="17"/>
       <c r="C587" s="17"/>
       <c r="D587" s="17"/>
@@ -12480,7 +12493,7 @@
       <c r="R587" s="17"/>
       <c r="S587" s="17"/>
     </row>
-    <row r="588" ht="14.25">
+    <row r="588" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B588" s="17"/>
       <c r="C588" s="17"/>
       <c r="D588" s="17"/>
@@ -12500,7 +12513,7 @@
       <c r="R588" s="17"/>
       <c r="S588" s="17"/>
     </row>
-    <row r="589" ht="14.25">
+    <row r="589" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B589" s="17"/>
       <c r="C589" s="17"/>
       <c r="D589" s="17"/>
@@ -12520,7 +12533,7 @@
       <c r="R589" s="17"/>
       <c r="S589" s="17"/>
     </row>
-    <row r="590" ht="14.25">
+    <row r="590" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B590" s="17"/>
       <c r="C590" s="17"/>
       <c r="D590" s="17"/>
@@ -12540,7 +12553,7 @@
       <c r="R590" s="17"/>
       <c r="S590" s="17"/>
     </row>
-    <row r="591" ht="14.25">
+    <row r="591" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B591" s="17"/>
       <c r="C591" s="17"/>
       <c r="D591" s="17"/>
@@ -12560,7 +12573,7 @@
       <c r="R591" s="17"/>
       <c r="S591" s="17"/>
     </row>
-    <row r="592" ht="14.25">
+    <row r="592" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B592" s="17"/>
       <c r="C592" s="17"/>
       <c r="D592" s="17"/>
@@ -12580,7 +12593,7 @@
       <c r="R592" s="17"/>
       <c r="S592" s="17"/>
     </row>
-    <row r="593" ht="14.25">
+    <row r="593" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B593" s="17"/>
       <c r="C593" s="17"/>
       <c r="D593" s="17"/>
@@ -12600,7 +12613,7 @@
       <c r="R593" s="17"/>
       <c r="S593" s="17"/>
     </row>
-    <row r="594" ht="14.25">
+    <row r="594" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B594" s="17"/>
       <c r="C594" s="17"/>
       <c r="D594" s="17"/>
@@ -12620,7 +12633,7 @@
       <c r="R594" s="17"/>
       <c r="S594" s="17"/>
     </row>
-    <row r="595" ht="14.25">
+    <row r="595" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B595" s="17"/>
       <c r="C595" s="17"/>
       <c r="D595" s="17"/>
@@ -12640,7 +12653,7 @@
       <c r="R595" s="17"/>
       <c r="S595" s="17"/>
     </row>
-    <row r="596" ht="14.25">
+    <row r="596" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B596" s="17"/>
       <c r="C596" s="17"/>
       <c r="D596" s="17"/>
@@ -12660,7 +12673,7 @@
       <c r="R596" s="17"/>
       <c r="S596" s="17"/>
     </row>
-    <row r="597" ht="14.25">
+    <row r="597" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B597" s="17"/>
       <c r="C597" s="17"/>
       <c r="D597" s="17"/>
@@ -12680,7 +12693,7 @@
       <c r="R597" s="17"/>
       <c r="S597" s="17"/>
     </row>
-    <row r="598" ht="14.25">
+    <row r="598" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B598" s="17"/>
       <c r="C598" s="17"/>
       <c r="D598" s="17"/>
@@ -12700,7 +12713,7 @@
       <c r="R598" s="17"/>
       <c r="S598" s="17"/>
     </row>
-    <row r="599" ht="14.25">
+    <row r="599" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B599" s="17"/>
       <c r="C599" s="17"/>
       <c r="D599" s="17"/>
@@ -12720,7 +12733,7 @@
       <c r="R599" s="17"/>
       <c r="S599" s="17"/>
     </row>
-    <row r="600" ht="14.25">
+    <row r="600" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B600" s="17"/>
       <c r="C600" s="17"/>
       <c r="D600" s="17"/>
@@ -12740,7 +12753,7 @@
       <c r="R600" s="17"/>
       <c r="S600" s="17"/>
     </row>
-    <row r="601" ht="14.25">
+    <row r="601" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B601" s="17"/>
       <c r="C601" s="17"/>
       <c r="D601" s="17"/>
@@ -12760,7 +12773,7 @@
       <c r="R601" s="17"/>
       <c r="S601" s="17"/>
     </row>
-    <row r="602" ht="14.25">
+    <row r="602" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B602" s="17"/>
       <c r="C602" s="17"/>
       <c r="D602" s="17"/>
@@ -12780,7 +12793,7 @@
       <c r="R602" s="17"/>
       <c r="S602" s="17"/>
     </row>
-    <row r="603" ht="14.25">
+    <row r="603" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B603" s="17"/>
       <c r="C603" s="17"/>
       <c r="D603" s="17"/>
@@ -12800,7 +12813,7 @@
       <c r="R603" s="17"/>
       <c r="S603" s="17"/>
     </row>
-    <row r="604" ht="14.25">
+    <row r="604" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B604" s="17"/>
       <c r="C604" s="17"/>
       <c r="D604" s="17"/>
@@ -12820,7 +12833,7 @@
       <c r="R604" s="17"/>
       <c r="S604" s="17"/>
     </row>
-    <row r="605" ht="14.25">
+    <row r="605" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B605" s="17"/>
       <c r="C605" s="17"/>
       <c r="D605" s="17"/>
@@ -12840,7 +12853,7 @@
       <c r="R605" s="17"/>
       <c r="S605" s="17"/>
     </row>
-    <row r="606" ht="14.25">
+    <row r="606" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B606" s="17"/>
       <c r="C606" s="17"/>
       <c r="D606" s="17"/>
@@ -12860,7 +12873,7 @@
       <c r="R606" s="17"/>
       <c r="S606" s="17"/>
     </row>
-    <row r="607" ht="14.25">
+    <row r="607" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B607" s="17"/>
       <c r="C607" s="17"/>
       <c r="D607" s="17"/>
@@ -12880,7 +12893,7 @@
       <c r="R607" s="17"/>
       <c r="S607" s="17"/>
     </row>
-    <row r="608" ht="14.25">
+    <row r="608" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B608" s="17"/>
       <c r="C608" s="17"/>
       <c r="D608" s="17"/>
@@ -12900,7 +12913,7 @@
       <c r="R608" s="17"/>
       <c r="S608" s="17"/>
     </row>
-    <row r="609" ht="14.25">
+    <row r="609" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B609" s="17"/>
       <c r="C609" s="17"/>
       <c r="D609" s="17"/>
@@ -12920,7 +12933,7 @@
       <c r="R609" s="17"/>
       <c r="S609" s="17"/>
     </row>
-    <row r="610" ht="14.25">
+    <row r="610" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B610" s="17"/>
       <c r="C610" s="17"/>
       <c r="D610" s="17"/>
@@ -12940,7 +12953,7 @@
       <c r="R610" s="17"/>
       <c r="S610" s="17"/>
     </row>
-    <row r="611" ht="14.25">
+    <row r="611" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B611" s="17"/>
       <c r="C611" s="17"/>
       <c r="D611" s="17"/>
@@ -12960,7 +12973,7 @@
       <c r="R611" s="17"/>
       <c r="S611" s="17"/>
     </row>
-    <row r="612" ht="14.25">
+    <row r="612" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B612" s="17"/>
       <c r="C612" s="17"/>
       <c r="D612" s="17"/>
@@ -12980,7 +12993,7 @@
       <c r="R612" s="17"/>
       <c r="S612" s="17"/>
     </row>
-    <row r="613" ht="14.25">
+    <row r="613" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B613" s="17"/>
       <c r="C613" s="17"/>
       <c r="D613" s="17"/>
@@ -13000,7 +13013,7 @@
       <c r="R613" s="17"/>
       <c r="S613" s="17"/>
     </row>
-    <row r="614" ht="14.25">
+    <row r="614" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B614" s="17"/>
       <c r="C614" s="17"/>
       <c r="D614" s="17"/>
@@ -13020,7 +13033,7 @@
       <c r="R614" s="17"/>
       <c r="S614" s="17"/>
     </row>
-    <row r="615" ht="14.25">
+    <row r="615" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B615" s="17"/>
       <c r="C615" s="17"/>
       <c r="D615" s="17"/>
@@ -13040,7 +13053,7 @@
       <c r="R615" s="17"/>
       <c r="S615" s="17"/>
     </row>
-    <row r="616" ht="14.25">
+    <row r="616" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B616" s="17"/>
       <c r="C616" s="17"/>
       <c r="D616" s="17"/>
@@ -13060,7 +13073,7 @@
       <c r="R616" s="17"/>
       <c r="S616" s="17"/>
     </row>
-    <row r="617" ht="14.25">
+    <row r="617" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B617" s="17"/>
       <c r="C617" s="17"/>
       <c r="D617" s="17"/>
@@ -13080,7 +13093,7 @@
       <c r="R617" s="17"/>
       <c r="S617" s="17"/>
     </row>
-    <row r="618" ht="14.25">
+    <row r="618" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B618" s="17"/>
       <c r="C618" s="17"/>
       <c r="D618" s="17"/>
@@ -13100,7 +13113,7 @@
       <c r="R618" s="17"/>
       <c r="S618" s="17"/>
     </row>
-    <row r="619" ht="14.25">
+    <row r="619" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B619" s="17"/>
       <c r="C619" s="17"/>
       <c r="D619" s="17"/>
@@ -13120,7 +13133,7 @@
       <c r="R619" s="17"/>
       <c r="S619" s="17"/>
     </row>
-    <row r="620" ht="14.25">
+    <row r="620" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B620" s="17"/>
       <c r="C620" s="17"/>
       <c r="D620" s="17"/>
@@ -13140,7 +13153,7 @@
       <c r="R620" s="17"/>
       <c r="S620" s="17"/>
     </row>
-    <row r="621" ht="14.25">
+    <row r="621" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B621" s="17"/>
       <c r="C621" s="17"/>
       <c r="D621" s="17"/>
@@ -13160,7 +13173,7 @@
       <c r="R621" s="17"/>
       <c r="S621" s="17"/>
     </row>
-    <row r="622" ht="14.25">
+    <row r="622" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B622" s="17"/>
       <c r="C622" s="17"/>
       <c r="D622" s="17"/>
@@ -13180,7 +13193,7 @@
       <c r="R622" s="17"/>
       <c r="S622" s="17"/>
     </row>
-    <row r="623" ht="14.25">
+    <row r="623" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B623" s="17"/>
       <c r="C623" s="17"/>
       <c r="D623" s="17"/>
@@ -13200,7 +13213,7 @@
       <c r="R623" s="17"/>
       <c r="S623" s="17"/>
     </row>
-    <row r="624" ht="14.25">
+    <row r="624" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B624" s="17"/>
       <c r="C624" s="17"/>
       <c r="D624" s="17"/>
@@ -13220,7 +13233,7 @@
       <c r="R624" s="17"/>
       <c r="S624" s="17"/>
     </row>
-    <row r="625" ht="14.25">
+    <row r="625" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B625" s="17"/>
       <c r="C625" s="17"/>
       <c r="D625" s="17"/>
@@ -13240,7 +13253,7 @@
       <c r="R625" s="17"/>
       <c r="S625" s="17"/>
     </row>
-    <row r="626" ht="14.25">
+    <row r="626" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B626" s="17"/>
       <c r="C626" s="17"/>
       <c r="D626" s="17"/>
@@ -13260,7 +13273,7 @@
       <c r="R626" s="17"/>
       <c r="S626" s="17"/>
     </row>
-    <row r="627" ht="14.25">
+    <row r="627" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B627" s="17"/>
       <c r="C627" s="17"/>
       <c r="D627" s="17"/>
@@ -13280,7 +13293,7 @@
       <c r="R627" s="17"/>
       <c r="S627" s="17"/>
     </row>
-    <row r="628" ht="14.25">
+    <row r="628" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B628" s="17"/>
       <c r="C628" s="17"/>
       <c r="D628" s="17"/>
@@ -13300,7 +13313,7 @@
       <c r="R628" s="17"/>
       <c r="S628" s="17"/>
     </row>
-    <row r="629" ht="14.25">
+    <row r="629" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B629" s="17"/>
       <c r="C629" s="17"/>
       <c r="D629" s="17"/>
@@ -13320,7 +13333,7 @@
       <c r="R629" s="17"/>
       <c r="S629" s="17"/>
     </row>
-    <row r="630" ht="14.25">
+    <row r="630" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B630" s="17"/>
       <c r="C630" s="17"/>
       <c r="D630" s="17"/>
@@ -13340,7 +13353,7 @@
       <c r="R630" s="17"/>
       <c r="S630" s="17"/>
     </row>
-    <row r="631" ht="14.25">
+    <row r="631" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B631" s="17"/>
       <c r="C631" s="17"/>
       <c r="D631" s="17"/>
@@ -13360,7 +13373,7 @@
       <c r="R631" s="17"/>
       <c r="S631" s="17"/>
     </row>
-    <row r="632" ht="14.25">
+    <row r="632" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B632" s="17"/>
       <c r="C632" s="17"/>
       <c r="D632" s="17"/>
@@ -13380,7 +13393,7 @@
       <c r="R632" s="17"/>
       <c r="S632" s="17"/>
     </row>
-    <row r="633" ht="14.25">
+    <row r="633" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B633" s="17"/>
       <c r="C633" s="17"/>
       <c r="D633" s="17"/>
@@ -13400,7 +13413,7 @@
       <c r="R633" s="17"/>
       <c r="S633" s="17"/>
     </row>
-    <row r="634" ht="14.25">
+    <row r="634" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B634" s="17"/>
       <c r="C634" s="17"/>
       <c r="D634" s="17"/>
@@ -13420,7 +13433,7 @@
       <c r="R634" s="17"/>
       <c r="S634" s="17"/>
     </row>
-    <row r="635" ht="14.25">
+    <row r="635" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B635" s="17"/>
       <c r="C635" s="17"/>
       <c r="D635" s="17"/>
@@ -13440,7 +13453,7 @@
       <c r="R635" s="17"/>
       <c r="S635" s="17"/>
     </row>
-    <row r="636" ht="14.25">
+    <row r="636" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B636" s="17"/>
       <c r="C636" s="17"/>
       <c r="D636" s="17"/>
@@ -13460,7 +13473,7 @@
       <c r="R636" s="17"/>
       <c r="S636" s="17"/>
     </row>
-    <row r="637" ht="14.25">
+    <row r="637" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B637" s="17"/>
       <c r="C637" s="17"/>
       <c r="D637" s="17"/>
@@ -13480,7 +13493,7 @@
       <c r="R637" s="17"/>
       <c r="S637" s="17"/>
     </row>
-    <row r="638" ht="14.25">
+    <row r="638" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B638" s="17"/>
       <c r="C638" s="17"/>
       <c r="D638" s="17"/>
@@ -13500,7 +13513,7 @@
       <c r="R638" s="17"/>
       <c r="S638" s="17"/>
     </row>
-    <row r="639" ht="14.25">
+    <row r="639" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B639" s="17"/>
       <c r="C639" s="17"/>
       <c r="D639" s="17"/>
@@ -13520,7 +13533,7 @@
       <c r="R639" s="17"/>
       <c r="S639" s="17"/>
     </row>
-    <row r="640" ht="14.25">
+    <row r="640" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B640" s="17"/>
       <c r="C640" s="17"/>
       <c r="D640" s="17"/>
@@ -13540,7 +13553,7 @@
       <c r="R640" s="17"/>
       <c r="S640" s="17"/>
     </row>
-    <row r="641" ht="14.25">
+    <row r="641" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B641" s="17"/>
       <c r="C641" s="17"/>
       <c r="D641" s="17"/>
@@ -13560,7 +13573,7 @@
       <c r="R641" s="17"/>
       <c r="S641" s="17"/>
     </row>
-    <row r="642" ht="14.25">
+    <row r="642" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B642" s="17"/>
       <c r="C642" s="17"/>
       <c r="D642" s="17"/>
@@ -13580,7 +13593,7 @@
       <c r="R642" s="17"/>
       <c r="S642" s="17"/>
     </row>
-    <row r="643" ht="14.25">
+    <row r="643" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B643" s="17"/>
       <c r="C643" s="17"/>
       <c r="D643" s="17"/>
@@ -13600,7 +13613,7 @@
       <c r="R643" s="17"/>
       <c r="S643" s="17"/>
     </row>
-    <row r="644" ht="14.25">
+    <row r="644" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B644" s="17"/>
       <c r="C644" s="17"/>
       <c r="D644" s="17"/>
@@ -13620,7 +13633,7 @@
       <c r="R644" s="17"/>
       <c r="S644" s="17"/>
     </row>
-    <row r="645" ht="14.25">
+    <row r="645" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B645" s="17"/>
       <c r="C645" s="17"/>
       <c r="D645" s="17"/>
@@ -13640,7 +13653,7 @@
       <c r="R645" s="17"/>
       <c r="S645" s="17"/>
     </row>
-    <row r="646" ht="14.25">
+    <row r="646" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B646" s="17"/>
       <c r="C646" s="17"/>
       <c r="D646" s="17"/>
@@ -13660,7 +13673,7 @@
       <c r="R646" s="17"/>
       <c r="S646" s="17"/>
     </row>
-    <row r="647" ht="14.25">
+    <row r="647" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B647" s="17"/>
       <c r="C647" s="17"/>
       <c r="D647" s="17"/>
@@ -13680,7 +13693,7 @@
       <c r="R647" s="17"/>
       <c r="S647" s="17"/>
     </row>
-    <row r="648" ht="14.25">
+    <row r="648" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B648" s="17"/>
       <c r="C648" s="17"/>
       <c r="D648" s="17"/>
@@ -13700,7 +13713,7 @@
       <c r="R648" s="17"/>
       <c r="S648" s="17"/>
     </row>
-    <row r="649" ht="14.25">
+    <row r="649" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B649" s="17"/>
       <c r="C649" s="17"/>
       <c r="D649" s="17"/>
@@ -13720,7 +13733,7 @@
       <c r="R649" s="17"/>
       <c r="S649" s="17"/>
     </row>
-    <row r="650" ht="14.25">
+    <row r="650" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B650" s="17"/>
       <c r="C650" s="17"/>
       <c r="D650" s="17"/>
@@ -13740,7 +13753,7 @@
       <c r="R650" s="17"/>
       <c r="S650" s="17"/>
     </row>
-    <row r="651" ht="14.25">
+    <row r="651" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B651" s="17"/>
       <c r="C651" s="17"/>
       <c r="D651" s="17"/>
@@ -13760,7 +13773,7 @@
       <c r="R651" s="17"/>
       <c r="S651" s="17"/>
     </row>
-    <row r="652" ht="14.25">
+    <row r="652" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B652" s="17"/>
       <c r="C652" s="17"/>
       <c r="D652" s="17"/>
@@ -13780,7 +13793,7 @@
       <c r="R652" s="17"/>
       <c r="S652" s="17"/>
     </row>
-    <row r="653" ht="14.25">
+    <row r="653" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B653" s="17"/>
       <c r="C653" s="17"/>
       <c r="D653" s="17"/>
@@ -13800,7 +13813,7 @@
       <c r="R653" s="17"/>
       <c r="S653" s="17"/>
     </row>
-    <row r="654" ht="14.25">
+    <row r="654" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B654" s="17"/>
       <c r="C654" s="17"/>
       <c r="D654" s="17"/>
@@ -13820,7 +13833,7 @@
       <c r="R654" s="17"/>
       <c r="S654" s="17"/>
     </row>
-    <row r="655" ht="14.25">
+    <row r="655" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B655" s="17"/>
       <c r="C655" s="17"/>
       <c r="D655" s="17"/>
@@ -13840,7 +13853,7 @@
       <c r="R655" s="17"/>
       <c r="S655" s="17"/>
     </row>
-    <row r="656" ht="14.25">
+    <row r="656" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B656" s="17"/>
       <c r="C656" s="17"/>
       <c r="D656" s="17"/>
@@ -13860,7 +13873,7 @@
       <c r="R656" s="17"/>
       <c r="S656" s="17"/>
     </row>
-    <row r="657" ht="14.25">
+    <row r="657" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B657" s="17"/>
       <c r="C657" s="17"/>
       <c r="D657" s="17"/>
@@ -13880,7 +13893,7 @@
       <c r="R657" s="17"/>
       <c r="S657" s="17"/>
     </row>
-    <row r="658" ht="14.25">
+    <row r="658" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B658" s="17"/>
       <c r="C658" s="17"/>
       <c r="D658" s="17"/>
@@ -13900,7 +13913,7 @@
       <c r="R658" s="17"/>
       <c r="S658" s="17"/>
     </row>
-    <row r="659" ht="14.25">
+    <row r="659" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B659" s="17"/>
       <c r="C659" s="17"/>
       <c r="D659" s="17"/>
@@ -13920,7 +13933,7 @@
       <c r="R659" s="17"/>
       <c r="S659" s="17"/>
     </row>
-    <row r="660" ht="14.25">
+    <row r="660" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B660" s="17"/>
       <c r="C660" s="17"/>
       <c r="D660" s="17"/>
@@ -13940,7 +13953,7 @@
       <c r="R660" s="17"/>
       <c r="S660" s="17"/>
     </row>
-    <row r="661" ht="14.25">
+    <row r="661" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B661" s="17"/>
       <c r="C661" s="17"/>
       <c r="D661" s="17"/>
@@ -13960,7 +13973,7 @@
       <c r="R661" s="17"/>
       <c r="S661" s="17"/>
     </row>
-    <row r="662" ht="14.25">
+    <row r="662" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B662" s="17"/>
       <c r="C662" s="17"/>
       <c r="D662" s="17"/>
@@ -13980,7 +13993,7 @@
       <c r="R662" s="17"/>
       <c r="S662" s="17"/>
     </row>
-    <row r="663" ht="14.25">
+    <row r="663" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B663" s="17"/>
       <c r="C663" s="17"/>
       <c r="D663" s="17"/>
@@ -14000,7 +14013,7 @@
       <c r="R663" s="17"/>
       <c r="S663" s="17"/>
     </row>
-    <row r="664" ht="14.25">
+    <row r="664" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B664" s="17"/>
       <c r="C664" s="17"/>
       <c r="D664" s="17"/>
@@ -14020,7 +14033,7 @@
       <c r="R664" s="17"/>
       <c r="S664" s="17"/>
     </row>
-    <row r="665" ht="14.25">
+    <row r="665" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B665" s="17"/>
       <c r="C665" s="17"/>
       <c r="D665" s="17"/>
@@ -14040,7 +14053,7 @@
       <c r="R665" s="17"/>
       <c r="S665" s="17"/>
     </row>
-    <row r="666" ht="14.25">
+    <row r="666" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B666" s="17"/>
       <c r="C666" s="17"/>
       <c r="D666" s="17"/>
@@ -14060,7 +14073,7 @@
       <c r="R666" s="17"/>
       <c r="S666" s="17"/>
     </row>
-    <row r="667" ht="14.25">
+    <row r="667" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B667" s="17"/>
       <c r="C667" s="17"/>
       <c r="D667" s="17"/>
@@ -14080,7 +14093,7 @@
       <c r="R667" s="17"/>
       <c r="S667" s="17"/>
     </row>
-    <row r="668" ht="14.25">
+    <row r="668" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B668" s="17"/>
       <c r="C668" s="17"/>
       <c r="D668" s="17"/>
@@ -14100,7 +14113,7 @@
       <c r="R668" s="17"/>
       <c r="S668" s="17"/>
     </row>
-    <row r="669" ht="14.25">
+    <row r="669" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B669" s="17"/>
       <c r="C669" s="17"/>
       <c r="D669" s="17"/>
@@ -14120,7 +14133,7 @@
       <c r="R669" s="17"/>
       <c r="S669" s="17"/>
     </row>
-    <row r="670" ht="14.25">
+    <row r="670" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B670" s="17"/>
       <c r="C670" s="17"/>
       <c r="D670" s="17"/>
@@ -14140,7 +14153,7 @@
       <c r="R670" s="17"/>
       <c r="S670" s="17"/>
     </row>
-    <row r="671" ht="14.25">
+    <row r="671" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B671" s="17"/>
       <c r="C671" s="17"/>
       <c r="D671" s="17"/>
@@ -14160,7 +14173,7 @@
       <c r="R671" s="17"/>
       <c r="S671" s="17"/>
     </row>
-    <row r="672" ht="14.25">
+    <row r="672" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B672" s="17"/>
       <c r="C672" s="17"/>
       <c r="D672" s="17"/>
@@ -14180,7 +14193,7 @@
       <c r="R672" s="17"/>
       <c r="S672" s="17"/>
     </row>
-    <row r="673" ht="14.25">
+    <row r="673" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B673" s="17"/>
       <c r="C673" s="17"/>
       <c r="D673" s="17"/>
@@ -14200,7 +14213,7 @@
       <c r="R673" s="17"/>
       <c r="S673" s="17"/>
     </row>
-    <row r="674" ht="14.25">
+    <row r="674" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B674" s="17"/>
       <c r="C674" s="17"/>
       <c r="D674" s="17"/>
@@ -14220,7 +14233,7 @@
       <c r="R674" s="17"/>
       <c r="S674" s="17"/>
     </row>
-    <row r="675" ht="14.25">
+    <row r="675" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B675" s="17"/>
       <c r="C675" s="17"/>
       <c r="D675" s="17"/>
@@ -14240,7 +14253,7 @@
       <c r="R675" s="17"/>
       <c r="S675" s="17"/>
     </row>
-    <row r="676" ht="14.25">
+    <row r="676" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B676" s="17"/>
       <c r="C676" s="17"/>
       <c r="D676" s="17"/>
@@ -14260,7 +14273,7 @@
       <c r="R676" s="17"/>
       <c r="S676" s="17"/>
     </row>
-    <row r="677" ht="14.25">
+    <row r="677" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B677" s="17"/>
       <c r="C677" s="17"/>
       <c r="D677" s="17"/>
@@ -14280,7 +14293,7 @@
       <c r="R677" s="17"/>
       <c r="S677" s="17"/>
     </row>
-    <row r="678" ht="14.25">
+    <row r="678" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B678" s="17"/>
       <c r="C678" s="17"/>
       <c r="D678" s="17"/>
@@ -14300,7 +14313,7 @@
       <c r="R678" s="17"/>
       <c r="S678" s="17"/>
     </row>
-    <row r="679" ht="14.25">
+    <row r="679" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B679" s="17"/>
       <c r="C679" s="17"/>
       <c r="D679" s="17"/>
@@ -14320,7 +14333,7 @@
       <c r="R679" s="17"/>
       <c r="S679" s="17"/>
     </row>
-    <row r="680" ht="14.25">
+    <row r="680" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B680" s="17"/>
       <c r="C680" s="17"/>
       <c r="D680" s="17"/>
@@ -14340,7 +14353,7 @@
       <c r="R680" s="17"/>
       <c r="S680" s="17"/>
     </row>
-    <row r="681" ht="14.25">
+    <row r="681" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B681" s="17"/>
       <c r="C681" s="17"/>
       <c r="D681" s="17"/>
@@ -14360,7 +14373,7 @@
       <c r="R681" s="17"/>
       <c r="S681" s="17"/>
     </row>
-    <row r="682" ht="14.25">
+    <row r="682" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B682" s="17"/>
       <c r="C682" s="17"/>
       <c r="D682" s="17"/>
@@ -14380,7 +14393,7 @@
       <c r="R682" s="17"/>
       <c r="S682" s="17"/>
     </row>
-    <row r="683" ht="14.25">
+    <row r="683" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B683" s="17"/>
       <c r="C683" s="17"/>
       <c r="D683" s="17"/>
@@ -14400,7 +14413,7 @@
       <c r="R683" s="17"/>
       <c r="S683" s="17"/>
     </row>
-    <row r="684" ht="14.25">
+    <row r="684" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B684" s="17"/>
       <c r="C684" s="17"/>
       <c r="D684" s="17"/>
@@ -14420,7 +14433,7 @@
       <c r="R684" s="17"/>
       <c r="S684" s="17"/>
     </row>
-    <row r="685" ht="14.25">
+    <row r="685" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B685" s="17"/>
       <c r="C685" s="17"/>
       <c r="D685" s="17"/>
@@ -14440,7 +14453,7 @@
       <c r="R685" s="17"/>
       <c r="S685" s="17"/>
     </row>
-    <row r="686" ht="14.25">
+    <row r="686" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B686" s="17"/>
       <c r="C686" s="17"/>
       <c r="D686" s="17"/>
@@ -14460,7 +14473,7 @@
       <c r="R686" s="17"/>
       <c r="S686" s="17"/>
     </row>
-    <row r="687" ht="14.25">
+    <row r="687" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B687" s="17"/>
       <c r="C687" s="17"/>
       <c r="D687" s="17"/>
@@ -14480,7 +14493,7 @@
       <c r="R687" s="17"/>
       <c r="S687" s="17"/>
     </row>
-    <row r="688" ht="14.25">
+    <row r="688" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B688" s="17"/>
       <c r="C688" s="17"/>
       <c r="D688" s="17"/>
@@ -14500,7 +14513,7 @@
       <c r="R688" s="17"/>
       <c r="S688" s="17"/>
     </row>
-    <row r="689" ht="14.25">
+    <row r="689" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B689" s="17"/>
       <c r="C689" s="17"/>
       <c r="D689" s="17"/>
@@ -14520,7 +14533,7 @@
       <c r="R689" s="17"/>
       <c r="S689" s="17"/>
     </row>
-    <row r="690" ht="14.25">
+    <row r="690" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B690" s="17"/>
       <c r="C690" s="17"/>
       <c r="D690" s="17"/>
@@ -14540,7 +14553,7 @@
       <c r="R690" s="17"/>
       <c r="S690" s="17"/>
     </row>
-    <row r="691" ht="14.25">
+    <row r="691" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B691" s="17"/>
       <c r="C691" s="17"/>
       <c r="D691" s="17"/>
@@ -14560,7 +14573,7 @@
       <c r="R691" s="17"/>
       <c r="S691" s="17"/>
     </row>
-    <row r="692" ht="14.25">
+    <row r="692" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B692" s="17"/>
       <c r="C692" s="17"/>
       <c r="D692" s="17"/>
@@ -14580,7 +14593,7 @@
       <c r="R692" s="17"/>
       <c r="S692" s="17"/>
     </row>
-    <row r="693" ht="14.25">
+    <row r="693" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B693" s="17"/>
       <c r="C693" s="17"/>
       <c r="D693" s="17"/>
@@ -14600,7 +14613,7 @@
       <c r="R693" s="17"/>
       <c r="S693" s="17"/>
     </row>
-    <row r="694" ht="14.25">
+    <row r="694" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B694" s="17"/>
       <c r="C694" s="17"/>
       <c r="D694" s="17"/>
@@ -14620,7 +14633,7 @@
       <c r="R694" s="17"/>
       <c r="S694" s="17"/>
     </row>
-    <row r="695" ht="14.25">
+    <row r="695" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B695" s="17"/>
       <c r="C695" s="17"/>
       <c r="D695" s="17"/>
@@ -14640,7 +14653,7 @@
       <c r="R695" s="17"/>
       <c r="S695" s="17"/>
     </row>
-    <row r="696" ht="14.25">
+    <row r="696" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B696" s="17"/>
       <c r="C696" s="17"/>
       <c r="D696" s="17"/>
@@ -14660,7 +14673,7 @@
       <c r="R696" s="17"/>
       <c r="S696" s="17"/>
     </row>
-    <row r="697" ht="14.25">
+    <row r="697" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B697" s="17"/>
       <c r="C697" s="17"/>
       <c r="D697" s="17"/>
@@ -14680,7 +14693,7 @@
       <c r="R697" s="17"/>
       <c r="S697" s="17"/>
     </row>
-    <row r="698" ht="14.25">
+    <row r="698" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B698" s="17"/>
       <c r="C698" s="17"/>
       <c r="D698" s="17"/>
@@ -14700,7 +14713,7 @@
       <c r="R698" s="17"/>
       <c r="S698" s="17"/>
     </row>
-    <row r="699" ht="14.25">
+    <row r="699" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B699" s="17"/>
       <c r="C699" s="17"/>
       <c r="D699" s="17"/>
@@ -14720,7 +14733,7 @@
       <c r="R699" s="17"/>
       <c r="S699" s="17"/>
     </row>
-    <row r="700" ht="14.25">
+    <row r="700" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B700" s="17"/>
       <c r="C700" s="17"/>
       <c r="D700" s="17"/>
@@ -14740,7 +14753,7 @@
       <c r="R700" s="17"/>
       <c r="S700" s="17"/>
     </row>
-    <row r="701" ht="14.25">
+    <row r="701" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B701" s="17"/>
       <c r="C701" s="17"/>
       <c r="D701" s="17"/>
@@ -14760,7 +14773,7 @@
       <c r="R701" s="17"/>
       <c r="S701" s="17"/>
     </row>
-    <row r="702" ht="14.25">
+    <row r="702" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B702" s="17"/>
       <c r="C702" s="17"/>
       <c r="D702" s="17"/>
@@ -14780,7 +14793,7 @@
       <c r="R702" s="17"/>
       <c r="S702" s="17"/>
     </row>
-    <row r="703" ht="14.25">
+    <row r="703" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B703" s="17"/>
       <c r="C703" s="17"/>
       <c r="D703" s="17"/>
@@ -14800,7 +14813,7 @@
       <c r="R703" s="17"/>
       <c r="S703" s="17"/>
     </row>
-    <row r="704" ht="14.25">
+    <row r="704" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B704" s="17"/>
       <c r="C704" s="17"/>
       <c r="D704" s="17"/>
@@ -14820,7 +14833,7 @@
       <c r="R704" s="17"/>
       <c r="S704" s="17"/>
     </row>
-    <row r="705" ht="14.25">
+    <row r="705" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B705" s="17"/>
       <c r="C705" s="17"/>
       <c r="D705" s="17"/>
@@ -14840,7 +14853,7 @@
       <c r="R705" s="17"/>
       <c r="S705" s="17"/>
     </row>
-    <row r="706" ht="14.25">
+    <row r="706" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B706" s="17"/>
       <c r="C706" s="17"/>
       <c r="D706" s="17"/>
@@ -14860,7 +14873,7 @@
       <c r="R706" s="17"/>
       <c r="S706" s="17"/>
     </row>
-    <row r="707" ht="14.25">
+    <row r="707" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B707" s="17"/>
       <c r="C707" s="17"/>
       <c r="D707" s="17"/>
@@ -14880,7 +14893,7 @@
       <c r="R707" s="17"/>
       <c r="S707" s="17"/>
     </row>
-    <row r="708" ht="14.25">
+    <row r="708" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B708" s="17"/>
       <c r="C708" s="17"/>
       <c r="D708" s="17"/>
@@ -14900,7 +14913,7 @@
       <c r="R708" s="17"/>
       <c r="S708" s="17"/>
     </row>
-    <row r="709" ht="14.25">
+    <row r="709" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B709" s="17"/>
       <c r="C709" s="17"/>
       <c r="D709" s="17"/>
@@ -14920,7 +14933,7 @@
       <c r="R709" s="17"/>
       <c r="S709" s="17"/>
     </row>
-    <row r="710" ht="14.25">
+    <row r="710" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B710" s="17"/>
       <c r="C710" s="17"/>
       <c r="D710" s="17"/>
@@ -14940,7 +14953,7 @@
       <c r="R710" s="17"/>
       <c r="S710" s="17"/>
     </row>
-    <row r="711" ht="14.25">
+    <row r="711" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B711" s="17"/>
       <c r="C711" s="17"/>
       <c r="D711" s="17"/>
@@ -14960,7 +14973,7 @@
       <c r="R711" s="17"/>
       <c r="S711" s="17"/>
     </row>
-    <row r="712" ht="14.25">
+    <row r="712" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B712" s="17"/>
       <c r="C712" s="17"/>
       <c r="D712" s="17"/>
@@ -14980,7 +14993,7 @@
       <c r="R712" s="17"/>
       <c r="S712" s="17"/>
     </row>
-    <row r="713" ht="14.25">
+    <row r="713" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B713" s="17"/>
       <c r="C713" s="17"/>
       <c r="D713" s="17"/>
@@ -15000,7 +15013,7 @@
       <c r="R713" s="17"/>
       <c r="S713" s="17"/>
     </row>
-    <row r="714" ht="14.25">
+    <row r="714" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B714" s="17"/>
       <c r="C714" s="17"/>
       <c r="D714" s="17"/>
@@ -15020,7 +15033,7 @@
       <c r="R714" s="17"/>
       <c r="S714" s="17"/>
     </row>
-    <row r="715" ht="14.25">
+    <row r="715" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B715" s="17"/>
       <c r="C715" s="17"/>
       <c r="D715" s="17"/>
@@ -15040,7 +15053,7 @@
       <c r="R715" s="17"/>
       <c r="S715" s="17"/>
     </row>
-    <row r="716" ht="14.25">
+    <row r="716" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B716" s="17"/>
       <c r="C716" s="17"/>
       <c r="D716" s="17"/>
@@ -15060,7 +15073,7 @@
       <c r="R716" s="17"/>
       <c r="S716" s="17"/>
     </row>
-    <row r="717" ht="14.25">
+    <row r="717" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B717" s="17"/>
       <c r="C717" s="17"/>
       <c r="D717" s="17"/>
@@ -15080,7 +15093,7 @@
       <c r="R717" s="17"/>
       <c r="S717" s="17"/>
     </row>
-    <row r="718" ht="14.25">
+    <row r="718" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B718" s="17"/>
       <c r="C718" s="17"/>
       <c r="D718" s="17"/>
@@ -15100,7 +15113,7 @@
       <c r="R718" s="17"/>
       <c r="S718" s="17"/>
     </row>
-    <row r="719" ht="14.25">
+    <row r="719" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B719" s="17"/>
       <c r="C719" s="17"/>
       <c r="D719" s="17"/>
@@ -15120,7 +15133,7 @@
       <c r="R719" s="17"/>
       <c r="S719" s="17"/>
     </row>
-    <row r="720" ht="14.25">
+    <row r="720" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B720" s="17"/>
       <c r="C720" s="17"/>
       <c r="D720" s="17"/>
@@ -15140,7 +15153,7 @@
       <c r="R720" s="17"/>
       <c r="S720" s="17"/>
     </row>
-    <row r="721" ht="14.25">
+    <row r="721" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B721" s="17"/>
       <c r="C721" s="17"/>
       <c r="D721" s="17"/>
@@ -15160,7 +15173,7 @@
       <c r="R721" s="17"/>
       <c r="S721" s="17"/>
     </row>
-    <row r="722" ht="14.25">
+    <row r="722" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B722" s="17"/>
       <c r="C722" s="17"/>
       <c r="D722" s="17"/>
@@ -15180,7 +15193,7 @@
       <c r="R722" s="17"/>
       <c r="S722" s="17"/>
     </row>
-    <row r="723" ht="14.25">
+    <row r="723" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B723" s="17"/>
       <c r="C723" s="17"/>
       <c r="D723" s="17"/>
@@ -15200,7 +15213,7 @@
       <c r="R723" s="17"/>
       <c r="S723" s="17"/>
     </row>
-    <row r="724" ht="14.25">
+    <row r="724" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B724" s="17"/>
       <c r="C724" s="17"/>
       <c r="D724" s="17"/>
@@ -15220,7 +15233,7 @@
       <c r="R724" s="17"/>
       <c r="S724" s="17"/>
     </row>
-    <row r="725" ht="14.25">
+    <row r="725" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B725" s="17"/>
       <c r="C725" s="17"/>
       <c r="D725" s="17"/>
@@ -15240,7 +15253,7 @@
       <c r="R725" s="17"/>
       <c r="S725" s="17"/>
     </row>
-    <row r="726" ht="14.25">
+    <row r="726" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B726" s="17"/>
       <c r="C726" s="17"/>
       <c r="D726" s="17"/>
@@ -15260,7 +15273,7 @@
       <c r="R726" s="17"/>
       <c r="S726" s="17"/>
     </row>
-    <row r="727" ht="14.25">
+    <row r="727" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B727" s="17"/>
       <c r="C727" s="17"/>
       <c r="D727" s="17"/>
@@ -15280,7 +15293,7 @@
       <c r="R727" s="17"/>
       <c r="S727" s="17"/>
     </row>
-    <row r="728" ht="14.25">
+    <row r="728" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B728" s="17"/>
       <c r="C728" s="17"/>
       <c r="D728" s="17"/>
@@ -15300,7 +15313,7 @@
       <c r="R728" s="17"/>
       <c r="S728" s="17"/>
     </row>
-    <row r="729" ht="14.25">
+    <row r="729" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B729" s="17"/>
       <c r="C729" s="17"/>
       <c r="D729" s="17"/>
@@ -15320,7 +15333,7 @@
       <c r="R729" s="17"/>
       <c r="S729" s="17"/>
     </row>
-    <row r="730" ht="14.25">
+    <row r="730" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B730" s="17"/>
       <c r="C730" s="17"/>
       <c r="D730" s="17"/>
@@ -15340,7 +15353,7 @@
       <c r="R730" s="17"/>
       <c r="S730" s="17"/>
     </row>
-    <row r="731" ht="14.25">
+    <row r="731" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B731" s="17"/>
       <c r="C731" s="17"/>
       <c r="D731" s="17"/>
@@ -15360,7 +15373,7 @@
       <c r="R731" s="17"/>
       <c r="S731" s="17"/>
     </row>
-    <row r="732" ht="14.25">
+    <row r="732" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B732" s="17"/>
       <c r="C732" s="17"/>
       <c r="D732" s="17"/>
@@ -15380,7 +15393,7 @@
       <c r="R732" s="17"/>
       <c r="S732" s="17"/>
     </row>
-    <row r="733" ht="14.25">
+    <row r="733" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B733" s="17"/>
       <c r="C733" s="17"/>
       <c r="D733" s="17"/>
@@ -15400,7 +15413,7 @@
       <c r="R733" s="17"/>
       <c r="S733" s="17"/>
     </row>
-    <row r="734" ht="14.25">
+    <row r="734" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B734" s="17"/>
       <c r="C734" s="17"/>
       <c r="D734" s="17"/>
@@ -15420,7 +15433,7 @@
       <c r="R734" s="17"/>
       <c r="S734" s="17"/>
     </row>
-    <row r="735" ht="14.25">
+    <row r="735" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B735" s="17"/>
       <c r="C735" s="17"/>
       <c r="D735" s="17"/>
@@ -15440,7 +15453,7 @@
       <c r="R735" s="17"/>
       <c r="S735" s="17"/>
     </row>
-    <row r="736" ht="14.25">
+    <row r="736" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B736" s="17"/>
       <c r="C736" s="17"/>
       <c r="D736" s="17"/>
@@ -15460,7 +15473,7 @@
       <c r="R736" s="17"/>
       <c r="S736" s="17"/>
     </row>
-    <row r="737" ht="14.25">
+    <row r="737" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B737" s="17"/>
       <c r="C737" s="17"/>
       <c r="D737" s="17"/>
@@ -15480,7 +15493,7 @@
       <c r="R737" s="17"/>
       <c r="S737" s="17"/>
     </row>
-    <row r="738" ht="14.25">
+    <row r="738" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B738" s="17"/>
       <c r="C738" s="17"/>
       <c r="D738" s="17"/>
@@ -15500,7 +15513,7 @@
       <c r="R738" s="17"/>
       <c r="S738" s="17"/>
     </row>
-    <row r="739" ht="14.25">
+    <row r="739" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B739" s="17"/>
       <c r="C739" s="17"/>
       <c r="D739" s="17"/>
@@ -15520,7 +15533,7 @@
       <c r="R739" s="17"/>
       <c r="S739" s="17"/>
     </row>
-    <row r="740" ht="14.25">
+    <row r="740" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B740" s="17"/>
       <c r="C740" s="17"/>
       <c r="D740" s="17"/>
@@ -15540,7 +15553,7 @@
       <c r="R740" s="17"/>
       <c r="S740" s="17"/>
     </row>
-    <row r="741" ht="14.25">
+    <row r="741" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B741" s="17"/>
       <c r="C741" s="17"/>
       <c r="D741" s="17"/>
@@ -15560,7 +15573,7 @@
       <c r="R741" s="17"/>
       <c r="S741" s="17"/>
     </row>
-    <row r="742" ht="14.25">
+    <row r="742" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B742" s="17"/>
       <c r="C742" s="17"/>
       <c r="D742" s="17"/>
@@ -15580,7 +15593,7 @@
       <c r="R742" s="17"/>
       <c r="S742" s="17"/>
     </row>
-    <row r="743" ht="14.25">
+    <row r="743" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B743" s="17"/>
       <c r="C743" s="17"/>
       <c r="D743" s="17"/>
@@ -15600,7 +15613,7 @@
       <c r="R743" s="17"/>
       <c r="S743" s="17"/>
     </row>
-    <row r="744" ht="14.25">
+    <row r="744" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B744" s="17"/>
       <c r="C744" s="17"/>
       <c r="D744" s="17"/>
@@ -15620,7 +15633,7 @@
       <c r="R744" s="17"/>
       <c r="S744" s="17"/>
     </row>
-    <row r="745" ht="14.25">
+    <row r="745" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B745" s="17"/>
       <c r="C745" s="17"/>
       <c r="D745" s="17"/>
@@ -15640,7 +15653,7 @@
       <c r="R745" s="17"/>
       <c r="S745" s="17"/>
     </row>
-    <row r="746" ht="14.25">
+    <row r="746" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B746" s="17"/>
       <c r="C746" s="17"/>
       <c r="D746" s="17"/>
@@ -15660,7 +15673,7 @@
       <c r="R746" s="17"/>
       <c r="S746" s="17"/>
     </row>
-    <row r="747" ht="14.25">
+    <row r="747" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B747" s="17"/>
       <c r="C747" s="17"/>
       <c r="D747" s="17"/>
@@ -15680,7 +15693,7 @@
       <c r="R747" s="17"/>
       <c r="S747" s="17"/>
     </row>
-    <row r="748" ht="14.25">
+    <row r="748" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B748" s="17"/>
       <c r="C748" s="17"/>
       <c r="D748" s="17"/>
@@ -15700,7 +15713,7 @@
       <c r="R748" s="17"/>
       <c r="S748" s="17"/>
     </row>
-    <row r="749" ht="14.25">
+    <row r="749" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B749" s="17"/>
       <c r="C749" s="17"/>
       <c r="D749" s="17"/>
@@ -15720,7 +15733,7 @@
       <c r="R749" s="17"/>
       <c r="S749" s="17"/>
     </row>
-    <row r="750" ht="14.25">
+    <row r="750" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B750" s="17"/>
       <c r="C750" s="17"/>
       <c r="D750" s="17"/>
@@ -15740,7 +15753,7 @@
       <c r="R750" s="17"/>
       <c r="S750" s="17"/>
     </row>
-    <row r="751" ht="14.25">
+    <row r="751" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B751" s="17"/>
       <c r="C751" s="17"/>
       <c r="D751" s="17"/>
@@ -15760,7 +15773,7 @@
       <c r="R751" s="17"/>
       <c r="S751" s="17"/>
     </row>
-    <row r="752" ht="14.25">
+    <row r="752" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B752" s="17"/>
       <c r="C752" s="17"/>
       <c r="D752" s="17"/>
@@ -15780,7 +15793,7 @@
       <c r="R752" s="17"/>
       <c r="S752" s="17"/>
     </row>
-    <row r="753" ht="14.25">
+    <row r="753" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B753" s="17"/>
       <c r="C753" s="17"/>
       <c r="D753" s="17"/>
@@ -15800,7 +15813,7 @@
       <c r="R753" s="17"/>
       <c r="S753" s="17"/>
     </row>
-    <row r="754" ht="14.25">
+    <row r="754" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B754" s="17"/>
       <c r="C754" s="17"/>
       <c r="D754" s="17"/>
@@ -15820,7 +15833,7 @@
       <c r="R754" s="17"/>
       <c r="S754" s="17"/>
     </row>
-    <row r="755" ht="14.25">
+    <row r="755" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B755" s="17"/>
       <c r="C755" s="17"/>
       <c r="D755" s="17"/>
@@ -15840,7 +15853,7 @@
       <c r="R755" s="17"/>
       <c r="S755" s="17"/>
     </row>
-    <row r="756" ht="14.25">
+    <row r="756" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B756" s="17"/>
       <c r="C756" s="17"/>
       <c r="D756" s="17"/>
@@ -15860,7 +15873,7 @@
       <c r="R756" s="17"/>
       <c r="S756" s="17"/>
     </row>
-    <row r="757" ht="14.25">
+    <row r="757" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B757" s="17"/>
       <c r="C757" s="17"/>
       <c r="D757" s="17"/>
@@ -15880,7 +15893,7 @@
       <c r="R757" s="17"/>
       <c r="S757" s="17"/>
     </row>
-    <row r="758" ht="14.25">
+    <row r="758" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B758" s="17"/>
       <c r="C758" s="17"/>
       <c r="D758" s="17"/>
@@ -15900,7 +15913,7 @@
       <c r="R758" s="17"/>
       <c r="S758" s="17"/>
     </row>
-    <row r="759" ht="14.25">
+    <row r="759" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B759" s="17"/>
       <c r="C759" s="17"/>
       <c r="D759" s="17"/>
@@ -15920,7 +15933,7 @@
       <c r="R759" s="17"/>
       <c r="S759" s="17"/>
     </row>
-    <row r="760" ht="14.25">
+    <row r="760" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B760" s="17"/>
       <c r="C760" s="17"/>
       <c r="D760" s="17"/>
@@ -15940,7 +15953,7 @@
       <c r="R760" s="17"/>
       <c r="S760" s="17"/>
     </row>
-    <row r="761" ht="14.25">
+    <row r="761" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B761" s="17"/>
       <c r="C761" s="17"/>
       <c r="D761" s="17"/>
@@ -15960,7 +15973,7 @@
       <c r="R761" s="17"/>
       <c r="S761" s="17"/>
     </row>
-    <row r="762" ht="14.25">
+    <row r="762" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B762" s="17"/>
       <c r="C762" s="17"/>
       <c r="D762" s="17"/>
@@ -15980,7 +15993,7 @@
       <c r="R762" s="17"/>
       <c r="S762" s="17"/>
     </row>
-    <row r="763" ht="14.25">
+    <row r="763" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B763" s="17"/>
       <c r="C763" s="17"/>
       <c r="D763" s="17"/>
@@ -16000,7 +16013,7 @@
       <c r="R763" s="17"/>
       <c r="S763" s="17"/>
     </row>
-    <row r="764" ht="14.25">
+    <row r="764" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B764" s="17"/>
       <c r="C764" s="17"/>
       <c r="D764" s="17"/>
@@ -16020,7 +16033,7 @@
       <c r="R764" s="17"/>
       <c r="S764" s="17"/>
     </row>
-    <row r="765" ht="14.25">
+    <row r="765" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B765" s="17"/>
       <c r="C765" s="17"/>
       <c r="D765" s="17"/>
@@ -16040,7 +16053,7 @@
       <c r="R765" s="17"/>
       <c r="S765" s="17"/>
     </row>
-    <row r="766" ht="14.25">
+    <row r="766" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B766" s="17"/>
       <c r="C766" s="17"/>
       <c r="D766" s="17"/>
@@ -16060,7 +16073,7 @@
       <c r="R766" s="17"/>
       <c r="S766" s="17"/>
     </row>
-    <row r="767" ht="14.25">
+    <row r="767" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B767" s="17"/>
       <c r="C767" s="17"/>
       <c r="D767" s="17"/>
@@ -16080,7 +16093,7 @@
       <c r="R767" s="17"/>
       <c r="S767" s="17"/>
     </row>
-    <row r="768" ht="14.25">
+    <row r="768" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B768" s="17"/>
       <c r="C768" s="17"/>
       <c r="D768" s="17"/>
@@ -16100,7 +16113,7 @@
       <c r="R768" s="17"/>
       <c r="S768" s="17"/>
     </row>
-    <row r="769" ht="14.25">
+    <row r="769" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B769" s="17"/>
       <c r="C769" s="17"/>
       <c r="D769" s="17"/>
@@ -16120,7 +16133,7 @@
       <c r="R769" s="17"/>
       <c r="S769" s="17"/>
     </row>
-    <row r="770" ht="14.25">
+    <row r="770" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B770" s="17"/>
       <c r="C770" s="17"/>
       <c r="D770" s="17"/>
@@ -16140,7 +16153,7 @@
       <c r="R770" s="17"/>
       <c r="S770" s="17"/>
     </row>
-    <row r="771" ht="14.25">
+    <row r="771" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B771" s="17"/>
       <c r="C771" s="17"/>
       <c r="D771" s="17"/>
@@ -16160,7 +16173,7 @@
       <c r="R771" s="17"/>
       <c r="S771" s="17"/>
     </row>
-    <row r="772" ht="14.25">
+    <row r="772" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B772" s="17"/>
       <c r="C772" s="17"/>
       <c r="D772" s="17"/>
@@ -16180,7 +16193,7 @@
       <c r="R772" s="17"/>
       <c r="S772" s="17"/>
     </row>
-    <row r="773" ht="14.25">
+    <row r="773" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B773" s="17"/>
       <c r="C773" s="17"/>
       <c r="D773" s="17"/>
@@ -16200,7 +16213,7 @@
       <c r="R773" s="17"/>
       <c r="S773" s="17"/>
     </row>
-    <row r="774" ht="14.25">
+    <row r="774" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B774" s="17"/>
       <c r="C774" s="17"/>
       <c r="D774" s="17"/>
@@ -16220,7 +16233,7 @@
       <c r="R774" s="17"/>
       <c r="S774" s="17"/>
     </row>
-    <row r="775" ht="14.25">
+    <row r="775" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B775" s="17"/>
       <c r="C775" s="17"/>
       <c r="D775" s="17"/>
@@ -16240,7 +16253,7 @@
       <c r="R775" s="17"/>
       <c r="S775" s="17"/>
     </row>
-    <row r="776" ht="14.25">
+    <row r="776" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B776" s="17"/>
       <c r="C776" s="17"/>
       <c r="D776" s="17"/>
@@ -16260,7 +16273,7 @@
       <c r="R776" s="17"/>
       <c r="S776" s="17"/>
     </row>
-    <row r="777" ht="14.25">
+    <row r="777" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B777" s="17"/>
       <c r="C777" s="17"/>
       <c r="D777" s="17"/>
@@ -16280,7 +16293,7 @@
       <c r="R777" s="17"/>
       <c r="S777" s="17"/>
     </row>
-    <row r="778" ht="14.25">
+    <row r="778" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B778" s="17"/>
       <c r="C778" s="17"/>
       <c r="D778" s="17"/>
@@ -16300,7 +16313,7 @@
       <c r="R778" s="17"/>
       <c r="S778" s="17"/>
     </row>
-    <row r="779" ht="14.25">
+    <row r="779" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B779" s="17"/>
       <c r="C779" s="17"/>
       <c r="D779" s="17"/>
@@ -16320,7 +16333,7 @@
       <c r="R779" s="17"/>
       <c r="S779" s="17"/>
     </row>
-    <row r="780" ht="14.25">
+    <row r="780" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B780" s="17"/>
       <c r="C780" s="17"/>
       <c r="D780" s="17"/>
@@ -16340,7 +16353,7 @@
       <c r="R780" s="17"/>
       <c r="S780" s="17"/>
     </row>
-    <row r="781" ht="14.25">
+    <row r="781" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B781" s="17"/>
       <c r="C781" s="17"/>
       <c r="D781" s="17"/>
@@ -16360,7 +16373,7 @@
       <c r="R781" s="17"/>
       <c r="S781" s="17"/>
     </row>
-    <row r="782" ht="14.25">
+    <row r="782" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B782" s="17"/>
       <c r="C782" s="17"/>
       <c r="D782" s="17"/>
@@ -16380,7 +16393,7 @@
       <c r="R782" s="17"/>
       <c r="S782" s="17"/>
     </row>
-    <row r="783" ht="14.25">
+    <row r="783" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B783" s="17"/>
       <c r="C783" s="17"/>
       <c r="D783" s="17"/>
@@ -16400,7 +16413,7 @@
       <c r="R783" s="17"/>
       <c r="S783" s="17"/>
     </row>
-    <row r="784" ht="14.25">
+    <row r="784" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B784" s="17"/>
       <c r="C784" s="17"/>
       <c r="D784" s="17"/>
@@ -16420,7 +16433,7 @@
       <c r="R784" s="17"/>
       <c r="S784" s="17"/>
     </row>
-    <row r="785" ht="14.25">
+    <row r="785" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B785" s="17"/>
       <c r="C785" s="17"/>
       <c r="D785" s="17"/>
@@ -16440,7 +16453,7 @@
       <c r="R785" s="17"/>
       <c r="S785" s="17"/>
     </row>
-    <row r="786" ht="14.25">
+    <row r="786" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B786" s="17"/>
       <c r="C786" s="17"/>
       <c r="D786" s="17"/>
@@ -16460,7 +16473,7 @@
       <c r="R786" s="17"/>
       <c r="S786" s="17"/>
     </row>
-    <row r="787" ht="14.25">
+    <row r="787" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B787" s="17"/>
       <c r="C787" s="17"/>
       <c r="D787" s="17"/>
@@ -16480,7 +16493,7 @@
       <c r="R787" s="17"/>
       <c r="S787" s="17"/>
     </row>
-    <row r="788" ht="14.25">
+    <row r="788" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B788" s="17"/>
       <c r="C788" s="17"/>
       <c r="D788" s="17"/>
@@ -16500,7 +16513,7 @@
       <c r="R788" s="17"/>
       <c r="S788" s="17"/>
     </row>
-    <row r="789" ht="14.25">
+    <row r="789" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B789" s="17"/>
       <c r="C789" s="17"/>
       <c r="D789" s="17"/>
@@ -16520,7 +16533,7 @@
       <c r="R789" s="17"/>
       <c r="S789" s="17"/>
     </row>
-    <row r="790" ht="14.25">
+    <row r="790" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B790" s="17"/>
       <c r="C790" s="17"/>
       <c r="D790" s="17"/>
@@ -16540,7 +16553,7 @@
       <c r="R790" s="17"/>
       <c r="S790" s="17"/>
     </row>
-    <row r="791" ht="14.25">
+    <row r="791" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B791" s="17"/>
       <c r="C791" s="17"/>
       <c r="D791" s="17"/>
@@ -16560,7 +16573,7 @@
       <c r="R791" s="17"/>
       <c r="S791" s="17"/>
     </row>
-    <row r="792" ht="14.25">
+    <row r="792" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B792" s="17"/>
       <c r="C792" s="17"/>
       <c r="D792" s="17"/>
@@ -16580,7 +16593,7 @@
       <c r="R792" s="17"/>
       <c r="S792" s="17"/>
     </row>
-    <row r="793" ht="14.25">
+    <row r="793" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B793" s="17"/>
       <c r="C793" s="17"/>
       <c r="D793" s="17"/>
@@ -16600,7 +16613,7 @@
       <c r="R793" s="17"/>
       <c r="S793" s="17"/>
     </row>
-    <row r="794" ht="14.25">
+    <row r="794" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B794" s="17"/>
       <c r="C794" s="17"/>
       <c r="D794" s="17"/>
@@ -16620,7 +16633,7 @@
       <c r="R794" s="17"/>
       <c r="S794" s="17"/>
     </row>
-    <row r="795" ht="14.25">
+    <row r="795" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B795" s="17"/>
       <c r="C795" s="17"/>
       <c r="D795" s="17"/>
@@ -16640,7 +16653,7 @@
       <c r="R795" s="17"/>
       <c r="S795" s="17"/>
     </row>
-    <row r="796" ht="14.25">
+    <row r="796" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B796" s="17"/>
       <c r="C796" s="17"/>
       <c r="D796" s="17"/>
@@ -16660,7 +16673,7 @@
       <c r="R796" s="17"/>
       <c r="S796" s="17"/>
     </row>
-    <row r="797" ht="14.25">
+    <row r="797" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B797" s="17"/>
       <c r="C797" s="17"/>
       <c r="D797" s="17"/>
@@ -16680,7 +16693,7 @@
       <c r="R797" s="17"/>
       <c r="S797" s="17"/>
     </row>
-    <row r="798" ht="14.25">
+    <row r="798" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B798" s="17"/>
       <c r="C798" s="17"/>
       <c r="D798" s="17"/>
@@ -16700,7 +16713,7 @@
       <c r="R798" s="17"/>
       <c r="S798" s="17"/>
     </row>
-    <row r="799" ht="14.25">
+    <row r="799" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B799" s="17"/>
       <c r="C799" s="17"/>
       <c r="D799" s="17"/>
@@ -16720,7 +16733,7 @@
       <c r="R799" s="17"/>
       <c r="S799" s="17"/>
     </row>
-    <row r="800" ht="14.25">
+    <row r="800" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B800" s="17"/>
       <c r="C800" s="17"/>
       <c r="D800" s="17"/>
@@ -16740,7 +16753,7 @@
       <c r="R800" s="17"/>
       <c r="S800" s="17"/>
     </row>
-    <row r="801" ht="14.25">
+    <row r="801" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B801" s="17"/>
       <c r="C801" s="17"/>
       <c r="D801" s="17"/>
@@ -16760,7 +16773,7 @@
       <c r="R801" s="17"/>
       <c r="S801" s="17"/>
     </row>
-    <row r="802" ht="14.25">
+    <row r="802" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B802" s="17"/>
       <c r="C802" s="17"/>
       <c r="D802" s="17"/>
@@ -16780,7 +16793,7 @@
       <c r="R802" s="17"/>
       <c r="S802" s="17"/>
     </row>
-    <row r="803" ht="14.25">
+    <row r="803" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B803" s="17"/>
       <c r="C803" s="17"/>
       <c r="D803" s="17"/>
@@ -16800,7 +16813,7 @@
       <c r="R803" s="17"/>
       <c r="S803" s="17"/>
     </row>
-    <row r="804" ht="14.25">
+    <row r="804" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B804" s="17"/>
       <c r="C804" s="17"/>
       <c r="D804" s="17"/>
@@ -16820,7 +16833,7 @@
       <c r="R804" s="17"/>
       <c r="S804" s="17"/>
     </row>
-    <row r="805" ht="14.25">
+    <row r="805" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B805" s="17"/>
       <c r="C805" s="17"/>
       <c r="D805" s="17"/>
@@ -16840,7 +16853,7 @@
       <c r="R805" s="17"/>
       <c r="S805" s="17"/>
     </row>
-    <row r="806" ht="14.25">
+    <row r="806" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B806" s="17"/>
       <c r="C806" s="17"/>
       <c r="D806" s="17"/>
@@ -16860,7 +16873,7 @@
       <c r="R806" s="17"/>
       <c r="S806" s="17"/>
     </row>
-    <row r="807" ht="14.25">
+    <row r="807" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B807" s="17"/>
       <c r="C807" s="17"/>
       <c r="D807" s="17"/>
@@ -16880,7 +16893,7 @@
       <c r="R807" s="17"/>
       <c r="S807" s="17"/>
     </row>
-    <row r="808" ht="14.25">
+    <row r="808" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B808" s="17"/>
       <c r="C808" s="17"/>
       <c r="D808" s="17"/>
@@ -16900,7 +16913,7 @@
       <c r="R808" s="17"/>
       <c r="S808" s="17"/>
     </row>
-    <row r="809" ht="14.25">
+    <row r="809" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B809" s="17"/>
       <c r="C809" s="17"/>
       <c r="D809" s="17"/>
@@ -16920,7 +16933,7 @@
       <c r="R809" s="17"/>
       <c r="S809" s="17"/>
     </row>
-    <row r="810" ht="14.25">
+    <row r="810" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B810" s="17"/>
       <c r="C810" s="17"/>
       <c r="D810" s="17"/>
@@ -16940,7 +16953,7 @@
       <c r="R810" s="17"/>
       <c r="S810" s="17"/>
     </row>
-    <row r="811" ht="14.25">
+    <row r="811" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B811" s="17"/>
       <c r="C811" s="17"/>
       <c r="D811" s="17"/>
@@ -16960,7 +16973,7 @@
       <c r="R811" s="17"/>
       <c r="S811" s="17"/>
     </row>
-    <row r="812" ht="14.25">
+    <row r="812" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B812" s="17"/>
       <c r="C812" s="17"/>
       <c r="D812" s="17"/>
@@ -16980,7 +16993,7 @@
       <c r="R812" s="17"/>
       <c r="S812" s="17"/>
     </row>
-    <row r="813" ht="14.25">
+    <row r="813" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B813" s="17"/>
       <c r="C813" s="17"/>
       <c r="D813" s="17"/>
@@ -17000,7 +17013,7 @@
       <c r="R813" s="17"/>
       <c r="S813" s="17"/>
     </row>
-    <row r="814" ht="14.25">
+    <row r="814" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B814" s="17"/>
       <c r="C814" s="17"/>
       <c r="D814" s="17"/>
@@ -17020,7 +17033,7 @@
       <c r="R814" s="17"/>
       <c r="S814" s="17"/>
     </row>
-    <row r="815" ht="14.25">
+    <row r="815" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B815" s="17"/>
       <c r="C815" s="17"/>
       <c r="D815" s="17"/>
@@ -17040,7 +17053,7 @@
       <c r="R815" s="17"/>
       <c r="S815" s="17"/>
     </row>
-    <row r="816" ht="14.25">
+    <row r="816" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B816" s="17"/>
       <c r="C816" s="17"/>
       <c r="D816" s="17"/>
@@ -17060,7 +17073,7 @@
       <c r="R816" s="17"/>
       <c r="S816" s="17"/>
     </row>
-    <row r="817" ht="14.25">
+    <row r="817" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B817" s="17"/>
       <c r="C817" s="17"/>
       <c r="D817" s="17"/>
@@ -17080,7 +17093,7 @@
       <c r="R817" s="17"/>
       <c r="S817" s="17"/>
     </row>
-    <row r="818" ht="14.25">
+    <row r="818" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B818" s="17"/>
       <c r="C818" s="17"/>
       <c r="D818" s="17"/>
@@ -17100,7 +17113,7 @@
       <c r="R818" s="17"/>
       <c r="S818" s="17"/>
     </row>
-    <row r="819" ht="14.25">
+    <row r="819" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B819" s="17"/>
       <c r="C819" s="17"/>
       <c r="D819" s="17"/>
@@ -17120,7 +17133,7 @@
       <c r="R819" s="17"/>
       <c r="S819" s="17"/>
     </row>
-    <row r="820" ht="14.25">
+    <row r="820" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B820" s="17"/>
       <c r="C820" s="17"/>
       <c r="D820" s="17"/>
@@ -17140,7 +17153,7 @@
       <c r="R820" s="17"/>
       <c r="S820" s="17"/>
     </row>
-    <row r="821" ht="14.25">
+    <row r="821" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B821" s="17"/>
       <c r="C821" s="17"/>
       <c r="D821" s="17"/>
@@ -17160,7 +17173,7 @@
       <c r="R821" s="17"/>
       <c r="S821" s="17"/>
     </row>
-    <row r="822" ht="14.25">
+    <row r="822" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B822" s="17"/>
       <c r="C822" s="17"/>
       <c r="D822" s="17"/>
@@ -17180,7 +17193,7 @@
       <c r="R822" s="17"/>
       <c r="S822" s="17"/>
     </row>
-    <row r="823" ht="14.25">
+    <row r="823" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B823" s="17"/>
       <c r="C823" s="17"/>
       <c r="D823" s="17"/>
@@ -17200,7 +17213,7 @@
       <c r="R823" s="17"/>
       <c r="S823" s="17"/>
     </row>
-    <row r="824" ht="14.25">
+    <row r="824" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B824" s="17"/>
       <c r="C824" s="17"/>
       <c r="D824" s="17"/>
@@ -17220,7 +17233,7 @@
       <c r="R824" s="17"/>
       <c r="S824" s="17"/>
     </row>
-    <row r="825" ht="14.25">
+    <row r="825" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B825" s="17"/>
       <c r="C825" s="17"/>
       <c r="D825" s="17"/>
@@ -17240,7 +17253,7 @@
       <c r="R825" s="17"/>
       <c r="S825" s="17"/>
     </row>
-    <row r="826" ht="14.25">
+    <row r="826" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B826" s="17"/>
       <c r="C826" s="17"/>
       <c r="D826" s="17"/>
@@ -17260,7 +17273,7 @@
       <c r="R826" s="17"/>
       <c r="S826" s="17"/>
     </row>
-    <row r="827" ht="14.25">
+    <row r="827" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B827" s="17"/>
       <c r="C827" s="17"/>
       <c r="D827" s="17"/>
@@ -17280,7 +17293,7 @@
       <c r="R827" s="17"/>
       <c r="S827" s="17"/>
     </row>
-    <row r="828" ht="14.25">
+    <row r="828" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B828" s="17"/>
       <c r="C828" s="17"/>
       <c r="D828" s="17"/>
@@ -17300,7 +17313,7 @@
       <c r="R828" s="17"/>
       <c r="S828" s="17"/>
     </row>
-    <row r="829" ht="14.25">
+    <row r="829" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B829" s="17"/>
       <c r="C829" s="17"/>
       <c r="D829" s="17"/>
@@ -17320,7 +17333,7 @@
       <c r="R829" s="17"/>
       <c r="S829" s="17"/>
     </row>
-    <row r="830" ht="14.25">
+    <row r="830" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B830" s="17"/>
       <c r="C830" s="17"/>
       <c r="D830" s="17"/>
@@ -17340,7 +17353,7 @@
       <c r="R830" s="17"/>
       <c r="S830" s="17"/>
     </row>
-    <row r="831" ht="14.25">
+    <row r="831" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B831" s="17"/>
       <c r="C831" s="17"/>
       <c r="D831" s="17"/>
@@ -17360,7 +17373,7 @@
       <c r="R831" s="17"/>
       <c r="S831" s="17"/>
     </row>
-    <row r="832" ht="14.25">
+    <row r="832" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B832" s="17"/>
       <c r="C832" s="17"/>
       <c r="D832" s="17"/>
@@ -17380,7 +17393,7 @@
       <c r="R832" s="17"/>
       <c r="S832" s="17"/>
     </row>
-    <row r="833" ht="14.25">
+    <row r="833" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B833" s="17"/>
       <c r="C833" s="17"/>
       <c r="D833" s="17"/>
@@ -17400,7 +17413,7 @@
       <c r="R833" s="17"/>
       <c r="S833" s="17"/>
     </row>
-    <row r="834" ht="14.25">
+    <row r="834" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B834" s="17"/>
       <c r="C834" s="17"/>
       <c r="D834" s="17"/>
@@ -17420,7 +17433,7 @@
       <c r="R834" s="17"/>
       <c r="S834" s="17"/>
     </row>
-    <row r="835" ht="14.25">
+    <row r="835" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B835" s="17"/>
       <c r="C835" s="17"/>
       <c r="D835" s="17"/>
@@ -17440,7 +17453,7 @@
       <c r="R835" s="17"/>
       <c r="S835" s="17"/>
     </row>
-    <row r="836" ht="14.25">
+    <row r="836" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B836" s="17"/>
       <c r="C836" s="17"/>
       <c r="D836" s="17"/>
@@ -17460,7 +17473,7 @@
       <c r="R836" s="17"/>
       <c r="S836" s="17"/>
     </row>
-    <row r="837" ht="14.25">
+    <row r="837" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B837" s="17"/>
       <c r="C837" s="17"/>
       <c r="D837" s="17"/>
@@ -17480,7 +17493,7 @@
       <c r="R837" s="17"/>
       <c r="S837" s="17"/>
     </row>
-    <row r="838" ht="14.25">
+    <row r="838" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B838" s="17"/>
       <c r="C838" s="17"/>
       <c r="D838" s="17"/>
@@ -17500,7 +17513,7 @@
       <c r="R838" s="17"/>
       <c r="S838" s="17"/>
     </row>
-    <row r="839" ht="14.25">
+    <row r="839" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B839" s="17"/>
       <c r="C839" s="17"/>
       <c r="D839" s="17"/>
@@ -17520,7 +17533,7 @@
       <c r="R839" s="17"/>
       <c r="S839" s="17"/>
     </row>
-    <row r="840" ht="14.25">
+    <row r="840" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B840" s="17"/>
       <c r="C840" s="17"/>
       <c r="D840" s="17"/>
@@ -17540,7 +17553,7 @@
       <c r="R840" s="17"/>
       <c r="S840" s="17"/>
     </row>
-    <row r="841" ht="14.25">
+    <row r="841" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B841" s="17"/>
       <c r="C841" s="17"/>
       <c r="D841" s="17"/>
@@ -17560,7 +17573,7 @@
       <c r="R841" s="17"/>
       <c r="S841" s="17"/>
     </row>
-    <row r="842" ht="14.25">
+    <row r="842" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B842" s="17"/>
       <c r="C842" s="17"/>
       <c r="D842" s="17"/>
@@ -17580,7 +17593,7 @@
       <c r="R842" s="17"/>
       <c r="S842" s="17"/>
     </row>
-    <row r="843" ht="14.25">
+    <row r="843" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B843" s="17"/>
       <c r="C843" s="17"/>
       <c r="D843" s="17"/>
@@ -17600,7 +17613,7 @@
       <c r="R843" s="17"/>
       <c r="S843" s="17"/>
     </row>
-    <row r="844" ht="14.25">
+    <row r="844" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B844" s="17"/>
       <c r="C844" s="17"/>
       <c r="D844" s="17"/>
@@ -17620,7 +17633,7 @@
       <c r="R844" s="17"/>
       <c r="S844" s="17"/>
     </row>
-    <row r="845" ht="14.25">
+    <row r="845" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B845" s="17"/>
       <c r="C845" s="17"/>
       <c r="D845" s="17"/>
@@ -17640,7 +17653,7 @@
       <c r="R845" s="17"/>
       <c r="S845" s="17"/>
     </row>
-    <row r="846" ht="14.25">
+    <row r="846" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B846" s="17"/>
       <c r="C846" s="17"/>
       <c r="D846" s="17"/>
@@ -17660,7 +17673,7 @@
       <c r="R846" s="17"/>
       <c r="S846" s="17"/>
     </row>
-    <row r="847" ht="14.25">
+    <row r="847" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B847" s="17"/>
       <c r="C847" s="17"/>
       <c r="D847" s="17"/>
@@ -17680,7 +17693,7 @@
       <c r="R847" s="17"/>
       <c r="S847" s="17"/>
     </row>
-    <row r="848" ht="14.25">
+    <row r="848" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B848" s="17"/>
       <c r="C848" s="17"/>
       <c r="D848" s="17"/>
@@ -17700,7 +17713,7 @@
       <c r="R848" s="17"/>
       <c r="S848" s="17"/>
     </row>
-    <row r="849" ht="14.25">
+    <row r="849" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B849" s="17"/>
       <c r="C849" s="17"/>
       <c r="D849" s="17"/>
@@ -17720,7 +17733,7 @@
       <c r="R849" s="17"/>
       <c r="S849" s="17"/>
     </row>
-    <row r="850" ht="14.25">
+    <row r="850" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B850" s="17"/>
       <c r="C850" s="17"/>
       <c r="D850" s="17"/>
@@ -17740,7 +17753,7 @@
       <c r="R850" s="17"/>
       <c r="S850" s="17"/>
     </row>
-    <row r="851" ht="14.25">
+    <row r="851" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B851" s="17"/>
       <c r="C851" s="17"/>
       <c r="D851" s="17"/>
@@ -17760,7 +17773,7 @@
       <c r="R851" s="17"/>
       <c r="S851" s="17"/>
     </row>
-    <row r="852" ht="14.25">
+    <row r="852" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B852" s="17"/>
       <c r="C852" s="17"/>
       <c r="D852" s="17"/>
@@ -17780,7 +17793,7 @@
       <c r="R852" s="17"/>
       <c r="S852" s="17"/>
     </row>
-    <row r="853" ht="14.25">
+    <row r="853" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B853" s="17"/>
       <c r="C853" s="17"/>
       <c r="D853" s="17"/>
@@ -17800,7 +17813,7 @@
       <c r="R853" s="17"/>
       <c r="S853" s="17"/>
     </row>
-    <row r="854" ht="14.25">
+    <row r="854" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B854" s="17"/>
       <c r="C854" s="17"/>
       <c r="D854" s="17"/>
@@ -17820,7 +17833,7 @@
       <c r="R854" s="17"/>
       <c r="S854" s="17"/>
     </row>
-    <row r="855" ht="14.25">
+    <row r="855" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B855" s="17"/>
       <c r="C855" s="17"/>
       <c r="D855" s="17"/>
@@ -17840,7 +17853,7 @@
       <c r="R855" s="17"/>
       <c r="S855" s="17"/>
     </row>
-    <row r="856" ht="14.25">
+    <row r="856" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B856" s="17"/>
       <c r="C856" s="17"/>
       <c r="D856" s="17"/>
@@ -17860,7 +17873,7 @@
       <c r="R856" s="17"/>
       <c r="S856" s="17"/>
     </row>
-    <row r="857" ht="14.25">
+    <row r="857" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B857" s="17"/>
       <c r="C857" s="17"/>
       <c r="D857" s="17"/>
@@ -17880,7 +17893,7 @@
       <c r="R857" s="17"/>
       <c r="S857" s="17"/>
     </row>
-    <row r="858" ht="14.25">
+    <row r="858" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B858" s="17"/>
       <c r="C858" s="17"/>
       <c r="D858" s="17"/>
@@ -17900,7 +17913,7 @@
       <c r="R858" s="17"/>
       <c r="S858" s="17"/>
     </row>
-    <row r="859" ht="14.25">
+    <row r="859" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B859" s="17"/>
       <c r="C859" s="17"/>
       <c r="D859" s="17"/>
@@ -17920,7 +17933,7 @@
       <c r="R859" s="17"/>
       <c r="S859" s="17"/>
     </row>
-    <row r="860" ht="14.25">
+    <row r="860" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B860" s="17"/>
       <c r="C860" s="17"/>
       <c r="D860" s="17"/>
@@ -17940,7 +17953,7 @@
       <c r="R860" s="17"/>
       <c r="S860" s="17"/>
     </row>
-    <row r="861" ht="14.25">
+    <row r="861" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B861" s="17"/>
       <c r="C861" s="17"/>
       <c r="D861" s="17"/>
@@ -17960,7 +17973,7 @@
       <c r="R861" s="17"/>
       <c r="S861" s="17"/>
     </row>
-    <row r="862" ht="14.25">
+    <row r="862" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B862" s="17"/>
       <c r="C862" s="17"/>
       <c r="D862" s="17"/>
@@ -17980,7 +17993,7 @@
       <c r="R862" s="17"/>
       <c r="S862" s="17"/>
     </row>
-    <row r="863" ht="14.25">
+    <row r="863" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B863" s="17"/>
       <c r="C863" s="17"/>
       <c r="D863" s="17"/>
@@ -18000,7 +18013,7 @@
       <c r="R863" s="17"/>
       <c r="S863" s="17"/>
     </row>
-    <row r="864" ht="14.25">
+    <row r="864" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B864" s="17"/>
       <c r="C864" s="17"/>
       <c r="D864" s="17"/>
@@ -18020,7 +18033,7 @@
       <c r="R864" s="17"/>
       <c r="S864" s="17"/>
     </row>
-    <row r="865" ht="14.25">
+    <row r="865" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B865" s="17"/>
       <c r="C865" s="17"/>
       <c r="D865" s="17"/>
@@ -18040,7 +18053,7 @@
       <c r="R865" s="17"/>
       <c r="S865" s="17"/>
     </row>
-    <row r="866" ht="14.25">
+    <row r="866" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B866" s="17"/>
       <c r="C866" s="17"/>
       <c r="D866" s="17"/>
@@ -18060,7 +18073,7 @@
       <c r="R866" s="17"/>
       <c r="S866" s="17"/>
     </row>
-    <row r="867" ht="14.25">
+    <row r="867" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B867" s="17"/>
       <c r="C867" s="17"/>
       <c r="D867" s="17"/>
@@ -18080,7 +18093,7 @@
       <c r="R867" s="17"/>
       <c r="S867" s="17"/>
     </row>
-    <row r="868" ht="14.25">
+    <row r="868" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B868" s="17"/>
       <c r="C868" s="17"/>
       <c r="D868" s="17"/>
@@ -18100,7 +18113,7 @@
       <c r="R868" s="17"/>
       <c r="S868" s="17"/>
     </row>
-    <row r="869" ht="14.25">
+    <row r="869" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B869" s="17"/>
       <c r="C869" s="17"/>
       <c r="D869" s="17"/>
@@ -18120,7 +18133,7 @@
       <c r="R869" s="17"/>
       <c r="S869" s="17"/>
     </row>
-    <row r="870" ht="14.25">
+    <row r="870" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B870" s="17"/>
       <c r="C870" s="17"/>
       <c r="D870" s="17"/>
@@ -18140,7 +18153,7 @@
       <c r="R870" s="17"/>
       <c r="S870" s="17"/>
     </row>
-    <row r="871" ht="14.25">
+    <row r="871" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B871" s="17"/>
       <c r="C871" s="17"/>
       <c r="D871" s="17"/>
@@ -18160,7 +18173,7 @@
       <c r="R871" s="17"/>
       <c r="S871" s="17"/>
     </row>
-    <row r="872" ht="14.25">
+    <row r="872" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B872" s="17"/>
       <c r="C872" s="17"/>
       <c r="D872" s="17"/>
@@ -18180,7 +18193,7 @@
       <c r="R872" s="17"/>
       <c r="S872" s="17"/>
     </row>
-    <row r="873" ht="14.25">
+    <row r="873" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B873" s="17"/>
       <c r="C873" s="17"/>
       <c r="D873" s="17"/>
@@ -18200,7 +18213,7 @@
       <c r="R873" s="17"/>
       <c r="S873" s="17"/>
     </row>
-    <row r="874" ht="14.25">
+    <row r="874" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B874" s="17"/>
       <c r="C874" s="17"/>
       <c r="D874" s="17"/>
@@ -18220,7 +18233,7 @@
       <c r="R874" s="17"/>
       <c r="S874" s="17"/>
     </row>
-    <row r="875" ht="14.25">
+    <row r="875" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B875" s="17"/>
       <c r="C875" s="17"/>
       <c r="D875" s="17"/>
@@ -18240,7 +18253,7 @@
       <c r="R875" s="17"/>
       <c r="S875" s="17"/>
     </row>
-    <row r="876" ht="14.25">
+    <row r="876" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B876" s="17"/>
       <c r="C876" s="17"/>
       <c r="D876" s="17"/>
@@ -18260,7 +18273,7 @@
       <c r="R876" s="17"/>
       <c r="S876" s="17"/>
     </row>
-    <row r="877" ht="14.25">
+    <row r="877" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B877" s="17"/>
       <c r="C877" s="17"/>
       <c r="D877" s="17"/>
@@ -18280,7 +18293,7 @@
       <c r="R877" s="17"/>
       <c r="S877" s="17"/>
     </row>
-    <row r="878" ht="14.25">
+    <row r="878" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B878" s="17"/>
       <c r="C878" s="17"/>
       <c r="D878" s="17"/>
@@ -18300,7 +18313,7 @@
       <c r="R878" s="17"/>
       <c r="S878" s="17"/>
     </row>
-    <row r="879" ht="14.25">
+    <row r="879" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B879" s="17"/>
       <c r="C879" s="17"/>
       <c r="D879" s="17"/>
@@ -18320,7 +18333,7 @@
       <c r="R879" s="17"/>
       <c r="S879" s="17"/>
     </row>
-    <row r="880" ht="14.25">
+    <row r="880" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B880" s="17"/>
       <c r="C880" s="17"/>
       <c r="D880" s="17"/>
@@ -18340,7 +18353,7 @@
       <c r="R880" s="17"/>
       <c r="S880" s="17"/>
     </row>
-    <row r="881" ht="14.25">
+    <row r="881" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B881" s="17"/>
       <c r="C881" s="17"/>
       <c r="D881" s="17"/>
@@ -18360,7 +18373,7 @@
       <c r="R881" s="17"/>
       <c r="S881" s="17"/>
     </row>
-    <row r="882" ht="14.25">
+    <row r="882" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B882" s="17"/>
       <c r="C882" s="17"/>
       <c r="D882" s="17"/>
@@ -18380,7 +18393,7 @@
       <c r="R882" s="17"/>
       <c r="S882" s="17"/>
     </row>
-    <row r="883" ht="14.25">
+    <row r="883" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B883" s="17"/>
       <c r="C883" s="17"/>
       <c r="D883" s="17"/>
@@ -18400,7 +18413,7 @@
       <c r="R883" s="17"/>
       <c r="S883" s="17"/>
     </row>
-    <row r="884" ht="14.25">
+    <row r="884" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B884" s="17"/>
       <c r="C884" s="17"/>
       <c r="D884" s="17"/>
@@ -18420,7 +18433,7 @@
       <c r="R884" s="17"/>
       <c r="S884" s="17"/>
     </row>
-    <row r="885" ht="14.25">
+    <row r="885" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B885" s="17"/>
       <c r="C885" s="17"/>
       <c r="D885" s="17"/>
@@ -18440,7 +18453,7 @@
       <c r="R885" s="17"/>
       <c r="S885" s="17"/>
     </row>
-    <row r="886" ht="14.25">
+    <row r="886" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B886" s="17"/>
       <c r="C886" s="17"/>
       <c r="D886" s="17"/>
@@ -18460,7 +18473,7 @@
       <c r="R886" s="17"/>
       <c r="S886" s="17"/>
     </row>
-    <row r="887" ht="14.25">
+    <row r="887" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B887" s="17"/>
       <c r="C887" s="17"/>
       <c r="D887" s="17"/>
@@ -18480,7 +18493,7 @@
       <c r="R887" s="17"/>
       <c r="S887" s="17"/>
     </row>
-    <row r="888" ht="14.25">
+    <row r="888" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B888" s="17"/>
       <c r="C888" s="17"/>
       <c r="D888" s="17"/>
@@ -18500,7 +18513,7 @@
       <c r="R888" s="17"/>
       <c r="S888" s="17"/>
     </row>
-    <row r="889" ht="14.25">
+    <row r="889" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B889" s="17"/>
       <c r="C889" s="17"/>
       <c r="D889" s="17"/>
@@ -18520,7 +18533,7 @@
       <c r="R889" s="17"/>
       <c r="S889" s="17"/>
     </row>
-    <row r="890" ht="14.25">
+    <row r="890" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B890" s="17"/>
       <c r="C890" s="17"/>
       <c r="D890" s="17"/>
@@ -18540,7 +18553,7 @@
       <c r="R890" s="17"/>
       <c r="S890" s="17"/>
     </row>
-    <row r="891" ht="14.25">
+    <row r="891" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B891" s="17"/>
       <c r="C891" s="17"/>
       <c r="D891" s="17"/>
@@ -18560,7 +18573,7 @@
       <c r="R891" s="17"/>
       <c r="S891" s="17"/>
     </row>
-    <row r="892" ht="14.25">
+    <row r="892" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B892" s="17"/>
       <c r="C892" s="17"/>
       <c r="D892" s="17"/>
@@ -18580,7 +18593,7 @@
       <c r="R892" s="17"/>
       <c r="S892" s="17"/>
     </row>
-    <row r="893" ht="14.25">
+    <row r="893" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B893" s="17"/>
       <c r="C893" s="17"/>
       <c r="D893" s="17"/>
@@ -18600,7 +18613,7 @@
       <c r="R893" s="17"/>
       <c r="S893" s="17"/>
     </row>
-    <row r="894" ht="14.25">
+    <row r="894" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B894" s="17"/>
       <c r="C894" s="17"/>
       <c r="D894" s="17"/>
@@ -18620,7 +18633,7 @@
       <c r="R894" s="17"/>
       <c r="S894" s="17"/>
     </row>
-    <row r="895" ht="14.25">
+    <row r="895" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B895" s="17"/>
       <c r="C895" s="17"/>
       <c r="D895" s="17"/>
@@ -18640,7 +18653,7 @@
       <c r="R895" s="17"/>
       <c r="S895" s="17"/>
     </row>
-    <row r="896" ht="14.25">
+    <row r="896" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B896" s="17"/>
       <c r="C896" s="17"/>
       <c r="D896" s="17"/>
@@ -18660,7 +18673,7 @@
       <c r="R896" s="17"/>
       <c r="S896" s="17"/>
     </row>
-    <row r="897" ht="14.25">
+    <row r="897" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B897" s="17"/>
       <c r="C897" s="17"/>
       <c r="D897" s="17"/>
@@ -18680,7 +18693,7 @@
       <c r="R897" s="17"/>
       <c r="S897" s="17"/>
     </row>
-    <row r="898" ht="14.25">
+    <row r="898" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B898" s="17"/>
       <c r="C898" s="17"/>
       <c r="D898" s="17"/>
@@ -18700,7 +18713,7 @@
       <c r="R898" s="17"/>
       <c r="S898" s="17"/>
     </row>
-    <row r="899" ht="14.25">
+    <row r="899" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B899" s="17"/>
       <c r="C899" s="17"/>
       <c r="D899" s="17"/>
@@ -18720,7 +18733,7 @@
       <c r="R899" s="17"/>
       <c r="S899" s="17"/>
     </row>
-    <row r="900" ht="14.25">
+    <row r="900" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B900" s="17"/>
       <c r="C900" s="17"/>
       <c r="D900" s="17"/>
@@ -18740,7 +18753,7 @@
       <c r="R900" s="17"/>
       <c r="S900" s="17"/>
     </row>
-    <row r="901" ht="14.25">
+    <row r="901" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B901" s="17"/>
       <c r="C901" s="17"/>
       <c r="D901" s="17"/>
@@ -18760,7 +18773,7 @@
       <c r="R901" s="17"/>
       <c r="S901" s="17"/>
     </row>
-    <row r="902" ht="14.25">
+    <row r="902" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B902" s="17"/>
       <c r="C902" s="17"/>
       <c r="D902" s="17"/>
@@ -18780,7 +18793,7 @@
       <c r="R902" s="17"/>
       <c r="S902" s="17"/>
     </row>
-    <row r="903" ht="14.25">
+    <row r="903" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B903" s="17"/>
       <c r="C903" s="17"/>
       <c r="D903" s="17"/>
@@ -18800,7 +18813,7 @@
       <c r="R903" s="17"/>
       <c r="S903" s="17"/>
     </row>
-    <row r="904" ht="14.25">
+    <row r="904" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B904" s="17"/>
       <c r="C904" s="17"/>
       <c r="D904" s="17"/>
@@ -18820,7 +18833,7 @@
       <c r="R904" s="17"/>
       <c r="S904" s="17"/>
     </row>
-    <row r="905" ht="14.25">
+    <row r="905" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B905" s="17"/>
       <c r="C905" s="17"/>
       <c r="D905" s="17"/>
@@ -18840,7 +18853,7 @@
       <c r="R905" s="17"/>
       <c r="S905" s="17"/>
     </row>
-    <row r="906" ht="14.25">
+    <row r="906" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B906" s="17"/>
       <c r="C906" s="17"/>
       <c r="D906" s="17"/>
@@ -18860,7 +18873,7 @@
       <c r="R906" s="17"/>
       <c r="S906" s="17"/>
     </row>
-    <row r="907" ht="14.25">
+    <row r="907" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B907" s="17"/>
       <c r="C907" s="17"/>
       <c r="D907" s="17"/>
@@ -18880,7 +18893,7 @@
       <c r="R907" s="17"/>
       <c r="S907" s="17"/>
     </row>
-    <row r="908" ht="14.25">
+    <row r="908" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B908" s="17"/>
       <c r="C908" s="17"/>
       <c r="D908" s="17"/>
@@ -18900,7 +18913,7 @@
       <c r="R908" s="17"/>
       <c r="S908" s="17"/>
     </row>
-    <row r="909" ht="14.25">
+    <row r="909" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B909" s="17"/>
       <c r="C909" s="17"/>
       <c r="D909" s="17"/>
@@ -18920,7 +18933,7 @@
       <c r="R909" s="17"/>
       <c r="S909" s="17"/>
     </row>
-    <row r="910" ht="14.25">
+    <row r="910" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B910" s="17"/>
       <c r="C910" s="17"/>
       <c r="D910" s="17"/>
@@ -18940,7 +18953,7 @@
       <c r="R910" s="17"/>
       <c r="S910" s="17"/>
     </row>
-    <row r="911" ht="14.25">
+    <row r="911" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B911" s="17"/>
       <c r="C911" s="17"/>
       <c r="D911" s="17"/>
@@ -18960,7 +18973,7 @@
       <c r="R911" s="17"/>
       <c r="S911" s="17"/>
     </row>
-    <row r="912" ht="14.25">
+    <row r="912" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B912" s="17"/>
       <c r="C912" s="17"/>
       <c r="D912" s="17"/>
@@ -18980,7 +18993,7 @@
       <c r="R912" s="17"/>
       <c r="S912" s="17"/>
     </row>
-    <row r="913" ht="14.25">
+    <row r="913" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B913" s="17"/>
       <c r="C913" s="17"/>
       <c r="D913" s="17"/>
@@ -19000,7 +19013,7 @@
       <c r="R913" s="17"/>
       <c r="S913" s="17"/>
     </row>
-    <row r="914" ht="14.25">
+    <row r="914" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B914" s="17"/>
       <c r="C914" s="17"/>
       <c r="D914" s="17"/>
@@ -19020,7 +19033,7 @@
       <c r="R914" s="17"/>
       <c r="S914" s="17"/>
     </row>
-    <row r="915" ht="14.25">
+    <row r="915" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B915" s="17"/>
       <c r="C915" s="17"/>
       <c r="D915" s="17"/>
@@ -19040,7 +19053,7 @@
       <c r="R915" s="17"/>
       <c r="S915" s="17"/>
     </row>
-    <row r="916" ht="14.25">
+    <row r="916" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B916" s="17"/>
       <c r="C916" s="17"/>
       <c r="D916" s="17"/>
@@ -19060,7 +19073,7 @@
       <c r="R916" s="17"/>
       <c r="S916" s="17"/>
     </row>
-    <row r="917" ht="14.25">
+    <row r="917" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B917" s="17"/>
       <c r="C917" s="17"/>
       <c r="D917" s="17"/>
@@ -19080,7 +19093,7 @@
       <c r="R917" s="17"/>
       <c r="S917" s="17"/>
     </row>
-    <row r="918" ht="14.25">
+    <row r="918" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B918" s="17"/>
       <c r="C918" s="17"/>
       <c r="D918" s="17"/>
@@ -19100,7 +19113,7 @@
       <c r="R918" s="17"/>
       <c r="S918" s="17"/>
     </row>
-    <row r="919" ht="14.25">
+    <row r="919" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B919" s="17"/>
       <c r="C919" s="17"/>
       <c r="D919" s="17"/>
@@ -19120,7 +19133,7 @@
       <c r="R919" s="17"/>
       <c r="S919" s="17"/>
     </row>
-    <row r="920" ht="14.25">
+    <row r="920" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B920" s="17"/>
       <c r="C920" s="17"/>
       <c r="D920" s="17"/>
@@ -19140,7 +19153,7 @@
       <c r="R920" s="17"/>
       <c r="S920" s="17"/>
     </row>
-    <row r="921" ht="14.25">
+    <row r="921" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B921" s="17"/>
       <c r="C921" s="17"/>
       <c r="D921" s="17"/>
@@ -19160,7 +19173,7 @@
       <c r="R921" s="17"/>
       <c r="S921" s="17"/>
     </row>
-    <row r="922" ht="14.25">
+    <row r="922" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B922" s="17"/>
       <c r="C922" s="17"/>
       <c r="D922" s="17"/>
@@ -19180,7 +19193,7 @@
       <c r="R922" s="17"/>
       <c r="S922" s="17"/>
     </row>
-    <row r="923" ht="14.25">
+    <row r="923" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B923" s="17"/>
       <c r="C923" s="17"/>
       <c r="D923" s="17"/>
@@ -19200,7 +19213,7 @@
       <c r="R923" s="17"/>
       <c r="S923" s="17"/>
     </row>
-    <row r="924" ht="14.25">
+    <row r="924" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B924" s="17"/>
       <c r="C924" s="17"/>
       <c r="D924" s="17"/>
@@ -19220,7 +19233,7 @@
       <c r="R924" s="17"/>
       <c r="S924" s="17"/>
     </row>
-    <row r="925" ht="14.25">
+    <row r="925" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B925" s="17"/>
       <c r="C925" s="17"/>
       <c r="D925" s="17"/>
@@ -19240,7 +19253,7 @@
       <c r="R925" s="17"/>
       <c r="S925" s="17"/>
     </row>
-    <row r="926" ht="14.25">
+    <row r="926" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B926" s="17"/>
       <c r="C926" s="17"/>
       <c r="D926" s="17"/>
@@ -19260,7 +19273,7 @@
       <c r="R926" s="17"/>
       <c r="S926" s="17"/>
     </row>
-    <row r="927" ht="14.25">
+    <row r="927" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B927" s="17"/>
       <c r="C927" s="17"/>
       <c r="D927" s="17"/>
@@ -19280,7 +19293,7 @@
       <c r="R927" s="17"/>
       <c r="S927" s="17"/>
     </row>
-    <row r="928" ht="14.25">
+    <row r="928" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B928" s="17"/>
       <c r="C928" s="17"/>
       <c r="D928" s="17"/>
@@ -19300,7 +19313,7 @@
       <c r="R928" s="17"/>
       <c r="S928" s="17"/>
     </row>
-    <row r="929" ht="14.25">
+    <row r="929" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B929" s="17"/>
       <c r="C929" s="17"/>
       <c r="D929" s="17"/>
@@ -19320,7 +19333,7 @@
       <c r="R929" s="17"/>
       <c r="S929" s="17"/>
     </row>
-    <row r="930" ht="14.25">
+    <row r="930" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B930" s="17"/>
       <c r="C930" s="17"/>
       <c r="D930" s="17"/>
@@ -19340,7 +19353,7 @@
       <c r="R930" s="17"/>
       <c r="S930" s="17"/>
     </row>
-    <row r="931" ht="14.25">
+    <row r="931" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B931" s="17"/>
       <c r="C931" s="17"/>
       <c r="D931" s="17"/>
@@ -19360,7 +19373,7 @@
       <c r="R931" s="17"/>
       <c r="S931" s="17"/>
     </row>
-    <row r="932" ht="14.25">
+    <row r="932" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B932" s="17"/>
       <c r="C932" s="17"/>
       <c r="D932" s="17"/>
@@ -19380,7 +19393,7 @@
       <c r="R932" s="17"/>
       <c r="S932" s="17"/>
     </row>
-    <row r="933" ht="14.25">
+    <row r="933" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B933" s="17"/>
       <c r="C933" s="17"/>
       <c r="D933" s="17"/>
@@ -19400,7 +19413,7 @@
       <c r="R933" s="17"/>
       <c r="S933" s="17"/>
     </row>
-    <row r="934" ht="14.25">
+    <row r="934" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B934" s="17"/>
       <c r="C934" s="17"/>
       <c r="D934" s="17"/>
@@ -19420,7 +19433,7 @@
       <c r="R934" s="17"/>
       <c r="S934" s="17"/>
     </row>
-    <row r="935" ht="14.25">
+    <row r="935" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B935" s="17"/>
       <c r="C935" s="17"/>
       <c r="D935" s="17"/>
@@ -19440,7 +19453,7 @@
       <c r="R935" s="17"/>
       <c r="S935" s="17"/>
     </row>
-    <row r="936" ht="14.25">
+    <row r="936" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B936" s="17"/>
       <c r="C936" s="17"/>
       <c r="D936" s="17"/>
@@ -19460,7 +19473,7 @@
       <c r="R936" s="17"/>
       <c r="S936" s="17"/>
     </row>
-    <row r="937" ht="14.25">
+    <row r="937" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B937" s="17"/>
       <c r="C937" s="17"/>
       <c r="D937" s="17"/>
@@ -19480,7 +19493,7 @@
       <c r="R937" s="17"/>
       <c r="S937" s="17"/>
     </row>
-    <row r="938" ht="14.25">
+    <row r="938" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B938" s="17"/>
       <c r="C938" s="17"/>
       <c r="D938" s="17"/>
@@ -19500,7 +19513,7 @@
       <c r="R938" s="17"/>
       <c r="S938" s="17"/>
     </row>
-    <row r="939" ht="14.25">
+    <row r="939" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B939" s="17"/>
       <c r="C939" s="17"/>
       <c r="D939" s="17"/>
@@ -19520,7 +19533,7 @@
       <c r="R939" s="17"/>
       <c r="S939" s="17"/>
     </row>
-    <row r="940" ht="14.25">
+    <row r="940" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B940" s="17"/>
       <c r="C940" s="17"/>
       <c r="D940" s="17"/>
@@ -19540,7 +19553,7 @@
       <c r="R940" s="17"/>
       <c r="S940" s="17"/>
     </row>
-    <row r="941" ht="14.25">
+    <row r="941" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B941" s="17"/>
       <c r="C941" s="17"/>
       <c r="D941" s="17"/>
@@ -19560,7 +19573,7 @@
       <c r="R941" s="17"/>
       <c r="S941" s="17"/>
     </row>
-    <row r="942" ht="14.25">
+    <row r="942" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B942" s="17"/>
       <c r="C942" s="17"/>
       <c r="D942" s="17"/>
@@ -19580,7 +19593,7 @@
       <c r="R942" s="17"/>
       <c r="S942" s="17"/>
     </row>
-    <row r="943" ht="14.25">
+    <row r="943" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B943" s="17"/>
       <c r="C943" s="17"/>
       <c r="D943" s="17"/>
@@ -19600,7 +19613,7 @@
       <c r="R943" s="17"/>
       <c r="S943" s="17"/>
     </row>
-    <row r="944" ht="14.25">
+    <row r="944" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B944" s="17"/>
       <c r="C944" s="17"/>
       <c r="D944" s="17"/>
@@ -19620,7 +19633,7 @@
       <c r="R944" s="17"/>
       <c r="S944" s="17"/>
     </row>
-    <row r="945" ht="14.25">
+    <row r="945" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B945" s="17"/>
       <c r="C945" s="17"/>
       <c r="D945" s="17"/>
@@ -19640,7 +19653,7 @@
       <c r="R945" s="17"/>
       <c r="S945" s="17"/>
     </row>
-    <row r="946" ht="14.25">
+    <row r="946" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B946" s="17"/>
       <c r="C946" s="17"/>
       <c r="D946" s="17"/>
@@ -19660,7 +19673,7 @@
       <c r="R946" s="17"/>
       <c r="S946" s="17"/>
     </row>
-    <row r="947" ht="14.25">
+    <row r="947" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B947" s="17"/>
       <c r="C947" s="17"/>
       <c r="D947" s="17"/>
@@ -19680,7 +19693,7 @@
       <c r="R947" s="17"/>
       <c r="S947" s="17"/>
     </row>
-    <row r="948" ht="14.25">
+    <row r="948" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B948" s="17"/>
       <c r="C948" s="17"/>
       <c r="D948" s="17"/>
@@ -19700,7 +19713,7 @@
       <c r="R948" s="17"/>
       <c r="S948" s="17"/>
     </row>
-    <row r="949" ht="14.25">
+    <row r="949" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B949" s="17"/>
       <c r="C949" s="17"/>
       <c r="D949" s="17"/>
@@ -19720,7 +19733,7 @@
       <c r="R949" s="17"/>
       <c r="S949" s="17"/>
     </row>
-    <row r="950" ht="14.25">
+    <row r="950" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B950" s="17"/>
       <c r="C950" s="17"/>
       <c r="D950" s="17"/>
@@ -19740,7 +19753,7 @@
       <c r="R950" s="17"/>
       <c r="S950" s="17"/>
     </row>
-    <row r="951" ht="14.25">
+    <row r="951" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B951" s="17"/>
       <c r="C951" s="17"/>
       <c r="D951" s="17"/>
@@ -19760,7 +19773,7 @@
       <c r="R951" s="17"/>
       <c r="S951" s="17"/>
     </row>
-    <row r="952" ht="14.25">
+    <row r="952" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B952" s="17"/>
       <c r="C952" s="17"/>
       <c r="D952" s="17"/>
@@ -19780,7 +19793,7 @@
       <c r="R952" s="17"/>
       <c r="S952" s="17"/>
     </row>
-    <row r="953" ht="14.25">
+    <row r="953" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B953" s="17"/>
       <c r="C953" s="17"/>
       <c r="D953" s="17"/>
@@ -19800,7 +19813,7 @@
       <c r="R953" s="17"/>
       <c r="S953" s="17"/>
     </row>
-    <row r="954" ht="14.25">
+    <row r="954" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B954" s="17"/>
       <c r="C954" s="17"/>
       <c r="D954" s="17"/>
@@ -19820,7 +19833,7 @@
       <c r="R954" s="17"/>
       <c r="S954" s="17"/>
     </row>
-    <row r="955" ht="14.25">
+    <row r="955" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B955" s="17"/>
       <c r="C955" s="17"/>
       <c r="D955" s="17"/>
@@ -19840,7 +19853,7 @@
       <c r="R955" s="17"/>
       <c r="S955" s="17"/>
     </row>
-    <row r="956" ht="14.25">
+    <row r="956" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B956" s="17"/>
       <c r="C956" s="17"/>
       <c r="D956" s="17"/>
@@ -19860,7 +19873,7 @@
       <c r="R956" s="17"/>
       <c r="S956" s="17"/>
     </row>
-    <row r="957" ht="14.25">
+    <row r="957" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B957" s="17"/>
       <c r="C957" s="17"/>
       <c r="D957" s="17"/>
@@ -19880,7 +19893,7 @@
       <c r="R957" s="17"/>
       <c r="S957" s="17"/>
     </row>
-    <row r="958" ht="14.25">
+    <row r="958" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B958" s="17"/>
       <c r="C958" s="17"/>
       <c r="D958" s="17"/>
@@ -19900,7 +19913,7 @@
       <c r="R958" s="17"/>
       <c r="S958" s="17"/>
     </row>
-    <row r="959" ht="14.25">
+    <row r="959" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B959" s="17"/>
       <c r="C959" s="17"/>
       <c r="D959" s="17"/>
@@ -19920,7 +19933,7 @@
       <c r="R959" s="17"/>
       <c r="S959" s="17"/>
     </row>
-    <row r="960" ht="14.25">
+    <row r="960" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B960" s="17"/>
       <c r="C960" s="17"/>
       <c r="D960" s="17"/>
@@ -19940,7 +19953,7 @@
       <c r="R960" s="17"/>
       <c r="S960" s="17"/>
     </row>
-    <row r="961" ht="14.25">
+    <row r="961" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B961" s="17"/>
       <c r="C961" s="17"/>
       <c r="D961" s="17"/>
@@ -19960,7 +19973,7 @@
       <c r="R961" s="17"/>
       <c r="S961" s="17"/>
     </row>
-    <row r="962" ht="14.25">
+    <row r="962" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B962" s="17"/>
       <c r="C962" s="17"/>
       <c r="D962" s="17"/>
@@ -19980,7 +19993,7 @@
       <c r="R962" s="17"/>
       <c r="S962" s="17"/>
     </row>
-    <row r="963" ht="14.25">
+    <row r="963" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B963" s="17"/>
       <c r="C963" s="17"/>
       <c r="D963" s="17"/>
@@ -20000,7 +20013,7 @@
       <c r="R963" s="17"/>
       <c r="S963" s="17"/>
     </row>
-    <row r="964" ht="14.25">
+    <row r="964" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B964" s="17"/>
       <c r="C964" s="17"/>
       <c r="D964" s="17"/>
@@ -20020,7 +20033,7 @@
       <c r="R964" s="17"/>
       <c r="S964" s="17"/>
     </row>
-    <row r="965" ht="14.25">
+    <row r="965" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B965" s="17"/>
       <c r="C965" s="17"/>
       <c r="D965" s="17"/>
@@ -20040,7 +20053,7 @@
       <c r="R965" s="17"/>
       <c r="S965" s="17"/>
     </row>
-    <row r="966" ht="14.25">
+    <row r="966" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B966" s="17"/>
       <c r="C966" s="17"/>
       <c r="D966" s="17"/>
@@ -20060,7 +20073,7 @@
       <c r="R966" s="17"/>
       <c r="S966" s="17"/>
     </row>
-    <row r="967" ht="14.25">
+    <row r="967" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B967" s="17"/>
       <c r="C967" s="17"/>
       <c r="D967" s="17"/>
@@ -20080,7 +20093,7 @@
       <c r="R967" s="17"/>
       <c r="S967" s="17"/>
     </row>
-    <row r="968" ht="14.25">
+    <row r="968" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B968" s="17"/>
       <c r="C968" s="17"/>
       <c r="D968" s="17"/>
@@ -20100,7 +20113,7 @@
       <c r="R968" s="17"/>
       <c r="S968" s="17"/>
     </row>
-    <row r="969" ht="14.25">
+    <row r="969" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B969" s="17"/>
       <c r="C969" s="17"/>
       <c r="D969" s="17"/>
@@ -20120,7 +20133,7 @@
       <c r="R969" s="17"/>
       <c r="S969" s="17"/>
     </row>
-    <row r="970" ht="14.25">
+    <row r="970" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B970" s="17"/>
       <c r="C970" s="17"/>
       <c r="D970" s="17"/>
@@ -20140,7 +20153,7 @@
       <c r="R970" s="17"/>
       <c r="S970" s="17"/>
     </row>
-    <row r="971" ht="14.25">
+    <row r="971" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B971" s="17"/>
       <c r="C971" s="17"/>
       <c r="D971" s="17"/>
@@ -20160,7 +20173,7 @@
       <c r="R971" s="17"/>
       <c r="S971" s="17"/>
     </row>
-    <row r="972" ht="14.25">
+    <row r="972" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B972" s="17"/>
       <c r="C972" s="17"/>
       <c r="D972" s="17"/>
@@ -20180,7 +20193,7 @@
       <c r="R972" s="17"/>
       <c r="S972" s="17"/>
     </row>
-    <row r="973" ht="14.25">
+    <row r="973" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B973" s="17"/>
       <c r="C973" s="17"/>
       <c r="D973" s="17"/>
@@ -20200,7 +20213,7 @@
       <c r="R973" s="17"/>
       <c r="S973" s="17"/>
     </row>
-    <row r="974" ht="14.25">
+    <row r="974" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B974" s="17"/>
       <c r="C974" s="17"/>
       <c r="D974" s="17"/>
@@ -20220,7 +20233,7 @@
       <c r="R974" s="17"/>
       <c r="S974" s="17"/>
     </row>
-    <row r="975" ht="14.25">
+    <row r="975" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B975" s="17"/>
       <c r="C975" s="17"/>
       <c r="D975" s="17"/>
@@ -20240,7 +20253,7 @@
       <c r="R975" s="17"/>
       <c r="S975" s="17"/>
     </row>
-    <row r="976" ht="14.25">
+    <row r="976" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B976" s="17"/>
       <c r="C976" s="17"/>
       <c r="D976" s="17"/>
@@ -20260,7 +20273,7 @@
       <c r="R976" s="17"/>
       <c r="S976" s="17"/>
     </row>
-    <row r="977" ht="14.25">
+    <row r="977" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B977" s="17"/>
       <c r="C977" s="17"/>
       <c r="D977" s="17"/>
@@ -20280,7 +20293,7 @@
       <c r="R977" s="17"/>
       <c r="S977" s="17"/>
     </row>
-    <row r="978" ht="14.25">
+    <row r="978" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B978" s="17"/>
       <c r="C978" s="17"/>
       <c r="D978" s="17"/>
@@ -20300,7 +20313,7 @@
       <c r="R978" s="17"/>
       <c r="S978" s="17"/>
     </row>
-    <row r="979" ht="14.25">
+    <row r="979" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B979" s="17"/>
       <c r="C979" s="17"/>
       <c r="D979" s="17"/>
@@ -20320,7 +20333,7 @@
       <c r="R979" s="17"/>
       <c r="S979" s="17"/>
     </row>
-    <row r="980" ht="14.25">
+    <row r="980" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B980" s="17"/>
       <c r="C980" s="17"/>
       <c r="D980" s="17"/>
@@ -20340,7 +20353,7 @@
       <c r="R980" s="17"/>
       <c r="S980" s="17"/>
     </row>
-    <row r="981" ht="14.25">
+    <row r="981" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B981" s="17"/>
       <c r="C981" s="17"/>
       <c r="D981" s="17"/>
@@ -20360,7 +20373,7 @@
       <c r="R981" s="17"/>
       <c r="S981" s="17"/>
     </row>
-    <row r="982" ht="14.25">
+    <row r="982" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B982" s="17"/>
       <c r="C982" s="17"/>
       <c r="D982" s="17"/>
@@ -20380,7 +20393,7 @@
       <c r="R982" s="17"/>
       <c r="S982" s="17"/>
     </row>
-    <row r="983" ht="14.25">
+    <row r="983" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B983" s="17"/>
       <c r="C983" s="17"/>
       <c r="D983" s="17"/>
@@ -20400,7 +20413,7 @@
       <c r="R983" s="17"/>
       <c r="S983" s="17"/>
     </row>
-    <row r="984" ht="14.25">
+    <row r="984" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B984" s="17"/>
       <c r="C984" s="17"/>
       <c r="D984" s="17"/>
@@ -20420,7 +20433,7 @@
       <c r="R984" s="17"/>
       <c r="S984" s="17"/>
     </row>
-    <row r="985" ht="14.25">
+    <row r="985" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B985" s="17"/>
       <c r="C985" s="17"/>
       <c r="D985" s="17"/>
@@ -20440,7 +20453,7 @@
       <c r="R985" s="17"/>
       <c r="S985" s="17"/>
     </row>
-    <row r="986" ht="14.25">
+    <row r="986" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B986" s="17"/>
       <c r="C986" s="17"/>
       <c r="D986" s="17"/>
@@ -20460,7 +20473,7 @@
       <c r="R986" s="17"/>
       <c r="S986" s="17"/>
     </row>
-    <row r="987" ht="14.25">
+    <row r="987" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B987" s="17"/>
       <c r="C987" s="17"/>
       <c r="D987" s="17"/>
@@ -20480,7 +20493,7 @@
       <c r="R987" s="17"/>
       <c r="S987" s="17"/>
     </row>
-    <row r="988" ht="14.25">
+    <row r="988" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B988" s="17"/>
       <c r="C988" s="17"/>
       <c r="D988" s="17"/>
@@ -20500,7 +20513,7 @@
       <c r="R988" s="17"/>
       <c r="S988" s="17"/>
     </row>
-    <row r="989" ht="14.25">
+    <row r="989" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B989" s="17"/>
       <c r="C989" s="17"/>
       <c r="D989" s="17"/>
@@ -20520,7 +20533,7 @@
       <c r="R989" s="17"/>
       <c r="S989" s="17"/>
     </row>
-    <row r="990" ht="14.25">
+    <row r="990" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B990" s="17"/>
       <c r="C990" s="17"/>
       <c r="D990" s="17"/>
@@ -20540,7 +20553,7 @@
       <c r="R990" s="17"/>
       <c r="S990" s="17"/>
     </row>
-    <row r="991" ht="14.25">
+    <row r="991" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B991" s="17"/>
       <c r="C991" s="17"/>
       <c r="D991" s="17"/>
@@ -20560,7 +20573,7 @@
       <c r="R991" s="17"/>
       <c r="S991" s="17"/>
     </row>
-    <row r="992" ht="14.25">
+    <row r="992" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B992" s="17"/>
       <c r="C992" s="17"/>
       <c r="D992" s="17"/>
@@ -20580,7 +20593,7 @@
       <c r="R992" s="17"/>
       <c r="S992" s="17"/>
     </row>
-    <row r="993" ht="14.25">
+    <row r="993" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B993" s="17"/>
       <c r="C993" s="17"/>
       <c r="D993" s="17"/>
@@ -20600,7 +20613,7 @@
       <c r="R993" s="17"/>
       <c r="S993" s="17"/>
     </row>
-    <row r="994" ht="14.25">
+    <row r="994" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B994" s="17"/>
       <c r="C994" s="17"/>
       <c r="D994" s="17"/>
@@ -20620,7 +20633,7 @@
       <c r="R994" s="17"/>
       <c r="S994" s="17"/>
     </row>
-    <row r="995" ht="14.25">
+    <row r="995" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B995" s="17"/>
       <c r="C995" s="17"/>
       <c r="D995" s="17"/>
@@ -20640,7 +20653,7 @@
       <c r="R995" s="17"/>
       <c r="S995" s="17"/>
     </row>
-    <row r="996" ht="14.25">
+    <row r="996" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B996" s="17"/>
       <c r="C996" s="17"/>
       <c r="D996" s="17"/>
@@ -20660,7 +20673,7 @@
       <c r="R996" s="17"/>
       <c r="S996" s="17"/>
     </row>
-    <row r="997" ht="14.25">
+    <row r="997" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B997" s="17"/>
       <c r="C997" s="17"/>
       <c r="D997" s="17"/>
@@ -20680,7 +20693,7 @@
       <c r="R997" s="17"/>
       <c r="S997" s="17"/>
     </row>
-    <row r="998" ht="14.25">
+    <row r="998" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B998" s="17"/>
       <c r="C998" s="17"/>
       <c r="D998" s="17"/>
@@ -20700,7 +20713,7 @@
       <c r="R998" s="17"/>
       <c r="S998" s="17"/>
     </row>
-    <row r="999" ht="14.25">
+    <row r="999" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B999" s="17"/>
       <c r="C999" s="17"/>
       <c r="D999" s="17"/>
@@ -20720,7 +20733,7 @@
       <c r="R999" s="17"/>
       <c r="S999" s="17"/>
     </row>
-    <row r="1000" ht="14.25">
+    <row r="1000" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1000" s="17"/>
       <c r="C1000" s="17"/>
       <c r="D1000" s="17"/>
@@ -20740,7 +20753,7 @@
       <c r="R1000" s="17"/>
       <c r="S1000" s="17"/>
     </row>
-    <row r="1001" ht="14.25">
+    <row r="1001" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1001" s="17"/>
       <c r="C1001" s="17"/>
       <c r="D1001" s="17"/>
@@ -20760,7 +20773,7 @@
       <c r="R1001" s="17"/>
       <c r="S1001" s="17"/>
     </row>
-    <row r="1002" ht="14.25">
+    <row r="1002" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1002" s="17"/>
       <c r="C1002" s="17"/>
       <c r="D1002" s="17"/>
@@ -20780,7 +20793,7 @@
       <c r="R1002" s="17"/>
       <c r="S1002" s="17"/>
     </row>
-    <row r="1003" ht="14.25">
+    <row r="1003" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1003" s="17"/>
       <c r="C1003" s="17"/>
       <c r="D1003" s="17"/>
@@ -20800,7 +20813,7 @@
       <c r="R1003" s="17"/>
       <c r="S1003" s="17"/>
     </row>
-    <row r="1004" ht="14.25">
+    <row r="1004" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1004" s="17"/>
       <c r="C1004" s="17"/>
       <c r="D1004" s="17"/>
@@ -20820,7 +20833,7 @@
       <c r="R1004" s="17"/>
       <c r="S1004" s="17"/>
     </row>
-    <row r="1005" ht="14.25">
+    <row r="1005" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1005" s="17"/>
       <c r="C1005" s="17"/>
       <c r="D1005" s="17"/>
@@ -20840,7 +20853,7 @@
       <c r="R1005" s="17"/>
       <c r="S1005" s="17"/>
     </row>
-    <row r="1006" ht="14.25">
+    <row r="1006" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1006" s="17"/>
       <c r="C1006" s="17"/>
       <c r="D1006" s="17"/>
@@ -20860,7 +20873,7 @@
       <c r="R1006" s="17"/>
       <c r="S1006" s="17"/>
     </row>
-    <row r="1007" ht="14.25">
+    <row r="1007" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1007" s="17"/>
       <c r="C1007" s="17"/>
       <c r="D1007" s="17"/>
@@ -20880,7 +20893,7 @@
       <c r="R1007" s="17"/>
       <c r="S1007" s="17"/>
     </row>
-    <row r="1008" ht="14.25">
+    <row r="1008" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1008" s="17"/>
       <c r="C1008" s="17"/>
       <c r="D1008" s="17"/>
@@ -20900,7 +20913,7 @@
       <c r="R1008" s="17"/>
       <c r="S1008" s="17"/>
     </row>
-    <row r="1009" ht="14.25">
+    <row r="1009" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1009" s="17"/>
       <c r="C1009" s="17"/>
       <c r="D1009" s="17"/>
@@ -20920,7 +20933,7 @@
       <c r="R1009" s="17"/>
       <c r="S1009" s="17"/>
     </row>
-    <row r="1010" ht="14.25">
+    <row r="1010" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1010" s="17"/>
       <c r="C1010" s="17"/>
       <c r="D1010" s="17"/>
@@ -20940,7 +20953,7 @@
       <c r="R1010" s="17"/>
       <c r="S1010" s="17"/>
     </row>
-    <row r="1011" ht="14.25">
+    <row r="1011" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1011" s="17"/>
       <c r="C1011" s="17"/>
       <c r="D1011" s="17"/>
@@ -20960,7 +20973,7 @@
       <c r="R1011" s="17"/>
       <c r="S1011" s="17"/>
     </row>
-    <row r="1012" ht="14.25">
+    <row r="1012" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1012" s="17"/>
       <c r="C1012" s="17"/>
       <c r="D1012" s="17"/>
@@ -20980,7 +20993,7 @@
       <c r="R1012" s="17"/>
       <c r="S1012" s="17"/>
     </row>
-    <row r="1013" ht="14.25">
+    <row r="1013" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1013" s="17"/>
       <c r="C1013" s="17"/>
       <c r="D1013" s="17"/>
@@ -21000,7 +21013,7 @@
       <c r="R1013" s="17"/>
       <c r="S1013" s="17"/>
     </row>
-    <row r="1014" ht="14.25">
+    <row r="1014" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1014" s="17"/>
       <c r="C1014" s="17"/>
       <c r="D1014" s="17"/>
@@ -21020,7 +21033,7 @@
       <c r="R1014" s="17"/>
       <c r="S1014" s="17"/>
     </row>
-    <row r="1015" ht="14.25">
+    <row r="1015" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1015" s="17"/>
       <c r="C1015" s="17"/>
       <c r="D1015" s="17"/>
@@ -21040,7 +21053,7 @@
       <c r="R1015" s="17"/>
       <c r="S1015" s="17"/>
     </row>
-    <row r="1016" ht="14.25">
+    <row r="1016" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1016" s="17"/>
       <c r="C1016" s="17"/>
       <c r="D1016" s="17"/>
@@ -21060,7 +21073,7 @@
       <c r="R1016" s="17"/>
       <c r="S1016" s="17"/>
     </row>
-    <row r="1017" ht="14.25">
+    <row r="1017" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1017" s="17"/>
       <c r="C1017" s="17"/>
       <c r="D1017" s="17"/>
@@ -21080,7 +21093,7 @@
       <c r="R1017" s="17"/>
       <c r="S1017" s="17"/>
     </row>
-    <row r="1018" ht="14.25">
+    <row r="1018" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1018" s="17"/>
       <c r="C1018" s="17"/>
       <c r="D1018" s="17"/>
@@ -21100,7 +21113,7 @@
       <c r="R1018" s="17"/>
       <c r="S1018" s="17"/>
     </row>
-    <row r="1019" ht="14.25">
+    <row r="1019" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1019" s="17"/>
       <c r="C1019" s="17"/>
       <c r="D1019" s="17"/>
@@ -21120,7 +21133,7 @@
       <c r="R1019" s="17"/>
       <c r="S1019" s="17"/>
     </row>
-    <row r="1020" ht="14.25">
+    <row r="1020" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1020" s="17"/>
       <c r="C1020" s="17"/>
       <c r="D1020" s="17"/>
@@ -21146,10 +21159,10 @@
     <mergeCell ref="B5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="I5:J6"/>
+    <mergeCell ref="L5:M6"/>
+    <mergeCell ref="O5:S6"/>
     <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:M6"/>
     <mergeCell ref="N5:N6"/>
-    <mergeCell ref="O5:S6"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="I7:J7"/>
@@ -26221,9 +26234,7 @@
     <mergeCell ref="L1020:M1020"/>
     <mergeCell ref="O1020:S1020"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600" verticalDpi="600" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
 </worksheet>
 </file>
--- a/database/datas.xlsx
+++ b/database/datas.xlsx
@@ -1,33 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="model" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet sheetId="1" name="model" state="visible" r:id="rId4"/>
   </sheets>
-  <calcPr/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
-  </extLst>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
   <si>
-    <t xml:space="preserve">LISTE D'ELEVES</t>
+    <t>LISTE D'ELEVES</t>
   </si>
   <si>
-    <t xml:space="preserve">NOM ET POSTNOM</t>
+    <t>NOM ET POSTNOM</t>
   </si>
   <si>
     <t>PRENOM</t>
   </si>
   <si>
-    <t xml:space="preserve">DATE DE NAISSANCE</t>
+    <t>DATE DE NAISSANCE</t>
   </si>
   <si>
     <t>GENRE</t>
@@ -42,7 +40,7 @@
     <t>OPTION</t>
   </si>
   <si>
-    <t xml:space="preserve">TSHIKAKU TSHITOMBENU</t>
+    <t>TSHIKAKU TSHITOMBENU</t>
   </si>
   <si>
     <t>JEAN</t>
@@ -51,28 +49,28 @@
     <t>M</t>
   </si>
   <si>
-    <t xml:space="preserve">16, Golf-Faustin/Lubumbashi/RDC</t>
+    <t>16, Golf-Faustin/Lubumbashi/RDC</t>
   </si>
   <si>
     <t>4ème</t>
   </si>
   <si>
-    <t xml:space="preserve">Comerciale et Gestion</t>
+    <t>Comerciale et Gestion</t>
   </si>
   <si>
-    <t xml:space="preserve">MUZALA MUKOSAYI</t>
+    <t>MUZALA MUKOSAYI</t>
   </si>
   <si>
     <t>JACQUES</t>
   </si>
   <si>
-    <t xml:space="preserve">30, Rwashi/Lubumbashi/RDC</t>
+    <t>30, Rwashi/Lubumbashi/RDC</t>
   </si>
   <si>
-    <t xml:space="preserve">Mécanique Générale</t>
+    <t>Mécanique Générale</t>
   </si>
   <si>
-    <t xml:space="preserve">NSENGA KATENDA</t>
+    <t>NSENGA KATENDA</t>
   </si>
   <si>
     <t>PAUL</t>
@@ -81,7 +79,7 @@
     <t>3,Golf-Plateau/Lubumbashi/RDC</t>
   </si>
   <si>
-    <t xml:space="preserve">KALOND MBAY</t>
+    <t>KALOND MBAY</t>
   </si>
   <si>
     <t>MARIETTE</t>
@@ -96,31 +94,38 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
       <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="20.000000"/>
       <color theme="1"/>
+      <sz val="20"/>
       <name val="Fira Code Medium"/>
     </font>
     <font>
-      <sz val="12.000000"/>
       <color theme="1"/>
+      <sz val="12"/>
       <name val="Fira Code Retina"/>
     </font>
     <font>
-      <sz val="12.000000"/>
       <color theme="1"/>
+      <sz val="12"/>
       <name val="Fira Code Light"/>
     </font>
   </fonts>
@@ -144,7 +149,14 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -211,81 +223,81 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="26">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="1" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="2" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="3" numFmtId="164" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="5" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="4" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="2" borderId="3" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -844,13 +856,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:S1021"/>
+  <sheetFormatPr defaultRowHeight="14.25" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="16384" width="9.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2" ht="14.25" customHeight="1" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F2" s="2" t="s">
         <v>0</v>
       </c>
@@ -862,7 +875,7 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
     </row>
-    <row r="3" ht="14.25" customHeight="1">
+    <row r="3" ht="14.25" customHeight="1" spans="6:13" x14ac:dyDescent="0.25">
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -872,7 +885,7 @@
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
     </row>
-    <row r="5" ht="14.25" customHeight="1">
+    <row r="5" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>1</v>
       </c>
@@ -906,7 +919,7 @@
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
     </row>
-    <row r="6" ht="14.25" customHeight="1">
+    <row r="6" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B6" s="3"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
@@ -926,7 +939,7 @@
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
     </row>
-    <row r="7" ht="14.25" customHeight="1">
+    <row r="7" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -946,7 +959,7 @@
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B8" s="8" t="s">
         <v>8</v>
       </c>
@@ -980,7 +993,7 @@
       <c r="R8" s="8"/>
       <c r="S8" s="8"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B9" s="16" t="s">
         <v>14</v>
       </c>
@@ -1014,7 +1027,7 @@
       <c r="R9" s="16"/>
       <c r="S9" s="16"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B10" s="16" t="s">
         <v>18</v>
       </c>
@@ -1048,7 +1061,7 @@
       <c r="R10" s="16"/>
       <c r="S10" s="16"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B11" s="16" t="s">
         <v>21</v>
       </c>
@@ -1082,7 +1095,7 @@
       <c r="R11" s="16"/>
       <c r="S11" s="16"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B12" s="16"/>
       <c r="C12" s="16"/>
       <c r="D12" s="16"/>
@@ -1102,7 +1115,7 @@
       <c r="R12" s="16"/>
       <c r="S12" s="16"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B13" s="16"/>
       <c r="C13" s="16"/>
       <c r="D13" s="16"/>
@@ -1122,7 +1135,7 @@
       <c r="R13" s="16"/>
       <c r="S13" s="16"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
@@ -1142,7 +1155,7 @@
       <c r="R14" s="16"/>
       <c r="S14" s="16"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B15" s="16"/>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
@@ -1162,7 +1175,7 @@
       <c r="R15" s="16"/>
       <c r="S15" s="16"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
       <c r="D16" s="16"/>
@@ -1182,7 +1195,7 @@
       <c r="R16" s="16"/>
       <c r="S16" s="16"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B17" s="16"/>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
@@ -1202,7 +1215,7 @@
       <c r="R17" s="16"/>
       <c r="S17" s="16"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B18" s="16"/>
       <c r="C18" s="16"/>
       <c r="D18" s="16"/>
@@ -1222,7 +1235,7 @@
       <c r="R18" s="16"/>
       <c r="S18" s="16"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
       <c r="D19" s="16"/>
@@ -1242,7 +1255,7 @@
       <c r="R19" s="16"/>
       <c r="S19" s="16"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B20" s="16"/>
       <c r="C20" s="16"/>
       <c r="D20" s="16"/>
@@ -1262,7 +1275,7 @@
       <c r="R20" s="16"/>
       <c r="S20" s="16"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
@@ -1282,7 +1295,7 @@
       <c r="R21" s="16"/>
       <c r="S21" s="16"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
       <c r="D22" s="16"/>
@@ -1302,7 +1315,7 @@
       <c r="R22" s="16"/>
       <c r="S22" s="16"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B23" s="16"/>
       <c r="C23" s="16"/>
       <c r="D23" s="16"/>
@@ -1322,7 +1335,7 @@
       <c r="R23" s="16"/>
       <c r="S23" s="16"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
       <c r="D24" s="16"/>
@@ -1342,7 +1355,7 @@
       <c r="R24" s="16"/>
       <c r="S24" s="16"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B25" s="16"/>
       <c r="C25" s="16"/>
       <c r="D25" s="16"/>
@@ -1362,7 +1375,7 @@
       <c r="R25" s="16"/>
       <c r="S25" s="16"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -1382,7 +1395,7 @@
       <c r="R26" s="16"/>
       <c r="S26" s="16"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B27" s="16"/>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -1402,7 +1415,7 @@
       <c r="R27" s="16"/>
       <c r="S27" s="16"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -1422,7 +1435,7 @@
       <c r="R28" s="16"/>
       <c r="S28" s="16"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
@@ -1442,7 +1455,7 @@
       <c r="R29" s="16"/>
       <c r="S29" s="16"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
@@ -1462,7 +1475,7 @@
       <c r="R30" s="16"/>
       <c r="S30" s="16"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
       <c r="D31" s="16"/>
@@ -1482,7 +1495,7 @@
       <c r="R31" s="16"/>
       <c r="S31" s="16"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
@@ -1502,7 +1515,7 @@
       <c r="R32" s="16"/>
       <c r="S32" s="16"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
       <c r="D33" s="16"/>
@@ -1522,7 +1535,7 @@
       <c r="R33" s="16"/>
       <c r="S33" s="16"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
       <c r="D34" s="16"/>
@@ -1542,7 +1555,7 @@
       <c r="R34" s="16"/>
       <c r="S34" s="16"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
@@ -1562,7 +1575,7 @@
       <c r="R35" s="16"/>
       <c r="S35" s="16"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
       <c r="D36" s="16"/>
@@ -1582,7 +1595,7 @@
       <c r="R36" s="16"/>
       <c r="S36" s="16"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
@@ -1602,7 +1615,7 @@
       <c r="R37" s="16"/>
       <c r="S37" s="16"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
       <c r="D38" s="16"/>
@@ -1622,7 +1635,7 @@
       <c r="R38" s="16"/>
       <c r="S38" s="16"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B39" s="16"/>
       <c r="C39" s="16"/>
       <c r="D39" s="16"/>
@@ -1642,7 +1655,7 @@
       <c r="R39" s="16"/>
       <c r="S39" s="16"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
       <c r="D40" s="16"/>
@@ -1662,7 +1675,7 @@
       <c r="R40" s="16"/>
       <c r="S40" s="16"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B41" s="16"/>
       <c r="C41" s="16"/>
       <c r="D41" s="16"/>
@@ -1682,7 +1695,7 @@
       <c r="R41" s="16"/>
       <c r="S41" s="16"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B42" s="16"/>
       <c r="C42" s="16"/>
       <c r="D42" s="16"/>
@@ -1702,7 +1715,7 @@
       <c r="R42" s="16"/>
       <c r="S42" s="16"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B43" s="16"/>
       <c r="C43" s="16"/>
       <c r="D43" s="16"/>
@@ -1722,7 +1735,7 @@
       <c r="R43" s="16"/>
       <c r="S43" s="16"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B44" s="16"/>
       <c r="C44" s="16"/>
       <c r="D44" s="16"/>
@@ -1742,7 +1755,7 @@
       <c r="R44" s="16"/>
       <c r="S44" s="16"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B45" s="16"/>
       <c r="C45" s="16"/>
       <c r="D45" s="16"/>
@@ -1762,7 +1775,7 @@
       <c r="R45" s="16"/>
       <c r="S45" s="16"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B46" s="16"/>
       <c r="C46" s="16"/>
       <c r="D46" s="16"/>
@@ -1782,7 +1795,7 @@
       <c r="R46" s="16"/>
       <c r="S46" s="16"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B47" s="16"/>
       <c r="C47" s="16"/>
       <c r="D47" s="16"/>
@@ -1802,7 +1815,7 @@
       <c r="R47" s="16"/>
       <c r="S47" s="16"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
       <c r="D48" s="16"/>
@@ -1822,7 +1835,7 @@
       <c r="R48" s="16"/>
       <c r="S48" s="16"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B49" s="16"/>
       <c r="C49" s="16"/>
       <c r="D49" s="16"/>
@@ -1842,7 +1855,7 @@
       <c r="R49" s="16"/>
       <c r="S49" s="16"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
       <c r="D50" s="16"/>
@@ -1862,7 +1875,7 @@
       <c r="R50" s="16"/>
       <c r="S50" s="16"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
       <c r="D51" s="16"/>
@@ -1882,7 +1895,7 @@
       <c r="R51" s="16"/>
       <c r="S51" s="16"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B52" s="16"/>
       <c r="C52" s="16"/>
       <c r="D52" s="16"/>
@@ -1902,7 +1915,7 @@
       <c r="R52" s="16"/>
       <c r="S52" s="16"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B53" s="16"/>
       <c r="C53" s="16"/>
       <c r="D53" s="16"/>
@@ -1922,7 +1935,7 @@
       <c r="R53" s="16"/>
       <c r="S53" s="16"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B54" s="16"/>
       <c r="C54" s="16"/>
       <c r="D54" s="16"/>
@@ -1942,7 +1955,7 @@
       <c r="R54" s="16"/>
       <c r="S54" s="16"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B55" s="16"/>
       <c r="C55" s="16"/>
       <c r="D55" s="16"/>
@@ -1962,7 +1975,7 @@
       <c r="R55" s="16"/>
       <c r="S55" s="16"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B56" s="16"/>
       <c r="C56" s="16"/>
       <c r="D56" s="16"/>
@@ -1982,7 +1995,7 @@
       <c r="R56" s="16"/>
       <c r="S56" s="16"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B57" s="16"/>
       <c r="C57" s="16"/>
       <c r="D57" s="16"/>
@@ -2002,7 +2015,7 @@
       <c r="R57" s="16"/>
       <c r="S57" s="16"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B58" s="16"/>
       <c r="C58" s="16"/>
       <c r="D58" s="16"/>
@@ -2022,7 +2035,7 @@
       <c r="R58" s="16"/>
       <c r="S58" s="16"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B59" s="16"/>
       <c r="C59" s="16"/>
       <c r="D59" s="16"/>
@@ -2042,7 +2055,7 @@
       <c r="R59" s="16"/>
       <c r="S59" s="16"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
       <c r="D60" s="16"/>
@@ -2062,7 +2075,7 @@
       <c r="R60" s="16"/>
       <c r="S60" s="16"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B61" s="16"/>
       <c r="C61" s="16"/>
       <c r="D61" s="16"/>
@@ -2082,7 +2095,7 @@
       <c r="R61" s="16"/>
       <c r="S61" s="16"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B62" s="16"/>
       <c r="C62" s="16"/>
       <c r="D62" s="16"/>
@@ -2102,7 +2115,7 @@
       <c r="R62" s="16"/>
       <c r="S62" s="16"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B63" s="16"/>
       <c r="C63" s="16"/>
       <c r="D63" s="16"/>
@@ -2122,7 +2135,7 @@
       <c r="R63" s="16"/>
       <c r="S63" s="16"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B64" s="16"/>
       <c r="C64" s="16"/>
       <c r="D64" s="16"/>
@@ -2142,7 +2155,7 @@
       <c r="R64" s="16"/>
       <c r="S64" s="16"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" ht="15.75" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B65" s="16"/>
       <c r="C65" s="16"/>
       <c r="D65" s="16"/>
@@ -2162,7 +2175,7 @@
       <c r="R65" s="16"/>
       <c r="S65" s="16"/>
     </row>
-    <row r="66" ht="14.25" customHeight="1">
+    <row r="66" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B66" s="16"/>
       <c r="C66" s="16"/>
       <c r="D66" s="16"/>
@@ -2182,7 +2195,7 @@
       <c r="R66" s="16"/>
       <c r="S66" s="16"/>
     </row>
-    <row r="67" ht="14.25" customHeight="1">
+    <row r="67" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B67" s="16"/>
       <c r="C67" s="16"/>
       <c r="D67" s="16"/>
@@ -2202,7 +2215,7 @@
       <c r="R67" s="16"/>
       <c r="S67" s="16"/>
     </row>
-    <row r="68" ht="14.25" customHeight="1">
+    <row r="68" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B68" s="16"/>
       <c r="C68" s="16"/>
       <c r="D68" s="16"/>
@@ -2222,7 +2235,7 @@
       <c r="R68" s="16"/>
       <c r="S68" s="16"/>
     </row>
-    <row r="69" ht="14.25" customHeight="1">
+    <row r="69" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B69" s="16"/>
       <c r="C69" s="16"/>
       <c r="D69" s="16"/>
@@ -2242,7 +2255,7 @@
       <c r="R69" s="16"/>
       <c r="S69" s="16"/>
     </row>
-    <row r="70" ht="14.25" customHeight="1">
+    <row r="70" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B70" s="16"/>
       <c r="C70" s="16"/>
       <c r="D70" s="16"/>
@@ -2262,7 +2275,7 @@
       <c r="R70" s="16"/>
       <c r="S70" s="16"/>
     </row>
-    <row r="71" ht="14.25" customHeight="1">
+    <row r="71" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B71" s="16"/>
       <c r="C71" s="16"/>
       <c r="D71" s="16"/>
@@ -2282,7 +2295,7 @@
       <c r="R71" s="16"/>
       <c r="S71" s="16"/>
     </row>
-    <row r="72" ht="14.25" customHeight="1">
+    <row r="72" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B72" s="16"/>
       <c r="C72" s="16"/>
       <c r="D72" s="16"/>
@@ -2302,7 +2315,7 @@
       <c r="R72" s="16"/>
       <c r="S72" s="16"/>
     </row>
-    <row r="73" ht="14.25" customHeight="1">
+    <row r="73" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B73" s="16"/>
       <c r="C73" s="16"/>
       <c r="D73" s="16"/>
@@ -2322,7 +2335,7 @@
       <c r="R73" s="16"/>
       <c r="S73" s="16"/>
     </row>
-    <row r="74" ht="14.25" customHeight="1">
+    <row r="74" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B74" s="16"/>
       <c r="C74" s="16"/>
       <c r="D74" s="16"/>
@@ -2342,7 +2355,7 @@
       <c r="R74" s="16"/>
       <c r="S74" s="16"/>
     </row>
-    <row r="75" ht="14.25" customHeight="1">
+    <row r="75" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B75" s="16"/>
       <c r="C75" s="16"/>
       <c r="D75" s="16"/>
@@ -2362,7 +2375,7 @@
       <c r="R75" s="16"/>
       <c r="S75" s="16"/>
     </row>
-    <row r="76" ht="14.25" customHeight="1">
+    <row r="76" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B76" s="16"/>
       <c r="C76" s="16"/>
       <c r="D76" s="16"/>
@@ -2382,7 +2395,7 @@
       <c r="R76" s="16"/>
       <c r="S76" s="16"/>
     </row>
-    <row r="77" ht="14.25" customHeight="1">
+    <row r="77" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B77" s="16"/>
       <c r="C77" s="16"/>
       <c r="D77" s="16"/>
@@ -2402,7 +2415,7 @@
       <c r="R77" s="16"/>
       <c r="S77" s="16"/>
     </row>
-    <row r="78" ht="14.25" customHeight="1">
+    <row r="78" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B78" s="16"/>
       <c r="C78" s="16"/>
       <c r="D78" s="16"/>
@@ -2422,7 +2435,7 @@
       <c r="R78" s="16"/>
       <c r="S78" s="16"/>
     </row>
-    <row r="79" ht="14.25" customHeight="1">
+    <row r="79" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B79" s="16"/>
       <c r="C79" s="16"/>
       <c r="D79" s="16"/>
@@ -2442,7 +2455,7 @@
       <c r="R79" s="16"/>
       <c r="S79" s="16"/>
     </row>
-    <row r="80" ht="14.25" customHeight="1">
+    <row r="80" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B80" s="16"/>
       <c r="C80" s="16"/>
       <c r="D80" s="16"/>
@@ -2462,7 +2475,7 @@
       <c r="R80" s="16"/>
       <c r="S80" s="16"/>
     </row>
-    <row r="81" ht="14.25" customHeight="1">
+    <row r="81" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B81" s="16"/>
       <c r="C81" s="16"/>
       <c r="D81" s="16"/>
@@ -2482,7 +2495,7 @@
       <c r="R81" s="16"/>
       <c r="S81" s="16"/>
     </row>
-    <row r="82" ht="14.25" customHeight="1">
+    <row r="82" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B82" s="16"/>
       <c r="C82" s="16"/>
       <c r="D82" s="16"/>
@@ -2502,7 +2515,7 @@
       <c r="R82" s="16"/>
       <c r="S82" s="16"/>
     </row>
-    <row r="83" ht="14.25" customHeight="1">
+    <row r="83" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B83" s="16"/>
       <c r="C83" s="16"/>
       <c r="D83" s="16"/>
@@ -2522,7 +2535,7 @@
       <c r="R83" s="16"/>
       <c r="S83" s="16"/>
     </row>
-    <row r="84" ht="14.25" customHeight="1">
+    <row r="84" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B84" s="16"/>
       <c r="C84" s="16"/>
       <c r="D84" s="16"/>
@@ -2542,7 +2555,7 @@
       <c r="R84" s="16"/>
       <c r="S84" s="16"/>
     </row>
-    <row r="85" ht="14.25" customHeight="1">
+    <row r="85" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B85" s="16"/>
       <c r="C85" s="16"/>
       <c r="D85" s="16"/>
@@ -2562,7 +2575,7 @@
       <c r="R85" s="16"/>
       <c r="S85" s="16"/>
     </row>
-    <row r="86" ht="14.25" customHeight="1">
+    <row r="86" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B86" s="16"/>
       <c r="C86" s="16"/>
       <c r="D86" s="16"/>
@@ -2582,7 +2595,7 @@
       <c r="R86" s="16"/>
       <c r="S86" s="16"/>
     </row>
-    <row r="87" ht="14.25" customHeight="1">
+    <row r="87" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B87" s="16"/>
       <c r="C87" s="16"/>
       <c r="D87" s="16"/>
@@ -2602,7 +2615,7 @@
       <c r="R87" s="16"/>
       <c r="S87" s="16"/>
     </row>
-    <row r="88" ht="14.25" customHeight="1">
+    <row r="88" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B88" s="16"/>
       <c r="C88" s="16"/>
       <c r="D88" s="16"/>
@@ -2622,7 +2635,7 @@
       <c r="R88" s="16"/>
       <c r="S88" s="16"/>
     </row>
-    <row r="89" ht="14.25" customHeight="1">
+    <row r="89" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B89" s="16"/>
       <c r="C89" s="16"/>
       <c r="D89" s="16"/>
@@ -2642,7 +2655,7 @@
       <c r="R89" s="16"/>
       <c r="S89" s="16"/>
     </row>
-    <row r="90" ht="14.25" customHeight="1">
+    <row r="90" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B90" s="16"/>
       <c r="C90" s="16"/>
       <c r="D90" s="16"/>
@@ -2662,7 +2675,7 @@
       <c r="R90" s="16"/>
       <c r="S90" s="16"/>
     </row>
-    <row r="91" ht="14.25" customHeight="1">
+    <row r="91" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B91" s="16"/>
       <c r="C91" s="16"/>
       <c r="D91" s="16"/>
@@ -2682,7 +2695,7 @@
       <c r="R91" s="16"/>
       <c r="S91" s="16"/>
     </row>
-    <row r="92" ht="14.25" customHeight="1">
+    <row r="92" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B92" s="16"/>
       <c r="C92" s="16"/>
       <c r="D92" s="16"/>
@@ -2702,7 +2715,7 @@
       <c r="R92" s="16"/>
       <c r="S92" s="16"/>
     </row>
-    <row r="93" ht="14.25" customHeight="1">
+    <row r="93" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B93" s="16"/>
       <c r="C93" s="16"/>
       <c r="D93" s="16"/>
@@ -2722,7 +2735,7 @@
       <c r="R93" s="16"/>
       <c r="S93" s="16"/>
     </row>
-    <row r="94" ht="14.25" customHeight="1">
+    <row r="94" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B94" s="16"/>
       <c r="C94" s="16"/>
       <c r="D94" s="16"/>
@@ -2742,7 +2755,7 @@
       <c r="R94" s="16"/>
       <c r="S94" s="16"/>
     </row>
-    <row r="95" ht="14.25" customHeight="1">
+    <row r="95" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B95" s="16"/>
       <c r="C95" s="16"/>
       <c r="D95" s="16"/>
@@ -2762,7 +2775,7 @@
       <c r="R95" s="16"/>
       <c r="S95" s="16"/>
     </row>
-    <row r="96" ht="14.25" customHeight="1">
+    <row r="96" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B96" s="16"/>
       <c r="C96" s="16"/>
       <c r="D96" s="16"/>
@@ -2782,7 +2795,7 @@
       <c r="R96" s="16"/>
       <c r="S96" s="16"/>
     </row>
-    <row r="97" ht="14.25" customHeight="1">
+    <row r="97" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B97" s="16"/>
       <c r="C97" s="16"/>
       <c r="D97" s="16"/>
@@ -2802,7 +2815,7 @@
       <c r="R97" s="16"/>
       <c r="S97" s="16"/>
     </row>
-    <row r="98" ht="14.25" customHeight="1">
+    <row r="98" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B98" s="16"/>
       <c r="C98" s="16"/>
       <c r="D98" s="16"/>
@@ -2822,7 +2835,7 @@
       <c r="R98" s="16"/>
       <c r="S98" s="16"/>
     </row>
-    <row r="99" ht="14.25" customHeight="1">
+    <row r="99" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B99" s="16"/>
       <c r="C99" s="16"/>
       <c r="D99" s="16"/>
@@ -2842,7 +2855,7 @@
       <c r="R99" s="16"/>
       <c r="S99" s="16"/>
     </row>
-    <row r="100" ht="14.25" customHeight="1">
+    <row r="100" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B100" s="16"/>
       <c r="C100" s="16"/>
       <c r="D100" s="16"/>
@@ -2862,7 +2875,7 @@
       <c r="R100" s="16"/>
       <c r="S100" s="16"/>
     </row>
-    <row r="101" ht="14.25" customHeight="1">
+    <row r="101" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B101" s="16"/>
       <c r="C101" s="16"/>
       <c r="D101" s="16"/>
@@ -2882,7 +2895,7 @@
       <c r="R101" s="16"/>
       <c r="S101" s="16"/>
     </row>
-    <row r="102" ht="14.25" customHeight="1">
+    <row r="102" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B102" s="16"/>
       <c r="C102" s="16"/>
       <c r="D102" s="16"/>
@@ -2902,7 +2915,7 @@
       <c r="R102" s="16"/>
       <c r="S102" s="16"/>
     </row>
-    <row r="103" ht="14.25" customHeight="1">
+    <row r="103" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B103" s="16"/>
       <c r="C103" s="16"/>
       <c r="D103" s="16"/>
@@ -2922,7 +2935,7 @@
       <c r="R103" s="16"/>
       <c r="S103" s="16"/>
     </row>
-    <row r="104" ht="14.25" customHeight="1">
+    <row r="104" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B104" s="16"/>
       <c r="C104" s="16"/>
       <c r="D104" s="16"/>
@@ -2942,7 +2955,7 @@
       <c r="R104" s="16"/>
       <c r="S104" s="16"/>
     </row>
-    <row r="105" ht="14.25" customHeight="1">
+    <row r="105" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B105" s="16"/>
       <c r="C105" s="16"/>
       <c r="D105" s="16"/>
@@ -2962,7 +2975,7 @@
       <c r="R105" s="16"/>
       <c r="S105" s="16"/>
     </row>
-    <row r="106" ht="14.25" customHeight="1">
+    <row r="106" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B106" s="16"/>
       <c r="C106" s="16"/>
       <c r="D106" s="16"/>
@@ -2982,7 +2995,7 @@
       <c r="R106" s="16"/>
       <c r="S106" s="16"/>
     </row>
-    <row r="107" ht="14.25" customHeight="1">
+    <row r="107" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B107" s="16"/>
       <c r="C107" s="16"/>
       <c r="D107" s="16"/>
@@ -3002,7 +3015,7 @@
       <c r="R107" s="16"/>
       <c r="S107" s="16"/>
     </row>
-    <row r="108" ht="14.25" customHeight="1">
+    <row r="108" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B108" s="16"/>
       <c r="C108" s="16"/>
       <c r="D108" s="16"/>
@@ -3022,7 +3035,7 @@
       <c r="R108" s="16"/>
       <c r="S108" s="16"/>
     </row>
-    <row r="109" ht="14.25" customHeight="1">
+    <row r="109" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B109" s="16"/>
       <c r="C109" s="16"/>
       <c r="D109" s="16"/>
@@ -3042,7 +3055,7 @@
       <c r="R109" s="16"/>
       <c r="S109" s="16"/>
     </row>
-    <row r="110" ht="14.25" customHeight="1">
+    <row r="110" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B110" s="16"/>
       <c r="C110" s="16"/>
       <c r="D110" s="16"/>
@@ -3062,7 +3075,7 @@
       <c r="R110" s="16"/>
       <c r="S110" s="16"/>
     </row>
-    <row r="111" ht="14.25" customHeight="1">
+    <row r="111" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B111" s="16"/>
       <c r="C111" s="16"/>
       <c r="D111" s="16"/>
@@ -3082,7 +3095,7 @@
       <c r="R111" s="16"/>
       <c r="S111" s="16"/>
     </row>
-    <row r="112" ht="14.25" customHeight="1">
+    <row r="112" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B112" s="16"/>
       <c r="C112" s="16"/>
       <c r="D112" s="16"/>
@@ -3102,7 +3115,7 @@
       <c r="R112" s="16"/>
       <c r="S112" s="16"/>
     </row>
-    <row r="113" ht="14.25" customHeight="1">
+    <row r="113" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B113" s="16"/>
       <c r="C113" s="16"/>
       <c r="D113" s="16"/>
@@ -3122,7 +3135,7 @@
       <c r="R113" s="16"/>
       <c r="S113" s="16"/>
     </row>
-    <row r="114" ht="14.25" customHeight="1">
+    <row r="114" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B114" s="16"/>
       <c r="C114" s="16"/>
       <c r="D114" s="16"/>
@@ -3142,7 +3155,7 @@
       <c r="R114" s="16"/>
       <c r="S114" s="16"/>
     </row>
-    <row r="115" ht="14.25" customHeight="1">
+    <row r="115" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B115" s="16"/>
       <c r="C115" s="16"/>
       <c r="D115" s="16"/>
@@ -3162,7 +3175,7 @@
       <c r="R115" s="16"/>
       <c r="S115" s="16"/>
     </row>
-    <row r="116" ht="14.25" customHeight="1">
+    <row r="116" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B116" s="16"/>
       <c r="C116" s="16"/>
       <c r="D116" s="16"/>
@@ -3182,7 +3195,7 @@
       <c r="R116" s="16"/>
       <c r="S116" s="16"/>
     </row>
-    <row r="117" ht="14.25" customHeight="1">
+    <row r="117" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B117" s="16"/>
       <c r="C117" s="16"/>
       <c r="D117" s="16"/>
@@ -3202,7 +3215,7 @@
       <c r="R117" s="16"/>
       <c r="S117" s="16"/>
     </row>
-    <row r="118" ht="14.25" customHeight="1">
+    <row r="118" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B118" s="16"/>
       <c r="C118" s="16"/>
       <c r="D118" s="16"/>
@@ -3222,7 +3235,7 @@
       <c r="R118" s="16"/>
       <c r="S118" s="16"/>
     </row>
-    <row r="119" ht="14.25" customHeight="1">
+    <row r="119" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B119" s="16"/>
       <c r="C119" s="16"/>
       <c r="D119" s="16"/>
@@ -3242,7 +3255,7 @@
       <c r="R119" s="16"/>
       <c r="S119" s="16"/>
     </row>
-    <row r="120" ht="14.25" customHeight="1">
+    <row r="120" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B120" s="16"/>
       <c r="C120" s="16"/>
       <c r="D120" s="16"/>
@@ -3262,7 +3275,7 @@
       <c r="R120" s="16"/>
       <c r="S120" s="16"/>
     </row>
-    <row r="121" ht="14.25" customHeight="1">
+    <row r="121" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B121" s="16"/>
       <c r="C121" s="16"/>
       <c r="D121" s="16"/>
@@ -3282,7 +3295,7 @@
       <c r="R121" s="16"/>
       <c r="S121" s="16"/>
     </row>
-    <row r="122" ht="14.25" customHeight="1">
+    <row r="122" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B122" s="16"/>
       <c r="C122" s="16"/>
       <c r="D122" s="16"/>
@@ -3302,7 +3315,7 @@
       <c r="R122" s="16"/>
       <c r="S122" s="16"/>
     </row>
-    <row r="123" ht="14.25" customHeight="1">
+    <row r="123" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B123" s="16"/>
       <c r="C123" s="16"/>
       <c r="D123" s="16"/>
@@ -3322,7 +3335,7 @@
       <c r="R123" s="16"/>
       <c r="S123" s="16"/>
     </row>
-    <row r="124" ht="14.25" customHeight="1">
+    <row r="124" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B124" s="16"/>
       <c r="C124" s="16"/>
       <c r="D124" s="16"/>
@@ -3342,7 +3355,7 @@
       <c r="R124" s="16"/>
       <c r="S124" s="16"/>
     </row>
-    <row r="125" ht="14.25" customHeight="1">
+    <row r="125" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B125" s="16"/>
       <c r="C125" s="16"/>
       <c r="D125" s="16"/>
@@ -3362,7 +3375,7 @@
       <c r="R125" s="16"/>
       <c r="S125" s="16"/>
     </row>
-    <row r="126" ht="14.25" customHeight="1">
+    <row r="126" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B126" s="16"/>
       <c r="C126" s="16"/>
       <c r="D126" s="16"/>
@@ -3382,7 +3395,7 @@
       <c r="R126" s="16"/>
       <c r="S126" s="16"/>
     </row>
-    <row r="127" ht="14.25" customHeight="1">
+    <row r="127" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B127" s="16"/>
       <c r="C127" s="16"/>
       <c r="D127" s="16"/>
@@ -3402,7 +3415,7 @@
       <c r="R127" s="16"/>
       <c r="S127" s="16"/>
     </row>
-    <row r="128" ht="14.25" customHeight="1">
+    <row r="128" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B128" s="16"/>
       <c r="C128" s="16"/>
       <c r="D128" s="16"/>
@@ -3422,7 +3435,7 @@
       <c r="R128" s="16"/>
       <c r="S128" s="16"/>
     </row>
-    <row r="129" ht="14.25" customHeight="1">
+    <row r="129" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B129" s="16"/>
       <c r="C129" s="16"/>
       <c r="D129" s="16"/>
@@ -3442,7 +3455,7 @@
       <c r="R129" s="16"/>
       <c r="S129" s="16"/>
     </row>
-    <row r="130" ht="14.25" customHeight="1">
+    <row r="130" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B130" s="16"/>
       <c r="C130" s="16"/>
       <c r="D130" s="16"/>
@@ -3462,7 +3475,7 @@
       <c r="R130" s="16"/>
       <c r="S130" s="16"/>
     </row>
-    <row r="131" ht="14.25" customHeight="1">
+    <row r="131" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B131" s="16"/>
       <c r="C131" s="16"/>
       <c r="D131" s="16"/>
@@ -3482,7 +3495,7 @@
       <c r="R131" s="16"/>
       <c r="S131" s="16"/>
     </row>
-    <row r="132" ht="14.25" customHeight="1">
+    <row r="132" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B132" s="16"/>
       <c r="C132" s="16"/>
       <c r="D132" s="16"/>
@@ -3502,7 +3515,7 @@
       <c r="R132" s="16"/>
       <c r="S132" s="16"/>
     </row>
-    <row r="133" ht="14.25" customHeight="1">
+    <row r="133" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B133" s="16"/>
       <c r="C133" s="16"/>
       <c r="D133" s="16"/>
@@ -3522,7 +3535,7 @@
       <c r="R133" s="16"/>
       <c r="S133" s="16"/>
     </row>
-    <row r="134" ht="14.25" customHeight="1">
+    <row r="134" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B134" s="16"/>
       <c r="C134" s="16"/>
       <c r="D134" s="16"/>
@@ -3542,7 +3555,7 @@
       <c r="R134" s="16"/>
       <c r="S134" s="16"/>
     </row>
-    <row r="135" ht="14.25" customHeight="1">
+    <row r="135" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B135" s="16"/>
       <c r="C135" s="16"/>
       <c r="D135" s="16"/>
@@ -3562,7 +3575,7 @@
       <c r="R135" s="16"/>
       <c r="S135" s="16"/>
     </row>
-    <row r="136" ht="14.25" customHeight="1">
+    <row r="136" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B136" s="16"/>
       <c r="C136" s="16"/>
       <c r="D136" s="16"/>
@@ -3582,7 +3595,7 @@
       <c r="R136" s="16"/>
       <c r="S136" s="16"/>
     </row>
-    <row r="137" ht="14.25" customHeight="1">
+    <row r="137" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B137" s="16"/>
       <c r="C137" s="16"/>
       <c r="D137" s="16"/>
@@ -3602,7 +3615,7 @@
       <c r="R137" s="16"/>
       <c r="S137" s="16"/>
     </row>
-    <row r="138" ht="14.25" customHeight="1">
+    <row r="138" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B138" s="16"/>
       <c r="C138" s="16"/>
       <c r="D138" s="16"/>
@@ -3622,7 +3635,7 @@
       <c r="R138" s="16"/>
       <c r="S138" s="16"/>
     </row>
-    <row r="139" ht="14.25" customHeight="1">
+    <row r="139" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B139" s="16"/>
       <c r="C139" s="16"/>
       <c r="D139" s="16"/>
@@ -3642,7 +3655,7 @@
       <c r="R139" s="16"/>
       <c r="S139" s="16"/>
     </row>
-    <row r="140" ht="14.25" customHeight="1">
+    <row r="140" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B140" s="16"/>
       <c r="C140" s="16"/>
       <c r="D140" s="16"/>
@@ -3662,7 +3675,7 @@
       <c r="R140" s="16"/>
       <c r="S140" s="16"/>
     </row>
-    <row r="141" ht="14.25" customHeight="1">
+    <row r="141" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B141" s="16"/>
       <c r="C141" s="16"/>
       <c r="D141" s="16"/>
@@ -3682,7 +3695,7 @@
       <c r="R141" s="16"/>
       <c r="S141" s="16"/>
     </row>
-    <row r="142" ht="14.25" customHeight="1">
+    <row r="142" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B142" s="16"/>
       <c r="C142" s="16"/>
       <c r="D142" s="16"/>
@@ -3702,7 +3715,7 @@
       <c r="R142" s="16"/>
       <c r="S142" s="16"/>
     </row>
-    <row r="143" ht="14.25" customHeight="1">
+    <row r="143" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B143" s="16"/>
       <c r="C143" s="16"/>
       <c r="D143" s="16"/>
@@ -3722,7 +3735,7 @@
       <c r="R143" s="16"/>
       <c r="S143" s="16"/>
     </row>
-    <row r="144" ht="14.25" customHeight="1">
+    <row r="144" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B144" s="16"/>
       <c r="C144" s="16"/>
       <c r="D144" s="16"/>
@@ -3742,7 +3755,7 @@
       <c r="R144" s="16"/>
       <c r="S144" s="16"/>
     </row>
-    <row r="145" ht="14.25" customHeight="1">
+    <row r="145" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B145" s="16"/>
       <c r="C145" s="16"/>
       <c r="D145" s="16"/>
@@ -3762,7 +3775,7 @@
       <c r="R145" s="16"/>
       <c r="S145" s="16"/>
     </row>
-    <row r="146" ht="14.25" customHeight="1">
+    <row r="146" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B146" s="16"/>
       <c r="C146" s="16"/>
       <c r="D146" s="16"/>
@@ -3782,7 +3795,7 @@
       <c r="R146" s="16"/>
       <c r="S146" s="16"/>
     </row>
-    <row r="147" ht="14.25" customHeight="1">
+    <row r="147" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B147" s="16"/>
       <c r="C147" s="16"/>
       <c r="D147" s="16"/>
@@ -3802,7 +3815,7 @@
       <c r="R147" s="16"/>
       <c r="S147" s="16"/>
     </row>
-    <row r="148" ht="14.25" customHeight="1">
+    <row r="148" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B148" s="16"/>
       <c r="C148" s="16"/>
       <c r="D148" s="16"/>
@@ -3822,7 +3835,7 @@
       <c r="R148" s="16"/>
       <c r="S148" s="16"/>
     </row>
-    <row r="149" ht="14.25" customHeight="1">
+    <row r="149" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B149" s="16"/>
       <c r="C149" s="16"/>
       <c r="D149" s="16"/>
@@ -3842,7 +3855,7 @@
       <c r="R149" s="16"/>
       <c r="S149" s="16"/>
     </row>
-    <row r="150" ht="14.25" customHeight="1">
+    <row r="150" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B150" s="16"/>
       <c r="C150" s="16"/>
       <c r="D150" s="16"/>
@@ -3862,7 +3875,7 @@
       <c r="R150" s="16"/>
       <c r="S150" s="16"/>
     </row>
-    <row r="151" ht="14.25" customHeight="1">
+    <row r="151" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B151" s="16"/>
       <c r="C151" s="16"/>
       <c r="D151" s="16"/>
@@ -3882,7 +3895,7 @@
       <c r="R151" s="16"/>
       <c r="S151" s="16"/>
     </row>
-    <row r="152" ht="14.25" customHeight="1">
+    <row r="152" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B152" s="16"/>
       <c r="C152" s="16"/>
       <c r="D152" s="16"/>
@@ -3902,7 +3915,7 @@
       <c r="R152" s="16"/>
       <c r="S152" s="16"/>
     </row>
-    <row r="153" ht="14.25" customHeight="1">
+    <row r="153" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B153" s="16"/>
       <c r="C153" s="16"/>
       <c r="D153" s="16"/>
@@ -3922,7 +3935,7 @@
       <c r="R153" s="16"/>
       <c r="S153" s="16"/>
     </row>
-    <row r="154" ht="14.25" customHeight="1">
+    <row r="154" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B154" s="16"/>
       <c r="C154" s="16"/>
       <c r="D154" s="16"/>
@@ -3942,7 +3955,7 @@
       <c r="R154" s="16"/>
       <c r="S154" s="16"/>
     </row>
-    <row r="155" ht="14.25" customHeight="1">
+    <row r="155" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B155" s="16"/>
       <c r="C155" s="16"/>
       <c r="D155" s="16"/>
@@ -3962,7 +3975,7 @@
       <c r="R155" s="16"/>
       <c r="S155" s="16"/>
     </row>
-    <row r="156" ht="14.25" customHeight="1">
+    <row r="156" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B156" s="16"/>
       <c r="C156" s="16"/>
       <c r="D156" s="16"/>
@@ -3982,7 +3995,7 @@
       <c r="R156" s="16"/>
       <c r="S156" s="16"/>
     </row>
-    <row r="157" ht="14.25" customHeight="1">
+    <row r="157" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B157" s="16"/>
       <c r="C157" s="16"/>
       <c r="D157" s="16"/>
@@ -4002,7 +4015,7 @@
       <c r="R157" s="16"/>
       <c r="S157" s="16"/>
     </row>
-    <row r="158" ht="14.25" customHeight="1">
+    <row r="158" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B158" s="16"/>
       <c r="C158" s="16"/>
       <c r="D158" s="16"/>
@@ -4022,7 +4035,7 @@
       <c r="R158" s="16"/>
       <c r="S158" s="16"/>
     </row>
-    <row r="159" ht="14.25" customHeight="1">
+    <row r="159" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B159" s="16"/>
       <c r="C159" s="16"/>
       <c r="D159" s="16"/>
@@ -4042,7 +4055,7 @@
       <c r="R159" s="16"/>
       <c r="S159" s="16"/>
     </row>
-    <row r="160" ht="14.25" customHeight="1">
+    <row r="160" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B160" s="16"/>
       <c r="C160" s="16"/>
       <c r="D160" s="16"/>
@@ -4062,7 +4075,7 @@
       <c r="R160" s="16"/>
       <c r="S160" s="16"/>
     </row>
-    <row r="161" ht="14.25" customHeight="1">
+    <row r="161" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B161" s="16"/>
       <c r="C161" s="16"/>
       <c r="D161" s="16"/>
@@ -4082,7 +4095,7 @@
       <c r="R161" s="16"/>
       <c r="S161" s="16"/>
     </row>
-    <row r="162" ht="14.25" customHeight="1">
+    <row r="162" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B162" s="16"/>
       <c r="C162" s="16"/>
       <c r="D162" s="16"/>
@@ -4102,7 +4115,7 @@
       <c r="R162" s="16"/>
       <c r="S162" s="16"/>
     </row>
-    <row r="163" ht="14.25" customHeight="1">
+    <row r="163" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B163" s="16"/>
       <c r="C163" s="16"/>
       <c r="D163" s="16"/>
@@ -4122,7 +4135,7 @@
       <c r="R163" s="16"/>
       <c r="S163" s="16"/>
     </row>
-    <row r="164" ht="14.25" customHeight="1">
+    <row r="164" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B164" s="16"/>
       <c r="C164" s="16"/>
       <c r="D164" s="16"/>
@@ -4142,7 +4155,7 @@
       <c r="R164" s="16"/>
       <c r="S164" s="16"/>
     </row>
-    <row r="165" ht="14.25" customHeight="1">
+    <row r="165" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B165" s="16"/>
       <c r="C165" s="16"/>
       <c r="D165" s="16"/>
@@ -4162,7 +4175,7 @@
       <c r="R165" s="16"/>
       <c r="S165" s="16"/>
     </row>
-    <row r="166" ht="14.25" customHeight="1">
+    <row r="166" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B166" s="16"/>
       <c r="C166" s="16"/>
       <c r="D166" s="16"/>
@@ -4182,7 +4195,7 @@
       <c r="R166" s="16"/>
       <c r="S166" s="16"/>
     </row>
-    <row r="167" ht="14.25" customHeight="1">
+    <row r="167" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B167" s="16"/>
       <c r="C167" s="16"/>
       <c r="D167" s="16"/>
@@ -4202,7 +4215,7 @@
       <c r="R167" s="16"/>
       <c r="S167" s="16"/>
     </row>
-    <row r="168" ht="14.25" customHeight="1">
+    <row r="168" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B168" s="16"/>
       <c r="C168" s="16"/>
       <c r="D168" s="16"/>
@@ -4222,7 +4235,7 @@
       <c r="R168" s="16"/>
       <c r="S168" s="16"/>
     </row>
-    <row r="169" ht="14.25" customHeight="1">
+    <row r="169" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B169" s="16"/>
       <c r="C169" s="16"/>
       <c r="D169" s="16"/>
@@ -4242,7 +4255,7 @@
       <c r="R169" s="16"/>
       <c r="S169" s="16"/>
     </row>
-    <row r="170" ht="14.25" customHeight="1">
+    <row r="170" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B170" s="16"/>
       <c r="C170" s="16"/>
       <c r="D170" s="16"/>
@@ -4262,7 +4275,7 @@
       <c r="R170" s="16"/>
       <c r="S170" s="16"/>
     </row>
-    <row r="171" ht="14.25" customHeight="1">
+    <row r="171" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B171" s="16"/>
       <c r="C171" s="16"/>
       <c r="D171" s="16"/>
@@ -4282,7 +4295,7 @@
       <c r="R171" s="16"/>
       <c r="S171" s="16"/>
     </row>
-    <row r="172" ht="14.25" customHeight="1">
+    <row r="172" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B172" s="16"/>
       <c r="C172" s="16"/>
       <c r="D172" s="16"/>
@@ -4302,7 +4315,7 @@
       <c r="R172" s="16"/>
       <c r="S172" s="16"/>
     </row>
-    <row r="173" ht="14.25" customHeight="1">
+    <row r="173" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B173" s="16"/>
       <c r="C173" s="16"/>
       <c r="D173" s="16"/>
@@ -4322,7 +4335,7 @@
       <c r="R173" s="16"/>
       <c r="S173" s="16"/>
     </row>
-    <row r="174" ht="14.25" customHeight="1">
+    <row r="174" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B174" s="16"/>
       <c r="C174" s="16"/>
       <c r="D174" s="16"/>
@@ -4342,7 +4355,7 @@
       <c r="R174" s="16"/>
       <c r="S174" s="16"/>
     </row>
-    <row r="175" ht="14.25" customHeight="1">
+    <row r="175" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B175" s="16"/>
       <c r="C175" s="16"/>
       <c r="D175" s="16"/>
@@ -4362,7 +4375,7 @@
       <c r="R175" s="16"/>
       <c r="S175" s="16"/>
     </row>
-    <row r="176" ht="14.25" customHeight="1">
+    <row r="176" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B176" s="16"/>
       <c r="C176" s="16"/>
       <c r="D176" s="16"/>
@@ -4382,7 +4395,7 @@
       <c r="R176" s="16"/>
       <c r="S176" s="16"/>
     </row>
-    <row r="177" ht="14.25" customHeight="1">
+    <row r="177" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B177" s="16"/>
       <c r="C177" s="16"/>
       <c r="D177" s="16"/>
@@ -4402,7 +4415,7 @@
       <c r="R177" s="16"/>
       <c r="S177" s="16"/>
     </row>
-    <row r="178" ht="14.25" customHeight="1">
+    <row r="178" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B178" s="16"/>
       <c r="C178" s="16"/>
       <c r="D178" s="16"/>
@@ -4422,7 +4435,7 @@
       <c r="R178" s="16"/>
       <c r="S178" s="16"/>
     </row>
-    <row r="179" ht="14.25" customHeight="1">
+    <row r="179" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B179" s="16"/>
       <c r="C179" s="16"/>
       <c r="D179" s="16"/>
@@ -4442,7 +4455,7 @@
       <c r="R179" s="16"/>
       <c r="S179" s="16"/>
     </row>
-    <row r="180" ht="14.25" customHeight="1">
+    <row r="180" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B180" s="16"/>
       <c r="C180" s="16"/>
       <c r="D180" s="16"/>
@@ -4462,7 +4475,7 @@
       <c r="R180" s="16"/>
       <c r="S180" s="16"/>
     </row>
-    <row r="181" ht="14.25" customHeight="1">
+    <row r="181" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B181" s="16"/>
       <c r="C181" s="16"/>
       <c r="D181" s="16"/>
@@ -4482,7 +4495,7 @@
       <c r="R181" s="16"/>
       <c r="S181" s="16"/>
     </row>
-    <row r="182" ht="14.25" customHeight="1">
+    <row r="182" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B182" s="16"/>
       <c r="C182" s="16"/>
       <c r="D182" s="16"/>
@@ -4502,7 +4515,7 @@
       <c r="R182" s="16"/>
       <c r="S182" s="16"/>
     </row>
-    <row r="183" ht="14.25" customHeight="1">
+    <row r="183" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B183" s="16"/>
       <c r="C183" s="16"/>
       <c r="D183" s="16"/>
@@ -4522,7 +4535,7 @@
       <c r="R183" s="16"/>
       <c r="S183" s="16"/>
     </row>
-    <row r="184" ht="14.25" customHeight="1">
+    <row r="184" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B184" s="16"/>
       <c r="C184" s="16"/>
       <c r="D184" s="16"/>
@@ -4542,7 +4555,7 @@
       <c r="R184" s="16"/>
       <c r="S184" s="16"/>
     </row>
-    <row r="185" ht="14.25" customHeight="1">
+    <row r="185" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B185" s="16"/>
       <c r="C185" s="16"/>
       <c r="D185" s="16"/>
@@ -4562,7 +4575,7 @@
       <c r="R185" s="16"/>
       <c r="S185" s="16"/>
     </row>
-    <row r="186" ht="14.25" customHeight="1">
+    <row r="186" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B186" s="16"/>
       <c r="C186" s="16"/>
       <c r="D186" s="16"/>
@@ -4582,7 +4595,7 @@
       <c r="R186" s="16"/>
       <c r="S186" s="16"/>
     </row>
-    <row r="187" ht="14.25" customHeight="1">
+    <row r="187" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B187" s="16"/>
       <c r="C187" s="16"/>
       <c r="D187" s="16"/>
@@ -4602,7 +4615,7 @@
       <c r="R187" s="16"/>
       <c r="S187" s="16"/>
     </row>
-    <row r="188" ht="14.25" customHeight="1">
+    <row r="188" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B188" s="16"/>
       <c r="C188" s="16"/>
       <c r="D188" s="16"/>
@@ -4622,7 +4635,7 @@
       <c r="R188" s="16"/>
       <c r="S188" s="16"/>
     </row>
-    <row r="189" ht="14.25" customHeight="1">
+    <row r="189" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B189" s="16"/>
       <c r="C189" s="16"/>
       <c r="D189" s="16"/>
@@ -4642,7 +4655,7 @@
       <c r="R189" s="16"/>
       <c r="S189" s="16"/>
     </row>
-    <row r="190" ht="14.25" customHeight="1">
+    <row r="190" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B190" s="16"/>
       <c r="C190" s="16"/>
       <c r="D190" s="16"/>
@@ -4662,7 +4675,7 @@
       <c r="R190" s="16"/>
       <c r="S190" s="16"/>
     </row>
-    <row r="191" ht="14.25" customHeight="1">
+    <row r="191" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B191" s="16"/>
       <c r="C191" s="16"/>
       <c r="D191" s="16"/>
@@ -4682,7 +4695,7 @@
       <c r="R191" s="16"/>
       <c r="S191" s="16"/>
     </row>
-    <row r="192" ht="14.25" customHeight="1">
+    <row r="192" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B192" s="16"/>
       <c r="C192" s="16"/>
       <c r="D192" s="16"/>
@@ -4702,7 +4715,7 @@
       <c r="R192" s="16"/>
       <c r="S192" s="16"/>
     </row>
-    <row r="193" ht="14.25" customHeight="1">
+    <row r="193" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B193" s="16"/>
       <c r="C193" s="16"/>
       <c r="D193" s="16"/>
@@ -4722,7 +4735,7 @@
       <c r="R193" s="16"/>
       <c r="S193" s="16"/>
     </row>
-    <row r="194" ht="14.25" customHeight="1">
+    <row r="194" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B194" s="16"/>
       <c r="C194" s="16"/>
       <c r="D194" s="16"/>
@@ -4742,7 +4755,7 @@
       <c r="R194" s="16"/>
       <c r="S194" s="16"/>
     </row>
-    <row r="195" ht="14.25" customHeight="1">
+    <row r="195" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B195" s="16"/>
       <c r="C195" s="16"/>
       <c r="D195" s="16"/>
@@ -4762,7 +4775,7 @@
       <c r="R195" s="16"/>
       <c r="S195" s="16"/>
     </row>
-    <row r="196" ht="14.25" customHeight="1">
+    <row r="196" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B196" s="16"/>
       <c r="C196" s="16"/>
       <c r="D196" s="16"/>
@@ -4782,7 +4795,7 @@
       <c r="R196" s="16"/>
       <c r="S196" s="16"/>
     </row>
-    <row r="197" ht="14.25" customHeight="1">
+    <row r="197" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B197" s="16"/>
       <c r="C197" s="16"/>
       <c r="D197" s="16"/>
@@ -4802,7 +4815,7 @@
       <c r="R197" s="16"/>
       <c r="S197" s="16"/>
     </row>
-    <row r="198" ht="14.25" customHeight="1">
+    <row r="198" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B198" s="16"/>
       <c r="C198" s="16"/>
       <c r="D198" s="16"/>
@@ -4822,7 +4835,7 @@
       <c r="R198" s="16"/>
       <c r="S198" s="16"/>
     </row>
-    <row r="199" ht="14.25" customHeight="1">
+    <row r="199" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B199" s="16"/>
       <c r="C199" s="16"/>
       <c r="D199" s="16"/>
@@ -4842,7 +4855,7 @@
       <c r="R199" s="16"/>
       <c r="S199" s="16"/>
     </row>
-    <row r="200" ht="14.25" customHeight="1">
+    <row r="200" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B200" s="16"/>
       <c r="C200" s="16"/>
       <c r="D200" s="16"/>
@@ -4862,7 +4875,7 @@
       <c r="R200" s="16"/>
       <c r="S200" s="16"/>
     </row>
-    <row r="201" ht="14.25" customHeight="1">
+    <row r="201" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B201" s="16"/>
       <c r="C201" s="16"/>
       <c r="D201" s="16"/>
@@ -4882,7 +4895,7 @@
       <c r="R201" s="16"/>
       <c r="S201" s="16"/>
     </row>
-    <row r="202" ht="14.25" customHeight="1">
+    <row r="202" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B202" s="16"/>
       <c r="C202" s="16"/>
       <c r="D202" s="16"/>
@@ -4902,7 +4915,7 @@
       <c r="R202" s="16"/>
       <c r="S202" s="16"/>
     </row>
-    <row r="203" ht="14.25" customHeight="1">
+    <row r="203" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B203" s="16"/>
       <c r="C203" s="16"/>
       <c r="D203" s="16"/>
@@ -4922,7 +4935,7 @@
       <c r="R203" s="16"/>
       <c r="S203" s="16"/>
     </row>
-    <row r="204" ht="14.25" customHeight="1">
+    <row r="204" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B204" s="16"/>
       <c r="C204" s="16"/>
       <c r="D204" s="16"/>
@@ -4942,7 +4955,7 @@
       <c r="R204" s="16"/>
       <c r="S204" s="16"/>
     </row>
-    <row r="205" ht="14.25" customHeight="1">
+    <row r="205" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B205" s="16"/>
       <c r="C205" s="16"/>
       <c r="D205" s="16"/>
@@ -4962,7 +4975,7 @@
       <c r="R205" s="16"/>
       <c r="S205" s="16"/>
     </row>
-    <row r="206" ht="14.25" customHeight="1">
+    <row r="206" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B206" s="16"/>
       <c r="C206" s="16"/>
       <c r="D206" s="16"/>
@@ -4982,7 +4995,7 @@
       <c r="R206" s="16"/>
       <c r="S206" s="16"/>
     </row>
-    <row r="207" ht="14.25" customHeight="1">
+    <row r="207" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B207" s="16"/>
       <c r="C207" s="16"/>
       <c r="D207" s="16"/>
@@ -5002,7 +5015,7 @@
       <c r="R207" s="16"/>
       <c r="S207" s="16"/>
     </row>
-    <row r="208" ht="14.25" customHeight="1">
+    <row r="208" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B208" s="16"/>
       <c r="C208" s="16"/>
       <c r="D208" s="16"/>
@@ -5022,7 +5035,7 @@
       <c r="R208" s="16"/>
       <c r="S208" s="16"/>
     </row>
-    <row r="209" ht="14.25" customHeight="1">
+    <row r="209" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B209" s="16"/>
       <c r="C209" s="16"/>
       <c r="D209" s="16"/>
@@ -5042,7 +5055,7 @@
       <c r="R209" s="16"/>
       <c r="S209" s="16"/>
     </row>
-    <row r="210" ht="14.25" customHeight="1">
+    <row r="210" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B210" s="16"/>
       <c r="C210" s="16"/>
       <c r="D210" s="16"/>
@@ -5062,7 +5075,7 @@
       <c r="R210" s="16"/>
       <c r="S210" s="16"/>
     </row>
-    <row r="211" ht="14.25" customHeight="1">
+    <row r="211" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B211" s="16"/>
       <c r="C211" s="16"/>
       <c r="D211" s="16"/>
@@ -5082,7 +5095,7 @@
       <c r="R211" s="16"/>
       <c r="S211" s="16"/>
     </row>
-    <row r="212" ht="14.25" customHeight="1">
+    <row r="212" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B212" s="16"/>
       <c r="C212" s="16"/>
       <c r="D212" s="16"/>
@@ -5102,7 +5115,7 @@
       <c r="R212" s="16"/>
       <c r="S212" s="16"/>
     </row>
-    <row r="213" ht="14.25" customHeight="1">
+    <row r="213" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B213" s="16"/>
       <c r="C213" s="16"/>
       <c r="D213" s="16"/>
@@ -5122,7 +5135,7 @@
       <c r="R213" s="16"/>
       <c r="S213" s="16"/>
     </row>
-    <row r="214" ht="14.25" customHeight="1">
+    <row r="214" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B214" s="16"/>
       <c r="C214" s="16"/>
       <c r="D214" s="16"/>
@@ -5142,7 +5155,7 @@
       <c r="R214" s="16"/>
       <c r="S214" s="16"/>
     </row>
-    <row r="215" ht="14.25" customHeight="1">
+    <row r="215" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B215" s="16"/>
       <c r="C215" s="16"/>
       <c r="D215" s="16"/>
@@ -5162,7 +5175,7 @@
       <c r="R215" s="16"/>
       <c r="S215" s="16"/>
     </row>
-    <row r="216" ht="14.25" customHeight="1">
+    <row r="216" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B216" s="16"/>
       <c r="C216" s="16"/>
       <c r="D216" s="16"/>
@@ -5182,7 +5195,7 @@
       <c r="R216" s="16"/>
       <c r="S216" s="16"/>
     </row>
-    <row r="217" ht="14.25" customHeight="1">
+    <row r="217" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B217" s="16"/>
       <c r="C217" s="16"/>
       <c r="D217" s="16"/>
@@ -5202,7 +5215,7 @@
       <c r="R217" s="16"/>
       <c r="S217" s="16"/>
     </row>
-    <row r="218" ht="14.25" customHeight="1">
+    <row r="218" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B218" s="16"/>
       <c r="C218" s="16"/>
       <c r="D218" s="16"/>
@@ -5222,7 +5235,7 @@
       <c r="R218" s="16"/>
       <c r="S218" s="16"/>
     </row>
-    <row r="219" ht="14.25" customHeight="1">
+    <row r="219" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B219" s="16"/>
       <c r="C219" s="16"/>
       <c r="D219" s="16"/>
@@ -5242,7 +5255,7 @@
       <c r="R219" s="16"/>
       <c r="S219" s="16"/>
     </row>
-    <row r="220" ht="14.25" customHeight="1">
+    <row r="220" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B220" s="16"/>
       <c r="C220" s="16"/>
       <c r="D220" s="16"/>
@@ -5262,7 +5275,7 @@
       <c r="R220" s="16"/>
       <c r="S220" s="16"/>
     </row>
-    <row r="221" ht="14.25" customHeight="1">
+    <row r="221" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B221" s="16"/>
       <c r="C221" s="16"/>
       <c r="D221" s="16"/>
@@ -5282,7 +5295,7 @@
       <c r="R221" s="16"/>
       <c r="S221" s="16"/>
     </row>
-    <row r="222" ht="14.25" customHeight="1">
+    <row r="222" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B222" s="16"/>
       <c r="C222" s="16"/>
       <c r="D222" s="16"/>
@@ -5302,7 +5315,7 @@
       <c r="R222" s="16"/>
       <c r="S222" s="16"/>
     </row>
-    <row r="223" ht="14.25" customHeight="1">
+    <row r="223" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B223" s="16"/>
       <c r="C223" s="16"/>
       <c r="D223" s="16"/>
@@ -5322,7 +5335,7 @@
       <c r="R223" s="16"/>
       <c r="S223" s="16"/>
     </row>
-    <row r="224" ht="14.25" customHeight="1">
+    <row r="224" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B224" s="16"/>
       <c r="C224" s="16"/>
       <c r="D224" s="16"/>
@@ -5342,7 +5355,7 @@
       <c r="R224" s="16"/>
       <c r="S224" s="16"/>
     </row>
-    <row r="225" ht="14.25" customHeight="1">
+    <row r="225" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B225" s="16"/>
       <c r="C225" s="16"/>
       <c r="D225" s="16"/>
@@ -5362,7 +5375,7 @@
       <c r="R225" s="16"/>
       <c r="S225" s="16"/>
     </row>
-    <row r="226" ht="14.25" customHeight="1">
+    <row r="226" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B226" s="16"/>
       <c r="C226" s="16"/>
       <c r="D226" s="16"/>
@@ -5382,7 +5395,7 @@
       <c r="R226" s="16"/>
       <c r="S226" s="16"/>
     </row>
-    <row r="227" ht="14.25" customHeight="1">
+    <row r="227" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B227" s="16"/>
       <c r="C227" s="16"/>
       <c r="D227" s="16"/>
@@ -5402,7 +5415,7 @@
       <c r="R227" s="16"/>
       <c r="S227" s="16"/>
     </row>
-    <row r="228" ht="14.25" customHeight="1">
+    <row r="228" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B228" s="16"/>
       <c r="C228" s="16"/>
       <c r="D228" s="16"/>
@@ -5422,7 +5435,7 @@
       <c r="R228" s="16"/>
       <c r="S228" s="16"/>
     </row>
-    <row r="229" ht="14.25" customHeight="1">
+    <row r="229" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B229" s="16"/>
       <c r="C229" s="16"/>
       <c r="D229" s="16"/>
@@ -5442,7 +5455,7 @@
       <c r="R229" s="16"/>
       <c r="S229" s="16"/>
     </row>
-    <row r="230" ht="14.25" customHeight="1">
+    <row r="230" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B230" s="16"/>
       <c r="C230" s="16"/>
       <c r="D230" s="16"/>
@@ -5462,7 +5475,7 @@
       <c r="R230" s="16"/>
       <c r="S230" s="16"/>
     </row>
-    <row r="231" ht="14.25" customHeight="1">
+    <row r="231" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B231" s="16"/>
       <c r="C231" s="16"/>
       <c r="D231" s="16"/>
@@ -5482,7 +5495,7 @@
       <c r="R231" s="16"/>
       <c r="S231" s="16"/>
     </row>
-    <row r="232" ht="14.25" customHeight="1">
+    <row r="232" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B232" s="16"/>
       <c r="C232" s="16"/>
       <c r="D232" s="16"/>
@@ -5502,7 +5515,7 @@
       <c r="R232" s="16"/>
       <c r="S232" s="16"/>
     </row>
-    <row r="233" ht="14.25" customHeight="1">
+    <row r="233" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B233" s="16"/>
       <c r="C233" s="16"/>
       <c r="D233" s="16"/>
@@ -5522,7 +5535,7 @@
       <c r="R233" s="16"/>
       <c r="S233" s="16"/>
     </row>
-    <row r="234" ht="14.25" customHeight="1">
+    <row r="234" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B234" s="16"/>
       <c r="C234" s="16"/>
       <c r="D234" s="16"/>
@@ -5542,7 +5555,7 @@
       <c r="R234" s="16"/>
       <c r="S234" s="16"/>
     </row>
-    <row r="235" ht="14.25" customHeight="1">
+    <row r="235" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B235" s="16"/>
       <c r="C235" s="16"/>
       <c r="D235" s="16"/>
@@ -5562,7 +5575,7 @@
       <c r="R235" s="16"/>
       <c r="S235" s="16"/>
     </row>
-    <row r="236" ht="14.25" customHeight="1">
+    <row r="236" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B236" s="16"/>
       <c r="C236" s="16"/>
       <c r="D236" s="16"/>
@@ -5582,7 +5595,7 @@
       <c r="R236" s="16"/>
       <c r="S236" s="16"/>
     </row>
-    <row r="237" ht="14.25" customHeight="1">
+    <row r="237" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B237" s="16"/>
       <c r="C237" s="16"/>
       <c r="D237" s="16"/>
@@ -5602,7 +5615,7 @@
       <c r="R237" s="16"/>
       <c r="S237" s="16"/>
     </row>
-    <row r="238" ht="14.25" customHeight="1">
+    <row r="238" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B238" s="16"/>
       <c r="C238" s="16"/>
       <c r="D238" s="16"/>
@@ -5622,7 +5635,7 @@
       <c r="R238" s="16"/>
       <c r="S238" s="16"/>
     </row>
-    <row r="239" ht="14.25" customHeight="1">
+    <row r="239" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B239" s="16"/>
       <c r="C239" s="16"/>
       <c r="D239" s="16"/>
@@ -5642,7 +5655,7 @@
       <c r="R239" s="16"/>
       <c r="S239" s="16"/>
     </row>
-    <row r="240" ht="14.25" customHeight="1">
+    <row r="240" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B240" s="16"/>
       <c r="C240" s="16"/>
       <c r="D240" s="16"/>
@@ -5662,7 +5675,7 @@
       <c r="R240" s="16"/>
       <c r="S240" s="16"/>
     </row>
-    <row r="241" ht="14.25" customHeight="1">
+    <row r="241" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B241" s="16"/>
       <c r="C241" s="16"/>
       <c r="D241" s="16"/>
@@ -5682,7 +5695,7 @@
       <c r="R241" s="16"/>
       <c r="S241" s="16"/>
     </row>
-    <row r="242" ht="14.25" customHeight="1">
+    <row r="242" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B242" s="16"/>
       <c r="C242" s="16"/>
       <c r="D242" s="16"/>
@@ -5702,7 +5715,7 @@
       <c r="R242" s="16"/>
       <c r="S242" s="16"/>
     </row>
-    <row r="243" ht="14.25" customHeight="1">
+    <row r="243" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B243" s="16"/>
       <c r="C243" s="16"/>
       <c r="D243" s="16"/>
@@ -5722,7 +5735,7 @@
       <c r="R243" s="16"/>
       <c r="S243" s="16"/>
     </row>
-    <row r="244" ht="14.25" customHeight="1">
+    <row r="244" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B244" s="16"/>
       <c r="C244" s="16"/>
       <c r="D244" s="16"/>
@@ -5742,7 +5755,7 @@
       <c r="R244" s="16"/>
       <c r="S244" s="16"/>
     </row>
-    <row r="245" ht="14.25" customHeight="1">
+    <row r="245" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B245" s="16"/>
       <c r="C245" s="16"/>
       <c r="D245" s="16"/>
@@ -5762,7 +5775,7 @@
       <c r="R245" s="16"/>
       <c r="S245" s="16"/>
     </row>
-    <row r="246" ht="14.25" customHeight="1">
+    <row r="246" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B246" s="16"/>
       <c r="C246" s="16"/>
       <c r="D246" s="16"/>
@@ -5782,7 +5795,7 @@
       <c r="R246" s="16"/>
       <c r="S246" s="16"/>
     </row>
-    <row r="247" ht="14.25" customHeight="1">
+    <row r="247" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B247" s="16"/>
       <c r="C247" s="16"/>
       <c r="D247" s="16"/>
@@ -5802,7 +5815,7 @@
       <c r="R247" s="16"/>
       <c r="S247" s="16"/>
     </row>
-    <row r="248" ht="14.25" customHeight="1">
+    <row r="248" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B248" s="16"/>
       <c r="C248" s="16"/>
       <c r="D248" s="16"/>
@@ -5822,7 +5835,7 @@
       <c r="R248" s="16"/>
       <c r="S248" s="16"/>
     </row>
-    <row r="249" ht="14.25" customHeight="1">
+    <row r="249" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B249" s="16"/>
       <c r="C249" s="16"/>
       <c r="D249" s="16"/>
@@ -5842,7 +5855,7 @@
       <c r="R249" s="16"/>
       <c r="S249" s="16"/>
     </row>
-    <row r="250" ht="14.25" customHeight="1">
+    <row r="250" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B250" s="16"/>
       <c r="C250" s="16"/>
       <c r="D250" s="16"/>
@@ -5862,7 +5875,7 @@
       <c r="R250" s="16"/>
       <c r="S250" s="16"/>
     </row>
-    <row r="251" ht="14.25" customHeight="1">
+    <row r="251" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B251" s="16"/>
       <c r="C251" s="16"/>
       <c r="D251" s="16"/>
@@ -5882,7 +5895,7 @@
       <c r="R251" s="16"/>
       <c r="S251" s="16"/>
     </row>
-    <row r="252" ht="14.25" customHeight="1">
+    <row r="252" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B252" s="16"/>
       <c r="C252" s="16"/>
       <c r="D252" s="16"/>
@@ -5902,7 +5915,7 @@
       <c r="R252" s="16"/>
       <c r="S252" s="16"/>
     </row>
-    <row r="253" ht="14.25" customHeight="1">
+    <row r="253" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B253" s="16"/>
       <c r="C253" s="16"/>
       <c r="D253" s="16"/>
@@ -5922,7 +5935,7 @@
       <c r="R253" s="16"/>
       <c r="S253" s="16"/>
     </row>
-    <row r="254" ht="14.25" customHeight="1">
+    <row r="254" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B254" s="16"/>
       <c r="C254" s="16"/>
       <c r="D254" s="16"/>
@@ -5942,7 +5955,7 @@
       <c r="R254" s="16"/>
       <c r="S254" s="16"/>
     </row>
-    <row r="255" ht="14.25" customHeight="1">
+    <row r="255" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B255" s="16"/>
       <c r="C255" s="16"/>
       <c r="D255" s="16"/>
@@ -5962,7 +5975,7 @@
       <c r="R255" s="16"/>
       <c r="S255" s="16"/>
     </row>
-    <row r="256" ht="14.25" customHeight="1">
+    <row r="256" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B256" s="16"/>
       <c r="C256" s="16"/>
       <c r="D256" s="16"/>
@@ -5982,7 +5995,7 @@
       <c r="R256" s="16"/>
       <c r="S256" s="16"/>
     </row>
-    <row r="257" ht="14.25" customHeight="1">
+    <row r="257" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B257" s="16"/>
       <c r="C257" s="16"/>
       <c r="D257" s="16"/>
@@ -6002,7 +6015,7 @@
       <c r="R257" s="16"/>
       <c r="S257" s="16"/>
     </row>
-    <row r="258" ht="14.25" customHeight="1">
+    <row r="258" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B258" s="16"/>
       <c r="C258" s="16"/>
       <c r="D258" s="16"/>
@@ -6022,7 +6035,7 @@
       <c r="R258" s="16"/>
       <c r="S258" s="16"/>
     </row>
-    <row r="259" ht="14.25" customHeight="1">
+    <row r="259" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B259" s="16"/>
       <c r="C259" s="16"/>
       <c r="D259" s="16"/>
@@ -6042,7 +6055,7 @@
       <c r="R259" s="16"/>
       <c r="S259" s="16"/>
     </row>
-    <row r="260" ht="14.25" customHeight="1">
+    <row r="260" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B260" s="16"/>
       <c r="C260" s="16"/>
       <c r="D260" s="16"/>
@@ -6062,7 +6075,7 @@
       <c r="R260" s="16"/>
       <c r="S260" s="16"/>
     </row>
-    <row r="261" ht="14.25" customHeight="1">
+    <row r="261" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B261" s="16"/>
       <c r="C261" s="16"/>
       <c r="D261" s="16"/>
@@ -6082,7 +6095,7 @@
       <c r="R261" s="16"/>
       <c r="S261" s="16"/>
     </row>
-    <row r="262" ht="14.25" customHeight="1">
+    <row r="262" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B262" s="16"/>
       <c r="C262" s="16"/>
       <c r="D262" s="16"/>
@@ -6102,7 +6115,7 @@
       <c r="R262" s="16"/>
       <c r="S262" s="16"/>
     </row>
-    <row r="263" ht="14.25" customHeight="1">
+    <row r="263" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B263" s="16"/>
       <c r="C263" s="16"/>
       <c r="D263" s="16"/>
@@ -6122,7 +6135,7 @@
       <c r="R263" s="16"/>
       <c r="S263" s="16"/>
     </row>
-    <row r="264" ht="14.25" customHeight="1">
+    <row r="264" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B264" s="16"/>
       <c r="C264" s="16"/>
       <c r="D264" s="16"/>
@@ -6142,7 +6155,7 @@
       <c r="R264" s="16"/>
       <c r="S264" s="16"/>
     </row>
-    <row r="265" ht="14.25" customHeight="1">
+    <row r="265" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B265" s="16"/>
       <c r="C265" s="16"/>
       <c r="D265" s="16"/>
@@ -6162,7 +6175,7 @@
       <c r="R265" s="16"/>
       <c r="S265" s="16"/>
     </row>
-    <row r="266" ht="14.25" customHeight="1">
+    <row r="266" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B266" s="16"/>
       <c r="C266" s="16"/>
       <c r="D266" s="16"/>
@@ -6182,7 +6195,7 @@
       <c r="R266" s="16"/>
       <c r="S266" s="16"/>
     </row>
-    <row r="267" ht="14.25" customHeight="1">
+    <row r="267" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B267" s="16"/>
       <c r="C267" s="16"/>
       <c r="D267" s="16"/>
@@ -6202,7 +6215,7 @@
       <c r="R267" s="16"/>
       <c r="S267" s="16"/>
     </row>
-    <row r="268" ht="14.25" customHeight="1">
+    <row r="268" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B268" s="16"/>
       <c r="C268" s="16"/>
       <c r="D268" s="16"/>
@@ -6222,7 +6235,7 @@
       <c r="R268" s="16"/>
       <c r="S268" s="16"/>
     </row>
-    <row r="269" ht="14.25" customHeight="1">
+    <row r="269" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B269" s="16"/>
       <c r="C269" s="16"/>
       <c r="D269" s="16"/>
@@ -6242,7 +6255,7 @@
       <c r="R269" s="16"/>
       <c r="S269" s="16"/>
     </row>
-    <row r="270" ht="14.25" customHeight="1">
+    <row r="270" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B270" s="16"/>
       <c r="C270" s="16"/>
       <c r="D270" s="16"/>
@@ -6262,7 +6275,7 @@
       <c r="R270" s="16"/>
       <c r="S270" s="16"/>
     </row>
-    <row r="271" ht="14.25" customHeight="1">
+    <row r="271" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B271" s="16"/>
       <c r="C271" s="16"/>
       <c r="D271" s="16"/>
@@ -6282,7 +6295,7 @@
       <c r="R271" s="16"/>
       <c r="S271" s="16"/>
     </row>
-    <row r="272" ht="14.25" customHeight="1">
+    <row r="272" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B272" s="16"/>
       <c r="C272" s="16"/>
       <c r="D272" s="16"/>
@@ -6302,7 +6315,7 @@
       <c r="R272" s="16"/>
       <c r="S272" s="16"/>
     </row>
-    <row r="273" ht="14.25" customHeight="1">
+    <row r="273" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B273" s="16"/>
       <c r="C273" s="16"/>
       <c r="D273" s="16"/>
@@ -6322,7 +6335,7 @@
       <c r="R273" s="16"/>
       <c r="S273" s="16"/>
     </row>
-    <row r="274" ht="14.25" customHeight="1">
+    <row r="274" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B274" s="16"/>
       <c r="C274" s="16"/>
       <c r="D274" s="16"/>
@@ -6342,7 +6355,7 @@
       <c r="R274" s="16"/>
       <c r="S274" s="16"/>
     </row>
-    <row r="275" ht="14.25" customHeight="1">
+    <row r="275" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B275" s="16"/>
       <c r="C275" s="16"/>
       <c r="D275" s="16"/>
@@ -6362,7 +6375,7 @@
       <c r="R275" s="16"/>
       <c r="S275" s="16"/>
     </row>
-    <row r="276" ht="14.25" customHeight="1">
+    <row r="276" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B276" s="16"/>
       <c r="C276" s="16"/>
       <c r="D276" s="16"/>
@@ -6382,7 +6395,7 @@
       <c r="R276" s="16"/>
       <c r="S276" s="16"/>
     </row>
-    <row r="277" ht="14.25" customHeight="1">
+    <row r="277" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B277" s="16"/>
       <c r="C277" s="16"/>
       <c r="D277" s="16"/>
@@ -6402,7 +6415,7 @@
       <c r="R277" s="16"/>
       <c r="S277" s="16"/>
     </row>
-    <row r="278" ht="14.25" customHeight="1">
+    <row r="278" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B278" s="16"/>
       <c r="C278" s="16"/>
       <c r="D278" s="16"/>
@@ -6422,7 +6435,7 @@
       <c r="R278" s="16"/>
       <c r="S278" s="16"/>
     </row>
-    <row r="279" ht="14.25" customHeight="1">
+    <row r="279" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B279" s="16"/>
       <c r="C279" s="16"/>
       <c r="D279" s="16"/>
@@ -6442,7 +6455,7 @@
       <c r="R279" s="16"/>
       <c r="S279" s="16"/>
     </row>
-    <row r="280" ht="14.25" customHeight="1">
+    <row r="280" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B280" s="16"/>
       <c r="C280" s="16"/>
       <c r="D280" s="16"/>
@@ -6462,7 +6475,7 @@
       <c r="R280" s="16"/>
       <c r="S280" s="16"/>
     </row>
-    <row r="281" ht="14.25" customHeight="1">
+    <row r="281" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B281" s="16"/>
       <c r="C281" s="16"/>
       <c r="D281" s="16"/>
@@ -6482,7 +6495,7 @@
       <c r="R281" s="16"/>
       <c r="S281" s="16"/>
     </row>
-    <row r="282" ht="14.25" customHeight="1">
+    <row r="282" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B282" s="16"/>
       <c r="C282" s="16"/>
       <c r="D282" s="16"/>
@@ -6502,7 +6515,7 @@
       <c r="R282" s="16"/>
       <c r="S282" s="16"/>
     </row>
-    <row r="283" ht="14.25" customHeight="1">
+    <row r="283" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B283" s="16"/>
       <c r="C283" s="16"/>
       <c r="D283" s="16"/>
@@ -6522,7 +6535,7 @@
       <c r="R283" s="16"/>
       <c r="S283" s="16"/>
     </row>
-    <row r="284" ht="14.25" customHeight="1">
+    <row r="284" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B284" s="16"/>
       <c r="C284" s="16"/>
       <c r="D284" s="16"/>
@@ -6542,7 +6555,7 @@
       <c r="R284" s="16"/>
       <c r="S284" s="16"/>
     </row>
-    <row r="285" ht="14.25" customHeight="1">
+    <row r="285" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B285" s="16"/>
       <c r="C285" s="16"/>
       <c r="D285" s="16"/>
@@ -6562,7 +6575,7 @@
       <c r="R285" s="16"/>
       <c r="S285" s="16"/>
     </row>
-    <row r="286" ht="14.25" customHeight="1">
+    <row r="286" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B286" s="16"/>
       <c r="C286" s="16"/>
       <c r="D286" s="16"/>
@@ -6582,7 +6595,7 @@
       <c r="R286" s="16"/>
       <c r="S286" s="16"/>
     </row>
-    <row r="287" ht="14.25" customHeight="1">
+    <row r="287" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B287" s="16"/>
       <c r="C287" s="16"/>
       <c r="D287" s="16"/>
@@ -6602,7 +6615,7 @@
       <c r="R287" s="16"/>
       <c r="S287" s="16"/>
     </row>
-    <row r="288" ht="14.25" customHeight="1">
+    <row r="288" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B288" s="16"/>
       <c r="C288" s="16"/>
       <c r="D288" s="16"/>
@@ -6622,7 +6635,7 @@
       <c r="R288" s="16"/>
       <c r="S288" s="16"/>
     </row>
-    <row r="289" ht="14.25" customHeight="1">
+    <row r="289" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B289" s="16"/>
       <c r="C289" s="16"/>
       <c r="D289" s="16"/>
@@ -6642,7 +6655,7 @@
       <c r="R289" s="16"/>
       <c r="S289" s="16"/>
     </row>
-    <row r="290" ht="14.25" customHeight="1">
+    <row r="290" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B290" s="16"/>
       <c r="C290" s="16"/>
       <c r="D290" s="16"/>
@@ -6662,7 +6675,7 @@
       <c r="R290" s="16"/>
       <c r="S290" s="16"/>
     </row>
-    <row r="291" ht="14.25" customHeight="1">
+    <row r="291" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B291" s="16"/>
       <c r="C291" s="16"/>
       <c r="D291" s="16"/>
@@ -6682,7 +6695,7 @@
       <c r="R291" s="16"/>
       <c r="S291" s="16"/>
     </row>
-    <row r="292" ht="14.25" customHeight="1">
+    <row r="292" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B292" s="16"/>
       <c r="C292" s="16"/>
       <c r="D292" s="16"/>
@@ -6702,7 +6715,7 @@
       <c r="R292" s="16"/>
       <c r="S292" s="16"/>
     </row>
-    <row r="293" ht="14.25" customHeight="1">
+    <row r="293" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B293" s="16"/>
       <c r="C293" s="16"/>
       <c r="D293" s="16"/>
@@ -6722,7 +6735,7 @@
       <c r="R293" s="16"/>
       <c r="S293" s="16"/>
     </row>
-    <row r="294" ht="14.25" customHeight="1">
+    <row r="294" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B294" s="16"/>
       <c r="C294" s="16"/>
       <c r="D294" s="16"/>
@@ -6742,7 +6755,7 @@
       <c r="R294" s="16"/>
       <c r="S294" s="16"/>
     </row>
-    <row r="295" ht="14.25" customHeight="1">
+    <row r="295" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B295" s="16"/>
       <c r="C295" s="16"/>
       <c r="D295" s="16"/>
@@ -6762,7 +6775,7 @@
       <c r="R295" s="16"/>
       <c r="S295" s="16"/>
     </row>
-    <row r="296" ht="14.25" customHeight="1">
+    <row r="296" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B296" s="16"/>
       <c r="C296" s="16"/>
       <c r="D296" s="16"/>
@@ -6782,7 +6795,7 @@
       <c r="R296" s="16"/>
       <c r="S296" s="16"/>
     </row>
-    <row r="297" ht="14.25" customHeight="1">
+    <row r="297" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B297" s="16"/>
       <c r="C297" s="16"/>
       <c r="D297" s="16"/>
@@ -6802,7 +6815,7 @@
       <c r="R297" s="16"/>
       <c r="S297" s="16"/>
     </row>
-    <row r="298" ht="14.25" customHeight="1">
+    <row r="298" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B298" s="16"/>
       <c r="C298" s="16"/>
       <c r="D298" s="16"/>
@@ -6822,7 +6835,7 @@
       <c r="R298" s="16"/>
       <c r="S298" s="16"/>
     </row>
-    <row r="299" ht="14.25" customHeight="1">
+    <row r="299" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B299" s="16"/>
       <c r="C299" s="16"/>
       <c r="D299" s="16"/>
@@ -6842,7 +6855,7 @@
       <c r="R299" s="16"/>
       <c r="S299" s="16"/>
     </row>
-    <row r="300" ht="14.25" customHeight="1">
+    <row r="300" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B300" s="16"/>
       <c r="C300" s="16"/>
       <c r="D300" s="16"/>
@@ -6862,7 +6875,7 @@
       <c r="R300" s="16"/>
       <c r="S300" s="16"/>
     </row>
-    <row r="301" ht="14.25" customHeight="1">
+    <row r="301" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B301" s="16"/>
       <c r="C301" s="16"/>
       <c r="D301" s="16"/>
@@ -6882,7 +6895,7 @@
       <c r="R301" s="16"/>
       <c r="S301" s="16"/>
     </row>
-    <row r="302" ht="14.25" customHeight="1">
+    <row r="302" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B302" s="16"/>
       <c r="C302" s="16"/>
       <c r="D302" s="16"/>
@@ -6902,7 +6915,7 @@
       <c r="R302" s="16"/>
       <c r="S302" s="16"/>
     </row>
-    <row r="303" ht="14.25" customHeight="1">
+    <row r="303" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B303" s="16"/>
       <c r="C303" s="16"/>
       <c r="D303" s="16"/>
@@ -6922,7 +6935,7 @@
       <c r="R303" s="16"/>
       <c r="S303" s="16"/>
     </row>
-    <row r="304" ht="14.25" customHeight="1">
+    <row r="304" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B304" s="16"/>
       <c r="C304" s="16"/>
       <c r="D304" s="16"/>
@@ -6942,7 +6955,7 @@
       <c r="R304" s="16"/>
       <c r="S304" s="16"/>
     </row>
-    <row r="305" ht="14.25" customHeight="1">
+    <row r="305" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B305" s="16"/>
       <c r="C305" s="16"/>
       <c r="D305" s="16"/>
@@ -6962,7 +6975,7 @@
       <c r="R305" s="16"/>
       <c r="S305" s="16"/>
     </row>
-    <row r="306" ht="14.25" customHeight="1">
+    <row r="306" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B306" s="16"/>
       <c r="C306" s="16"/>
       <c r="D306" s="16"/>
@@ -6982,7 +6995,7 @@
       <c r="R306" s="16"/>
       <c r="S306" s="16"/>
     </row>
-    <row r="307" ht="14.25" customHeight="1">
+    <row r="307" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B307" s="16"/>
       <c r="C307" s="16"/>
       <c r="D307" s="16"/>
@@ -7002,7 +7015,7 @@
       <c r="R307" s="16"/>
       <c r="S307" s="16"/>
     </row>
-    <row r="308" ht="14.25" customHeight="1">
+    <row r="308" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B308" s="16"/>
       <c r="C308" s="16"/>
       <c r="D308" s="16"/>
@@ -7022,7 +7035,7 @@
       <c r="R308" s="16"/>
       <c r="S308" s="16"/>
     </row>
-    <row r="309" ht="14.25" customHeight="1">
+    <row r="309" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B309" s="16"/>
       <c r="C309" s="16"/>
       <c r="D309" s="16"/>
@@ -7042,7 +7055,7 @@
       <c r="R309" s="16"/>
       <c r="S309" s="16"/>
     </row>
-    <row r="310" ht="14.25" customHeight="1">
+    <row r="310" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B310" s="16"/>
       <c r="C310" s="16"/>
       <c r="D310" s="16"/>
@@ -7062,7 +7075,7 @@
       <c r="R310" s="16"/>
       <c r="S310" s="16"/>
     </row>
-    <row r="311" ht="14.25" customHeight="1">
+    <row r="311" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B311" s="16"/>
       <c r="C311" s="16"/>
       <c r="D311" s="16"/>
@@ -7082,7 +7095,7 @@
       <c r="R311" s="16"/>
       <c r="S311" s="16"/>
     </row>
-    <row r="312" ht="14.25" customHeight="1">
+    <row r="312" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B312" s="16"/>
       <c r="C312" s="16"/>
       <c r="D312" s="16"/>
@@ -7102,7 +7115,7 @@
       <c r="R312" s="16"/>
       <c r="S312" s="16"/>
     </row>
-    <row r="313" ht="14.25" customHeight="1">
+    <row r="313" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B313" s="16"/>
       <c r="C313" s="16"/>
       <c r="D313" s="16"/>
@@ -7122,7 +7135,7 @@
       <c r="R313" s="16"/>
       <c r="S313" s="16"/>
     </row>
-    <row r="314" ht="14.25" customHeight="1">
+    <row r="314" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B314" s="16"/>
       <c r="C314" s="16"/>
       <c r="D314" s="16"/>
@@ -7142,7 +7155,7 @@
       <c r="R314" s="16"/>
       <c r="S314" s="16"/>
     </row>
-    <row r="315" ht="14.25" customHeight="1">
+    <row r="315" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B315" s="16"/>
       <c r="C315" s="16"/>
       <c r="D315" s="16"/>
@@ -7162,7 +7175,7 @@
       <c r="R315" s="16"/>
       <c r="S315" s="16"/>
     </row>
-    <row r="316" ht="14.25" customHeight="1">
+    <row r="316" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B316" s="16"/>
       <c r="C316" s="16"/>
       <c r="D316" s="16"/>
@@ -7182,7 +7195,7 @@
       <c r="R316" s="16"/>
       <c r="S316" s="16"/>
     </row>
-    <row r="317" ht="14.25" customHeight="1">
+    <row r="317" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B317" s="16"/>
       <c r="C317" s="16"/>
       <c r="D317" s="16"/>
@@ -7202,7 +7215,7 @@
       <c r="R317" s="16"/>
       <c r="S317" s="16"/>
     </row>
-    <row r="318" ht="14.25" customHeight="1">
+    <row r="318" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B318" s="16"/>
       <c r="C318" s="16"/>
       <c r="D318" s="16"/>
@@ -7222,7 +7235,7 @@
       <c r="R318" s="16"/>
       <c r="S318" s="16"/>
     </row>
-    <row r="319" ht="14.25" customHeight="1">
+    <row r="319" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B319" s="16"/>
       <c r="C319" s="16"/>
       <c r="D319" s="16"/>
@@ -7242,7 +7255,7 @@
       <c r="R319" s="16"/>
       <c r="S319" s="16"/>
     </row>
-    <row r="320" ht="14.25" customHeight="1">
+    <row r="320" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B320" s="16"/>
       <c r="C320" s="16"/>
       <c r="D320" s="16"/>
@@ -7262,7 +7275,7 @@
       <c r="R320" s="16"/>
       <c r="S320" s="16"/>
     </row>
-    <row r="321" ht="14.25" customHeight="1">
+    <row r="321" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B321" s="16"/>
       <c r="C321" s="16"/>
       <c r="D321" s="16"/>
@@ -7282,7 +7295,7 @@
       <c r="R321" s="16"/>
       <c r="S321" s="16"/>
     </row>
-    <row r="322" ht="14.25" customHeight="1">
+    <row r="322" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B322" s="16"/>
       <c r="C322" s="16"/>
       <c r="D322" s="16"/>
@@ -7302,7 +7315,7 @@
       <c r="R322" s="16"/>
       <c r="S322" s="16"/>
     </row>
-    <row r="323" ht="14.25" customHeight="1">
+    <row r="323" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B323" s="16"/>
       <c r="C323" s="16"/>
       <c r="D323" s="16"/>
@@ -7322,7 +7335,7 @@
       <c r="R323" s="16"/>
       <c r="S323" s="16"/>
     </row>
-    <row r="324" ht="14.25" customHeight="1">
+    <row r="324" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B324" s="16"/>
       <c r="C324" s="16"/>
       <c r="D324" s="16"/>
@@ -7342,7 +7355,7 @@
       <c r="R324" s="16"/>
       <c r="S324" s="16"/>
     </row>
-    <row r="325" ht="14.25" customHeight="1">
+    <row r="325" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B325" s="16"/>
       <c r="C325" s="16"/>
       <c r="D325" s="16"/>
@@ -7362,7 +7375,7 @@
       <c r="R325" s="16"/>
       <c r="S325" s="16"/>
     </row>
-    <row r="326" ht="14.25" customHeight="1">
+    <row r="326" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B326" s="16"/>
       <c r="C326" s="16"/>
       <c r="D326" s="16"/>
@@ -7382,7 +7395,7 @@
       <c r="R326" s="16"/>
       <c r="S326" s="16"/>
     </row>
-    <row r="327" ht="14.25" customHeight="1">
+    <row r="327" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B327" s="16"/>
       <c r="C327" s="16"/>
       <c r="D327" s="16"/>
@@ -7402,7 +7415,7 @@
       <c r="R327" s="16"/>
       <c r="S327" s="16"/>
     </row>
-    <row r="328" ht="14.25" customHeight="1">
+    <row r="328" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B328" s="16"/>
       <c r="C328" s="16"/>
       <c r="D328" s="16"/>
@@ -7422,7 +7435,7 @@
       <c r="R328" s="16"/>
       <c r="S328" s="16"/>
     </row>
-    <row r="329" ht="14.25" customHeight="1">
+    <row r="329" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B329" s="16"/>
       <c r="C329" s="16"/>
       <c r="D329" s="16"/>
@@ -7442,7 +7455,7 @@
       <c r="R329" s="16"/>
       <c r="S329" s="16"/>
     </row>
-    <row r="330" ht="14.25" customHeight="1">
+    <row r="330" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B330" s="16"/>
       <c r="C330" s="16"/>
       <c r="D330" s="16"/>
@@ -7462,7 +7475,7 @@
       <c r="R330" s="16"/>
       <c r="S330" s="16"/>
     </row>
-    <row r="331" ht="14.25" customHeight="1">
+    <row r="331" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B331" s="16"/>
       <c r="C331" s="16"/>
       <c r="D331" s="16"/>
@@ -7482,7 +7495,7 @@
       <c r="R331" s="16"/>
       <c r="S331" s="16"/>
     </row>
-    <row r="332" ht="14.25" customHeight="1">
+    <row r="332" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B332" s="16"/>
       <c r="C332" s="16"/>
       <c r="D332" s="16"/>
@@ -7502,7 +7515,7 @@
       <c r="R332" s="16"/>
       <c r="S332" s="16"/>
     </row>
-    <row r="333" ht="14.25" customHeight="1">
+    <row r="333" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B333" s="16"/>
       <c r="C333" s="16"/>
       <c r="D333" s="16"/>
@@ -7522,7 +7535,7 @@
       <c r="R333" s="16"/>
       <c r="S333" s="16"/>
     </row>
-    <row r="334" ht="14.25" customHeight="1">
+    <row r="334" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B334" s="16"/>
       <c r="C334" s="16"/>
       <c r="D334" s="16"/>
@@ -7542,7 +7555,7 @@
       <c r="R334" s="16"/>
       <c r="S334" s="16"/>
     </row>
-    <row r="335" ht="14.25" customHeight="1">
+    <row r="335" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B335" s="16"/>
       <c r="C335" s="16"/>
       <c r="D335" s="16"/>
@@ -7562,7 +7575,7 @@
       <c r="R335" s="16"/>
       <c r="S335" s="16"/>
     </row>
-    <row r="336" ht="14.25" customHeight="1">
+    <row r="336" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B336" s="16"/>
       <c r="C336" s="16"/>
       <c r="D336" s="16"/>
@@ -7582,7 +7595,7 @@
       <c r="R336" s="16"/>
       <c r="S336" s="16"/>
     </row>
-    <row r="337" ht="14.25" customHeight="1">
+    <row r="337" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B337" s="16"/>
       <c r="C337" s="16"/>
       <c r="D337" s="16"/>
@@ -7602,7 +7615,7 @@
       <c r="R337" s="16"/>
       <c r="S337" s="16"/>
     </row>
-    <row r="338" ht="14.25" customHeight="1">
+    <row r="338" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B338" s="16"/>
       <c r="C338" s="16"/>
       <c r="D338" s="16"/>
@@ -7622,7 +7635,7 @@
       <c r="R338" s="16"/>
       <c r="S338" s="16"/>
     </row>
-    <row r="339" ht="14.25" customHeight="1">
+    <row r="339" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B339" s="16"/>
       <c r="C339" s="16"/>
       <c r="D339" s="16"/>
@@ -7642,7 +7655,7 @@
       <c r="R339" s="16"/>
       <c r="S339" s="16"/>
     </row>
-    <row r="340" ht="14.25" customHeight="1">
+    <row r="340" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B340" s="16"/>
       <c r="C340" s="16"/>
       <c r="D340" s="16"/>
@@ -7662,7 +7675,7 @@
       <c r="R340" s="16"/>
       <c r="S340" s="16"/>
     </row>
-    <row r="341" ht="14.25" customHeight="1">
+    <row r="341" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B341" s="16"/>
       <c r="C341" s="16"/>
       <c r="D341" s="16"/>
@@ -7682,7 +7695,7 @@
       <c r="R341" s="16"/>
       <c r="S341" s="16"/>
     </row>
-    <row r="342" ht="14.25" customHeight="1">
+    <row r="342" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B342" s="16"/>
       <c r="C342" s="16"/>
       <c r="D342" s="16"/>
@@ -7702,7 +7715,7 @@
       <c r="R342" s="16"/>
       <c r="S342" s="16"/>
     </row>
-    <row r="343" ht="14.25" customHeight="1">
+    <row r="343" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B343" s="16"/>
       <c r="C343" s="16"/>
       <c r="D343" s="16"/>
@@ -7722,7 +7735,7 @@
       <c r="R343" s="16"/>
       <c r="S343" s="16"/>
     </row>
-    <row r="344" ht="14.25" customHeight="1">
+    <row r="344" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B344" s="16"/>
       <c r="C344" s="16"/>
       <c r="D344" s="16"/>
@@ -7742,7 +7755,7 @@
       <c r="R344" s="16"/>
       <c r="S344" s="16"/>
     </row>
-    <row r="345" ht="14.25" customHeight="1">
+    <row r="345" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B345" s="16"/>
       <c r="C345" s="16"/>
       <c r="D345" s="16"/>
@@ -7762,7 +7775,7 @@
       <c r="R345" s="16"/>
       <c r="S345" s="16"/>
     </row>
-    <row r="346" ht="14.25" customHeight="1">
+    <row r="346" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B346" s="16"/>
       <c r="C346" s="16"/>
       <c r="D346" s="16"/>
@@ -7782,7 +7795,7 @@
       <c r="R346" s="16"/>
       <c r="S346" s="16"/>
     </row>
-    <row r="347" ht="14.25" customHeight="1">
+    <row r="347" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B347" s="16"/>
       <c r="C347" s="16"/>
       <c r="D347" s="16"/>
@@ -7802,7 +7815,7 @@
       <c r="R347" s="16"/>
       <c r="S347" s="16"/>
     </row>
-    <row r="348" ht="14.25" customHeight="1">
+    <row r="348" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B348" s="16"/>
       <c r="C348" s="16"/>
       <c r="D348" s="16"/>
@@ -7822,7 +7835,7 @@
       <c r="R348" s="16"/>
       <c r="S348" s="16"/>
     </row>
-    <row r="349" ht="14.25" customHeight="1">
+    <row r="349" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B349" s="16"/>
       <c r="C349" s="16"/>
       <c r="D349" s="16"/>
@@ -7842,7 +7855,7 @@
       <c r="R349" s="16"/>
       <c r="S349" s="16"/>
     </row>
-    <row r="350" ht="14.25" customHeight="1">
+    <row r="350" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B350" s="16"/>
       <c r="C350" s="16"/>
       <c r="D350" s="16"/>
@@ -7862,7 +7875,7 @@
       <c r="R350" s="16"/>
       <c r="S350" s="16"/>
     </row>
-    <row r="351" ht="14.25" customHeight="1">
+    <row r="351" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B351" s="16"/>
       <c r="C351" s="16"/>
       <c r="D351" s="16"/>
@@ -7882,7 +7895,7 @@
       <c r="R351" s="16"/>
       <c r="S351" s="16"/>
     </row>
-    <row r="352" ht="14.25" customHeight="1">
+    <row r="352" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B352" s="16"/>
       <c r="C352" s="16"/>
       <c r="D352" s="16"/>
@@ -7902,7 +7915,7 @@
       <c r="R352" s="16"/>
       <c r="S352" s="16"/>
     </row>
-    <row r="353" ht="14.25" customHeight="1">
+    <row r="353" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B353" s="16"/>
       <c r="C353" s="16"/>
       <c r="D353" s="16"/>
@@ -7922,7 +7935,7 @@
       <c r="R353" s="16"/>
       <c r="S353" s="16"/>
     </row>
-    <row r="354" ht="14.25" customHeight="1">
+    <row r="354" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B354" s="16"/>
       <c r="C354" s="16"/>
       <c r="D354" s="16"/>
@@ -7942,7 +7955,7 @@
       <c r="R354" s="16"/>
       <c r="S354" s="16"/>
     </row>
-    <row r="355" ht="14.25" customHeight="1">
+    <row r="355" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B355" s="16"/>
       <c r="C355" s="16"/>
       <c r="D355" s="16"/>
@@ -7962,7 +7975,7 @@
       <c r="R355" s="16"/>
       <c r="S355" s="16"/>
     </row>
-    <row r="356" ht="14.25" customHeight="1">
+    <row r="356" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B356" s="16"/>
       <c r="C356" s="16"/>
       <c r="D356" s="16"/>
@@ -7982,7 +7995,7 @@
       <c r="R356" s="16"/>
       <c r="S356" s="16"/>
     </row>
-    <row r="357" ht="14.25" customHeight="1">
+    <row r="357" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B357" s="16"/>
       <c r="C357" s="16"/>
       <c r="D357" s="16"/>
@@ -8002,7 +8015,7 @@
       <c r="R357" s="16"/>
       <c r="S357" s="16"/>
     </row>
-    <row r="358" ht="14.25" customHeight="1">
+    <row r="358" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B358" s="16"/>
       <c r="C358" s="16"/>
       <c r="D358" s="16"/>
@@ -8022,7 +8035,7 @@
       <c r="R358" s="16"/>
       <c r="S358" s="16"/>
     </row>
-    <row r="359" ht="14.25" customHeight="1">
+    <row r="359" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B359" s="16"/>
       <c r="C359" s="16"/>
       <c r="D359" s="16"/>
@@ -8042,7 +8055,7 @@
       <c r="R359" s="16"/>
       <c r="S359" s="16"/>
     </row>
-    <row r="360" ht="14.25" customHeight="1">
+    <row r="360" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B360" s="16"/>
       <c r="C360" s="16"/>
       <c r="D360" s="16"/>
@@ -8062,7 +8075,7 @@
       <c r="R360" s="16"/>
       <c r="S360" s="16"/>
     </row>
-    <row r="361" ht="14.25" customHeight="1">
+    <row r="361" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B361" s="16"/>
       <c r="C361" s="16"/>
       <c r="D361" s="16"/>
@@ -8082,7 +8095,7 @@
       <c r="R361" s="16"/>
       <c r="S361" s="16"/>
     </row>
-    <row r="362" ht="14.25" customHeight="1">
+    <row r="362" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B362" s="16"/>
       <c r="C362" s="16"/>
       <c r="D362" s="16"/>
@@ -8102,7 +8115,7 @@
       <c r="R362" s="16"/>
       <c r="S362" s="16"/>
     </row>
-    <row r="363" ht="14.25" customHeight="1">
+    <row r="363" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B363" s="16"/>
       <c r="C363" s="16"/>
       <c r="D363" s="16"/>
@@ -8122,7 +8135,7 @@
       <c r="R363" s="16"/>
       <c r="S363" s="16"/>
     </row>
-    <row r="364" ht="14.25" customHeight="1">
+    <row r="364" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B364" s="16"/>
       <c r="C364" s="16"/>
       <c r="D364" s="16"/>
@@ -8142,7 +8155,7 @@
       <c r="R364" s="16"/>
       <c r="S364" s="16"/>
     </row>
-    <row r="365" ht="14.25" customHeight="1">
+    <row r="365" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B365" s="16"/>
       <c r="C365" s="16"/>
       <c r="D365" s="16"/>
@@ -8162,7 +8175,7 @@
       <c r="R365" s="16"/>
       <c r="S365" s="16"/>
     </row>
-    <row r="366" ht="14.25" customHeight="1">
+    <row r="366" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B366" s="16"/>
       <c r="C366" s="16"/>
       <c r="D366" s="16"/>
@@ -8182,7 +8195,7 @@
       <c r="R366" s="16"/>
       <c r="S366" s="16"/>
     </row>
-    <row r="367" ht="14.25" customHeight="1">
+    <row r="367" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B367" s="16"/>
       <c r="C367" s="16"/>
       <c r="D367" s="16"/>
@@ -8202,7 +8215,7 @@
       <c r="R367" s="16"/>
       <c r="S367" s="16"/>
     </row>
-    <row r="368" ht="14.25" customHeight="1">
+    <row r="368" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B368" s="16"/>
       <c r="C368" s="16"/>
       <c r="D368" s="16"/>
@@ -8222,7 +8235,7 @@
       <c r="R368" s="16"/>
       <c r="S368" s="16"/>
     </row>
-    <row r="369" ht="14.25" customHeight="1">
+    <row r="369" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B369" s="16"/>
       <c r="C369" s="16"/>
       <c r="D369" s="16"/>
@@ -8242,7 +8255,7 @@
       <c r="R369" s="16"/>
       <c r="S369" s="16"/>
     </row>
-    <row r="370" ht="14.25" customHeight="1">
+    <row r="370" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B370" s="16"/>
       <c r="C370" s="16"/>
       <c r="D370" s="16"/>
@@ -8262,7 +8275,7 @@
       <c r="R370" s="16"/>
       <c r="S370" s="16"/>
     </row>
-    <row r="371" ht="14.25" customHeight="1">
+    <row r="371" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B371" s="16"/>
       <c r="C371" s="16"/>
       <c r="D371" s="16"/>
@@ -8282,7 +8295,7 @@
       <c r="R371" s="16"/>
       <c r="S371" s="16"/>
     </row>
-    <row r="372" ht="14.25" customHeight="1">
+    <row r="372" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B372" s="16"/>
       <c r="C372" s="16"/>
       <c r="D372" s="16"/>
@@ -8302,7 +8315,7 @@
       <c r="R372" s="16"/>
       <c r="S372" s="16"/>
     </row>
-    <row r="373" ht="14.25" customHeight="1">
+    <row r="373" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B373" s="16"/>
       <c r="C373" s="16"/>
       <c r="D373" s="16"/>
@@ -8322,7 +8335,7 @@
       <c r="R373" s="16"/>
       <c r="S373" s="16"/>
     </row>
-    <row r="374" ht="14.25" customHeight="1">
+    <row r="374" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B374" s="16"/>
       <c r="C374" s="16"/>
       <c r="D374" s="16"/>
@@ -8342,7 +8355,7 @@
       <c r="R374" s="16"/>
       <c r="S374" s="16"/>
     </row>
-    <row r="375" ht="14.25" customHeight="1">
+    <row r="375" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B375" s="16"/>
       <c r="C375" s="16"/>
       <c r="D375" s="16"/>
@@ -8362,7 +8375,7 @@
       <c r="R375" s="16"/>
       <c r="S375" s="16"/>
     </row>
-    <row r="376" ht="14.25" customHeight="1">
+    <row r="376" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B376" s="16"/>
       <c r="C376" s="16"/>
       <c r="D376" s="16"/>
@@ -8382,7 +8395,7 @@
       <c r="R376" s="16"/>
       <c r="S376" s="16"/>
     </row>
-    <row r="377" ht="14.25" customHeight="1">
+    <row r="377" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B377" s="16"/>
       <c r="C377" s="16"/>
       <c r="D377" s="16"/>
@@ -8402,7 +8415,7 @@
       <c r="R377" s="16"/>
       <c r="S377" s="16"/>
     </row>
-    <row r="378" ht="14.25" customHeight="1">
+    <row r="378" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B378" s="16"/>
       <c r="C378" s="16"/>
       <c r="D378" s="16"/>
@@ -8422,7 +8435,7 @@
       <c r="R378" s="16"/>
       <c r="S378" s="16"/>
     </row>
-    <row r="379" ht="14.25" customHeight="1">
+    <row r="379" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B379" s="16"/>
       <c r="C379" s="16"/>
       <c r="D379" s="16"/>
@@ -8442,7 +8455,7 @@
       <c r="R379" s="16"/>
       <c r="S379" s="16"/>
     </row>
-    <row r="380" ht="14.25" customHeight="1">
+    <row r="380" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B380" s="16"/>
       <c r="C380" s="16"/>
       <c r="D380" s="16"/>
@@ -8462,7 +8475,7 @@
       <c r="R380" s="16"/>
       <c r="S380" s="16"/>
     </row>
-    <row r="381" ht="14.25" customHeight="1">
+    <row r="381" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B381" s="16"/>
       <c r="C381" s="16"/>
       <c r="D381" s="16"/>
@@ -8482,7 +8495,7 @@
       <c r="R381" s="16"/>
       <c r="S381" s="16"/>
     </row>
-    <row r="382" ht="14.25" customHeight="1">
+    <row r="382" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B382" s="16"/>
       <c r="C382" s="16"/>
       <c r="D382" s="16"/>
@@ -8502,7 +8515,7 @@
       <c r="R382" s="16"/>
       <c r="S382" s="16"/>
     </row>
-    <row r="383" ht="14.25" customHeight="1">
+    <row r="383" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B383" s="16"/>
       <c r="C383" s="16"/>
       <c r="D383" s="16"/>
@@ -8522,7 +8535,7 @@
       <c r="R383" s="16"/>
       <c r="S383" s="16"/>
     </row>
-    <row r="384" ht="14.25" customHeight="1">
+    <row r="384" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B384" s="16"/>
       <c r="C384" s="16"/>
       <c r="D384" s="16"/>
@@ -8542,7 +8555,7 @@
       <c r="R384" s="16"/>
       <c r="S384" s="16"/>
     </row>
-    <row r="385" ht="14.25" customHeight="1">
+    <row r="385" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B385" s="16"/>
       <c r="C385" s="16"/>
       <c r="D385" s="16"/>
@@ -8562,7 +8575,7 @@
       <c r="R385" s="16"/>
       <c r="S385" s="16"/>
     </row>
-    <row r="386" ht="14.25" customHeight="1">
+    <row r="386" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B386" s="16"/>
       <c r="C386" s="16"/>
       <c r="D386" s="16"/>
@@ -8582,7 +8595,7 @@
       <c r="R386" s="16"/>
       <c r="S386" s="16"/>
     </row>
-    <row r="387" ht="14.25" customHeight="1">
+    <row r="387" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B387" s="16"/>
       <c r="C387" s="16"/>
       <c r="D387" s="16"/>
@@ -8602,7 +8615,7 @@
       <c r="R387" s="16"/>
       <c r="S387" s="16"/>
     </row>
-    <row r="388" ht="14.25" customHeight="1">
+    <row r="388" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B388" s="16"/>
       <c r="C388" s="16"/>
       <c r="D388" s="16"/>
@@ -8622,7 +8635,7 @@
       <c r="R388" s="16"/>
       <c r="S388" s="16"/>
     </row>
-    <row r="389" ht="14.25" customHeight="1">
+    <row r="389" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B389" s="16"/>
       <c r="C389" s="16"/>
       <c r="D389" s="16"/>
@@ -8642,7 +8655,7 @@
       <c r="R389" s="16"/>
       <c r="S389" s="16"/>
     </row>
-    <row r="390" ht="14.25" customHeight="1">
+    <row r="390" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B390" s="16"/>
       <c r="C390" s="16"/>
       <c r="D390" s="16"/>
@@ -8662,7 +8675,7 @@
       <c r="R390" s="16"/>
       <c r="S390" s="16"/>
     </row>
-    <row r="391" ht="14.25" customHeight="1">
+    <row r="391" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B391" s="16"/>
       <c r="C391" s="16"/>
       <c r="D391" s="16"/>
@@ -8682,7 +8695,7 @@
       <c r="R391" s="16"/>
       <c r="S391" s="16"/>
     </row>
-    <row r="392" ht="14.25" customHeight="1">
+    <row r="392" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B392" s="16"/>
       <c r="C392" s="16"/>
       <c r="D392" s="16"/>
@@ -8702,7 +8715,7 @@
       <c r="R392" s="16"/>
       <c r="S392" s="16"/>
     </row>
-    <row r="393" ht="14.25" customHeight="1">
+    <row r="393" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B393" s="16"/>
       <c r="C393" s="16"/>
       <c r="D393" s="16"/>
@@ -8722,7 +8735,7 @@
       <c r="R393" s="16"/>
       <c r="S393" s="16"/>
     </row>
-    <row r="394" ht="14.25" customHeight="1">
+    <row r="394" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B394" s="16"/>
       <c r="C394" s="16"/>
       <c r="D394" s="16"/>
@@ -8742,7 +8755,7 @@
       <c r="R394" s="16"/>
       <c r="S394" s="16"/>
     </row>
-    <row r="395" ht="14.25" customHeight="1">
+    <row r="395" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B395" s="16"/>
       <c r="C395" s="16"/>
       <c r="D395" s="16"/>
@@ -8762,7 +8775,7 @@
       <c r="R395" s="16"/>
       <c r="S395" s="16"/>
     </row>
-    <row r="396" ht="14.25" customHeight="1">
+    <row r="396" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B396" s="16"/>
       <c r="C396" s="16"/>
       <c r="D396" s="16"/>
@@ -8782,7 +8795,7 @@
       <c r="R396" s="16"/>
       <c r="S396" s="16"/>
     </row>
-    <row r="397" ht="14.25" customHeight="1">
+    <row r="397" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B397" s="16"/>
       <c r="C397" s="16"/>
       <c r="D397" s="16"/>
@@ -8802,7 +8815,7 @@
       <c r="R397" s="16"/>
       <c r="S397" s="16"/>
     </row>
-    <row r="398" ht="14.25" customHeight="1">
+    <row r="398" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B398" s="16"/>
       <c r="C398" s="16"/>
       <c r="D398" s="16"/>
@@ -8822,7 +8835,7 @@
       <c r="R398" s="16"/>
       <c r="S398" s="16"/>
     </row>
-    <row r="399" ht="14.25" customHeight="1">
+    <row r="399" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B399" s="16"/>
       <c r="C399" s="16"/>
       <c r="D399" s="16"/>
@@ -8842,7 +8855,7 @@
       <c r="R399" s="16"/>
       <c r="S399" s="16"/>
     </row>
-    <row r="400" ht="14.25" customHeight="1">
+    <row r="400" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B400" s="16"/>
       <c r="C400" s="16"/>
       <c r="D400" s="16"/>
@@ -8862,7 +8875,7 @@
       <c r="R400" s="16"/>
       <c r="S400" s="16"/>
     </row>
-    <row r="401" ht="14.25" customHeight="1">
+    <row r="401" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B401" s="16"/>
       <c r="C401" s="16"/>
       <c r="D401" s="16"/>
@@ -8882,7 +8895,7 @@
       <c r="R401" s="16"/>
       <c r="S401" s="16"/>
     </row>
-    <row r="402" ht="14.25" customHeight="1">
+    <row r="402" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B402" s="16"/>
       <c r="C402" s="16"/>
       <c r="D402" s="16"/>
@@ -8902,7 +8915,7 @@
       <c r="R402" s="16"/>
       <c r="S402" s="16"/>
     </row>
-    <row r="403" ht="14.25" customHeight="1">
+    <row r="403" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B403" s="16"/>
       <c r="C403" s="16"/>
       <c r="D403" s="16"/>
@@ -8922,7 +8935,7 @@
       <c r="R403" s="16"/>
       <c r="S403" s="16"/>
     </row>
-    <row r="404" ht="14.25" customHeight="1">
+    <row r="404" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B404" s="16"/>
       <c r="C404" s="16"/>
       <c r="D404" s="16"/>
@@ -8942,7 +8955,7 @@
       <c r="R404" s="16"/>
       <c r="S404" s="16"/>
     </row>
-    <row r="405" ht="14.25" customHeight="1">
+    <row r="405" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B405" s="16"/>
       <c r="C405" s="16"/>
       <c r="D405" s="16"/>
@@ -8962,7 +8975,7 @@
       <c r="R405" s="16"/>
       <c r="S405" s="16"/>
     </row>
-    <row r="406" ht="14.25" customHeight="1">
+    <row r="406" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B406" s="16"/>
       <c r="C406" s="16"/>
       <c r="D406" s="16"/>
@@ -8982,7 +8995,7 @@
       <c r="R406" s="16"/>
       <c r="S406" s="16"/>
     </row>
-    <row r="407" ht="14.25" customHeight="1">
+    <row r="407" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B407" s="16"/>
       <c r="C407" s="16"/>
       <c r="D407" s="16"/>
@@ -9002,7 +9015,7 @@
       <c r="R407" s="16"/>
       <c r="S407" s="16"/>
     </row>
-    <row r="408" ht="14.25" customHeight="1">
+    <row r="408" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B408" s="16"/>
       <c r="C408" s="16"/>
       <c r="D408" s="16"/>
@@ -9022,7 +9035,7 @@
       <c r="R408" s="16"/>
       <c r="S408" s="16"/>
     </row>
-    <row r="409" ht="14.25" customHeight="1">
+    <row r="409" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B409" s="16"/>
       <c r="C409" s="16"/>
       <c r="D409" s="16"/>
@@ -9042,7 +9055,7 @@
       <c r="R409" s="16"/>
       <c r="S409" s="16"/>
     </row>
-    <row r="410" ht="14.25" customHeight="1">
+    <row r="410" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B410" s="16"/>
       <c r="C410" s="16"/>
       <c r="D410" s="16"/>
@@ -9062,7 +9075,7 @@
       <c r="R410" s="16"/>
       <c r="S410" s="16"/>
     </row>
-    <row r="411" ht="14.25" customHeight="1">
+    <row r="411" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B411" s="16"/>
       <c r="C411" s="16"/>
       <c r="D411" s="16"/>
@@ -9082,7 +9095,7 @@
       <c r="R411" s="16"/>
       <c r="S411" s="16"/>
     </row>
-    <row r="412" ht="14.25" customHeight="1">
+    <row r="412" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B412" s="16"/>
       <c r="C412" s="16"/>
       <c r="D412" s="16"/>
@@ -9102,7 +9115,7 @@
       <c r="R412" s="16"/>
       <c r="S412" s="16"/>
     </row>
-    <row r="413" ht="14.25" customHeight="1">
+    <row r="413" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B413" s="16"/>
       <c r="C413" s="16"/>
       <c r="D413" s="16"/>
@@ -9122,7 +9135,7 @@
       <c r="R413" s="16"/>
       <c r="S413" s="16"/>
     </row>
-    <row r="414" ht="14.25" customHeight="1">
+    <row r="414" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B414" s="16"/>
       <c r="C414" s="16"/>
       <c r="D414" s="16"/>
@@ -9142,7 +9155,7 @@
       <c r="R414" s="16"/>
       <c r="S414" s="16"/>
     </row>
-    <row r="415" ht="14.25" customHeight="1">
+    <row r="415" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B415" s="16"/>
       <c r="C415" s="16"/>
       <c r="D415" s="16"/>
@@ -9162,7 +9175,7 @@
       <c r="R415" s="16"/>
       <c r="S415" s="16"/>
     </row>
-    <row r="416" ht="14.25" customHeight="1">
+    <row r="416" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B416" s="16"/>
       <c r="C416" s="16"/>
       <c r="D416" s="16"/>
@@ -9182,7 +9195,7 @@
       <c r="R416" s="16"/>
       <c r="S416" s="16"/>
     </row>
-    <row r="417" ht="14.25" customHeight="1">
+    <row r="417" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B417" s="16"/>
       <c r="C417" s="16"/>
       <c r="D417" s="16"/>
@@ -9202,7 +9215,7 @@
       <c r="R417" s="16"/>
       <c r="S417" s="16"/>
     </row>
-    <row r="418" ht="14.25" customHeight="1">
+    <row r="418" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B418" s="16"/>
       <c r="C418" s="16"/>
       <c r="D418" s="16"/>
@@ -9222,7 +9235,7 @@
       <c r="R418" s="16"/>
       <c r="S418" s="16"/>
     </row>
-    <row r="419" ht="14.25" customHeight="1">
+    <row r="419" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B419" s="16"/>
       <c r="C419" s="16"/>
       <c r="D419" s="16"/>
@@ -9242,7 +9255,7 @@
       <c r="R419" s="16"/>
       <c r="S419" s="16"/>
     </row>
-    <row r="420" ht="14.25" customHeight="1">
+    <row r="420" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B420" s="16"/>
       <c r="C420" s="16"/>
       <c r="D420" s="16"/>
@@ -9262,7 +9275,7 @@
       <c r="R420" s="16"/>
       <c r="S420" s="16"/>
     </row>
-    <row r="421" ht="14.25" customHeight="1">
+    <row r="421" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B421" s="16"/>
       <c r="C421" s="16"/>
       <c r="D421" s="16"/>
@@ -9282,7 +9295,7 @@
       <c r="R421" s="16"/>
       <c r="S421" s="16"/>
     </row>
-    <row r="422" ht="14.25" customHeight="1">
+    <row r="422" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B422" s="16"/>
       <c r="C422" s="16"/>
       <c r="D422" s="16"/>
@@ -9302,7 +9315,7 @@
       <c r="R422" s="16"/>
       <c r="S422" s="16"/>
     </row>
-    <row r="423" ht="14.25" customHeight="1">
+    <row r="423" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B423" s="16"/>
       <c r="C423" s="16"/>
       <c r="D423" s="16"/>
@@ -9322,7 +9335,7 @@
       <c r="R423" s="16"/>
       <c r="S423" s="16"/>
     </row>
-    <row r="424" ht="14.25" customHeight="1">
+    <row r="424" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B424" s="16"/>
       <c r="C424" s="16"/>
       <c r="D424" s="16"/>
@@ -9342,7 +9355,7 @@
       <c r="R424" s="16"/>
       <c r="S424" s="16"/>
     </row>
-    <row r="425" ht="14.25" customHeight="1">
+    <row r="425" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B425" s="16"/>
       <c r="C425" s="16"/>
       <c r="D425" s="16"/>
@@ -9362,7 +9375,7 @@
       <c r="R425" s="16"/>
       <c r="S425" s="16"/>
     </row>
-    <row r="426" ht="14.25" customHeight="1">
+    <row r="426" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B426" s="16"/>
       <c r="C426" s="16"/>
       <c r="D426" s="16"/>
@@ -9382,7 +9395,7 @@
       <c r="R426" s="16"/>
       <c r="S426" s="16"/>
     </row>
-    <row r="427" ht="14.25" customHeight="1">
+    <row r="427" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B427" s="16"/>
       <c r="C427" s="16"/>
       <c r="D427" s="16"/>
@@ -9402,7 +9415,7 @@
       <c r="R427" s="16"/>
       <c r="S427" s="16"/>
     </row>
-    <row r="428" ht="14.25" customHeight="1">
+    <row r="428" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B428" s="16"/>
       <c r="C428" s="16"/>
       <c r="D428" s="16"/>
@@ -9422,7 +9435,7 @@
       <c r="R428" s="16"/>
       <c r="S428" s="16"/>
     </row>
-    <row r="429" ht="14.25" customHeight="1">
+    <row r="429" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B429" s="16"/>
       <c r="C429" s="16"/>
       <c r="D429" s="16"/>
@@ -9442,7 +9455,7 @@
       <c r="R429" s="16"/>
       <c r="S429" s="16"/>
     </row>
-    <row r="430" ht="14.25" customHeight="1">
+    <row r="430" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B430" s="16"/>
       <c r="C430" s="16"/>
       <c r="D430" s="16"/>
@@ -9462,7 +9475,7 @@
       <c r="R430" s="16"/>
       <c r="S430" s="16"/>
     </row>
-    <row r="431" ht="14.25" customHeight="1">
+    <row r="431" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B431" s="16"/>
       <c r="C431" s="16"/>
       <c r="D431" s="16"/>
@@ -9482,7 +9495,7 @@
       <c r="R431" s="16"/>
       <c r="S431" s="16"/>
     </row>
-    <row r="432" ht="14.25" customHeight="1">
+    <row r="432" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B432" s="16"/>
       <c r="C432" s="16"/>
       <c r="D432" s="16"/>
@@ -9502,7 +9515,7 @@
       <c r="R432" s="16"/>
       <c r="S432" s="16"/>
     </row>
-    <row r="433" ht="14.25" customHeight="1">
+    <row r="433" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B433" s="16"/>
       <c r="C433" s="16"/>
       <c r="D433" s="16"/>
@@ -9522,7 +9535,7 @@
       <c r="R433" s="16"/>
       <c r="S433" s="16"/>
     </row>
-    <row r="434" ht="14.25" customHeight="1">
+    <row r="434" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B434" s="16"/>
       <c r="C434" s="16"/>
       <c r="D434" s="16"/>
@@ -9542,7 +9555,7 @@
       <c r="R434" s="16"/>
       <c r="S434" s="16"/>
     </row>
-    <row r="435" ht="14.25" customHeight="1">
+    <row r="435" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B435" s="16"/>
       <c r="C435" s="16"/>
       <c r="D435" s="16"/>
@@ -9562,7 +9575,7 @@
       <c r="R435" s="16"/>
       <c r="S435" s="16"/>
     </row>
-    <row r="436" ht="14.25" customHeight="1">
+    <row r="436" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B436" s="16"/>
       <c r="C436" s="16"/>
       <c r="D436" s="16"/>
@@ -9582,7 +9595,7 @@
       <c r="R436" s="16"/>
       <c r="S436" s="16"/>
     </row>
-    <row r="437" ht="14.25" customHeight="1">
+    <row r="437" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B437" s="16"/>
       <c r="C437" s="16"/>
       <c r="D437" s="16"/>
@@ -9602,7 +9615,7 @@
       <c r="R437" s="16"/>
       <c r="S437" s="16"/>
     </row>
-    <row r="438" ht="14.25" customHeight="1">
+    <row r="438" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B438" s="16"/>
       <c r="C438" s="16"/>
       <c r="D438" s="16"/>
@@ -9622,7 +9635,7 @@
       <c r="R438" s="16"/>
       <c r="S438" s="16"/>
     </row>
-    <row r="439" ht="14.25" customHeight="1">
+    <row r="439" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B439" s="16"/>
       <c r="C439" s="16"/>
       <c r="D439" s="16"/>
@@ -9642,7 +9655,7 @@
       <c r="R439" s="16"/>
       <c r="S439" s="16"/>
     </row>
-    <row r="440" ht="14.25" customHeight="1">
+    <row r="440" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B440" s="16"/>
       <c r="C440" s="16"/>
       <c r="D440" s="16"/>
@@ -9662,7 +9675,7 @@
       <c r="R440" s="16"/>
       <c r="S440" s="16"/>
     </row>
-    <row r="441" ht="14.25" customHeight="1">
+    <row r="441" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B441" s="16"/>
       <c r="C441" s="16"/>
       <c r="D441" s="16"/>
@@ -9682,7 +9695,7 @@
       <c r="R441" s="16"/>
       <c r="S441" s="16"/>
     </row>
-    <row r="442" ht="14.25" customHeight="1">
+    <row r="442" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B442" s="16"/>
       <c r="C442" s="16"/>
       <c r="D442" s="16"/>
@@ -9702,7 +9715,7 @@
       <c r="R442" s="16"/>
       <c r="S442" s="16"/>
     </row>
-    <row r="443" ht="14.25" customHeight="1">
+    <row r="443" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B443" s="16"/>
       <c r="C443" s="16"/>
       <c r="D443" s="16"/>
@@ -9722,7 +9735,7 @@
       <c r="R443" s="16"/>
       <c r="S443" s="16"/>
     </row>
-    <row r="444" ht="14.25" customHeight="1">
+    <row r="444" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B444" s="16"/>
       <c r="C444" s="16"/>
       <c r="D444" s="16"/>
@@ -9742,7 +9755,7 @@
       <c r="R444" s="16"/>
       <c r="S444" s="16"/>
     </row>
-    <row r="445" ht="14.25" customHeight="1">
+    <row r="445" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B445" s="16"/>
       <c r="C445" s="16"/>
       <c r="D445" s="16"/>
@@ -9762,7 +9775,7 @@
       <c r="R445" s="16"/>
       <c r="S445" s="16"/>
     </row>
-    <row r="446" ht="14.25" customHeight="1">
+    <row r="446" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B446" s="16"/>
       <c r="C446" s="16"/>
       <c r="D446" s="16"/>
@@ -9782,7 +9795,7 @@
       <c r="R446" s="16"/>
       <c r="S446" s="16"/>
     </row>
-    <row r="447" ht="14.25" customHeight="1">
+    <row r="447" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B447" s="16"/>
       <c r="C447" s="16"/>
       <c r="D447" s="16"/>
@@ -9802,7 +9815,7 @@
       <c r="R447" s="16"/>
       <c r="S447" s="16"/>
     </row>
-    <row r="448" ht="14.25" customHeight="1">
+    <row r="448" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B448" s="16"/>
       <c r="C448" s="16"/>
       <c r="D448" s="16"/>
@@ -9822,7 +9835,7 @@
       <c r="R448" s="16"/>
       <c r="S448" s="16"/>
     </row>
-    <row r="449" ht="14.25" customHeight="1">
+    <row r="449" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B449" s="16"/>
       <c r="C449" s="16"/>
       <c r="D449" s="16"/>
@@ -9842,7 +9855,7 @@
       <c r="R449" s="16"/>
       <c r="S449" s="16"/>
     </row>
-    <row r="450" ht="14.25" customHeight="1">
+    <row r="450" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B450" s="16"/>
       <c r="C450" s="16"/>
       <c r="D450" s="16"/>
@@ -9862,7 +9875,7 @@
       <c r="R450" s="16"/>
       <c r="S450" s="16"/>
     </row>
-    <row r="451" ht="14.25" customHeight="1">
+    <row r="451" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B451" s="16"/>
       <c r="C451" s="16"/>
       <c r="D451" s="16"/>
@@ -9882,7 +9895,7 @@
       <c r="R451" s="16"/>
       <c r="S451" s="16"/>
     </row>
-    <row r="452" ht="14.25" customHeight="1">
+    <row r="452" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B452" s="16"/>
       <c r="C452" s="16"/>
       <c r="D452" s="16"/>
@@ -9902,7 +9915,7 @@
       <c r="R452" s="16"/>
       <c r="S452" s="16"/>
     </row>
-    <row r="453" ht="14.25" customHeight="1">
+    <row r="453" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B453" s="16"/>
       <c r="C453" s="16"/>
       <c r="D453" s="16"/>
@@ -9922,7 +9935,7 @@
       <c r="R453" s="16"/>
       <c r="S453" s="16"/>
     </row>
-    <row r="454" ht="14.25" customHeight="1">
+    <row r="454" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B454" s="16"/>
       <c r="C454" s="16"/>
       <c r="D454" s="16"/>
@@ -9942,7 +9955,7 @@
       <c r="R454" s="16"/>
       <c r="S454" s="16"/>
     </row>
-    <row r="455" ht="14.25" customHeight="1">
+    <row r="455" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B455" s="16"/>
       <c r="C455" s="16"/>
       <c r="D455" s="16"/>
@@ -9962,7 +9975,7 @@
       <c r="R455" s="16"/>
       <c r="S455" s="16"/>
     </row>
-    <row r="456" ht="14.25" customHeight="1">
+    <row r="456" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B456" s="16"/>
       <c r="C456" s="16"/>
       <c r="D456" s="16"/>
@@ -9982,7 +9995,7 @@
       <c r="R456" s="16"/>
       <c r="S456" s="16"/>
     </row>
-    <row r="457" ht="14.25" customHeight="1">
+    <row r="457" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B457" s="16"/>
       <c r="C457" s="16"/>
       <c r="D457" s="16"/>
@@ -10002,7 +10015,7 @@
       <c r="R457" s="16"/>
       <c r="S457" s="16"/>
     </row>
-    <row r="458" ht="14.25" customHeight="1">
+    <row r="458" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B458" s="16"/>
       <c r="C458" s="16"/>
       <c r="D458" s="16"/>
@@ -10022,7 +10035,7 @@
       <c r="R458" s="16"/>
       <c r="S458" s="16"/>
     </row>
-    <row r="459" ht="14.25" customHeight="1">
+    <row r="459" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B459" s="16"/>
       <c r="C459" s="16"/>
       <c r="D459" s="16"/>
@@ -10042,7 +10055,7 @@
       <c r="R459" s="16"/>
       <c r="S459" s="16"/>
     </row>
-    <row r="460" ht="14.25" customHeight="1">
+    <row r="460" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B460" s="16"/>
       <c r="C460" s="16"/>
       <c r="D460" s="16"/>
@@ -10062,7 +10075,7 @@
       <c r="R460" s="16"/>
       <c r="S460" s="16"/>
     </row>
-    <row r="461" ht="14.25" customHeight="1">
+    <row r="461" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B461" s="16"/>
       <c r="C461" s="16"/>
       <c r="D461" s="16"/>
@@ -10082,7 +10095,7 @@
       <c r="R461" s="16"/>
       <c r="S461" s="16"/>
     </row>
-    <row r="462" ht="14.25" customHeight="1">
+    <row r="462" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B462" s="16"/>
       <c r="C462" s="16"/>
       <c r="D462" s="16"/>
@@ -10102,7 +10115,7 @@
       <c r="R462" s="16"/>
       <c r="S462" s="16"/>
     </row>
-    <row r="463" ht="14.25" customHeight="1">
+    <row r="463" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B463" s="16"/>
       <c r="C463" s="16"/>
       <c r="D463" s="16"/>
@@ -10122,7 +10135,7 @@
       <c r="R463" s="16"/>
       <c r="S463" s="16"/>
     </row>
-    <row r="464" ht="14.25" customHeight="1">
+    <row r="464" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B464" s="16"/>
       <c r="C464" s="16"/>
       <c r="D464" s="16"/>
@@ -10142,7 +10155,7 @@
       <c r="R464" s="16"/>
       <c r="S464" s="16"/>
     </row>
-    <row r="465" ht="14.25" customHeight="1">
+    <row r="465" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B465" s="16"/>
       <c r="C465" s="16"/>
       <c r="D465" s="16"/>
@@ -10162,7 +10175,7 @@
       <c r="R465" s="16"/>
       <c r="S465" s="16"/>
     </row>
-    <row r="466" ht="14.25" customHeight="1">
+    <row r="466" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B466" s="16"/>
       <c r="C466" s="16"/>
       <c r="D466" s="16"/>
@@ -10182,7 +10195,7 @@
       <c r="R466" s="16"/>
       <c r="S466" s="16"/>
     </row>
-    <row r="467" ht="14.25" customHeight="1">
+    <row r="467" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B467" s="16"/>
       <c r="C467" s="16"/>
       <c r="D467" s="16"/>
@@ -10202,7 +10215,7 @@
       <c r="R467" s="16"/>
       <c r="S467" s="16"/>
     </row>
-    <row r="468" ht="14.25" customHeight="1">
+    <row r="468" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B468" s="16"/>
       <c r="C468" s="16"/>
       <c r="D468" s="16"/>
@@ -10222,7 +10235,7 @@
       <c r="R468" s="16"/>
       <c r="S468" s="16"/>
     </row>
-    <row r="469" ht="14.25" customHeight="1">
+    <row r="469" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B469" s="16"/>
       <c r="C469" s="16"/>
       <c r="D469" s="16"/>
@@ -10242,7 +10255,7 @@
       <c r="R469" s="16"/>
       <c r="S469" s="16"/>
     </row>
-    <row r="470" ht="14.25" customHeight="1">
+    <row r="470" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B470" s="16"/>
       <c r="C470" s="16"/>
       <c r="D470" s="16"/>
@@ -10262,7 +10275,7 @@
       <c r="R470" s="16"/>
       <c r="S470" s="16"/>
     </row>
-    <row r="471" ht="14.25" customHeight="1">
+    <row r="471" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B471" s="16"/>
       <c r="C471" s="16"/>
       <c r="D471" s="16"/>
@@ -10282,7 +10295,7 @@
       <c r="R471" s="16"/>
       <c r="S471" s="16"/>
     </row>
-    <row r="472" ht="14.25" customHeight="1">
+    <row r="472" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B472" s="16"/>
       <c r="C472" s="16"/>
       <c r="D472" s="16"/>
@@ -10302,7 +10315,7 @@
       <c r="R472" s="16"/>
       <c r="S472" s="16"/>
     </row>
-    <row r="473" ht="14.25" customHeight="1">
+    <row r="473" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B473" s="16"/>
       <c r="C473" s="16"/>
       <c r="D473" s="16"/>
@@ -10322,7 +10335,7 @@
       <c r="R473" s="16"/>
       <c r="S473" s="16"/>
     </row>
-    <row r="474" ht="14.25" customHeight="1">
+    <row r="474" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B474" s="16"/>
       <c r="C474" s="16"/>
       <c r="D474" s="16"/>
@@ -10342,7 +10355,7 @@
       <c r="R474" s="16"/>
       <c r="S474" s="16"/>
     </row>
-    <row r="475" ht="14.25" customHeight="1">
+    <row r="475" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B475" s="16"/>
       <c r="C475" s="16"/>
       <c r="D475" s="16"/>
@@ -10362,7 +10375,7 @@
       <c r="R475" s="16"/>
       <c r="S475" s="16"/>
     </row>
-    <row r="476" ht="14.25" customHeight="1">
+    <row r="476" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B476" s="16"/>
       <c r="C476" s="16"/>
       <c r="D476" s="16"/>
@@ -10382,7 +10395,7 @@
       <c r="R476" s="16"/>
       <c r="S476" s="16"/>
     </row>
-    <row r="477" ht="14.25" customHeight="1">
+    <row r="477" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B477" s="16"/>
       <c r="C477" s="16"/>
       <c r="D477" s="16"/>
@@ -10402,7 +10415,7 @@
       <c r="R477" s="16"/>
       <c r="S477" s="16"/>
     </row>
-    <row r="478" ht="14.25" customHeight="1">
+    <row r="478" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B478" s="16"/>
       <c r="C478" s="16"/>
       <c r="D478" s="16"/>
@@ -10422,7 +10435,7 @@
       <c r="R478" s="16"/>
       <c r="S478" s="16"/>
     </row>
-    <row r="479" ht="14.25" customHeight="1">
+    <row r="479" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B479" s="16"/>
       <c r="C479" s="16"/>
       <c r="D479" s="16"/>
@@ -10442,7 +10455,7 @@
       <c r="R479" s="16"/>
       <c r="S479" s="16"/>
     </row>
-    <row r="480" ht="14.25" customHeight="1">
+    <row r="480" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B480" s="16"/>
       <c r="C480" s="16"/>
       <c r="D480" s="16"/>
@@ -10462,7 +10475,7 @@
       <c r="R480" s="16"/>
       <c r="S480" s="16"/>
     </row>
-    <row r="481" ht="14.25" customHeight="1">
+    <row r="481" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B481" s="16"/>
       <c r="C481" s="16"/>
       <c r="D481" s="16"/>
@@ -10482,7 +10495,7 @@
       <c r="R481" s="16"/>
       <c r="S481" s="16"/>
     </row>
-    <row r="482" ht="14.25" customHeight="1">
+    <row r="482" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B482" s="16"/>
       <c r="C482" s="16"/>
       <c r="D482" s="16"/>
@@ -10502,7 +10515,7 @@
       <c r="R482" s="16"/>
       <c r="S482" s="16"/>
     </row>
-    <row r="483" ht="14.25" customHeight="1">
+    <row r="483" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B483" s="16"/>
       <c r="C483" s="16"/>
       <c r="D483" s="16"/>
@@ -10522,7 +10535,7 @@
       <c r="R483" s="16"/>
       <c r="S483" s="16"/>
     </row>
-    <row r="484" ht="14.25" customHeight="1">
+    <row r="484" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B484" s="16"/>
       <c r="C484" s="16"/>
       <c r="D484" s="16"/>
@@ -10542,7 +10555,7 @@
       <c r="R484" s="16"/>
       <c r="S484" s="16"/>
     </row>
-    <row r="485" ht="14.25" customHeight="1">
+    <row r="485" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B485" s="16"/>
       <c r="C485" s="16"/>
       <c r="D485" s="16"/>
@@ -10562,7 +10575,7 @@
       <c r="R485" s="16"/>
       <c r="S485" s="16"/>
     </row>
-    <row r="486" ht="14.25" customHeight="1">
+    <row r="486" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B486" s="16"/>
       <c r="C486" s="16"/>
       <c r="D486" s="16"/>
@@ -10582,7 +10595,7 @@
       <c r="R486" s="16"/>
       <c r="S486" s="16"/>
     </row>
-    <row r="487" ht="14.25" customHeight="1">
+    <row r="487" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B487" s="16"/>
       <c r="C487" s="16"/>
       <c r="D487" s="16"/>
@@ -10602,7 +10615,7 @@
       <c r="R487" s="16"/>
       <c r="S487" s="16"/>
     </row>
-    <row r="488" ht="14.25" customHeight="1">
+    <row r="488" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B488" s="16"/>
       <c r="C488" s="16"/>
       <c r="D488" s="16"/>
@@ -10622,7 +10635,7 @@
       <c r="R488" s="16"/>
       <c r="S488" s="16"/>
     </row>
-    <row r="489" ht="14.25" customHeight="1">
+    <row r="489" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B489" s="16"/>
       <c r="C489" s="16"/>
       <c r="D489" s="16"/>
@@ -10642,7 +10655,7 @@
       <c r="R489" s="16"/>
       <c r="S489" s="16"/>
     </row>
-    <row r="490" ht="14.25" customHeight="1">
+    <row r="490" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B490" s="16"/>
       <c r="C490" s="16"/>
       <c r="D490" s="16"/>
@@ -10662,7 +10675,7 @@
       <c r="R490" s="16"/>
       <c r="S490" s="16"/>
     </row>
-    <row r="491" ht="14.25" customHeight="1">
+    <row r="491" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B491" s="16"/>
       <c r="C491" s="16"/>
       <c r="D491" s="16"/>
@@ -10682,7 +10695,7 @@
       <c r="R491" s="16"/>
       <c r="S491" s="16"/>
     </row>
-    <row r="492" ht="14.25" customHeight="1">
+    <row r="492" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B492" s="16"/>
       <c r="C492" s="16"/>
       <c r="D492" s="16"/>
@@ -10702,7 +10715,7 @@
       <c r="R492" s="16"/>
       <c r="S492" s="16"/>
     </row>
-    <row r="493" ht="14.25" customHeight="1">
+    <row r="493" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B493" s="16"/>
       <c r="C493" s="16"/>
       <c r="D493" s="16"/>
@@ -10722,7 +10735,7 @@
       <c r="R493" s="16"/>
       <c r="S493" s="16"/>
     </row>
-    <row r="494" ht="14.25" customHeight="1">
+    <row r="494" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B494" s="16"/>
       <c r="C494" s="16"/>
       <c r="D494" s="16"/>
@@ -10742,7 +10755,7 @@
       <c r="R494" s="16"/>
       <c r="S494" s="16"/>
     </row>
-    <row r="495" ht="14.25" customHeight="1">
+    <row r="495" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B495" s="16"/>
       <c r="C495" s="16"/>
       <c r="D495" s="16"/>
@@ -10762,7 +10775,7 @@
       <c r="R495" s="16"/>
       <c r="S495" s="16"/>
     </row>
-    <row r="496" ht="14.25" customHeight="1">
+    <row r="496" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B496" s="16"/>
       <c r="C496" s="16"/>
       <c r="D496" s="16"/>
@@ -10782,7 +10795,7 @@
       <c r="R496" s="16"/>
       <c r="S496" s="16"/>
     </row>
-    <row r="497" ht="14.25" customHeight="1">
+    <row r="497" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B497" s="16"/>
       <c r="C497" s="16"/>
       <c r="D497" s="16"/>
@@ -10802,7 +10815,7 @@
       <c r="R497" s="16"/>
       <c r="S497" s="16"/>
     </row>
-    <row r="498" ht="14.25" customHeight="1">
+    <row r="498" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B498" s="16"/>
       <c r="C498" s="16"/>
       <c r="D498" s="16"/>
@@ -10822,7 +10835,7 @@
       <c r="R498" s="16"/>
       <c r="S498" s="16"/>
     </row>
-    <row r="499" ht="14.25" customHeight="1">
+    <row r="499" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B499" s="16"/>
       <c r="C499" s="16"/>
       <c r="D499" s="16"/>
@@ -10842,7 +10855,7 @@
       <c r="R499" s="16"/>
       <c r="S499" s="16"/>
     </row>
-    <row r="500" ht="14.25" customHeight="1">
+    <row r="500" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B500" s="16"/>
       <c r="C500" s="16"/>
       <c r="D500" s="16"/>
@@ -10862,7 +10875,7 @@
       <c r="R500" s="16"/>
       <c r="S500" s="16"/>
     </row>
-    <row r="501" ht="14.25" customHeight="1">
+    <row r="501" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B501" s="16"/>
       <c r="C501" s="16"/>
       <c r="D501" s="16"/>
@@ -10882,7 +10895,7 @@
       <c r="R501" s="16"/>
       <c r="S501" s="16"/>
     </row>
-    <row r="502" ht="14.25" customHeight="1">
+    <row r="502" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B502" s="16"/>
       <c r="C502" s="16"/>
       <c r="D502" s="16"/>
@@ -10902,7 +10915,7 @@
       <c r="R502" s="16"/>
       <c r="S502" s="16"/>
     </row>
-    <row r="503" ht="14.25" customHeight="1">
+    <row r="503" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B503" s="16"/>
       <c r="C503" s="16"/>
       <c r="D503" s="16"/>
@@ -10922,7 +10935,7 @@
       <c r="R503" s="16"/>
       <c r="S503" s="16"/>
     </row>
-    <row r="504" ht="14.25" customHeight="1">
+    <row r="504" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B504" s="16"/>
       <c r="C504" s="16"/>
       <c r="D504" s="16"/>
@@ -10942,7 +10955,7 @@
       <c r="R504" s="16"/>
       <c r="S504" s="16"/>
     </row>
-    <row r="505" ht="14.25" customHeight="1">
+    <row r="505" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B505" s="16"/>
       <c r="C505" s="16"/>
       <c r="D505" s="16"/>
@@ -10962,7 +10975,7 @@
       <c r="R505" s="16"/>
       <c r="S505" s="16"/>
     </row>
-    <row r="506" ht="14.25" customHeight="1">
+    <row r="506" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B506" s="16"/>
       <c r="C506" s="16"/>
       <c r="D506" s="16"/>
@@ -10982,7 +10995,7 @@
       <c r="R506" s="16"/>
       <c r="S506" s="16"/>
     </row>
-    <row r="507" ht="14.25" customHeight="1">
+    <row r="507" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B507" s="16"/>
       <c r="C507" s="16"/>
       <c r="D507" s="16"/>
@@ -11002,7 +11015,7 @@
       <c r="R507" s="16"/>
       <c r="S507" s="16"/>
     </row>
-    <row r="508" ht="14.25" customHeight="1">
+    <row r="508" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B508" s="16"/>
       <c r="C508" s="16"/>
       <c r="D508" s="16"/>
@@ -11022,7 +11035,7 @@
       <c r="R508" s="16"/>
       <c r="S508" s="16"/>
     </row>
-    <row r="509" ht="14.25" customHeight="1">
+    <row r="509" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B509" s="16"/>
       <c r="C509" s="16"/>
       <c r="D509" s="16"/>
@@ -11042,7 +11055,7 @@
       <c r="R509" s="16"/>
       <c r="S509" s="16"/>
     </row>
-    <row r="510" ht="14.25" customHeight="1">
+    <row r="510" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B510" s="16"/>
       <c r="C510" s="16"/>
       <c r="D510" s="16"/>
@@ -11062,7 +11075,7 @@
       <c r="R510" s="16"/>
       <c r="S510" s="16"/>
     </row>
-    <row r="511" ht="14.25" customHeight="1">
+    <row r="511" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B511" s="16"/>
       <c r="C511" s="16"/>
       <c r="D511" s="16"/>
@@ -11082,7 +11095,7 @@
       <c r="R511" s="16"/>
       <c r="S511" s="16"/>
     </row>
-    <row r="512" ht="14.25" customHeight="1">
+    <row r="512" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B512" s="16"/>
       <c r="C512" s="16"/>
       <c r="D512" s="16"/>
@@ -11102,7 +11115,7 @@
       <c r="R512" s="16"/>
       <c r="S512" s="16"/>
     </row>
-    <row r="513" ht="14.25" customHeight="1">
+    <row r="513" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B513" s="16"/>
       <c r="C513" s="16"/>
       <c r="D513" s="16"/>
@@ -11122,7 +11135,7 @@
       <c r="R513" s="16"/>
       <c r="S513" s="16"/>
     </row>
-    <row r="514" ht="14.25" customHeight="1">
+    <row r="514" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B514" s="16"/>
       <c r="C514" s="16"/>
       <c r="D514" s="16"/>
@@ -11142,7 +11155,7 @@
       <c r="R514" s="16"/>
       <c r="S514" s="16"/>
     </row>
-    <row r="515" ht="14.25" customHeight="1">
+    <row r="515" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B515" s="16"/>
       <c r="C515" s="16"/>
       <c r="D515" s="16"/>
@@ -11162,7 +11175,7 @@
       <c r="R515" s="16"/>
       <c r="S515" s="16"/>
     </row>
-    <row r="516" ht="14.25" customHeight="1">
+    <row r="516" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B516" s="16"/>
       <c r="C516" s="16"/>
       <c r="D516" s="16"/>
@@ -11182,7 +11195,7 @@
       <c r="R516" s="16"/>
       <c r="S516" s="16"/>
     </row>
-    <row r="517" ht="14.25" customHeight="1">
+    <row r="517" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B517" s="16"/>
       <c r="C517" s="16"/>
       <c r="D517" s="16"/>
@@ -11202,7 +11215,7 @@
       <c r="R517" s="16"/>
       <c r="S517" s="16"/>
     </row>
-    <row r="518" ht="14.25" customHeight="1">
+    <row r="518" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B518" s="16"/>
       <c r="C518" s="16"/>
       <c r="D518" s="16"/>
@@ -11222,7 +11235,7 @@
       <c r="R518" s="16"/>
       <c r="S518" s="16"/>
     </row>
-    <row r="519" ht="14.25" customHeight="1">
+    <row r="519" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B519" s="16"/>
       <c r="C519" s="16"/>
       <c r="D519" s="16"/>
@@ -11242,7 +11255,7 @@
       <c r="R519" s="16"/>
       <c r="S519" s="16"/>
     </row>
-    <row r="520" ht="14.25" customHeight="1">
+    <row r="520" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B520" s="16"/>
       <c r="C520" s="16"/>
       <c r="D520" s="16"/>
@@ -11262,7 +11275,7 @@
       <c r="R520" s="16"/>
       <c r="S520" s="16"/>
     </row>
-    <row r="521" ht="14.25" customHeight="1">
+    <row r="521" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B521" s="16"/>
       <c r="C521" s="16"/>
       <c r="D521" s="16"/>
@@ -11282,7 +11295,7 @@
       <c r="R521" s="16"/>
       <c r="S521" s="16"/>
     </row>
-    <row r="522" ht="14.25" customHeight="1">
+    <row r="522" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B522" s="16"/>
       <c r="C522" s="16"/>
       <c r="D522" s="16"/>
@@ -11302,7 +11315,7 @@
       <c r="R522" s="16"/>
       <c r="S522" s="16"/>
     </row>
-    <row r="523" ht="14.25" customHeight="1">
+    <row r="523" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B523" s="16"/>
       <c r="C523" s="16"/>
       <c r="D523" s="16"/>
@@ -11322,7 +11335,7 @@
       <c r="R523" s="16"/>
       <c r="S523" s="16"/>
     </row>
-    <row r="524" ht="14.25" customHeight="1">
+    <row r="524" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B524" s="16"/>
       <c r="C524" s="16"/>
       <c r="D524" s="16"/>
@@ -11342,7 +11355,7 @@
       <c r="R524" s="16"/>
       <c r="S524" s="16"/>
     </row>
-    <row r="525" ht="14.25" customHeight="1">
+    <row r="525" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B525" s="16"/>
       <c r="C525" s="16"/>
       <c r="D525" s="16"/>
@@ -11362,7 +11375,7 @@
       <c r="R525" s="16"/>
       <c r="S525" s="16"/>
     </row>
-    <row r="526" ht="14.25" customHeight="1">
+    <row r="526" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B526" s="16"/>
       <c r="C526" s="16"/>
       <c r="D526" s="16"/>
@@ -11382,7 +11395,7 @@
       <c r="R526" s="16"/>
       <c r="S526" s="16"/>
     </row>
-    <row r="527" ht="14.25" customHeight="1">
+    <row r="527" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B527" s="16"/>
       <c r="C527" s="16"/>
       <c r="D527" s="16"/>
@@ -11402,7 +11415,7 @@
       <c r="R527" s="16"/>
       <c r="S527" s="16"/>
     </row>
-    <row r="528" ht="14.25" customHeight="1">
+    <row r="528" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B528" s="16"/>
       <c r="C528" s="16"/>
       <c r="D528" s="16"/>
@@ -11422,7 +11435,7 @@
       <c r="R528" s="16"/>
       <c r="S528" s="16"/>
     </row>
-    <row r="529" ht="14.25" customHeight="1">
+    <row r="529" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B529" s="16"/>
       <c r="C529" s="16"/>
       <c r="D529" s="16"/>
@@ -11442,7 +11455,7 @@
       <c r="R529" s="16"/>
       <c r="S529" s="16"/>
     </row>
-    <row r="530" ht="14.25" customHeight="1">
+    <row r="530" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B530" s="16"/>
       <c r="C530" s="16"/>
       <c r="D530" s="16"/>
@@ -11462,7 +11475,7 @@
       <c r="R530" s="16"/>
       <c r="S530" s="16"/>
     </row>
-    <row r="531" ht="14.25" customHeight="1">
+    <row r="531" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B531" s="16"/>
       <c r="C531" s="16"/>
       <c r="D531" s="16"/>
@@ -11482,7 +11495,7 @@
       <c r="R531" s="16"/>
       <c r="S531" s="16"/>
     </row>
-    <row r="532" ht="14.25" customHeight="1">
+    <row r="532" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B532" s="16"/>
       <c r="C532" s="16"/>
       <c r="D532" s="16"/>
@@ -11502,7 +11515,7 @@
       <c r="R532" s="16"/>
       <c r="S532" s="16"/>
     </row>
-    <row r="533" ht="14.25" customHeight="1">
+    <row r="533" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B533" s="16"/>
       <c r="C533" s="16"/>
       <c r="D533" s="16"/>
@@ -11522,7 +11535,7 @@
       <c r="R533" s="16"/>
       <c r="S533" s="16"/>
     </row>
-    <row r="534" ht="14.25" customHeight="1">
+    <row r="534" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B534" s="16"/>
       <c r="C534" s="16"/>
       <c r="D534" s="16"/>
@@ -11542,7 +11555,7 @@
       <c r="R534" s="16"/>
       <c r="S534" s="16"/>
     </row>
-    <row r="535" ht="14.25" customHeight="1">
+    <row r="535" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B535" s="16"/>
       <c r="C535" s="16"/>
       <c r="D535" s="16"/>
@@ -11562,7 +11575,7 @@
       <c r="R535" s="16"/>
       <c r="S535" s="16"/>
     </row>
-    <row r="536" ht="14.25" customHeight="1">
+    <row r="536" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B536" s="16"/>
       <c r="C536" s="16"/>
       <c r="D536" s="16"/>
@@ -11582,7 +11595,7 @@
       <c r="R536" s="16"/>
       <c r="S536" s="16"/>
     </row>
-    <row r="537" ht="14.25" customHeight="1">
+    <row r="537" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B537" s="16"/>
       <c r="C537" s="16"/>
       <c r="D537" s="16"/>
@@ -11602,7 +11615,7 @@
       <c r="R537" s="16"/>
       <c r="S537" s="16"/>
     </row>
-    <row r="538" ht="14.25" customHeight="1">
+    <row r="538" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B538" s="16"/>
       <c r="C538" s="16"/>
       <c r="D538" s="16"/>
@@ -11622,7 +11635,7 @@
       <c r="R538" s="16"/>
       <c r="S538" s="16"/>
     </row>
-    <row r="539" ht="14.25" customHeight="1">
+    <row r="539" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B539" s="16"/>
       <c r="C539" s="16"/>
       <c r="D539" s="16"/>
@@ -11642,7 +11655,7 @@
       <c r="R539" s="16"/>
       <c r="S539" s="16"/>
     </row>
-    <row r="540" ht="14.25" customHeight="1">
+    <row r="540" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B540" s="16"/>
       <c r="C540" s="16"/>
       <c r="D540" s="16"/>
@@ -11662,7 +11675,7 @@
       <c r="R540" s="16"/>
       <c r="S540" s="16"/>
     </row>
-    <row r="541" ht="14.25" customHeight="1">
+    <row r="541" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B541" s="16"/>
       <c r="C541" s="16"/>
       <c r="D541" s="16"/>
@@ -11682,7 +11695,7 @@
       <c r="R541" s="16"/>
       <c r="S541" s="16"/>
     </row>
-    <row r="542" ht="14.25" customHeight="1">
+    <row r="542" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B542" s="16"/>
       <c r="C542" s="16"/>
       <c r="D542" s="16"/>
@@ -11702,7 +11715,7 @@
       <c r="R542" s="16"/>
       <c r="S542" s="16"/>
     </row>
-    <row r="543" ht="14.25" customHeight="1">
+    <row r="543" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B543" s="16"/>
       <c r="C543" s="16"/>
       <c r="D543" s="16"/>
@@ -11722,7 +11735,7 @@
       <c r="R543" s="16"/>
       <c r="S543" s="16"/>
     </row>
-    <row r="544" ht="14.25" customHeight="1">
+    <row r="544" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B544" s="16"/>
       <c r="C544" s="16"/>
       <c r="D544" s="16"/>
@@ -11742,7 +11755,7 @@
       <c r="R544" s="16"/>
       <c r="S544" s="16"/>
     </row>
-    <row r="545" ht="14.25" customHeight="1">
+    <row r="545" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B545" s="16"/>
       <c r="C545" s="16"/>
       <c r="D545" s="16"/>
@@ -11762,7 +11775,7 @@
       <c r="R545" s="16"/>
       <c r="S545" s="16"/>
     </row>
-    <row r="546" ht="14.25" customHeight="1">
+    <row r="546" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B546" s="16"/>
       <c r="C546" s="16"/>
       <c r="D546" s="16"/>
@@ -11782,7 +11795,7 @@
       <c r="R546" s="16"/>
       <c r="S546" s="16"/>
     </row>
-    <row r="547" ht="14.25" customHeight="1">
+    <row r="547" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B547" s="16"/>
       <c r="C547" s="16"/>
       <c r="D547" s="16"/>
@@ -11802,7 +11815,7 @@
       <c r="R547" s="16"/>
       <c r="S547" s="16"/>
     </row>
-    <row r="548" ht="14.25" customHeight="1">
+    <row r="548" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B548" s="16"/>
       <c r="C548" s="16"/>
       <c r="D548" s="16"/>
@@ -11822,7 +11835,7 @@
       <c r="R548" s="16"/>
       <c r="S548" s="16"/>
     </row>
-    <row r="549" ht="14.25" customHeight="1">
+    <row r="549" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B549" s="16"/>
       <c r="C549" s="16"/>
       <c r="D549" s="16"/>
@@ -11842,7 +11855,7 @@
       <c r="R549" s="16"/>
       <c r="S549" s="16"/>
     </row>
-    <row r="550" ht="14.25" customHeight="1">
+    <row r="550" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B550" s="16"/>
       <c r="C550" s="16"/>
       <c r="D550" s="16"/>
@@ -11862,7 +11875,7 @@
       <c r="R550" s="16"/>
       <c r="S550" s="16"/>
     </row>
-    <row r="551" ht="14.25" customHeight="1">
+    <row r="551" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B551" s="16"/>
       <c r="C551" s="16"/>
       <c r="D551" s="16"/>
@@ -11882,7 +11895,7 @@
       <c r="R551" s="16"/>
       <c r="S551" s="16"/>
     </row>
-    <row r="552" ht="14.25" customHeight="1">
+    <row r="552" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B552" s="16"/>
       <c r="C552" s="16"/>
       <c r="D552" s="16"/>
@@ -11902,7 +11915,7 @@
       <c r="R552" s="16"/>
       <c r="S552" s="16"/>
     </row>
-    <row r="553" ht="14.25" customHeight="1">
+    <row r="553" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B553" s="16"/>
       <c r="C553" s="16"/>
       <c r="D553" s="16"/>
@@ -11922,7 +11935,7 @@
       <c r="R553" s="16"/>
       <c r="S553" s="16"/>
     </row>
-    <row r="554" ht="14.25" customHeight="1">
+    <row r="554" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B554" s="16"/>
       <c r="C554" s="16"/>
       <c r="D554" s="16"/>
@@ -11942,7 +11955,7 @@
       <c r="R554" s="16"/>
       <c r="S554" s="16"/>
     </row>
-    <row r="555" ht="14.25" customHeight="1">
+    <row r="555" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B555" s="16"/>
       <c r="C555" s="16"/>
       <c r="D555" s="16"/>
@@ -11962,7 +11975,7 @@
       <c r="R555" s="16"/>
       <c r="S555" s="16"/>
     </row>
-    <row r="556" ht="14.25" customHeight="1">
+    <row r="556" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B556" s="16"/>
       <c r="C556" s="16"/>
       <c r="D556" s="16"/>
@@ -11982,7 +11995,7 @@
       <c r="R556" s="16"/>
       <c r="S556" s="16"/>
     </row>
-    <row r="557" ht="14.25" customHeight="1">
+    <row r="557" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B557" s="16"/>
       <c r="C557" s="16"/>
       <c r="D557" s="16"/>
@@ -12002,7 +12015,7 @@
       <c r="R557" s="16"/>
       <c r="S557" s="16"/>
     </row>
-    <row r="558" ht="14.25" customHeight="1">
+    <row r="558" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B558" s="16"/>
       <c r="C558" s="16"/>
       <c r="D558" s="16"/>
@@ -12022,7 +12035,7 @@
       <c r="R558" s="16"/>
       <c r="S558" s="16"/>
     </row>
-    <row r="559" ht="14.25" customHeight="1">
+    <row r="559" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B559" s="16"/>
       <c r="C559" s="16"/>
       <c r="D559" s="16"/>
@@ -12042,7 +12055,7 @@
       <c r="R559" s="16"/>
       <c r="S559" s="16"/>
     </row>
-    <row r="560" ht="14.25" customHeight="1">
+    <row r="560" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B560" s="16"/>
       <c r="C560" s="16"/>
       <c r="D560" s="16"/>
@@ -12062,7 +12075,7 @@
       <c r="R560" s="16"/>
       <c r="S560" s="16"/>
     </row>
-    <row r="561" ht="14.25" customHeight="1">
+    <row r="561" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B561" s="16"/>
       <c r="C561" s="16"/>
       <c r="D561" s="16"/>
@@ -12082,7 +12095,7 @@
       <c r="R561" s="16"/>
       <c r="S561" s="16"/>
     </row>
-    <row r="562" ht="14.25" customHeight="1">
+    <row r="562" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B562" s="16"/>
       <c r="C562" s="16"/>
       <c r="D562" s="16"/>
@@ -12102,7 +12115,7 @@
       <c r="R562" s="16"/>
       <c r="S562" s="16"/>
     </row>
-    <row r="563" ht="14.25" customHeight="1">
+    <row r="563" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B563" s="16"/>
       <c r="C563" s="16"/>
       <c r="D563" s="16"/>
@@ -12122,7 +12135,7 @@
       <c r="R563" s="16"/>
       <c r="S563" s="16"/>
     </row>
-    <row r="564" ht="14.25" customHeight="1">
+    <row r="564" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B564" s="16"/>
       <c r="C564" s="16"/>
       <c r="D564" s="16"/>
@@ -12142,7 +12155,7 @@
       <c r="R564" s="16"/>
       <c r="S564" s="16"/>
     </row>
-    <row r="565" ht="14.25" customHeight="1">
+    <row r="565" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B565" s="16"/>
       <c r="C565" s="16"/>
       <c r="D565" s="16"/>
@@ -12162,7 +12175,7 @@
       <c r="R565" s="16"/>
       <c r="S565" s="16"/>
     </row>
-    <row r="566" ht="14.25" customHeight="1">
+    <row r="566" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B566" s="16"/>
       <c r="C566" s="16"/>
       <c r="D566" s="16"/>
@@ -12182,7 +12195,7 @@
       <c r="R566" s="16"/>
       <c r="S566" s="16"/>
     </row>
-    <row r="567" ht="14.25" customHeight="1">
+    <row r="567" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B567" s="16"/>
       <c r="C567" s="16"/>
       <c r="D567" s="16"/>
@@ -12202,7 +12215,7 @@
       <c r="R567" s="16"/>
       <c r="S567" s="16"/>
     </row>
-    <row r="568" ht="14.25" customHeight="1">
+    <row r="568" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B568" s="16"/>
       <c r="C568" s="16"/>
       <c r="D568" s="16"/>
@@ -12222,7 +12235,7 @@
       <c r="R568" s="16"/>
       <c r="S568" s="16"/>
     </row>
-    <row r="569" ht="14.25" customHeight="1">
+    <row r="569" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B569" s="16"/>
       <c r="C569" s="16"/>
       <c r="D569" s="16"/>
@@ -12242,7 +12255,7 @@
       <c r="R569" s="16"/>
       <c r="S569" s="16"/>
     </row>
-    <row r="570" ht="14.25" customHeight="1">
+    <row r="570" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B570" s="16"/>
       <c r="C570" s="16"/>
       <c r="D570" s="16"/>
@@ -12262,7 +12275,7 @@
       <c r="R570" s="16"/>
       <c r="S570" s="16"/>
     </row>
-    <row r="571" ht="14.25" customHeight="1">
+    <row r="571" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B571" s="16"/>
       <c r="C571" s="16"/>
       <c r="D571" s="16"/>
@@ -12282,7 +12295,7 @@
       <c r="R571" s="16"/>
       <c r="S571" s="16"/>
     </row>
-    <row r="572" ht="14.25" customHeight="1">
+    <row r="572" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B572" s="16"/>
       <c r="C572" s="16"/>
       <c r="D572" s="16"/>
@@ -12302,7 +12315,7 @@
       <c r="R572" s="16"/>
       <c r="S572" s="16"/>
     </row>
-    <row r="573" ht="14.25" customHeight="1">
+    <row r="573" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B573" s="16"/>
       <c r="C573" s="16"/>
       <c r="D573" s="16"/>
@@ -12322,7 +12335,7 @@
       <c r="R573" s="16"/>
       <c r="S573" s="16"/>
     </row>
-    <row r="574" ht="14.25" customHeight="1">
+    <row r="574" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B574" s="16"/>
       <c r="C574" s="16"/>
       <c r="D574" s="16"/>
@@ -12342,7 +12355,7 @@
       <c r="R574" s="16"/>
       <c r="S574" s="16"/>
     </row>
-    <row r="575" ht="14.25" customHeight="1">
+    <row r="575" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B575" s="16"/>
       <c r="C575" s="16"/>
       <c r="D575" s="16"/>
@@ -12362,7 +12375,7 @@
       <c r="R575" s="16"/>
       <c r="S575" s="16"/>
     </row>
-    <row r="576" ht="14.25" customHeight="1">
+    <row r="576" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B576" s="16"/>
       <c r="C576" s="16"/>
       <c r="D576" s="16"/>
@@ -12382,7 +12395,7 @@
       <c r="R576" s="16"/>
       <c r="S576" s="16"/>
     </row>
-    <row r="577" ht="14.25" customHeight="1">
+    <row r="577" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B577" s="16"/>
       <c r="C577" s="16"/>
       <c r="D577" s="16"/>
@@ -12402,7 +12415,7 @@
       <c r="R577" s="16"/>
       <c r="S577" s="16"/>
     </row>
-    <row r="578" ht="14.25" customHeight="1">
+    <row r="578" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B578" s="16"/>
       <c r="C578" s="16"/>
       <c r="D578" s="16"/>
@@ -12422,7 +12435,7 @@
       <c r="R578" s="16"/>
       <c r="S578" s="16"/>
     </row>
-    <row r="579" ht="14.25" customHeight="1">
+    <row r="579" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B579" s="16"/>
       <c r="C579" s="16"/>
       <c r="D579" s="16"/>
@@ -12442,7 +12455,7 @@
       <c r="R579" s="16"/>
       <c r="S579" s="16"/>
     </row>
-    <row r="580" ht="14.25" customHeight="1">
+    <row r="580" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B580" s="16"/>
       <c r="C580" s="16"/>
       <c r="D580" s="16"/>
@@ -12462,7 +12475,7 @@
       <c r="R580" s="16"/>
       <c r="S580" s="16"/>
     </row>
-    <row r="581" ht="14.25" customHeight="1">
+    <row r="581" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B581" s="16"/>
       <c r="C581" s="16"/>
       <c r="D581" s="16"/>
@@ -12482,7 +12495,7 @@
       <c r="R581" s="16"/>
       <c r="S581" s="16"/>
     </row>
-    <row r="582" ht="14.25" customHeight="1">
+    <row r="582" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B582" s="16"/>
       <c r="C582" s="16"/>
       <c r="D582" s="16"/>
@@ -12502,7 +12515,7 @@
       <c r="R582" s="16"/>
       <c r="S582" s="16"/>
     </row>
-    <row r="583" ht="14.25" customHeight="1">
+    <row r="583" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B583" s="16"/>
       <c r="C583" s="16"/>
       <c r="D583" s="16"/>
@@ -12522,7 +12535,7 @@
       <c r="R583" s="16"/>
       <c r="S583" s="16"/>
     </row>
-    <row r="584" ht="14.25" customHeight="1">
+    <row r="584" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B584" s="16"/>
       <c r="C584" s="16"/>
       <c r="D584" s="16"/>
@@ -12542,7 +12555,7 @@
       <c r="R584" s="16"/>
       <c r="S584" s="16"/>
     </row>
-    <row r="585" ht="14.25" customHeight="1">
+    <row r="585" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B585" s="16"/>
       <c r="C585" s="16"/>
       <c r="D585" s="16"/>
@@ -12562,7 +12575,7 @@
       <c r="R585" s="16"/>
       <c r="S585" s="16"/>
     </row>
-    <row r="586" ht="14.25" customHeight="1">
+    <row r="586" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B586" s="16"/>
       <c r="C586" s="16"/>
       <c r="D586" s="16"/>
@@ -12582,7 +12595,7 @@
       <c r="R586" s="16"/>
       <c r="S586" s="16"/>
     </row>
-    <row r="587" ht="14.25" customHeight="1">
+    <row r="587" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B587" s="16"/>
       <c r="C587" s="16"/>
       <c r="D587" s="16"/>
@@ -12602,7 +12615,7 @@
       <c r="R587" s="16"/>
       <c r="S587" s="16"/>
     </row>
-    <row r="588" ht="14.25" customHeight="1">
+    <row r="588" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B588" s="16"/>
       <c r="C588" s="16"/>
       <c r="D588" s="16"/>
@@ -12622,7 +12635,7 @@
       <c r="R588" s="16"/>
       <c r="S588" s="16"/>
     </row>
-    <row r="589" ht="14.25" customHeight="1">
+    <row r="589" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B589" s="16"/>
       <c r="C589" s="16"/>
       <c r="D589" s="16"/>
@@ -12642,7 +12655,7 @@
       <c r="R589" s="16"/>
       <c r="S589" s="16"/>
     </row>
-    <row r="590" ht="14.25" customHeight="1">
+    <row r="590" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B590" s="16"/>
       <c r="C590" s="16"/>
       <c r="D590" s="16"/>
@@ -12662,7 +12675,7 @@
       <c r="R590" s="16"/>
       <c r="S590" s="16"/>
     </row>
-    <row r="591" ht="14.25" customHeight="1">
+    <row r="591" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B591" s="16"/>
       <c r="C591" s="16"/>
       <c r="D591" s="16"/>
@@ -12682,7 +12695,7 @@
       <c r="R591" s="16"/>
       <c r="S591" s="16"/>
     </row>
-    <row r="592" ht="14.25" customHeight="1">
+    <row r="592" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B592" s="16"/>
       <c r="C592" s="16"/>
       <c r="D592" s="16"/>
@@ -12702,7 +12715,7 @@
       <c r="R592" s="16"/>
       <c r="S592" s="16"/>
     </row>
-    <row r="593" ht="14.25" customHeight="1">
+    <row r="593" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B593" s="16"/>
       <c r="C593" s="16"/>
       <c r="D593" s="16"/>
@@ -12722,7 +12735,7 @@
       <c r="R593" s="16"/>
       <c r="S593" s="16"/>
     </row>
-    <row r="594" ht="14.25" customHeight="1">
+    <row r="594" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B594" s="16"/>
       <c r="C594" s="16"/>
       <c r="D594" s="16"/>
@@ -12742,7 +12755,7 @@
       <c r="R594" s="16"/>
       <c r="S594" s="16"/>
     </row>
-    <row r="595" ht="14.25" customHeight="1">
+    <row r="595" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B595" s="16"/>
       <c r="C595" s="16"/>
       <c r="D595" s="16"/>
@@ -12762,7 +12775,7 @@
       <c r="R595" s="16"/>
       <c r="S595" s="16"/>
     </row>
-    <row r="596" ht="14.25" customHeight="1">
+    <row r="596" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B596" s="16"/>
       <c r="C596" s="16"/>
       <c r="D596" s="16"/>
@@ -12782,7 +12795,7 @@
       <c r="R596" s="16"/>
       <c r="S596" s="16"/>
     </row>
-    <row r="597" ht="14.25" customHeight="1">
+    <row r="597" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B597" s="16"/>
       <c r="C597" s="16"/>
       <c r="D597" s="16"/>
@@ -12802,7 +12815,7 @@
       <c r="R597" s="16"/>
       <c r="S597" s="16"/>
     </row>
-    <row r="598" ht="14.25" customHeight="1">
+    <row r="598" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B598" s="16"/>
       <c r="C598" s="16"/>
       <c r="D598" s="16"/>
@@ -12822,7 +12835,7 @@
       <c r="R598" s="16"/>
       <c r="S598" s="16"/>
     </row>
-    <row r="599" ht="14.25" customHeight="1">
+    <row r="599" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B599" s="16"/>
       <c r="C599" s="16"/>
       <c r="D599" s="16"/>
@@ -12842,7 +12855,7 @@
       <c r="R599" s="16"/>
       <c r="S599" s="16"/>
     </row>
-    <row r="600" ht="14.25" customHeight="1">
+    <row r="600" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B600" s="16"/>
       <c r="C600" s="16"/>
       <c r="D600" s="16"/>
@@ -12862,7 +12875,7 @@
       <c r="R600" s="16"/>
       <c r="S600" s="16"/>
     </row>
-    <row r="601" ht="14.25" customHeight="1">
+    <row r="601" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B601" s="16"/>
       <c r="C601" s="16"/>
       <c r="D601" s="16"/>
@@ -12882,7 +12895,7 @@
       <c r="R601" s="16"/>
       <c r="S601" s="16"/>
     </row>
-    <row r="602" ht="14.25" customHeight="1">
+    <row r="602" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B602" s="16"/>
       <c r="C602" s="16"/>
       <c r="D602" s="16"/>
@@ -12902,7 +12915,7 @@
       <c r="R602" s="16"/>
       <c r="S602" s="16"/>
     </row>
-    <row r="603" ht="14.25" customHeight="1">
+    <row r="603" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B603" s="16"/>
       <c r="C603" s="16"/>
       <c r="D603" s="16"/>
@@ -12922,7 +12935,7 @@
       <c r="R603" s="16"/>
       <c r="S603" s="16"/>
     </row>
-    <row r="604" ht="14.25" customHeight="1">
+    <row r="604" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B604" s="16"/>
       <c r="C604" s="16"/>
       <c r="D604" s="16"/>
@@ -12942,7 +12955,7 @@
       <c r="R604" s="16"/>
       <c r="S604" s="16"/>
     </row>
-    <row r="605" ht="14.25" customHeight="1">
+    <row r="605" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B605" s="16"/>
       <c r="C605" s="16"/>
       <c r="D605" s="16"/>
@@ -12962,7 +12975,7 @@
       <c r="R605" s="16"/>
       <c r="S605" s="16"/>
     </row>
-    <row r="606" ht="14.25" customHeight="1">
+    <row r="606" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B606" s="16"/>
       <c r="C606" s="16"/>
       <c r="D606" s="16"/>
@@ -12982,7 +12995,7 @@
       <c r="R606" s="16"/>
       <c r="S606" s="16"/>
     </row>
-    <row r="607" ht="14.25" customHeight="1">
+    <row r="607" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B607" s="16"/>
       <c r="C607" s="16"/>
       <c r="D607" s="16"/>
@@ -13002,7 +13015,7 @@
       <c r="R607" s="16"/>
       <c r="S607" s="16"/>
     </row>
-    <row r="608" ht="14.25" customHeight="1">
+    <row r="608" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B608" s="16"/>
       <c r="C608" s="16"/>
       <c r="D608" s="16"/>
@@ -13022,7 +13035,7 @@
       <c r="R608" s="16"/>
       <c r="S608" s="16"/>
     </row>
-    <row r="609" ht="14.25" customHeight="1">
+    <row r="609" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B609" s="16"/>
       <c r="C609" s="16"/>
       <c r="D609" s="16"/>
@@ -13042,7 +13055,7 @@
       <c r="R609" s="16"/>
       <c r="S609" s="16"/>
     </row>
-    <row r="610" ht="14.25" customHeight="1">
+    <row r="610" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B610" s="16"/>
       <c r="C610" s="16"/>
       <c r="D610" s="16"/>
@@ -13062,7 +13075,7 @@
       <c r="R610" s="16"/>
       <c r="S610" s="16"/>
     </row>
-    <row r="611" ht="14.25" customHeight="1">
+    <row r="611" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B611" s="16"/>
       <c r="C611" s="16"/>
       <c r="D611" s="16"/>
@@ -13082,7 +13095,7 @@
       <c r="R611" s="16"/>
       <c r="S611" s="16"/>
     </row>
-    <row r="612" ht="14.25" customHeight="1">
+    <row r="612" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B612" s="16"/>
       <c r="C612" s="16"/>
       <c r="D612" s="16"/>
@@ -13102,7 +13115,7 @@
       <c r="R612" s="16"/>
       <c r="S612" s="16"/>
     </row>
-    <row r="613" ht="14.25" customHeight="1">
+    <row r="613" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B613" s="16"/>
       <c r="C613" s="16"/>
       <c r="D613" s="16"/>
@@ -13122,7 +13135,7 @@
       <c r="R613" s="16"/>
       <c r="S613" s="16"/>
     </row>
-    <row r="614" ht="14.25" customHeight="1">
+    <row r="614" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B614" s="16"/>
       <c r="C614" s="16"/>
       <c r="D614" s="16"/>
@@ -13142,7 +13155,7 @@
       <c r="R614" s="16"/>
       <c r="S614" s="16"/>
     </row>
-    <row r="615" ht="14.25" customHeight="1">
+    <row r="615" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B615" s="16"/>
       <c r="C615" s="16"/>
       <c r="D615" s="16"/>
@@ -13162,7 +13175,7 @@
       <c r="R615" s="16"/>
       <c r="S615" s="16"/>
     </row>
-    <row r="616" ht="14.25" customHeight="1">
+    <row r="616" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B616" s="16"/>
       <c r="C616" s="16"/>
       <c r="D616" s="16"/>
@@ -13182,7 +13195,7 @@
       <c r="R616" s="16"/>
       <c r="S616" s="16"/>
     </row>
-    <row r="617" ht="14.25" customHeight="1">
+    <row r="617" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B617" s="16"/>
       <c r="C617" s="16"/>
       <c r="D617" s="16"/>
@@ -13202,7 +13215,7 @@
       <c r="R617" s="16"/>
       <c r="S617" s="16"/>
     </row>
-    <row r="618" ht="14.25" customHeight="1">
+    <row r="618" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B618" s="16"/>
       <c r="C618" s="16"/>
       <c r="D618" s="16"/>
@@ -13222,7 +13235,7 @@
       <c r="R618" s="16"/>
       <c r="S618" s="16"/>
     </row>
-    <row r="619" ht="14.25" customHeight="1">
+    <row r="619" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B619" s="16"/>
       <c r="C619" s="16"/>
       <c r="D619" s="16"/>
@@ -13242,7 +13255,7 @@
       <c r="R619" s="16"/>
       <c r="S619" s="16"/>
     </row>
-    <row r="620" ht="14.25" customHeight="1">
+    <row r="620" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B620" s="16"/>
       <c r="C620" s="16"/>
       <c r="D620" s="16"/>
@@ -13262,7 +13275,7 @@
       <c r="R620" s="16"/>
       <c r="S620" s="16"/>
     </row>
-    <row r="621" ht="14.25" customHeight="1">
+    <row r="621" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B621" s="16"/>
       <c r="C621" s="16"/>
       <c r="D621" s="16"/>
@@ -13282,7 +13295,7 @@
       <c r="R621" s="16"/>
       <c r="S621" s="16"/>
     </row>
-    <row r="622" ht="14.25" customHeight="1">
+    <row r="622" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B622" s="16"/>
       <c r="C622" s="16"/>
       <c r="D622" s="16"/>
@@ -13302,7 +13315,7 @@
       <c r="R622" s="16"/>
       <c r="S622" s="16"/>
     </row>
-    <row r="623" ht="14.25" customHeight="1">
+    <row r="623" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B623" s="16"/>
       <c r="C623" s="16"/>
       <c r="D623" s="16"/>
@@ -13322,7 +13335,7 @@
       <c r="R623" s="16"/>
       <c r="S623" s="16"/>
     </row>
-    <row r="624" ht="14.25" customHeight="1">
+    <row r="624" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B624" s="16"/>
       <c r="C624" s="16"/>
       <c r="D624" s="16"/>
@@ -13342,7 +13355,7 @@
       <c r="R624" s="16"/>
       <c r="S624" s="16"/>
     </row>
-    <row r="625" ht="14.25" customHeight="1">
+    <row r="625" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B625" s="16"/>
       <c r="C625" s="16"/>
       <c r="D625" s="16"/>
@@ -13362,7 +13375,7 @@
       <c r="R625" s="16"/>
       <c r="S625" s="16"/>
     </row>
-    <row r="626" ht="14.25" customHeight="1">
+    <row r="626" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B626" s="16"/>
       <c r="C626" s="16"/>
       <c r="D626" s="16"/>
@@ -13382,7 +13395,7 @@
       <c r="R626" s="16"/>
       <c r="S626" s="16"/>
     </row>
-    <row r="627" ht="14.25" customHeight="1">
+    <row r="627" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B627" s="16"/>
       <c r="C627" s="16"/>
       <c r="D627" s="16"/>
@@ -13402,7 +13415,7 @@
       <c r="R627" s="16"/>
       <c r="S627" s="16"/>
     </row>
-    <row r="628" ht="14.25" customHeight="1">
+    <row r="628" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B628" s="16"/>
       <c r="C628" s="16"/>
       <c r="D628" s="16"/>
@@ -13422,7 +13435,7 @@
       <c r="R628" s="16"/>
       <c r="S628" s="16"/>
     </row>
-    <row r="629" ht="14.25" customHeight="1">
+    <row r="629" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B629" s="16"/>
       <c r="C629" s="16"/>
       <c r="D629" s="16"/>
@@ -13442,7 +13455,7 @@
       <c r="R629" s="16"/>
       <c r="S629" s="16"/>
     </row>
-    <row r="630" ht="14.25" customHeight="1">
+    <row r="630" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B630" s="16"/>
       <c r="C630" s="16"/>
       <c r="D630" s="16"/>
@@ -13462,7 +13475,7 @@
       <c r="R630" s="16"/>
       <c r="S630" s="16"/>
     </row>
-    <row r="631" ht="14.25" customHeight="1">
+    <row r="631" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B631" s="16"/>
       <c r="C631" s="16"/>
       <c r="D631" s="16"/>
@@ -13482,7 +13495,7 @@
       <c r="R631" s="16"/>
       <c r="S631" s="16"/>
     </row>
-    <row r="632" ht="14.25" customHeight="1">
+    <row r="632" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B632" s="16"/>
       <c r="C632" s="16"/>
       <c r="D632" s="16"/>
@@ -13502,7 +13515,7 @@
       <c r="R632" s="16"/>
       <c r="S632" s="16"/>
     </row>
-    <row r="633" ht="14.25" customHeight="1">
+    <row r="633" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B633" s="16"/>
       <c r="C633" s="16"/>
       <c r="D633" s="16"/>
@@ -13522,7 +13535,7 @@
       <c r="R633" s="16"/>
       <c r="S633" s="16"/>
     </row>
-    <row r="634" ht="14.25" customHeight="1">
+    <row r="634" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B634" s="16"/>
       <c r="C634" s="16"/>
       <c r="D634" s="16"/>
@@ -13542,7 +13555,7 @@
       <c r="R634" s="16"/>
       <c r="S634" s="16"/>
     </row>
-    <row r="635" ht="14.25" customHeight="1">
+    <row r="635" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B635" s="16"/>
       <c r="C635" s="16"/>
       <c r="D635" s="16"/>
@@ -13562,7 +13575,7 @@
       <c r="R635" s="16"/>
       <c r="S635" s="16"/>
     </row>
-    <row r="636" ht="14.25" customHeight="1">
+    <row r="636" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B636" s="16"/>
       <c r="C636" s="16"/>
       <c r="D636" s="16"/>
@@ -13582,7 +13595,7 @@
       <c r="R636" s="16"/>
       <c r="S636" s="16"/>
     </row>
-    <row r="637" ht="14.25" customHeight="1">
+    <row r="637" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B637" s="16"/>
       <c r="C637" s="16"/>
       <c r="D637" s="16"/>
@@ -13602,7 +13615,7 @@
       <c r="R637" s="16"/>
       <c r="S637" s="16"/>
     </row>
-    <row r="638" ht="14.25" customHeight="1">
+    <row r="638" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B638" s="16"/>
       <c r="C638" s="16"/>
       <c r="D638" s="16"/>
@@ -13622,7 +13635,7 @@
       <c r="R638" s="16"/>
       <c r="S638" s="16"/>
     </row>
-    <row r="639" ht="14.25" customHeight="1">
+    <row r="639" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B639" s="16"/>
       <c r="C639" s="16"/>
       <c r="D639" s="16"/>
@@ -13642,7 +13655,7 @@
       <c r="R639" s="16"/>
       <c r="S639" s="16"/>
     </row>
-    <row r="640" ht="14.25" customHeight="1">
+    <row r="640" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B640" s="16"/>
       <c r="C640" s="16"/>
       <c r="D640" s="16"/>
@@ -13662,7 +13675,7 @@
       <c r="R640" s="16"/>
       <c r="S640" s="16"/>
     </row>
-    <row r="641" ht="14.25" customHeight="1">
+    <row r="641" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B641" s="16"/>
       <c r="C641" s="16"/>
       <c r="D641" s="16"/>
@@ -13682,7 +13695,7 @@
       <c r="R641" s="16"/>
       <c r="S641" s="16"/>
     </row>
-    <row r="642" ht="14.25" customHeight="1">
+    <row r="642" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B642" s="16"/>
       <c r="C642" s="16"/>
       <c r="D642" s="16"/>
@@ -13702,7 +13715,7 @@
       <c r="R642" s="16"/>
       <c r="S642" s="16"/>
     </row>
-    <row r="643" ht="14.25" customHeight="1">
+    <row r="643" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B643" s="16"/>
       <c r="C643" s="16"/>
       <c r="D643" s="16"/>
@@ -13722,7 +13735,7 @@
       <c r="R643" s="16"/>
       <c r="S643" s="16"/>
     </row>
-    <row r="644" ht="14.25" customHeight="1">
+    <row r="644" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B644" s="16"/>
       <c r="C644" s="16"/>
       <c r="D644" s="16"/>
@@ -13742,7 +13755,7 @@
       <c r="R644" s="16"/>
       <c r="S644" s="16"/>
     </row>
-    <row r="645" ht="14.25" customHeight="1">
+    <row r="645" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B645" s="16"/>
       <c r="C645" s="16"/>
       <c r="D645" s="16"/>
@@ -13762,7 +13775,7 @@
       <c r="R645" s="16"/>
       <c r="S645" s="16"/>
     </row>
-    <row r="646" ht="14.25" customHeight="1">
+    <row r="646" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B646" s="16"/>
       <c r="C646" s="16"/>
       <c r="D646" s="16"/>
@@ -13782,7 +13795,7 @@
       <c r="R646" s="16"/>
       <c r="S646" s="16"/>
     </row>
-    <row r="647" ht="14.25" customHeight="1">
+    <row r="647" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B647" s="16"/>
       <c r="C647" s="16"/>
       <c r="D647" s="16"/>
@@ -13802,7 +13815,7 @@
       <c r="R647" s="16"/>
       <c r="S647" s="16"/>
     </row>
-    <row r="648" ht="14.25" customHeight="1">
+    <row r="648" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B648" s="16"/>
       <c r="C648" s="16"/>
       <c r="D648" s="16"/>
@@ -13822,7 +13835,7 @@
       <c r="R648" s="16"/>
       <c r="S648" s="16"/>
     </row>
-    <row r="649" ht="14.25" customHeight="1">
+    <row r="649" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B649" s="16"/>
       <c r="C649" s="16"/>
       <c r="D649" s="16"/>
@@ -13842,7 +13855,7 @@
       <c r="R649" s="16"/>
       <c r="S649" s="16"/>
     </row>
-    <row r="650" ht="14.25" customHeight="1">
+    <row r="650" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B650" s="16"/>
       <c r="C650" s="16"/>
       <c r="D650" s="16"/>
@@ -13862,7 +13875,7 @@
       <c r="R650" s="16"/>
       <c r="S650" s="16"/>
     </row>
-    <row r="651" ht="14.25" customHeight="1">
+    <row r="651" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B651" s="16"/>
       <c r="C651" s="16"/>
       <c r="D651" s="16"/>
@@ -13882,7 +13895,7 @@
       <c r="R651" s="16"/>
       <c r="S651" s="16"/>
     </row>
-    <row r="652" ht="14.25" customHeight="1">
+    <row r="652" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B652" s="16"/>
       <c r="C652" s="16"/>
       <c r="D652" s="16"/>
@@ -13902,7 +13915,7 @@
       <c r="R652" s="16"/>
       <c r="S652" s="16"/>
     </row>
-    <row r="653" ht="14.25" customHeight="1">
+    <row r="653" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B653" s="16"/>
       <c r="C653" s="16"/>
       <c r="D653" s="16"/>
@@ -13922,7 +13935,7 @@
       <c r="R653" s="16"/>
       <c r="S653" s="16"/>
     </row>
-    <row r="654" ht="14.25" customHeight="1">
+    <row r="654" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B654" s="16"/>
       <c r="C654" s="16"/>
       <c r="D654" s="16"/>
@@ -13942,7 +13955,7 @@
       <c r="R654" s="16"/>
       <c r="S654" s="16"/>
     </row>
-    <row r="655" ht="14.25" customHeight="1">
+    <row r="655" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B655" s="16"/>
       <c r="C655" s="16"/>
       <c r="D655" s="16"/>
@@ -13962,7 +13975,7 @@
       <c r="R655" s="16"/>
       <c r="S655" s="16"/>
     </row>
-    <row r="656" ht="14.25" customHeight="1">
+    <row r="656" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B656" s="16"/>
       <c r="C656" s="16"/>
       <c r="D656" s="16"/>
@@ -13982,7 +13995,7 @@
       <c r="R656" s="16"/>
       <c r="S656" s="16"/>
     </row>
-    <row r="657" ht="14.25" customHeight="1">
+    <row r="657" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B657" s="16"/>
       <c r="C657" s="16"/>
       <c r="D657" s="16"/>
@@ -14002,7 +14015,7 @@
       <c r="R657" s="16"/>
       <c r="S657" s="16"/>
     </row>
-    <row r="658" ht="14.25" customHeight="1">
+    <row r="658" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B658" s="16"/>
       <c r="C658" s="16"/>
       <c r="D658" s="16"/>
@@ -14022,7 +14035,7 @@
       <c r="R658" s="16"/>
       <c r="S658" s="16"/>
     </row>
-    <row r="659" ht="14.25" customHeight="1">
+    <row r="659" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B659" s="16"/>
       <c r="C659" s="16"/>
       <c r="D659" s="16"/>
@@ -14042,7 +14055,7 @@
       <c r="R659" s="16"/>
       <c r="S659" s="16"/>
     </row>
-    <row r="660" ht="14.25" customHeight="1">
+    <row r="660" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B660" s="16"/>
       <c r="C660" s="16"/>
       <c r="D660" s="16"/>
@@ -14062,7 +14075,7 @@
       <c r="R660" s="16"/>
       <c r="S660" s="16"/>
     </row>
-    <row r="661" ht="14.25" customHeight="1">
+    <row r="661" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B661" s="16"/>
       <c r="C661" s="16"/>
       <c r="D661" s="16"/>
@@ -14082,7 +14095,7 @@
       <c r="R661" s="16"/>
       <c r="S661" s="16"/>
     </row>
-    <row r="662" ht="14.25" customHeight="1">
+    <row r="662" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B662" s="16"/>
       <c r="C662" s="16"/>
       <c r="D662" s="16"/>
@@ -14102,7 +14115,7 @@
       <c r="R662" s="16"/>
       <c r="S662" s="16"/>
     </row>
-    <row r="663" ht="14.25" customHeight="1">
+    <row r="663" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B663" s="16"/>
       <c r="C663" s="16"/>
       <c r="D663" s="16"/>
@@ -14122,7 +14135,7 @@
       <c r="R663" s="16"/>
       <c r="S663" s="16"/>
     </row>
-    <row r="664" ht="14.25" customHeight="1">
+    <row r="664" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B664" s="16"/>
       <c r="C664" s="16"/>
       <c r="D664" s="16"/>
@@ -14142,7 +14155,7 @@
       <c r="R664" s="16"/>
       <c r="S664" s="16"/>
     </row>
-    <row r="665" ht="14.25" customHeight="1">
+    <row r="665" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B665" s="16"/>
       <c r="C665" s="16"/>
       <c r="D665" s="16"/>
@@ -14162,7 +14175,7 @@
       <c r="R665" s="16"/>
       <c r="S665" s="16"/>
     </row>
-    <row r="666" ht="14.25" customHeight="1">
+    <row r="666" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B666" s="16"/>
       <c r="C666" s="16"/>
       <c r="D666" s="16"/>
@@ -14182,7 +14195,7 @@
       <c r="R666" s="16"/>
       <c r="S666" s="16"/>
     </row>
-    <row r="667" ht="14.25" customHeight="1">
+    <row r="667" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B667" s="16"/>
       <c r="C667" s="16"/>
       <c r="D667" s="16"/>
@@ -14202,7 +14215,7 @@
       <c r="R667" s="16"/>
       <c r="S667" s="16"/>
     </row>
-    <row r="668" ht="14.25" customHeight="1">
+    <row r="668" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B668" s="16"/>
       <c r="C668" s="16"/>
       <c r="D668" s="16"/>
@@ -14222,7 +14235,7 @@
       <c r="R668" s="16"/>
       <c r="S668" s="16"/>
     </row>
-    <row r="669" ht="14.25" customHeight="1">
+    <row r="669" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B669" s="16"/>
       <c r="C669" s="16"/>
       <c r="D669" s="16"/>
@@ -14242,7 +14255,7 @@
       <c r="R669" s="16"/>
       <c r="S669" s="16"/>
     </row>
-    <row r="670" ht="14.25" customHeight="1">
+    <row r="670" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B670" s="16"/>
       <c r="C670" s="16"/>
       <c r="D670" s="16"/>
@@ -14262,7 +14275,7 @@
       <c r="R670" s="16"/>
       <c r="S670" s="16"/>
     </row>
-    <row r="671" ht="14.25" customHeight="1">
+    <row r="671" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B671" s="16"/>
       <c r="C671" s="16"/>
       <c r="D671" s="16"/>
@@ -14282,7 +14295,7 @@
       <c r="R671" s="16"/>
       <c r="S671" s="16"/>
     </row>
-    <row r="672" ht="14.25" customHeight="1">
+    <row r="672" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B672" s="16"/>
       <c r="C672" s="16"/>
       <c r="D672" s="16"/>
@@ -14302,7 +14315,7 @@
       <c r="R672" s="16"/>
       <c r="S672" s="16"/>
     </row>
-    <row r="673" ht="14.25" customHeight="1">
+    <row r="673" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B673" s="16"/>
       <c r="C673" s="16"/>
       <c r="D673" s="16"/>
@@ -14322,7 +14335,7 @@
       <c r="R673" s="16"/>
       <c r="S673" s="16"/>
     </row>
-    <row r="674" ht="14.25" customHeight="1">
+    <row r="674" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B674" s="16"/>
       <c r="C674" s="16"/>
       <c r="D674" s="16"/>
@@ -14342,7 +14355,7 @@
       <c r="R674" s="16"/>
       <c r="S674" s="16"/>
     </row>
-    <row r="675" ht="14.25" customHeight="1">
+    <row r="675" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B675" s="16"/>
       <c r="C675" s="16"/>
       <c r="D675" s="16"/>
@@ -14362,7 +14375,7 @@
       <c r="R675" s="16"/>
       <c r="S675" s="16"/>
     </row>
-    <row r="676" ht="14.25" customHeight="1">
+    <row r="676" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B676" s="16"/>
       <c r="C676" s="16"/>
       <c r="D676" s="16"/>
@@ -14382,7 +14395,7 @@
       <c r="R676" s="16"/>
       <c r="S676" s="16"/>
     </row>
-    <row r="677" ht="14.25" customHeight="1">
+    <row r="677" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B677" s="16"/>
       <c r="C677" s="16"/>
       <c r="D677" s="16"/>
@@ -14402,7 +14415,7 @@
       <c r="R677" s="16"/>
       <c r="S677" s="16"/>
     </row>
-    <row r="678" ht="14.25" customHeight="1">
+    <row r="678" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B678" s="16"/>
       <c r="C678" s="16"/>
       <c r="D678" s="16"/>
@@ -14422,7 +14435,7 @@
       <c r="R678" s="16"/>
       <c r="S678" s="16"/>
     </row>
-    <row r="679" ht="14.25" customHeight="1">
+    <row r="679" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B679" s="16"/>
       <c r="C679" s="16"/>
       <c r="D679" s="16"/>
@@ -14442,7 +14455,7 @@
       <c r="R679" s="16"/>
       <c r="S679" s="16"/>
     </row>
-    <row r="680" ht="14.25" customHeight="1">
+    <row r="680" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B680" s="16"/>
       <c r="C680" s="16"/>
       <c r="D680" s="16"/>
@@ -14462,7 +14475,7 @@
       <c r="R680" s="16"/>
       <c r="S680" s="16"/>
     </row>
-    <row r="681" ht="14.25" customHeight="1">
+    <row r="681" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B681" s="16"/>
       <c r="C681" s="16"/>
       <c r="D681" s="16"/>
@@ -14482,7 +14495,7 @@
       <c r="R681" s="16"/>
       <c r="S681" s="16"/>
     </row>
-    <row r="682" ht="14.25" customHeight="1">
+    <row r="682" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B682" s="16"/>
       <c r="C682" s="16"/>
       <c r="D682" s="16"/>
@@ -14502,7 +14515,7 @@
       <c r="R682" s="16"/>
       <c r="S682" s="16"/>
     </row>
-    <row r="683" ht="14.25" customHeight="1">
+    <row r="683" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B683" s="16"/>
       <c r="C683" s="16"/>
       <c r="D683" s="16"/>
@@ -14522,7 +14535,7 @@
       <c r="R683" s="16"/>
       <c r="S683" s="16"/>
     </row>
-    <row r="684" ht="14.25" customHeight="1">
+    <row r="684" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B684" s="16"/>
       <c r="C684" s="16"/>
       <c r="D684" s="16"/>
@@ -14542,7 +14555,7 @@
       <c r="R684" s="16"/>
       <c r="S684" s="16"/>
     </row>
-    <row r="685" ht="14.25" customHeight="1">
+    <row r="685" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B685" s="16"/>
       <c r="C685" s="16"/>
       <c r="D685" s="16"/>
@@ -14562,7 +14575,7 @@
       <c r="R685" s="16"/>
       <c r="S685" s="16"/>
     </row>
-    <row r="686" ht="14.25" customHeight="1">
+    <row r="686" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B686" s="16"/>
       <c r="C686" s="16"/>
       <c r="D686" s="16"/>
@@ -14582,7 +14595,7 @@
       <c r="R686" s="16"/>
       <c r="S686" s="16"/>
     </row>
-    <row r="687" ht="14.25" customHeight="1">
+    <row r="687" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B687" s="16"/>
       <c r="C687" s="16"/>
       <c r="D687" s="16"/>
@@ -14602,7 +14615,7 @@
       <c r="R687" s="16"/>
       <c r="S687" s="16"/>
     </row>
-    <row r="688" ht="14.25" customHeight="1">
+    <row r="688" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B688" s="16"/>
       <c r="C688" s="16"/>
       <c r="D688" s="16"/>
@@ -14622,7 +14635,7 @@
       <c r="R688" s="16"/>
       <c r="S688" s="16"/>
     </row>
-    <row r="689" ht="14.25" customHeight="1">
+    <row r="689" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B689" s="16"/>
       <c r="C689" s="16"/>
       <c r="D689" s="16"/>
@@ -14642,7 +14655,7 @@
       <c r="R689" s="16"/>
       <c r="S689" s="16"/>
     </row>
-    <row r="690" ht="14.25" customHeight="1">
+    <row r="690" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B690" s="16"/>
       <c r="C690" s="16"/>
       <c r="D690" s="16"/>
@@ -14662,7 +14675,7 @@
       <c r="R690" s="16"/>
       <c r="S690" s="16"/>
     </row>
-    <row r="691" ht="14.25" customHeight="1">
+    <row r="691" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B691" s="16"/>
       <c r="C691" s="16"/>
       <c r="D691" s="16"/>
@@ -14682,7 +14695,7 @@
       <c r="R691" s="16"/>
       <c r="S691" s="16"/>
     </row>
-    <row r="692" ht="14.25" customHeight="1">
+    <row r="692" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B692" s="16"/>
       <c r="C692" s="16"/>
       <c r="D692" s="16"/>
@@ -14702,7 +14715,7 @@
       <c r="R692" s="16"/>
       <c r="S692" s="16"/>
     </row>
-    <row r="693" ht="14.25" customHeight="1">
+    <row r="693" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B693" s="16"/>
       <c r="C693" s="16"/>
       <c r="D693" s="16"/>
@@ -14722,7 +14735,7 @@
       <c r="R693" s="16"/>
       <c r="S693" s="16"/>
     </row>
-    <row r="694" ht="14.25" customHeight="1">
+    <row r="694" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B694" s="16"/>
       <c r="C694" s="16"/>
       <c r="D694" s="16"/>
@@ -14742,7 +14755,7 @@
       <c r="R694" s="16"/>
       <c r="S694" s="16"/>
     </row>
-    <row r="695" ht="14.25" customHeight="1">
+    <row r="695" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B695" s="16"/>
       <c r="C695" s="16"/>
       <c r="D695" s="16"/>
@@ -14762,7 +14775,7 @@
       <c r="R695" s="16"/>
       <c r="S695" s="16"/>
     </row>
-    <row r="696" ht="14.25" customHeight="1">
+    <row r="696" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B696" s="16"/>
       <c r="C696" s="16"/>
       <c r="D696" s="16"/>
@@ -14782,7 +14795,7 @@
       <c r="R696" s="16"/>
       <c r="S696" s="16"/>
     </row>
-    <row r="697" ht="14.25" customHeight="1">
+    <row r="697" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B697" s="16"/>
       <c r="C697" s="16"/>
       <c r="D697" s="16"/>
@@ -14802,7 +14815,7 @@
       <c r="R697" s="16"/>
       <c r="S697" s="16"/>
     </row>
-    <row r="698" ht="14.25" customHeight="1">
+    <row r="698" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B698" s="16"/>
       <c r="C698" s="16"/>
       <c r="D698" s="16"/>
@@ -14822,7 +14835,7 @@
       <c r="R698" s="16"/>
       <c r="S698" s="16"/>
     </row>
-    <row r="699" ht="14.25" customHeight="1">
+    <row r="699" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B699" s="16"/>
       <c r="C699" s="16"/>
       <c r="D699" s="16"/>
@@ -14842,7 +14855,7 @@
       <c r="R699" s="16"/>
       <c r="S699" s="16"/>
     </row>
-    <row r="700" ht="14.25" customHeight="1">
+    <row r="700" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B700" s="16"/>
       <c r="C700" s="16"/>
       <c r="D700" s="16"/>
@@ -14862,7 +14875,7 @@
       <c r="R700" s="16"/>
       <c r="S700" s="16"/>
     </row>
-    <row r="701" ht="14.25" customHeight="1">
+    <row r="701" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B701" s="16"/>
       <c r="C701" s="16"/>
       <c r="D701" s="16"/>
@@ -14882,7 +14895,7 @@
       <c r="R701" s="16"/>
       <c r="S701" s="16"/>
     </row>
-    <row r="702" ht="14.25" customHeight="1">
+    <row r="702" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B702" s="16"/>
       <c r="C702" s="16"/>
       <c r="D702" s="16"/>
@@ -14902,7 +14915,7 @@
       <c r="R702" s="16"/>
       <c r="S702" s="16"/>
     </row>
-    <row r="703" ht="14.25" customHeight="1">
+    <row r="703" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B703" s="16"/>
       <c r="C703" s="16"/>
       <c r="D703" s="16"/>
@@ -14922,7 +14935,7 @@
       <c r="R703" s="16"/>
       <c r="S703" s="16"/>
     </row>
-    <row r="704" ht="14.25" customHeight="1">
+    <row r="704" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B704" s="16"/>
       <c r="C704" s="16"/>
       <c r="D704" s="16"/>
@@ -14942,7 +14955,7 @@
       <c r="R704" s="16"/>
       <c r="S704" s="16"/>
     </row>
-    <row r="705" ht="14.25" customHeight="1">
+    <row r="705" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B705" s="16"/>
       <c r="C705" s="16"/>
       <c r="D705" s="16"/>
@@ -14962,7 +14975,7 @@
       <c r="R705" s="16"/>
       <c r="S705" s="16"/>
     </row>
-    <row r="706" ht="14.25" customHeight="1">
+    <row r="706" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B706" s="16"/>
       <c r="C706" s="16"/>
       <c r="D706" s="16"/>
@@ -14982,7 +14995,7 @@
       <c r="R706" s="16"/>
       <c r="S706" s="16"/>
     </row>
-    <row r="707" ht="14.25" customHeight="1">
+    <row r="707" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B707" s="16"/>
       <c r="C707" s="16"/>
       <c r="D707" s="16"/>
@@ -15002,7 +15015,7 @@
       <c r="R707" s="16"/>
       <c r="S707" s="16"/>
     </row>
-    <row r="708" ht="14.25" customHeight="1">
+    <row r="708" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B708" s="16"/>
       <c r="C708" s="16"/>
       <c r="D708" s="16"/>
@@ -15022,7 +15035,7 @@
       <c r="R708" s="16"/>
       <c r="S708" s="16"/>
     </row>
-    <row r="709" ht="14.25" customHeight="1">
+    <row r="709" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B709" s="16"/>
       <c r="C709" s="16"/>
       <c r="D709" s="16"/>
@@ -15042,7 +15055,7 @@
       <c r="R709" s="16"/>
       <c r="S709" s="16"/>
     </row>
-    <row r="710" ht="14.25" customHeight="1">
+    <row r="710" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B710" s="16"/>
       <c r="C710" s="16"/>
       <c r="D710" s="16"/>
@@ -15062,7 +15075,7 @@
       <c r="R710" s="16"/>
       <c r="S710" s="16"/>
     </row>
-    <row r="711" ht="14.25" customHeight="1">
+    <row r="711" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B711" s="16"/>
       <c r="C711" s="16"/>
       <c r="D711" s="16"/>
@@ -15082,7 +15095,7 @@
       <c r="R711" s="16"/>
       <c r="S711" s="16"/>
     </row>
-    <row r="712" ht="14.25" customHeight="1">
+    <row r="712" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B712" s="16"/>
       <c r="C712" s="16"/>
       <c r="D712" s="16"/>
@@ -15102,7 +15115,7 @@
       <c r="R712" s="16"/>
       <c r="S712" s="16"/>
     </row>
-    <row r="713" ht="14.25" customHeight="1">
+    <row r="713" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B713" s="16"/>
       <c r="C713" s="16"/>
       <c r="D713" s="16"/>
@@ -15122,7 +15135,7 @@
       <c r="R713" s="16"/>
       <c r="S713" s="16"/>
     </row>
-    <row r="714" ht="14.25" customHeight="1">
+    <row r="714" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B714" s="16"/>
       <c r="C714" s="16"/>
       <c r="D714" s="16"/>
@@ -15142,7 +15155,7 @@
       <c r="R714" s="16"/>
       <c r="S714" s="16"/>
     </row>
-    <row r="715" ht="14.25" customHeight="1">
+    <row r="715" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B715" s="16"/>
       <c r="C715" s="16"/>
       <c r="D715" s="16"/>
@@ -15162,7 +15175,7 @@
       <c r="R715" s="16"/>
       <c r="S715" s="16"/>
     </row>
-    <row r="716" ht="14.25" customHeight="1">
+    <row r="716" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B716" s="16"/>
       <c r="C716" s="16"/>
       <c r="D716" s="16"/>
@@ -15182,7 +15195,7 @@
       <c r="R716" s="16"/>
       <c r="S716" s="16"/>
     </row>
-    <row r="717" ht="14.25" customHeight="1">
+    <row r="717" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B717" s="16"/>
       <c r="C717" s="16"/>
       <c r="D717" s="16"/>
@@ -15202,7 +15215,7 @@
       <c r="R717" s="16"/>
       <c r="S717" s="16"/>
     </row>
-    <row r="718" ht="14.25" customHeight="1">
+    <row r="718" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B718" s="16"/>
       <c r="C718" s="16"/>
       <c r="D718" s="16"/>
@@ -15222,7 +15235,7 @@
       <c r="R718" s="16"/>
       <c r="S718" s="16"/>
     </row>
-    <row r="719" ht="14.25" customHeight="1">
+    <row r="719" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B719" s="16"/>
       <c r="C719" s="16"/>
       <c r="D719" s="16"/>
@@ -15242,7 +15255,7 @@
       <c r="R719" s="16"/>
       <c r="S719" s="16"/>
     </row>
-    <row r="720" ht="14.25" customHeight="1">
+    <row r="720" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B720" s="16"/>
       <c r="C720" s="16"/>
       <c r="D720" s="16"/>
@@ -15262,7 +15275,7 @@
       <c r="R720" s="16"/>
       <c r="S720" s="16"/>
     </row>
-    <row r="721" ht="14.25" customHeight="1">
+    <row r="721" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B721" s="16"/>
       <c r="C721" s="16"/>
       <c r="D721" s="16"/>
@@ -15282,7 +15295,7 @@
       <c r="R721" s="16"/>
       <c r="S721" s="16"/>
     </row>
-    <row r="722" ht="14.25" customHeight="1">
+    <row r="722" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B722" s="16"/>
       <c r="C722" s="16"/>
       <c r="D722" s="16"/>
@@ -15302,7 +15315,7 @@
       <c r="R722" s="16"/>
       <c r="S722" s="16"/>
     </row>
-    <row r="723" ht="14.25" customHeight="1">
+    <row r="723" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B723" s="16"/>
       <c r="C723" s="16"/>
       <c r="D723" s="16"/>
@@ -15322,7 +15335,7 @@
       <c r="R723" s="16"/>
       <c r="S723" s="16"/>
     </row>
-    <row r="724" ht="14.25" customHeight="1">
+    <row r="724" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B724" s="16"/>
       <c r="C724" s="16"/>
       <c r="D724" s="16"/>
@@ -15342,7 +15355,7 @@
       <c r="R724" s="16"/>
       <c r="S724" s="16"/>
     </row>
-    <row r="725" ht="14.25" customHeight="1">
+    <row r="725" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B725" s="16"/>
       <c r="C725" s="16"/>
       <c r="D725" s="16"/>
@@ -15362,7 +15375,7 @@
       <c r="R725" s="16"/>
       <c r="S725" s="16"/>
     </row>
-    <row r="726" ht="14.25" customHeight="1">
+    <row r="726" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B726" s="16"/>
       <c r="C726" s="16"/>
       <c r="D726" s="16"/>
@@ -15382,7 +15395,7 @@
       <c r="R726" s="16"/>
       <c r="S726" s="16"/>
     </row>
-    <row r="727" ht="14.25" customHeight="1">
+    <row r="727" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B727" s="16"/>
       <c r="C727" s="16"/>
       <c r="D727" s="16"/>
@@ -15402,7 +15415,7 @@
       <c r="R727" s="16"/>
       <c r="S727" s="16"/>
     </row>
-    <row r="728" ht="14.25" customHeight="1">
+    <row r="728" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B728" s="16"/>
       <c r="C728" s="16"/>
       <c r="D728" s="16"/>
@@ -15422,7 +15435,7 @@
       <c r="R728" s="16"/>
       <c r="S728" s="16"/>
     </row>
-    <row r="729" ht="14.25" customHeight="1">
+    <row r="729" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B729" s="16"/>
       <c r="C729" s="16"/>
       <c r="D729" s="16"/>
@@ -15442,7 +15455,7 @@
       <c r="R729" s="16"/>
       <c r="S729" s="16"/>
     </row>
-    <row r="730" ht="14.25" customHeight="1">
+    <row r="730" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B730" s="16"/>
       <c r="C730" s="16"/>
       <c r="D730" s="16"/>
@@ -15462,7 +15475,7 @@
       <c r="R730" s="16"/>
       <c r="S730" s="16"/>
     </row>
-    <row r="731" ht="14.25" customHeight="1">
+    <row r="731" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B731" s="16"/>
       <c r="C731" s="16"/>
       <c r="D731" s="16"/>
@@ -15482,7 +15495,7 @@
       <c r="R731" s="16"/>
       <c r="S731" s="16"/>
     </row>
-    <row r="732" ht="14.25" customHeight="1">
+    <row r="732" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B732" s="16"/>
       <c r="C732" s="16"/>
       <c r="D732" s="16"/>
@@ -15502,7 +15515,7 @@
       <c r="R732" s="16"/>
       <c r="S732" s="16"/>
     </row>
-    <row r="733" ht="14.25" customHeight="1">
+    <row r="733" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B733" s="16"/>
       <c r="C733" s="16"/>
       <c r="D733" s="16"/>
@@ -15522,7 +15535,7 @@
       <c r="R733" s="16"/>
       <c r="S733" s="16"/>
     </row>
-    <row r="734" ht="14.25" customHeight="1">
+    <row r="734" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B734" s="16"/>
       <c r="C734" s="16"/>
       <c r="D734" s="16"/>
@@ -15542,7 +15555,7 @@
       <c r="R734" s="16"/>
       <c r="S734" s="16"/>
     </row>
-    <row r="735" ht="14.25" customHeight="1">
+    <row r="735" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B735" s="16"/>
       <c r="C735" s="16"/>
       <c r="D735" s="16"/>
@@ -15562,7 +15575,7 @@
       <c r="R735" s="16"/>
       <c r="S735" s="16"/>
     </row>
-    <row r="736" ht="14.25" customHeight="1">
+    <row r="736" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B736" s="16"/>
       <c r="C736" s="16"/>
       <c r="D736" s="16"/>
@@ -15582,7 +15595,7 @@
       <c r="R736" s="16"/>
       <c r="S736" s="16"/>
     </row>
-    <row r="737" ht="14.25" customHeight="1">
+    <row r="737" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B737" s="16"/>
       <c r="C737" s="16"/>
       <c r="D737" s="16"/>
@@ -15602,7 +15615,7 @@
       <c r="R737" s="16"/>
       <c r="S737" s="16"/>
     </row>
-    <row r="738" ht="14.25" customHeight="1">
+    <row r="738" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B738" s="16"/>
       <c r="C738" s="16"/>
       <c r="D738" s="16"/>
@@ -15622,7 +15635,7 @@
       <c r="R738" s="16"/>
       <c r="S738" s="16"/>
     </row>
-    <row r="739" ht="14.25" customHeight="1">
+    <row r="739" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B739" s="16"/>
       <c r="C739" s="16"/>
       <c r="D739" s="16"/>
@@ -15642,7 +15655,7 @@
       <c r="R739" s="16"/>
       <c r="S739" s="16"/>
     </row>
-    <row r="740" ht="14.25" customHeight="1">
+    <row r="740" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B740" s="16"/>
       <c r="C740" s="16"/>
       <c r="D740" s="16"/>
@@ -15662,7 +15675,7 @@
       <c r="R740" s="16"/>
       <c r="S740" s="16"/>
     </row>
-    <row r="741" ht="14.25" customHeight="1">
+    <row r="741" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B741" s="16"/>
       <c r="C741" s="16"/>
       <c r="D741" s="16"/>
@@ -15682,7 +15695,7 @@
       <c r="R741" s="16"/>
       <c r="S741" s="16"/>
     </row>
-    <row r="742" ht="14.25" customHeight="1">
+    <row r="742" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B742" s="16"/>
       <c r="C742" s="16"/>
       <c r="D742" s="16"/>
@@ -15702,7 +15715,7 @@
       <c r="R742" s="16"/>
       <c r="S742" s="16"/>
     </row>
-    <row r="743" ht="14.25" customHeight="1">
+    <row r="743" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B743" s="16"/>
       <c r="C743" s="16"/>
       <c r="D743" s="16"/>
@@ -15722,7 +15735,7 @@
       <c r="R743" s="16"/>
       <c r="S743" s="16"/>
     </row>
-    <row r="744" ht="14.25" customHeight="1">
+    <row r="744" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B744" s="16"/>
       <c r="C744" s="16"/>
       <c r="D744" s="16"/>
@@ -15742,7 +15755,7 @@
       <c r="R744" s="16"/>
       <c r="S744" s="16"/>
     </row>
-    <row r="745" ht="14.25" customHeight="1">
+    <row r="745" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B745" s="16"/>
       <c r="C745" s="16"/>
       <c r="D745" s="16"/>
@@ -15762,7 +15775,7 @@
       <c r="R745" s="16"/>
       <c r="S745" s="16"/>
     </row>
-    <row r="746" ht="14.25" customHeight="1">
+    <row r="746" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B746" s="16"/>
       <c r="C746" s="16"/>
       <c r="D746" s="16"/>
@@ -15782,7 +15795,7 @@
       <c r="R746" s="16"/>
       <c r="S746" s="16"/>
     </row>
-    <row r="747" ht="14.25" customHeight="1">
+    <row r="747" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B747" s="16"/>
       <c r="C747" s="16"/>
       <c r="D747" s="16"/>
@@ -15802,7 +15815,7 @@
       <c r="R747" s="16"/>
       <c r="S747" s="16"/>
     </row>
-    <row r="748" ht="14.25" customHeight="1">
+    <row r="748" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B748" s="16"/>
       <c r="C748" s="16"/>
       <c r="D748" s="16"/>
@@ -15822,7 +15835,7 @@
       <c r="R748" s="16"/>
       <c r="S748" s="16"/>
     </row>
-    <row r="749" ht="14.25" customHeight="1">
+    <row r="749" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B749" s="16"/>
       <c r="C749" s="16"/>
       <c r="D749" s="16"/>
@@ -15842,7 +15855,7 @@
       <c r="R749" s="16"/>
       <c r="S749" s="16"/>
     </row>
-    <row r="750" ht="14.25" customHeight="1">
+    <row r="750" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B750" s="16"/>
       <c r="C750" s="16"/>
       <c r="D750" s="16"/>
@@ -15862,7 +15875,7 @@
       <c r="R750" s="16"/>
       <c r="S750" s="16"/>
     </row>
-    <row r="751" ht="14.25" customHeight="1">
+    <row r="751" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B751" s="16"/>
       <c r="C751" s="16"/>
       <c r="D751" s="16"/>
@@ -15882,7 +15895,7 @@
       <c r="R751" s="16"/>
       <c r="S751" s="16"/>
     </row>
-    <row r="752" ht="14.25" customHeight="1">
+    <row r="752" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B752" s="16"/>
       <c r="C752" s="16"/>
       <c r="D752" s="16"/>
@@ -15902,7 +15915,7 @@
       <c r="R752" s="16"/>
       <c r="S752" s="16"/>
     </row>
-    <row r="753" ht="14.25" customHeight="1">
+    <row r="753" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B753" s="16"/>
       <c r="C753" s="16"/>
       <c r="D753" s="16"/>
@@ -15922,7 +15935,7 @@
       <c r="R753" s="16"/>
       <c r="S753" s="16"/>
     </row>
-    <row r="754" ht="14.25" customHeight="1">
+    <row r="754" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B754" s="16"/>
       <c r="C754" s="16"/>
       <c r="D754" s="16"/>
@@ -15942,7 +15955,7 @@
       <c r="R754" s="16"/>
       <c r="S754" s="16"/>
     </row>
-    <row r="755" ht="14.25" customHeight="1">
+    <row r="755" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B755" s="16"/>
       <c r="C755" s="16"/>
       <c r="D755" s="16"/>
@@ -15962,7 +15975,7 @@
       <c r="R755" s="16"/>
       <c r="S755" s="16"/>
     </row>
-    <row r="756" ht="14.25" customHeight="1">
+    <row r="756" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B756" s="16"/>
       <c r="C756" s="16"/>
       <c r="D756" s="16"/>
@@ -15982,7 +15995,7 @@
       <c r="R756" s="16"/>
       <c r="S756" s="16"/>
     </row>
-    <row r="757" ht="14.25" customHeight="1">
+    <row r="757" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B757" s="16"/>
       <c r="C757" s="16"/>
       <c r="D757" s="16"/>
@@ -16002,7 +16015,7 @@
       <c r="R757" s="16"/>
       <c r="S757" s="16"/>
     </row>
-    <row r="758" ht="14.25" customHeight="1">
+    <row r="758" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B758" s="16"/>
       <c r="C758" s="16"/>
       <c r="D758" s="16"/>
@@ -16022,7 +16035,7 @@
       <c r="R758" s="16"/>
       <c r="S758" s="16"/>
     </row>
-    <row r="759" ht="14.25" customHeight="1">
+    <row r="759" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B759" s="16"/>
       <c r="C759" s="16"/>
       <c r="D759" s="16"/>
@@ -16042,7 +16055,7 @@
       <c r="R759" s="16"/>
       <c r="S759" s="16"/>
     </row>
-    <row r="760" ht="14.25" customHeight="1">
+    <row r="760" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B760" s="16"/>
       <c r="C760" s="16"/>
       <c r="D760" s="16"/>
@@ -16062,7 +16075,7 @@
       <c r="R760" s="16"/>
       <c r="S760" s="16"/>
     </row>
-    <row r="761" ht="14.25" customHeight="1">
+    <row r="761" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B761" s="16"/>
       <c r="C761" s="16"/>
       <c r="D761" s="16"/>
@@ -16082,7 +16095,7 @@
       <c r="R761" s="16"/>
       <c r="S761" s="16"/>
     </row>
-    <row r="762" ht="14.25" customHeight="1">
+    <row r="762" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B762" s="16"/>
       <c r="C762" s="16"/>
       <c r="D762" s="16"/>
@@ -16102,7 +16115,7 @@
       <c r="R762" s="16"/>
       <c r="S762" s="16"/>
     </row>
-    <row r="763" ht="14.25" customHeight="1">
+    <row r="763" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B763" s="16"/>
       <c r="C763" s="16"/>
       <c r="D763" s="16"/>
@@ -16122,7 +16135,7 @@
       <c r="R763" s="16"/>
       <c r="S763" s="16"/>
     </row>
-    <row r="764" ht="14.25" customHeight="1">
+    <row r="764" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B764" s="16"/>
       <c r="C764" s="16"/>
       <c r="D764" s="16"/>
@@ -16142,7 +16155,7 @@
       <c r="R764" s="16"/>
       <c r="S764" s="16"/>
     </row>
-    <row r="765" ht="14.25" customHeight="1">
+    <row r="765" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B765" s="16"/>
       <c r="C765" s="16"/>
       <c r="D765" s="16"/>
@@ -16162,7 +16175,7 @@
       <c r="R765" s="16"/>
       <c r="S765" s="16"/>
     </row>
-    <row r="766" ht="14.25" customHeight="1">
+    <row r="766" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B766" s="16"/>
       <c r="C766" s="16"/>
       <c r="D766" s="16"/>
@@ -16182,7 +16195,7 @@
       <c r="R766" s="16"/>
       <c r="S766" s="16"/>
     </row>
-    <row r="767" ht="14.25" customHeight="1">
+    <row r="767" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B767" s="16"/>
       <c r="C767" s="16"/>
       <c r="D767" s="16"/>
@@ -16202,7 +16215,7 @@
       <c r="R767" s="16"/>
       <c r="S767" s="16"/>
     </row>
-    <row r="768" ht="14.25" customHeight="1">
+    <row r="768" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B768" s="16"/>
       <c r="C768" s="16"/>
       <c r="D768" s="16"/>
@@ -16222,7 +16235,7 @@
       <c r="R768" s="16"/>
       <c r="S768" s="16"/>
     </row>
-    <row r="769" ht="14.25" customHeight="1">
+    <row r="769" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B769" s="16"/>
       <c r="C769" s="16"/>
       <c r="D769" s="16"/>
@@ -16242,7 +16255,7 @@
       <c r="R769" s="16"/>
       <c r="S769" s="16"/>
     </row>
-    <row r="770" ht="14.25" customHeight="1">
+    <row r="770" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B770" s="16"/>
       <c r="C770" s="16"/>
       <c r="D770" s="16"/>
@@ -16262,7 +16275,7 @@
       <c r="R770" s="16"/>
       <c r="S770" s="16"/>
     </row>
-    <row r="771" ht="14.25" customHeight="1">
+    <row r="771" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B771" s="16"/>
       <c r="C771" s="16"/>
       <c r="D771" s="16"/>
@@ -16282,7 +16295,7 @@
       <c r="R771" s="16"/>
       <c r="S771" s="16"/>
     </row>
-    <row r="772" ht="14.25" customHeight="1">
+    <row r="772" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B772" s="16"/>
       <c r="C772" s="16"/>
       <c r="D772" s="16"/>
@@ -16302,7 +16315,7 @@
       <c r="R772" s="16"/>
       <c r="S772" s="16"/>
     </row>
-    <row r="773" ht="14.25" customHeight="1">
+    <row r="773" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B773" s="16"/>
       <c r="C773" s="16"/>
       <c r="D773" s="16"/>
@@ -16322,7 +16335,7 @@
       <c r="R773" s="16"/>
       <c r="S773" s="16"/>
     </row>
-    <row r="774" ht="14.25" customHeight="1">
+    <row r="774" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B774" s="16"/>
       <c r="C774" s="16"/>
       <c r="D774" s="16"/>
@@ -16342,7 +16355,7 @@
       <c r="R774" s="16"/>
       <c r="S774" s="16"/>
     </row>
-    <row r="775" ht="14.25" customHeight="1">
+    <row r="775" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B775" s="16"/>
       <c r="C775" s="16"/>
       <c r="D775" s="16"/>
@@ -16362,7 +16375,7 @@
       <c r="R775" s="16"/>
       <c r="S775" s="16"/>
     </row>
-    <row r="776" ht="14.25" customHeight="1">
+    <row r="776" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B776" s="16"/>
       <c r="C776" s="16"/>
       <c r="D776" s="16"/>
@@ -16382,7 +16395,7 @@
       <c r="R776" s="16"/>
       <c r="S776" s="16"/>
     </row>
-    <row r="777" ht="14.25" customHeight="1">
+    <row r="777" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B777" s="16"/>
       <c r="C777" s="16"/>
       <c r="D777" s="16"/>
@@ -16402,7 +16415,7 @@
       <c r="R777" s="16"/>
       <c r="S777" s="16"/>
     </row>
-    <row r="778" ht="14.25" customHeight="1">
+    <row r="778" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B778" s="16"/>
       <c r="C778" s="16"/>
       <c r="D778" s="16"/>
@@ -16422,7 +16435,7 @@
       <c r="R778" s="16"/>
       <c r="S778" s="16"/>
     </row>
-    <row r="779" ht="14.25" customHeight="1">
+    <row r="779" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B779" s="16"/>
       <c r="C779" s="16"/>
       <c r="D779" s="16"/>
@@ -16442,7 +16455,7 @@
       <c r="R779" s="16"/>
       <c r="S779" s="16"/>
     </row>
-    <row r="780" ht="14.25" customHeight="1">
+    <row r="780" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B780" s="16"/>
       <c r="C780" s="16"/>
       <c r="D780" s="16"/>
@@ -16462,7 +16475,7 @@
       <c r="R780" s="16"/>
       <c r="S780" s="16"/>
     </row>
-    <row r="781" ht="14.25" customHeight="1">
+    <row r="781" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B781" s="16"/>
       <c r="C781" s="16"/>
       <c r="D781" s="16"/>
@@ -16482,7 +16495,7 @@
       <c r="R781" s="16"/>
       <c r="S781" s="16"/>
     </row>
-    <row r="782" ht="14.25" customHeight="1">
+    <row r="782" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B782" s="16"/>
       <c r="C782" s="16"/>
       <c r="D782" s="16"/>
@@ -16502,7 +16515,7 @@
       <c r="R782" s="16"/>
       <c r="S782" s="16"/>
     </row>
-    <row r="783" ht="14.25" customHeight="1">
+    <row r="783" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B783" s="16"/>
       <c r="C783" s="16"/>
       <c r="D783" s="16"/>
@@ -16522,7 +16535,7 @@
       <c r="R783" s="16"/>
       <c r="S783" s="16"/>
     </row>
-    <row r="784" ht="14.25" customHeight="1">
+    <row r="784" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B784" s="16"/>
       <c r="C784" s="16"/>
       <c r="D784" s="16"/>
@@ -16542,7 +16555,7 @@
       <c r="R784" s="16"/>
       <c r="S784" s="16"/>
     </row>
-    <row r="785" ht="14.25" customHeight="1">
+    <row r="785" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B785" s="16"/>
       <c r="C785" s="16"/>
       <c r="D785" s="16"/>
@@ -16562,7 +16575,7 @@
       <c r="R785" s="16"/>
       <c r="S785" s="16"/>
     </row>
-    <row r="786" ht="14.25" customHeight="1">
+    <row r="786" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B786" s="16"/>
       <c r="C786" s="16"/>
       <c r="D786" s="16"/>
@@ -16582,7 +16595,7 @@
       <c r="R786" s="16"/>
       <c r="S786" s="16"/>
     </row>
-    <row r="787" ht="14.25" customHeight="1">
+    <row r="787" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B787" s="16"/>
       <c r="C787" s="16"/>
       <c r="D787" s="16"/>
@@ -16602,7 +16615,7 @@
       <c r="R787" s="16"/>
       <c r="S787" s="16"/>
     </row>
-    <row r="788" ht="14.25" customHeight="1">
+    <row r="788" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B788" s="16"/>
       <c r="C788" s="16"/>
       <c r="D788" s="16"/>
@@ -16622,7 +16635,7 @@
       <c r="R788" s="16"/>
       <c r="S788" s="16"/>
     </row>
-    <row r="789" ht="14.25" customHeight="1">
+    <row r="789" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B789" s="16"/>
       <c r="C789" s="16"/>
       <c r="D789" s="16"/>
@@ -16642,7 +16655,7 @@
       <c r="R789" s="16"/>
       <c r="S789" s="16"/>
     </row>
-    <row r="790" ht="14.25" customHeight="1">
+    <row r="790" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B790" s="16"/>
       <c r="C790" s="16"/>
       <c r="D790" s="16"/>
@@ -16662,7 +16675,7 @@
       <c r="R790" s="16"/>
       <c r="S790" s="16"/>
     </row>
-    <row r="791" ht="14.25" customHeight="1">
+    <row r="791" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B791" s="16"/>
       <c r="C791" s="16"/>
       <c r="D791" s="16"/>
@@ -16682,7 +16695,7 @@
       <c r="R791" s="16"/>
       <c r="S791" s="16"/>
     </row>
-    <row r="792" ht="14.25" customHeight="1">
+    <row r="792" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B792" s="16"/>
       <c r="C792" s="16"/>
       <c r="D792" s="16"/>
@@ -16702,7 +16715,7 @@
       <c r="R792" s="16"/>
       <c r="S792" s="16"/>
     </row>
-    <row r="793" ht="14.25" customHeight="1">
+    <row r="793" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B793" s="16"/>
       <c r="C793" s="16"/>
       <c r="D793" s="16"/>
@@ -16722,7 +16735,7 @@
       <c r="R793" s="16"/>
       <c r="S793" s="16"/>
     </row>
-    <row r="794" ht="14.25" customHeight="1">
+    <row r="794" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B794" s="16"/>
       <c r="C794" s="16"/>
       <c r="D794" s="16"/>
@@ -16742,7 +16755,7 @@
       <c r="R794" s="16"/>
       <c r="S794" s="16"/>
     </row>
-    <row r="795" ht="14.25" customHeight="1">
+    <row r="795" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B795" s="16"/>
       <c r="C795" s="16"/>
       <c r="D795" s="16"/>
@@ -16762,7 +16775,7 @@
       <c r="R795" s="16"/>
       <c r="S795" s="16"/>
     </row>
-    <row r="796" ht="14.25" customHeight="1">
+    <row r="796" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B796" s="16"/>
       <c r="C796" s="16"/>
       <c r="D796" s="16"/>
@@ -16782,7 +16795,7 @@
       <c r="R796" s="16"/>
       <c r="S796" s="16"/>
     </row>
-    <row r="797" ht="14.25" customHeight="1">
+    <row r="797" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B797" s="16"/>
       <c r="C797" s="16"/>
       <c r="D797" s="16"/>
@@ -16802,7 +16815,7 @@
       <c r="R797" s="16"/>
       <c r="S797" s="16"/>
     </row>
-    <row r="798" ht="14.25" customHeight="1">
+    <row r="798" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B798" s="16"/>
       <c r="C798" s="16"/>
       <c r="D798" s="16"/>
@@ -16822,7 +16835,7 @@
       <c r="R798" s="16"/>
       <c r="S798" s="16"/>
     </row>
-    <row r="799" ht="14.25" customHeight="1">
+    <row r="799" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B799" s="16"/>
       <c r="C799" s="16"/>
       <c r="D799" s="16"/>
@@ -16842,7 +16855,7 @@
       <c r="R799" s="16"/>
       <c r="S799" s="16"/>
     </row>
-    <row r="800" ht="14.25" customHeight="1">
+    <row r="800" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B800" s="16"/>
       <c r="C800" s="16"/>
       <c r="D800" s="16"/>
@@ -16862,7 +16875,7 @@
       <c r="R800" s="16"/>
       <c r="S800" s="16"/>
     </row>
-    <row r="801" ht="14.25" customHeight="1">
+    <row r="801" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B801" s="16"/>
       <c r="C801" s="16"/>
       <c r="D801" s="16"/>
@@ -16882,7 +16895,7 @@
       <c r="R801" s="16"/>
       <c r="S801" s="16"/>
     </row>
-    <row r="802" ht="14.25" customHeight="1">
+    <row r="802" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B802" s="16"/>
       <c r="C802" s="16"/>
       <c r="D802" s="16"/>
@@ -16902,7 +16915,7 @@
       <c r="R802" s="16"/>
       <c r="S802" s="16"/>
     </row>
-    <row r="803" ht="14.25" customHeight="1">
+    <row r="803" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B803" s="16"/>
       <c r="C803" s="16"/>
       <c r="D803" s="16"/>
@@ -16922,7 +16935,7 @@
       <c r="R803" s="16"/>
       <c r="S803" s="16"/>
     </row>
-    <row r="804" ht="14.25" customHeight="1">
+    <row r="804" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B804" s="16"/>
       <c r="C804" s="16"/>
       <c r="D804" s="16"/>
@@ -16942,7 +16955,7 @@
       <c r="R804" s="16"/>
       <c r="S804" s="16"/>
     </row>
-    <row r="805" ht="14.25" customHeight="1">
+    <row r="805" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B805" s="16"/>
       <c r="C805" s="16"/>
       <c r="D805" s="16"/>
@@ -16962,7 +16975,7 @@
       <c r="R805" s="16"/>
       <c r="S805" s="16"/>
     </row>
-    <row r="806" ht="14.25" customHeight="1">
+    <row r="806" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B806" s="16"/>
       <c r="C806" s="16"/>
       <c r="D806" s="16"/>
@@ -16982,7 +16995,7 @@
       <c r="R806" s="16"/>
       <c r="S806" s="16"/>
     </row>
-    <row r="807" ht="14.25" customHeight="1">
+    <row r="807" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B807" s="16"/>
       <c r="C807" s="16"/>
       <c r="D807" s="16"/>
@@ -17002,7 +17015,7 @@
       <c r="R807" s="16"/>
       <c r="S807" s="16"/>
     </row>
-    <row r="808" ht="14.25" customHeight="1">
+    <row r="808" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B808" s="16"/>
       <c r="C808" s="16"/>
       <c r="D808" s="16"/>
@@ -17022,7 +17035,7 @@
       <c r="R808" s="16"/>
       <c r="S808" s="16"/>
     </row>
-    <row r="809" ht="14.25" customHeight="1">
+    <row r="809" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B809" s="16"/>
       <c r="C809" s="16"/>
       <c r="D809" s="16"/>
@@ -17042,7 +17055,7 @@
       <c r="R809" s="16"/>
       <c r="S809" s="16"/>
     </row>
-    <row r="810" ht="14.25" customHeight="1">
+    <row r="810" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B810" s="16"/>
       <c r="C810" s="16"/>
       <c r="D810" s="16"/>
@@ -17062,7 +17075,7 @@
       <c r="R810" s="16"/>
       <c r="S810" s="16"/>
     </row>
-    <row r="811" ht="14.25" customHeight="1">
+    <row r="811" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B811" s="16"/>
       <c r="C811" s="16"/>
       <c r="D811" s="16"/>
@@ -17082,7 +17095,7 @@
       <c r="R811" s="16"/>
       <c r="S811" s="16"/>
     </row>
-    <row r="812" ht="14.25" customHeight="1">
+    <row r="812" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B812" s="16"/>
       <c r="C812" s="16"/>
       <c r="D812" s="16"/>
@@ -17102,7 +17115,7 @@
       <c r="R812" s="16"/>
       <c r="S812" s="16"/>
     </row>
-    <row r="813" ht="14.25" customHeight="1">
+    <row r="813" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B813" s="16"/>
       <c r="C813" s="16"/>
       <c r="D813" s="16"/>
@@ -17122,7 +17135,7 @@
       <c r="R813" s="16"/>
       <c r="S813" s="16"/>
     </row>
-    <row r="814" ht="14.25" customHeight="1">
+    <row r="814" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B814" s="16"/>
       <c r="C814" s="16"/>
       <c r="D814" s="16"/>
@@ -17142,7 +17155,7 @@
       <c r="R814" s="16"/>
       <c r="S814" s="16"/>
     </row>
-    <row r="815" ht="14.25" customHeight="1">
+    <row r="815" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B815" s="16"/>
       <c r="C815" s="16"/>
       <c r="D815" s="16"/>
@@ -17162,7 +17175,7 @@
       <c r="R815" s="16"/>
       <c r="S815" s="16"/>
     </row>
-    <row r="816" ht="14.25" customHeight="1">
+    <row r="816" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B816" s="16"/>
       <c r="C816" s="16"/>
       <c r="D816" s="16"/>
@@ -17182,7 +17195,7 @@
       <c r="R816" s="16"/>
       <c r="S816" s="16"/>
     </row>
-    <row r="817" ht="14.25" customHeight="1">
+    <row r="817" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B817" s="16"/>
       <c r="C817" s="16"/>
       <c r="D817" s="16"/>
@@ -17202,7 +17215,7 @@
       <c r="R817" s="16"/>
       <c r="S817" s="16"/>
     </row>
-    <row r="818" ht="14.25" customHeight="1">
+    <row r="818" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B818" s="16"/>
       <c r="C818" s="16"/>
       <c r="D818" s="16"/>
@@ -17222,7 +17235,7 @@
       <c r="R818" s="16"/>
       <c r="S818" s="16"/>
     </row>
-    <row r="819" ht="14.25" customHeight="1">
+    <row r="819" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B819" s="16"/>
       <c r="C819" s="16"/>
       <c r="D819" s="16"/>
@@ -17242,7 +17255,7 @@
       <c r="R819" s="16"/>
       <c r="S819" s="16"/>
     </row>
-    <row r="820" ht="14.25" customHeight="1">
+    <row r="820" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B820" s="16"/>
       <c r="C820" s="16"/>
       <c r="D820" s="16"/>
@@ -17262,7 +17275,7 @@
       <c r="R820" s="16"/>
       <c r="S820" s="16"/>
     </row>
-    <row r="821" ht="14.25" customHeight="1">
+    <row r="821" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B821" s="16"/>
       <c r="C821" s="16"/>
       <c r="D821" s="16"/>
@@ -17282,7 +17295,7 @@
       <c r="R821" s="16"/>
       <c r="S821" s="16"/>
     </row>
-    <row r="822" ht="14.25" customHeight="1">
+    <row r="822" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B822" s="16"/>
       <c r="C822" s="16"/>
       <c r="D822" s="16"/>
@@ -17302,7 +17315,7 @@
       <c r="R822" s="16"/>
       <c r="S822" s="16"/>
     </row>
-    <row r="823" ht="14.25" customHeight="1">
+    <row r="823" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B823" s="16"/>
       <c r="C823" s="16"/>
       <c r="D823" s="16"/>
@@ -17322,7 +17335,7 @@
       <c r="R823" s="16"/>
       <c r="S823" s="16"/>
     </row>
-    <row r="824" ht="14.25" customHeight="1">
+    <row r="824" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B824" s="16"/>
       <c r="C824" s="16"/>
       <c r="D824" s="16"/>
@@ -17342,7 +17355,7 @@
       <c r="R824" s="16"/>
       <c r="S824" s="16"/>
     </row>
-    <row r="825" ht="14.25" customHeight="1">
+    <row r="825" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B825" s="16"/>
       <c r="C825" s="16"/>
       <c r="D825" s="16"/>
@@ -17362,7 +17375,7 @@
       <c r="R825" s="16"/>
       <c r="S825" s="16"/>
     </row>
-    <row r="826" ht="14.25" customHeight="1">
+    <row r="826" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B826" s="16"/>
       <c r="C826" s="16"/>
       <c r="D826" s="16"/>
@@ -17382,7 +17395,7 @@
       <c r="R826" s="16"/>
       <c r="S826" s="16"/>
     </row>
-    <row r="827" ht="14.25" customHeight="1">
+    <row r="827" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B827" s="16"/>
       <c r="C827" s="16"/>
       <c r="D827" s="16"/>
@@ -17402,7 +17415,7 @@
       <c r="R827" s="16"/>
       <c r="S827" s="16"/>
     </row>
-    <row r="828" ht="14.25" customHeight="1">
+    <row r="828" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B828" s="16"/>
       <c r="C828" s="16"/>
       <c r="D828" s="16"/>
@@ -17422,7 +17435,7 @@
       <c r="R828" s="16"/>
       <c r="S828" s="16"/>
     </row>
-    <row r="829" ht="14.25" customHeight="1">
+    <row r="829" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B829" s="16"/>
       <c r="C829" s="16"/>
       <c r="D829" s="16"/>
@@ -17442,7 +17455,7 @@
       <c r="R829" s="16"/>
       <c r="S829" s="16"/>
     </row>
-    <row r="830" ht="14.25" customHeight="1">
+    <row r="830" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B830" s="16"/>
       <c r="C830" s="16"/>
       <c r="D830" s="16"/>
@@ -17462,7 +17475,7 @@
       <c r="R830" s="16"/>
       <c r="S830" s="16"/>
     </row>
-    <row r="831" ht="14.25" customHeight="1">
+    <row r="831" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B831" s="16"/>
       <c r="C831" s="16"/>
       <c r="D831" s="16"/>
@@ -17482,7 +17495,7 @@
       <c r="R831" s="16"/>
       <c r="S831" s="16"/>
     </row>
-    <row r="832" ht="14.25" customHeight="1">
+    <row r="832" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B832" s="16"/>
       <c r="C832" s="16"/>
       <c r="D832" s="16"/>
@@ -17502,7 +17515,7 @@
       <c r="R832" s="16"/>
       <c r="S832" s="16"/>
     </row>
-    <row r="833" ht="14.25" customHeight="1">
+    <row r="833" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B833" s="16"/>
       <c r="C833" s="16"/>
       <c r="D833" s="16"/>
@@ -17522,7 +17535,7 @@
       <c r="R833" s="16"/>
       <c r="S833" s="16"/>
     </row>
-    <row r="834" ht="14.25" customHeight="1">
+    <row r="834" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B834" s="16"/>
       <c r="C834" s="16"/>
       <c r="D834" s="16"/>
@@ -17542,7 +17555,7 @@
       <c r="R834" s="16"/>
       <c r="S834" s="16"/>
     </row>
-    <row r="835" ht="14.25" customHeight="1">
+    <row r="835" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B835" s="16"/>
       <c r="C835" s="16"/>
       <c r="D835" s="16"/>
@@ -17562,7 +17575,7 @@
       <c r="R835" s="16"/>
       <c r="S835" s="16"/>
     </row>
-    <row r="836" ht="14.25" customHeight="1">
+    <row r="836" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B836" s="16"/>
       <c r="C836" s="16"/>
       <c r="D836" s="16"/>
@@ -17582,7 +17595,7 @@
       <c r="R836" s="16"/>
       <c r="S836" s="16"/>
     </row>
-    <row r="837" ht="14.25" customHeight="1">
+    <row r="837" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B837" s="16"/>
       <c r="C837" s="16"/>
       <c r="D837" s="16"/>
@@ -17602,7 +17615,7 @@
       <c r="R837" s="16"/>
       <c r="S837" s="16"/>
     </row>
-    <row r="838" ht="14.25" customHeight="1">
+    <row r="838" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B838" s="16"/>
       <c r="C838" s="16"/>
       <c r="D838" s="16"/>
@@ -17622,7 +17635,7 @@
       <c r="R838" s="16"/>
       <c r="S838" s="16"/>
     </row>
-    <row r="839" ht="14.25" customHeight="1">
+    <row r="839" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B839" s="16"/>
       <c r="C839" s="16"/>
       <c r="D839" s="16"/>
@@ -17642,7 +17655,7 @@
       <c r="R839" s="16"/>
       <c r="S839" s="16"/>
     </row>
-    <row r="840" ht="14.25" customHeight="1">
+    <row r="840" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B840" s="16"/>
       <c r="C840" s="16"/>
       <c r="D840" s="16"/>
@@ -17662,7 +17675,7 @@
       <c r="R840" s="16"/>
       <c r="S840" s="16"/>
     </row>
-    <row r="841" ht="14.25" customHeight="1">
+    <row r="841" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B841" s="16"/>
       <c r="C841" s="16"/>
       <c r="D841" s="16"/>
@@ -17682,7 +17695,7 @@
       <c r="R841" s="16"/>
       <c r="S841" s="16"/>
     </row>
-    <row r="842" ht="14.25" customHeight="1">
+    <row r="842" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B842" s="16"/>
       <c r="C842" s="16"/>
       <c r="D842" s="16"/>
@@ -17702,7 +17715,7 @@
       <c r="R842" s="16"/>
       <c r="S842" s="16"/>
     </row>
-    <row r="843" ht="14.25" customHeight="1">
+    <row r="843" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B843" s="16"/>
       <c r="C843" s="16"/>
       <c r="D843" s="16"/>
@@ -17722,7 +17735,7 @@
       <c r="R843" s="16"/>
       <c r="S843" s="16"/>
     </row>
-    <row r="844" ht="14.25" customHeight="1">
+    <row r="844" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B844" s="16"/>
       <c r="C844" s="16"/>
       <c r="D844" s="16"/>
@@ -17742,7 +17755,7 @@
       <c r="R844" s="16"/>
       <c r="S844" s="16"/>
     </row>
-    <row r="845" ht="14.25" customHeight="1">
+    <row r="845" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B845" s="16"/>
       <c r="C845" s="16"/>
       <c r="D845" s="16"/>
@@ -17762,7 +17775,7 @@
       <c r="R845" s="16"/>
       <c r="S845" s="16"/>
     </row>
-    <row r="846" ht="14.25" customHeight="1">
+    <row r="846" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B846" s="16"/>
       <c r="C846" s="16"/>
       <c r="D846" s="16"/>
@@ -17782,7 +17795,7 @@
       <c r="R846" s="16"/>
       <c r="S846" s="16"/>
     </row>
-    <row r="847" ht="14.25" customHeight="1">
+    <row r="847" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B847" s="16"/>
       <c r="C847" s="16"/>
       <c r="D847" s="16"/>
@@ -17802,7 +17815,7 @@
       <c r="R847" s="16"/>
       <c r="S847" s="16"/>
     </row>
-    <row r="848" ht="14.25" customHeight="1">
+    <row r="848" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B848" s="16"/>
       <c r="C848" s="16"/>
       <c r="D848" s="16"/>
@@ -17822,7 +17835,7 @@
       <c r="R848" s="16"/>
       <c r="S848" s="16"/>
     </row>
-    <row r="849" ht="14.25" customHeight="1">
+    <row r="849" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B849" s="16"/>
       <c r="C849" s="16"/>
       <c r="D849" s="16"/>
@@ -17842,7 +17855,7 @@
       <c r="R849" s="16"/>
       <c r="S849" s="16"/>
     </row>
-    <row r="850" ht="14.25" customHeight="1">
+    <row r="850" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B850" s="16"/>
       <c r="C850" s="16"/>
       <c r="D850" s="16"/>
@@ -17862,7 +17875,7 @@
       <c r="R850" s="16"/>
       <c r="S850" s="16"/>
     </row>
-    <row r="851" ht="14.25" customHeight="1">
+    <row r="851" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B851" s="16"/>
       <c r="C851" s="16"/>
       <c r="D851" s="16"/>
@@ -17882,7 +17895,7 @@
       <c r="R851" s="16"/>
       <c r="S851" s="16"/>
     </row>
-    <row r="852" ht="14.25" customHeight="1">
+    <row r="852" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B852" s="16"/>
       <c r="C852" s="16"/>
       <c r="D852" s="16"/>
@@ -17902,7 +17915,7 @@
       <c r="R852" s="16"/>
       <c r="S852" s="16"/>
     </row>
-    <row r="853" ht="14.25" customHeight="1">
+    <row r="853" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B853" s="16"/>
       <c r="C853" s="16"/>
       <c r="D853" s="16"/>
@@ -17922,7 +17935,7 @@
       <c r="R853" s="16"/>
       <c r="S853" s="16"/>
     </row>
-    <row r="854" ht="14.25" customHeight="1">
+    <row r="854" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B854" s="16"/>
       <c r="C854" s="16"/>
       <c r="D854" s="16"/>
@@ -17942,7 +17955,7 @@
       <c r="R854" s="16"/>
       <c r="S854" s="16"/>
     </row>
-    <row r="855" ht="14.25" customHeight="1">
+    <row r="855" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B855" s="16"/>
       <c r="C855" s="16"/>
       <c r="D855" s="16"/>
@@ -17962,7 +17975,7 @@
       <c r="R855" s="16"/>
       <c r="S855" s="16"/>
     </row>
-    <row r="856" ht="14.25" customHeight="1">
+    <row r="856" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B856" s="16"/>
       <c r="C856" s="16"/>
       <c r="D856" s="16"/>
@@ -17982,7 +17995,7 @@
       <c r="R856" s="16"/>
       <c r="S856" s="16"/>
     </row>
-    <row r="857" ht="14.25" customHeight="1">
+    <row r="857" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B857" s="16"/>
       <c r="C857" s="16"/>
       <c r="D857" s="16"/>
@@ -18002,7 +18015,7 @@
       <c r="R857" s="16"/>
       <c r="S857" s="16"/>
     </row>
-    <row r="858" ht="14.25" customHeight="1">
+    <row r="858" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B858" s="16"/>
       <c r="C858" s="16"/>
       <c r="D858" s="16"/>
@@ -18022,7 +18035,7 @@
       <c r="R858" s="16"/>
       <c r="S858" s="16"/>
     </row>
-    <row r="859" ht="14.25" customHeight="1">
+    <row r="859" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B859" s="16"/>
       <c r="C859" s="16"/>
       <c r="D859" s="16"/>
@@ -18042,7 +18055,7 @@
       <c r="R859" s="16"/>
       <c r="S859" s="16"/>
     </row>
-    <row r="860" ht="14.25" customHeight="1">
+    <row r="860" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B860" s="16"/>
       <c r="C860" s="16"/>
       <c r="D860" s="16"/>
@@ -18062,7 +18075,7 @@
       <c r="R860" s="16"/>
       <c r="S860" s="16"/>
     </row>
-    <row r="861" ht="14.25" customHeight="1">
+    <row r="861" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B861" s="16"/>
       <c r="C861" s="16"/>
       <c r="D861" s="16"/>
@@ -18082,7 +18095,7 @@
       <c r="R861" s="16"/>
       <c r="S861" s="16"/>
     </row>
-    <row r="862" ht="14.25" customHeight="1">
+    <row r="862" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B862" s="16"/>
       <c r="C862" s="16"/>
       <c r="D862" s="16"/>
@@ -18102,7 +18115,7 @@
       <c r="R862" s="16"/>
       <c r="S862" s="16"/>
     </row>
-    <row r="863" ht="14.25" customHeight="1">
+    <row r="863" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B863" s="16"/>
       <c r="C863" s="16"/>
       <c r="D863" s="16"/>
@@ -18122,7 +18135,7 @@
       <c r="R863" s="16"/>
       <c r="S863" s="16"/>
     </row>
-    <row r="864" ht="14.25" customHeight="1">
+    <row r="864" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B864" s="16"/>
       <c r="C864" s="16"/>
       <c r="D864" s="16"/>
@@ -18142,7 +18155,7 @@
       <c r="R864" s="16"/>
       <c r="S864" s="16"/>
     </row>
-    <row r="865" ht="14.25" customHeight="1">
+    <row r="865" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B865" s="16"/>
       <c r="C865" s="16"/>
       <c r="D865" s="16"/>
@@ -18162,7 +18175,7 @@
       <c r="R865" s="16"/>
       <c r="S865" s="16"/>
     </row>
-    <row r="866" ht="14.25" customHeight="1">
+    <row r="866" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B866" s="16"/>
       <c r="C866" s="16"/>
       <c r="D866" s="16"/>
@@ -18182,7 +18195,7 @@
       <c r="R866" s="16"/>
       <c r="S866" s="16"/>
     </row>
-    <row r="867" ht="14.25" customHeight="1">
+    <row r="867" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B867" s="16"/>
       <c r="C867" s="16"/>
       <c r="D867" s="16"/>
@@ -18202,7 +18215,7 @@
       <c r="R867" s="16"/>
       <c r="S867" s="16"/>
     </row>
-    <row r="868" ht="14.25" customHeight="1">
+    <row r="868" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B868" s="16"/>
       <c r="C868" s="16"/>
       <c r="D868" s="16"/>
@@ -18222,7 +18235,7 @@
       <c r="R868" s="16"/>
       <c r="S868" s="16"/>
     </row>
-    <row r="869" ht="14.25" customHeight="1">
+    <row r="869" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B869" s="16"/>
       <c r="C869" s="16"/>
       <c r="D869" s="16"/>
@@ -18242,7 +18255,7 @@
       <c r="R869" s="16"/>
       <c r="S869" s="16"/>
     </row>
-    <row r="870" ht="14.25" customHeight="1">
+    <row r="870" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B870" s="16"/>
       <c r="C870" s="16"/>
       <c r="D870" s="16"/>
@@ -18262,7 +18275,7 @@
       <c r="R870" s="16"/>
       <c r="S870" s="16"/>
     </row>
-    <row r="871" ht="14.25" customHeight="1">
+    <row r="871" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B871" s="16"/>
       <c r="C871" s="16"/>
       <c r="D871" s="16"/>
@@ -18282,7 +18295,7 @@
       <c r="R871" s="16"/>
       <c r="S871" s="16"/>
     </row>
-    <row r="872" ht="14.25" customHeight="1">
+    <row r="872" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B872" s="16"/>
       <c r="C872" s="16"/>
       <c r="D872" s="16"/>
@@ -18302,7 +18315,7 @@
       <c r="R872" s="16"/>
       <c r="S872" s="16"/>
     </row>
-    <row r="873" ht="14.25" customHeight="1">
+    <row r="873" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B873" s="16"/>
       <c r="C873" s="16"/>
       <c r="D873" s="16"/>
@@ -18322,7 +18335,7 @@
       <c r="R873" s="16"/>
       <c r="S873" s="16"/>
     </row>
-    <row r="874" ht="14.25" customHeight="1">
+    <row r="874" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B874" s="16"/>
       <c r="C874" s="16"/>
       <c r="D874" s="16"/>
@@ -18342,7 +18355,7 @@
       <c r="R874" s="16"/>
       <c r="S874" s="16"/>
     </row>
-    <row r="875" ht="14.25" customHeight="1">
+    <row r="875" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B875" s="16"/>
       <c r="C875" s="16"/>
       <c r="D875" s="16"/>
@@ -18362,7 +18375,7 @@
       <c r="R875" s="16"/>
       <c r="S875" s="16"/>
     </row>
-    <row r="876" ht="14.25" customHeight="1">
+    <row r="876" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B876" s="16"/>
       <c r="C876" s="16"/>
       <c r="D876" s="16"/>
@@ -18382,7 +18395,7 @@
       <c r="R876" s="16"/>
       <c r="S876" s="16"/>
     </row>
-    <row r="877" ht="14.25" customHeight="1">
+    <row r="877" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B877" s="16"/>
       <c r="C877" s="16"/>
       <c r="D877" s="16"/>
@@ -18402,7 +18415,7 @@
       <c r="R877" s="16"/>
       <c r="S877" s="16"/>
     </row>
-    <row r="878" ht="14.25" customHeight="1">
+    <row r="878" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B878" s="16"/>
       <c r="C878" s="16"/>
       <c r="D878" s="16"/>
@@ -18422,7 +18435,7 @@
       <c r="R878" s="16"/>
       <c r="S878" s="16"/>
     </row>
-    <row r="879" ht="14.25" customHeight="1">
+    <row r="879" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B879" s="16"/>
       <c r="C879" s="16"/>
       <c r="D879" s="16"/>
@@ -18442,7 +18455,7 @@
       <c r="R879" s="16"/>
       <c r="S879" s="16"/>
     </row>
-    <row r="880" ht="14.25" customHeight="1">
+    <row r="880" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B880" s="16"/>
       <c r="C880" s="16"/>
       <c r="D880" s="16"/>
@@ -18462,7 +18475,7 @@
       <c r="R880" s="16"/>
       <c r="S880" s="16"/>
     </row>
-    <row r="881" ht="14.25" customHeight="1">
+    <row r="881" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B881" s="16"/>
       <c r="C881" s="16"/>
       <c r="D881" s="16"/>
@@ -18482,7 +18495,7 @@
       <c r="R881" s="16"/>
       <c r="S881" s="16"/>
     </row>
-    <row r="882" ht="14.25" customHeight="1">
+    <row r="882" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B882" s="16"/>
       <c r="C882" s="16"/>
       <c r="D882" s="16"/>
@@ -18502,7 +18515,7 @@
       <c r="R882" s="16"/>
       <c r="S882" s="16"/>
     </row>
-    <row r="883" ht="14.25" customHeight="1">
+    <row r="883" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B883" s="16"/>
       <c r="C883" s="16"/>
       <c r="D883" s="16"/>
@@ -18522,7 +18535,7 @@
       <c r="R883" s="16"/>
       <c r="S883" s="16"/>
     </row>
-    <row r="884" ht="14.25" customHeight="1">
+    <row r="884" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B884" s="16"/>
       <c r="C884" s="16"/>
       <c r="D884" s="16"/>
@@ -18542,7 +18555,7 @@
       <c r="R884" s="16"/>
       <c r="S884" s="16"/>
     </row>
-    <row r="885" ht="14.25" customHeight="1">
+    <row r="885" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B885" s="16"/>
       <c r="C885" s="16"/>
       <c r="D885" s="16"/>
@@ -18562,7 +18575,7 @@
       <c r="R885" s="16"/>
       <c r="S885" s="16"/>
     </row>
-    <row r="886" ht="14.25" customHeight="1">
+    <row r="886" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B886" s="16"/>
       <c r="C886" s="16"/>
       <c r="D886" s="16"/>
@@ -18582,7 +18595,7 @@
       <c r="R886" s="16"/>
       <c r="S886" s="16"/>
     </row>
-    <row r="887" ht="14.25" customHeight="1">
+    <row r="887" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B887" s="16"/>
       <c r="C887" s="16"/>
       <c r="D887" s="16"/>
@@ -18602,7 +18615,7 @@
       <c r="R887" s="16"/>
       <c r="S887" s="16"/>
     </row>
-    <row r="888" ht="14.25" customHeight="1">
+    <row r="888" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B888" s="16"/>
       <c r="C888" s="16"/>
       <c r="D888" s="16"/>
@@ -18622,7 +18635,7 @@
       <c r="R888" s="16"/>
       <c r="S888" s="16"/>
     </row>
-    <row r="889" ht="14.25" customHeight="1">
+    <row r="889" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B889" s="16"/>
       <c r="C889" s="16"/>
       <c r="D889" s="16"/>
@@ -18642,7 +18655,7 @@
       <c r="R889" s="16"/>
       <c r="S889" s="16"/>
     </row>
-    <row r="890" ht="14.25" customHeight="1">
+    <row r="890" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B890" s="16"/>
       <c r="C890" s="16"/>
       <c r="D890" s="16"/>
@@ -18662,7 +18675,7 @@
       <c r="R890" s="16"/>
       <c r="S890" s="16"/>
     </row>
-    <row r="891" ht="14.25" customHeight="1">
+    <row r="891" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B891" s="16"/>
       <c r="C891" s="16"/>
       <c r="D891" s="16"/>
@@ -18682,7 +18695,7 @@
       <c r="R891" s="16"/>
       <c r="S891" s="16"/>
     </row>
-    <row r="892" ht="14.25" customHeight="1">
+    <row r="892" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B892" s="16"/>
       <c r="C892" s="16"/>
       <c r="D892" s="16"/>
@@ -18702,7 +18715,7 @@
       <c r="R892" s="16"/>
       <c r="S892" s="16"/>
     </row>
-    <row r="893" ht="14.25" customHeight="1">
+    <row r="893" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B893" s="16"/>
       <c r="C893" s="16"/>
       <c r="D893" s="16"/>
@@ -18722,7 +18735,7 @@
       <c r="R893" s="16"/>
       <c r="S893" s="16"/>
     </row>
-    <row r="894" ht="14.25" customHeight="1">
+    <row r="894" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B894" s="16"/>
       <c r="C894" s="16"/>
       <c r="D894" s="16"/>
@@ -18742,7 +18755,7 @@
       <c r="R894" s="16"/>
       <c r="S894" s="16"/>
     </row>
-    <row r="895" ht="14.25" customHeight="1">
+    <row r="895" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B895" s="16"/>
       <c r="C895" s="16"/>
       <c r="D895" s="16"/>
@@ -18762,7 +18775,7 @@
       <c r="R895" s="16"/>
       <c r="S895" s="16"/>
     </row>
-    <row r="896" ht="14.25" customHeight="1">
+    <row r="896" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B896" s="16"/>
       <c r="C896" s="16"/>
       <c r="D896" s="16"/>
@@ -18782,7 +18795,7 @@
       <c r="R896" s="16"/>
       <c r="S896" s="16"/>
     </row>
-    <row r="897" ht="14.25" customHeight="1">
+    <row r="897" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B897" s="16"/>
       <c r="C897" s="16"/>
       <c r="D897" s="16"/>
@@ -18802,7 +18815,7 @@
       <c r="R897" s="16"/>
       <c r="S897" s="16"/>
     </row>
-    <row r="898" ht="14.25" customHeight="1">
+    <row r="898" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B898" s="16"/>
       <c r="C898" s="16"/>
       <c r="D898" s="16"/>
@@ -18822,7 +18835,7 @@
       <c r="R898" s="16"/>
       <c r="S898" s="16"/>
     </row>
-    <row r="899" ht="14.25" customHeight="1">
+    <row r="899" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B899" s="16"/>
       <c r="C899" s="16"/>
       <c r="D899" s="16"/>
@@ -18842,7 +18855,7 @@
       <c r="R899" s="16"/>
       <c r="S899" s="16"/>
     </row>
-    <row r="900" ht="14.25" customHeight="1">
+    <row r="900" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B900" s="16"/>
       <c r="C900" s="16"/>
       <c r="D900" s="16"/>
@@ -18862,7 +18875,7 @@
       <c r="R900" s="16"/>
       <c r="S900" s="16"/>
     </row>
-    <row r="901" ht="14.25" customHeight="1">
+    <row r="901" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B901" s="16"/>
       <c r="C901" s="16"/>
       <c r="D901" s="16"/>
@@ -18882,7 +18895,7 @@
       <c r="R901" s="16"/>
       <c r="S901" s="16"/>
     </row>
-    <row r="902" ht="14.25" customHeight="1">
+    <row r="902" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B902" s="16"/>
       <c r="C902" s="16"/>
       <c r="D902" s="16"/>
@@ -18902,7 +18915,7 @@
       <c r="R902" s="16"/>
       <c r="S902" s="16"/>
     </row>
-    <row r="903" ht="14.25" customHeight="1">
+    <row r="903" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B903" s="16"/>
       <c r="C903" s="16"/>
       <c r="D903" s="16"/>
@@ -18922,7 +18935,7 @@
       <c r="R903" s="16"/>
       <c r="S903" s="16"/>
     </row>
-    <row r="904" ht="14.25" customHeight="1">
+    <row r="904" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B904" s="16"/>
       <c r="C904" s="16"/>
       <c r="D904" s="16"/>
@@ -18942,7 +18955,7 @@
       <c r="R904" s="16"/>
       <c r="S904" s="16"/>
     </row>
-    <row r="905" ht="14.25" customHeight="1">
+    <row r="905" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B905" s="16"/>
       <c r="C905" s="16"/>
       <c r="D905" s="16"/>
@@ -18962,7 +18975,7 @@
       <c r="R905" s="16"/>
       <c r="S905" s="16"/>
     </row>
-    <row r="906" ht="14.25" customHeight="1">
+    <row r="906" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B906" s="16"/>
       <c r="C906" s="16"/>
       <c r="D906" s="16"/>
@@ -18982,7 +18995,7 @@
       <c r="R906" s="16"/>
       <c r="S906" s="16"/>
     </row>
-    <row r="907" ht="14.25" customHeight="1">
+    <row r="907" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B907" s="16"/>
       <c r="C907" s="16"/>
       <c r="D907" s="16"/>
@@ -19002,7 +19015,7 @@
       <c r="R907" s="16"/>
       <c r="S907" s="16"/>
     </row>
-    <row r="908" ht="14.25" customHeight="1">
+    <row r="908" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B908" s="16"/>
       <c r="C908" s="16"/>
       <c r="D908" s="16"/>
@@ -19022,7 +19035,7 @@
       <c r="R908" s="16"/>
       <c r="S908" s="16"/>
     </row>
-    <row r="909" ht="14.25" customHeight="1">
+    <row r="909" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B909" s="16"/>
       <c r="C909" s="16"/>
       <c r="D909" s="16"/>
@@ -19042,7 +19055,7 @@
       <c r="R909" s="16"/>
       <c r="S909" s="16"/>
     </row>
-    <row r="910" ht="14.25" customHeight="1">
+    <row r="910" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B910" s="16"/>
       <c r="C910" s="16"/>
       <c r="D910" s="16"/>
@@ -19062,7 +19075,7 @@
       <c r="R910" s="16"/>
       <c r="S910" s="16"/>
     </row>
-    <row r="911" ht="14.25" customHeight="1">
+    <row r="911" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B911" s="16"/>
       <c r="C911" s="16"/>
       <c r="D911" s="16"/>
@@ -19082,7 +19095,7 @@
       <c r="R911" s="16"/>
       <c r="S911" s="16"/>
     </row>
-    <row r="912" ht="14.25" customHeight="1">
+    <row r="912" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B912" s="16"/>
       <c r="C912" s="16"/>
       <c r="D912" s="16"/>
@@ -19102,7 +19115,7 @@
       <c r="R912" s="16"/>
       <c r="S912" s="16"/>
     </row>
-    <row r="913" ht="14.25" customHeight="1">
+    <row r="913" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B913" s="16"/>
       <c r="C913" s="16"/>
       <c r="D913" s="16"/>
@@ -19122,7 +19135,7 @@
       <c r="R913" s="16"/>
       <c r="S913" s="16"/>
     </row>
-    <row r="914" ht="14.25" customHeight="1">
+    <row r="914" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B914" s="16"/>
       <c r="C914" s="16"/>
       <c r="D914" s="16"/>
@@ -19142,7 +19155,7 @@
       <c r="R914" s="16"/>
       <c r="S914" s="16"/>
     </row>
-    <row r="915" ht="14.25" customHeight="1">
+    <row r="915" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B915" s="16"/>
       <c r="C915" s="16"/>
       <c r="D915" s="16"/>
@@ -19162,7 +19175,7 @@
       <c r="R915" s="16"/>
       <c r="S915" s="16"/>
     </row>
-    <row r="916" ht="14.25" customHeight="1">
+    <row r="916" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B916" s="16"/>
       <c r="C916" s="16"/>
       <c r="D916" s="16"/>
@@ -19182,7 +19195,7 @@
       <c r="R916" s="16"/>
       <c r="S916" s="16"/>
     </row>
-    <row r="917" ht="14.25" customHeight="1">
+    <row r="917" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B917" s="16"/>
       <c r="C917" s="16"/>
       <c r="D917" s="16"/>
@@ -19202,7 +19215,7 @@
       <c r="R917" s="16"/>
       <c r="S917" s="16"/>
     </row>
-    <row r="918" ht="14.25" customHeight="1">
+    <row r="918" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B918" s="16"/>
       <c r="C918" s="16"/>
       <c r="D918" s="16"/>
@@ -19222,7 +19235,7 @@
       <c r="R918" s="16"/>
       <c r="S918" s="16"/>
     </row>
-    <row r="919" ht="14.25" customHeight="1">
+    <row r="919" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B919" s="16"/>
       <c r="C919" s="16"/>
       <c r="D919" s="16"/>
@@ -19242,7 +19255,7 @@
       <c r="R919" s="16"/>
       <c r="S919" s="16"/>
     </row>
-    <row r="920" ht="14.25" customHeight="1">
+    <row r="920" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B920" s="16"/>
       <c r="C920" s="16"/>
       <c r="D920" s="16"/>
@@ -19262,7 +19275,7 @@
       <c r="R920" s="16"/>
       <c r="S920" s="16"/>
     </row>
-    <row r="921" ht="14.25" customHeight="1">
+    <row r="921" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B921" s="16"/>
       <c r="C921" s="16"/>
       <c r="D921" s="16"/>
@@ -19282,7 +19295,7 @@
       <c r="R921" s="16"/>
       <c r="S921" s="16"/>
     </row>
-    <row r="922" ht="14.25" customHeight="1">
+    <row r="922" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B922" s="16"/>
       <c r="C922" s="16"/>
       <c r="D922" s="16"/>
@@ -19302,7 +19315,7 @@
       <c r="R922" s="16"/>
       <c r="S922" s="16"/>
     </row>
-    <row r="923" ht="14.25" customHeight="1">
+    <row r="923" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B923" s="16"/>
       <c r="C923" s="16"/>
       <c r="D923" s="16"/>
@@ -19322,7 +19335,7 @@
       <c r="R923" s="16"/>
       <c r="S923" s="16"/>
     </row>
-    <row r="924" ht="14.25" customHeight="1">
+    <row r="924" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B924" s="16"/>
       <c r="C924" s="16"/>
       <c r="D924" s="16"/>
@@ -19342,7 +19355,7 @@
       <c r="R924" s="16"/>
       <c r="S924" s="16"/>
     </row>
-    <row r="925" ht="14.25" customHeight="1">
+    <row r="925" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B925" s="16"/>
       <c r="C925" s="16"/>
       <c r="D925" s="16"/>
@@ -19362,7 +19375,7 @@
       <c r="R925" s="16"/>
       <c r="S925" s="16"/>
     </row>
-    <row r="926" ht="14.25" customHeight="1">
+    <row r="926" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B926" s="16"/>
       <c r="C926" s="16"/>
       <c r="D926" s="16"/>
@@ -19382,7 +19395,7 @@
       <c r="R926" s="16"/>
       <c r="S926" s="16"/>
     </row>
-    <row r="927" ht="14.25" customHeight="1">
+    <row r="927" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B927" s="16"/>
       <c r="C927" s="16"/>
       <c r="D927" s="16"/>
@@ -19402,7 +19415,7 @@
       <c r="R927" s="16"/>
       <c r="S927" s="16"/>
     </row>
-    <row r="928" ht="14.25" customHeight="1">
+    <row r="928" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B928" s="16"/>
       <c r="C928" s="16"/>
       <c r="D928" s="16"/>
@@ -19422,7 +19435,7 @@
       <c r="R928" s="16"/>
       <c r="S928" s="16"/>
     </row>
-    <row r="929" ht="14.25" customHeight="1">
+    <row r="929" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B929" s="16"/>
       <c r="C929" s="16"/>
       <c r="D929" s="16"/>
@@ -19442,7 +19455,7 @@
       <c r="R929" s="16"/>
       <c r="S929" s="16"/>
     </row>
-    <row r="930" ht="14.25" customHeight="1">
+    <row r="930" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B930" s="16"/>
       <c r="C930" s="16"/>
       <c r="D930" s="16"/>
@@ -19462,7 +19475,7 @@
       <c r="R930" s="16"/>
       <c r="S930" s="16"/>
     </row>
-    <row r="931" ht="14.25" customHeight="1">
+    <row r="931" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B931" s="16"/>
       <c r="C931" s="16"/>
       <c r="D931" s="16"/>
@@ -19482,7 +19495,7 @@
       <c r="R931" s="16"/>
       <c r="S931" s="16"/>
     </row>
-    <row r="932" ht="14.25" customHeight="1">
+    <row r="932" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B932" s="16"/>
       <c r="C932" s="16"/>
       <c r="D932" s="16"/>
@@ -19502,7 +19515,7 @@
       <c r="R932" s="16"/>
       <c r="S932" s="16"/>
     </row>
-    <row r="933" ht="14.25" customHeight="1">
+    <row r="933" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B933" s="16"/>
       <c r="C933" s="16"/>
       <c r="D933" s="16"/>
@@ -19522,7 +19535,7 @@
       <c r="R933" s="16"/>
       <c r="S933" s="16"/>
     </row>
-    <row r="934" ht="14.25" customHeight="1">
+    <row r="934" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B934" s="16"/>
       <c r="C934" s="16"/>
       <c r="D934" s="16"/>
@@ -19542,7 +19555,7 @@
       <c r="R934" s="16"/>
       <c r="S934" s="16"/>
     </row>
-    <row r="935" ht="14.25" customHeight="1">
+    <row r="935" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B935" s="16"/>
       <c r="C935" s="16"/>
       <c r="D935" s="16"/>
@@ -19562,7 +19575,7 @@
       <c r="R935" s="16"/>
       <c r="S935" s="16"/>
     </row>
-    <row r="936" ht="14.25" customHeight="1">
+    <row r="936" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B936" s="16"/>
       <c r="C936" s="16"/>
       <c r="D936" s="16"/>
@@ -19582,7 +19595,7 @@
       <c r="R936" s="16"/>
       <c r="S936" s="16"/>
     </row>
-    <row r="937" ht="14.25" customHeight="1">
+    <row r="937" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B937" s="16"/>
       <c r="C937" s="16"/>
       <c r="D937" s="16"/>
@@ -19602,7 +19615,7 @@
       <c r="R937" s="16"/>
       <c r="S937" s="16"/>
     </row>
-    <row r="938" ht="14.25" customHeight="1">
+    <row r="938" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B938" s="16"/>
       <c r="C938" s="16"/>
       <c r="D938" s="16"/>
@@ -19622,7 +19635,7 @@
       <c r="R938" s="16"/>
       <c r="S938" s="16"/>
     </row>
-    <row r="939" ht="14.25" customHeight="1">
+    <row r="939" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B939" s="16"/>
       <c r="C939" s="16"/>
       <c r="D939" s="16"/>
@@ -19642,7 +19655,7 @@
       <c r="R939" s="16"/>
       <c r="S939" s="16"/>
     </row>
-    <row r="940" ht="14.25" customHeight="1">
+    <row r="940" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B940" s="16"/>
       <c r="C940" s="16"/>
       <c r="D940" s="16"/>
@@ -19662,7 +19675,7 @@
       <c r="R940" s="16"/>
       <c r="S940" s="16"/>
     </row>
-    <row r="941" ht="14.25" customHeight="1">
+    <row r="941" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B941" s="16"/>
       <c r="C941" s="16"/>
       <c r="D941" s="16"/>
@@ -19682,7 +19695,7 @@
       <c r="R941" s="16"/>
       <c r="S941" s="16"/>
     </row>
-    <row r="942" ht="14.25" customHeight="1">
+    <row r="942" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B942" s="16"/>
       <c r="C942" s="16"/>
       <c r="D942" s="16"/>
@@ -19702,7 +19715,7 @@
       <c r="R942" s="16"/>
       <c r="S942" s="16"/>
     </row>
-    <row r="943" ht="14.25" customHeight="1">
+    <row r="943" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B943" s="16"/>
       <c r="C943" s="16"/>
       <c r="D943" s="16"/>
@@ -19722,7 +19735,7 @@
       <c r="R943" s="16"/>
       <c r="S943" s="16"/>
     </row>
-    <row r="944" ht="14.25" customHeight="1">
+    <row r="944" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B944" s="16"/>
       <c r="C944" s="16"/>
       <c r="D944" s="16"/>
@@ -19742,7 +19755,7 @@
       <c r="R944" s="16"/>
       <c r="S944" s="16"/>
     </row>
-    <row r="945" ht="14.25" customHeight="1">
+    <row r="945" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B945" s="16"/>
       <c r="C945" s="16"/>
       <c r="D945" s="16"/>
@@ -19762,7 +19775,7 @@
       <c r="R945" s="16"/>
       <c r="S945" s="16"/>
     </row>
-    <row r="946" ht="14.25" customHeight="1">
+    <row r="946" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B946" s="16"/>
       <c r="C946" s="16"/>
       <c r="D946" s="16"/>
@@ -19782,7 +19795,7 @@
       <c r="R946" s="16"/>
       <c r="S946" s="16"/>
     </row>
-    <row r="947" ht="14.25" customHeight="1">
+    <row r="947" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B947" s="16"/>
       <c r="C947" s="16"/>
       <c r="D947" s="16"/>
@@ -19802,7 +19815,7 @@
       <c r="R947" s="16"/>
       <c r="S947" s="16"/>
     </row>
-    <row r="948" ht="14.25" customHeight="1">
+    <row r="948" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B948" s="16"/>
       <c r="C948" s="16"/>
       <c r="D948" s="16"/>
@@ -19822,7 +19835,7 @@
       <c r="R948" s="16"/>
       <c r="S948" s="16"/>
     </row>
-    <row r="949" ht="14.25" customHeight="1">
+    <row r="949" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B949" s="16"/>
       <c r="C949" s="16"/>
       <c r="D949" s="16"/>
@@ -19842,7 +19855,7 @@
       <c r="R949" s="16"/>
       <c r="S949" s="16"/>
     </row>
-    <row r="950" ht="14.25" customHeight="1">
+    <row r="950" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B950" s="16"/>
       <c r="C950" s="16"/>
       <c r="D950" s="16"/>
@@ -19862,7 +19875,7 @@
       <c r="R950" s="16"/>
       <c r="S950" s="16"/>
     </row>
-    <row r="951" ht="14.25" customHeight="1">
+    <row r="951" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B951" s="16"/>
       <c r="C951" s="16"/>
       <c r="D951" s="16"/>
@@ -19882,7 +19895,7 @@
       <c r="R951" s="16"/>
       <c r="S951" s="16"/>
     </row>
-    <row r="952" ht="14.25" customHeight="1">
+    <row r="952" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B952" s="16"/>
       <c r="C952" s="16"/>
       <c r="D952" s="16"/>
@@ -19902,7 +19915,7 @@
       <c r="R952" s="16"/>
       <c r="S952" s="16"/>
     </row>
-    <row r="953" ht="14.25" customHeight="1">
+    <row r="953" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B953" s="16"/>
       <c r="C953" s="16"/>
       <c r="D953" s="16"/>
@@ -19922,7 +19935,7 @@
       <c r="R953" s="16"/>
       <c r="S953" s="16"/>
     </row>
-    <row r="954" ht="14.25" customHeight="1">
+    <row r="954" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B954" s="16"/>
       <c r="C954" s="16"/>
       <c r="D954" s="16"/>
@@ -19942,7 +19955,7 @@
       <c r="R954" s="16"/>
       <c r="S954" s="16"/>
     </row>
-    <row r="955" ht="14.25" customHeight="1">
+    <row r="955" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B955" s="16"/>
       <c r="C955" s="16"/>
       <c r="D955" s="16"/>
@@ -19962,7 +19975,7 @@
       <c r="R955" s="16"/>
       <c r="S955" s="16"/>
     </row>
-    <row r="956" ht="14.25" customHeight="1">
+    <row r="956" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B956" s="16"/>
       <c r="C956" s="16"/>
       <c r="D956" s="16"/>
@@ -19982,7 +19995,7 @@
       <c r="R956" s="16"/>
       <c r="S956" s="16"/>
     </row>
-    <row r="957" ht="14.25" customHeight="1">
+    <row r="957" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B957" s="16"/>
       <c r="C957" s="16"/>
       <c r="D957" s="16"/>
@@ -20002,7 +20015,7 @@
       <c r="R957" s="16"/>
       <c r="S957" s="16"/>
     </row>
-    <row r="958" ht="14.25" customHeight="1">
+    <row r="958" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B958" s="16"/>
       <c r="C958" s="16"/>
       <c r="D958" s="16"/>
@@ -20022,7 +20035,7 @@
       <c r="R958" s="16"/>
       <c r="S958" s="16"/>
     </row>
-    <row r="959" ht="14.25" customHeight="1">
+    <row r="959" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B959" s="16"/>
       <c r="C959" s="16"/>
       <c r="D959" s="16"/>
@@ -20042,7 +20055,7 @@
       <c r="R959" s="16"/>
       <c r="S959" s="16"/>
     </row>
-    <row r="960" ht="14.25" customHeight="1">
+    <row r="960" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B960" s="16"/>
       <c r="C960" s="16"/>
       <c r="D960" s="16"/>
@@ -20062,7 +20075,7 @@
       <c r="R960" s="16"/>
       <c r="S960" s="16"/>
     </row>
-    <row r="961" ht="14.25" customHeight="1">
+    <row r="961" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B961" s="16"/>
       <c r="C961" s="16"/>
       <c r="D961" s="16"/>
@@ -20082,7 +20095,7 @@
       <c r="R961" s="16"/>
       <c r="S961" s="16"/>
     </row>
-    <row r="962" ht="14.25" customHeight="1">
+    <row r="962" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B962" s="16"/>
       <c r="C962" s="16"/>
       <c r="D962" s="16"/>
@@ -20102,7 +20115,7 @@
       <c r="R962" s="16"/>
       <c r="S962" s="16"/>
     </row>
-    <row r="963" ht="14.25" customHeight="1">
+    <row r="963" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B963" s="16"/>
       <c r="C963" s="16"/>
       <c r="D963" s="16"/>
@@ -20122,7 +20135,7 @@
       <c r="R963" s="16"/>
       <c r="S963" s="16"/>
     </row>
-    <row r="964" ht="14.25" customHeight="1">
+    <row r="964" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B964" s="16"/>
       <c r="C964" s="16"/>
       <c r="D964" s="16"/>
@@ -20142,7 +20155,7 @@
       <c r="R964" s="16"/>
       <c r="S964" s="16"/>
     </row>
-    <row r="965" ht="14.25" customHeight="1">
+    <row r="965" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B965" s="16"/>
       <c r="C965" s="16"/>
       <c r="D965" s="16"/>
@@ -20162,7 +20175,7 @@
       <c r="R965" s="16"/>
       <c r="S965" s="16"/>
     </row>
-    <row r="966" ht="14.25" customHeight="1">
+    <row r="966" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B966" s="16"/>
       <c r="C966" s="16"/>
       <c r="D966" s="16"/>
@@ -20182,7 +20195,7 @@
       <c r="R966" s="16"/>
       <c r="S966" s="16"/>
     </row>
-    <row r="967" ht="14.25" customHeight="1">
+    <row r="967" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B967" s="16"/>
       <c r="C967" s="16"/>
       <c r="D967" s="16"/>
@@ -20202,7 +20215,7 @@
       <c r="R967" s="16"/>
       <c r="S967" s="16"/>
     </row>
-    <row r="968" ht="14.25" customHeight="1">
+    <row r="968" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B968" s="16"/>
       <c r="C968" s="16"/>
       <c r="D968" s="16"/>
@@ -20222,7 +20235,7 @@
       <c r="R968" s="16"/>
       <c r="S968" s="16"/>
     </row>
-    <row r="969" ht="14.25" customHeight="1">
+    <row r="969" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B969" s="16"/>
       <c r="C969" s="16"/>
       <c r="D969" s="16"/>
@@ -20242,7 +20255,7 @@
       <c r="R969" s="16"/>
       <c r="S969" s="16"/>
     </row>
-    <row r="970" ht="14.25" customHeight="1">
+    <row r="970" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B970" s="16"/>
       <c r="C970" s="16"/>
       <c r="D970" s="16"/>
@@ -20262,7 +20275,7 @@
       <c r="R970" s="16"/>
       <c r="S970" s="16"/>
     </row>
-    <row r="971" ht="14.25" customHeight="1">
+    <row r="971" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B971" s="16"/>
       <c r="C971" s="16"/>
       <c r="D971" s="16"/>
@@ -20282,7 +20295,7 @@
       <c r="R971" s="16"/>
       <c r="S971" s="16"/>
     </row>
-    <row r="972" ht="14.25" customHeight="1">
+    <row r="972" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B972" s="16"/>
       <c r="C972" s="16"/>
       <c r="D972" s="16"/>
@@ -20302,7 +20315,7 @@
       <c r="R972" s="16"/>
       <c r="S972" s="16"/>
     </row>
-    <row r="973" ht="14.25" customHeight="1">
+    <row r="973" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B973" s="16"/>
       <c r="C973" s="16"/>
       <c r="D973" s="16"/>
@@ -20322,7 +20335,7 @@
       <c r="R973" s="16"/>
       <c r="S973" s="16"/>
     </row>
-    <row r="974" ht="14.25" customHeight="1">
+    <row r="974" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B974" s="16"/>
       <c r="C974" s="16"/>
       <c r="D974" s="16"/>
@@ -20342,7 +20355,7 @@
       <c r="R974" s="16"/>
       <c r="S974" s="16"/>
     </row>
-    <row r="975" ht="14.25" customHeight="1">
+    <row r="975" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B975" s="16"/>
       <c r="C975" s="16"/>
       <c r="D975" s="16"/>
@@ -20362,7 +20375,7 @@
       <c r="R975" s="16"/>
       <c r="S975" s="16"/>
     </row>
-    <row r="976" ht="14.25" customHeight="1">
+    <row r="976" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B976" s="16"/>
       <c r="C976" s="16"/>
       <c r="D976" s="16"/>
@@ -20382,7 +20395,7 @@
       <c r="R976" s="16"/>
       <c r="S976" s="16"/>
     </row>
-    <row r="977" ht="14.25" customHeight="1">
+    <row r="977" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B977" s="16"/>
       <c r="C977" s="16"/>
       <c r="D977" s="16"/>
@@ -20402,7 +20415,7 @@
       <c r="R977" s="16"/>
       <c r="S977" s="16"/>
     </row>
-    <row r="978" ht="14.25" customHeight="1">
+    <row r="978" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B978" s="16"/>
       <c r="C978" s="16"/>
       <c r="D978" s="16"/>
@@ -20422,7 +20435,7 @@
       <c r="R978" s="16"/>
       <c r="S978" s="16"/>
     </row>
-    <row r="979" ht="14.25" customHeight="1">
+    <row r="979" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B979" s="16"/>
       <c r="C979" s="16"/>
       <c r="D979" s="16"/>
@@ -20442,7 +20455,7 @@
       <c r="R979" s="16"/>
       <c r="S979" s="16"/>
     </row>
-    <row r="980" ht="14.25" customHeight="1">
+    <row r="980" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B980" s="16"/>
       <c r="C980" s="16"/>
       <c r="D980" s="16"/>
@@ -20462,7 +20475,7 @@
       <c r="R980" s="16"/>
       <c r="S980" s="16"/>
     </row>
-    <row r="981" ht="14.25" customHeight="1">
+    <row r="981" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B981" s="16"/>
       <c r="C981" s="16"/>
       <c r="D981" s="16"/>
@@ -20482,7 +20495,7 @@
       <c r="R981" s="16"/>
       <c r="S981" s="16"/>
     </row>
-    <row r="982" ht="14.25" customHeight="1">
+    <row r="982" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B982" s="16"/>
       <c r="C982" s="16"/>
       <c r="D982" s="16"/>
@@ -20502,7 +20515,7 @@
       <c r="R982" s="16"/>
       <c r="S982" s="16"/>
     </row>
-    <row r="983" ht="14.25" customHeight="1">
+    <row r="983" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B983" s="16"/>
       <c r="C983" s="16"/>
       <c r="D983" s="16"/>
@@ -20522,7 +20535,7 @@
       <c r="R983" s="16"/>
       <c r="S983" s="16"/>
     </row>
-    <row r="984" ht="14.25" customHeight="1">
+    <row r="984" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B984" s="16"/>
       <c r="C984" s="16"/>
       <c r="D984" s="16"/>
@@ -20542,7 +20555,7 @@
       <c r="R984" s="16"/>
       <c r="S984" s="16"/>
     </row>
-    <row r="985" ht="14.25" customHeight="1">
+    <row r="985" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B985" s="16"/>
       <c r="C985" s="16"/>
       <c r="D985" s="16"/>
@@ -20562,7 +20575,7 @@
       <c r="R985" s="16"/>
       <c r="S985" s="16"/>
     </row>
-    <row r="986" ht="14.25" customHeight="1">
+    <row r="986" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B986" s="16"/>
       <c r="C986" s="16"/>
       <c r="D986" s="16"/>
@@ -20582,7 +20595,7 @@
       <c r="R986" s="16"/>
       <c r="S986" s="16"/>
     </row>
-    <row r="987" ht="14.25" customHeight="1">
+    <row r="987" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B987" s="16"/>
       <c r="C987" s="16"/>
       <c r="D987" s="16"/>
@@ -20602,7 +20615,7 @@
       <c r="R987" s="16"/>
       <c r="S987" s="16"/>
     </row>
-    <row r="988" ht="14.25" customHeight="1">
+    <row r="988" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B988" s="16"/>
       <c r="C988" s="16"/>
       <c r="D988" s="16"/>
@@ -20622,7 +20635,7 @@
       <c r="R988" s="16"/>
       <c r="S988" s="16"/>
     </row>
-    <row r="989" ht="14.25" customHeight="1">
+    <row r="989" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B989" s="16"/>
       <c r="C989" s="16"/>
       <c r="D989" s="16"/>
@@ -20642,7 +20655,7 @@
       <c r="R989" s="16"/>
       <c r="S989" s="16"/>
     </row>
-    <row r="990" ht="14.25" customHeight="1">
+    <row r="990" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B990" s="16"/>
       <c r="C990" s="16"/>
       <c r="D990" s="16"/>
@@ -20662,7 +20675,7 @@
       <c r="R990" s="16"/>
       <c r="S990" s="16"/>
     </row>
-    <row r="991" ht="14.25" customHeight="1">
+    <row r="991" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B991" s="16"/>
       <c r="C991" s="16"/>
       <c r="D991" s="16"/>
@@ -20682,7 +20695,7 @@
       <c r="R991" s="16"/>
       <c r="S991" s="16"/>
     </row>
-    <row r="992" ht="14.25" customHeight="1">
+    <row r="992" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B992" s="16"/>
       <c r="C992" s="16"/>
       <c r="D992" s="16"/>
@@ -20702,7 +20715,7 @@
       <c r="R992" s="16"/>
       <c r="S992" s="16"/>
     </row>
-    <row r="993" ht="14.25" customHeight="1">
+    <row r="993" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B993" s="16"/>
       <c r="C993" s="16"/>
       <c r="D993" s="16"/>
@@ -20722,7 +20735,7 @@
       <c r="R993" s="16"/>
       <c r="S993" s="16"/>
     </row>
-    <row r="994" ht="14.25" customHeight="1">
+    <row r="994" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B994" s="16"/>
       <c r="C994" s="16"/>
       <c r="D994" s="16"/>
@@ -20742,7 +20755,7 @@
       <c r="R994" s="16"/>
       <c r="S994" s="16"/>
     </row>
-    <row r="995" ht="14.25" customHeight="1">
+    <row r="995" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B995" s="16"/>
       <c r="C995" s="16"/>
       <c r="D995" s="16"/>
@@ -20762,7 +20775,7 @@
       <c r="R995" s="16"/>
       <c r="S995" s="16"/>
     </row>
-    <row r="996" ht="14.25" customHeight="1">
+    <row r="996" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B996" s="16"/>
       <c r="C996" s="16"/>
       <c r="D996" s="16"/>
@@ -20782,7 +20795,7 @@
       <c r="R996" s="16"/>
       <c r="S996" s="16"/>
     </row>
-    <row r="997" ht="14.25" customHeight="1">
+    <row r="997" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B997" s="16"/>
       <c r="C997" s="16"/>
       <c r="D997" s="16"/>
@@ -20802,7 +20815,7 @@
       <c r="R997" s="16"/>
       <c r="S997" s="16"/>
     </row>
-    <row r="998" ht="14.25" customHeight="1">
+    <row r="998" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B998" s="16"/>
       <c r="C998" s="16"/>
       <c r="D998" s="16"/>
@@ -20822,7 +20835,7 @@
       <c r="R998" s="16"/>
       <c r="S998" s="16"/>
     </row>
-    <row r="999" ht="14.25" customHeight="1">
+    <row r="999" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B999" s="16"/>
       <c r="C999" s="16"/>
       <c r="D999" s="16"/>
@@ -20842,7 +20855,7 @@
       <c r="R999" s="16"/>
       <c r="S999" s="16"/>
     </row>
-    <row r="1000" ht="14.25" customHeight="1">
+    <row r="1000" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1000" s="16"/>
       <c r="C1000" s="16"/>
       <c r="D1000" s="16"/>
@@ -20862,7 +20875,7 @@
       <c r="R1000" s="16"/>
       <c r="S1000" s="16"/>
     </row>
-    <row r="1001" ht="14.25" customHeight="1">
+    <row r="1001" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1001" s="16"/>
       <c r="C1001" s="16"/>
       <c r="D1001" s="16"/>
@@ -20882,7 +20895,7 @@
       <c r="R1001" s="16"/>
       <c r="S1001" s="16"/>
     </row>
-    <row r="1002" ht="14.25" customHeight="1">
+    <row r="1002" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1002" s="16"/>
       <c r="C1002" s="16"/>
       <c r="D1002" s="16"/>
@@ -20902,7 +20915,7 @@
       <c r="R1002" s="16"/>
       <c r="S1002" s="16"/>
     </row>
-    <row r="1003" ht="14.25" customHeight="1">
+    <row r="1003" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1003" s="16"/>
       <c r="C1003" s="16"/>
       <c r="D1003" s="16"/>
@@ -20922,7 +20935,7 @@
       <c r="R1003" s="16"/>
       <c r="S1003" s="16"/>
     </row>
-    <row r="1004" ht="14.25" customHeight="1">
+    <row r="1004" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1004" s="16"/>
       <c r="C1004" s="16"/>
       <c r="D1004" s="16"/>
@@ -20942,7 +20955,7 @@
       <c r="R1004" s="16"/>
       <c r="S1004" s="16"/>
     </row>
-    <row r="1005" ht="14.25" customHeight="1">
+    <row r="1005" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1005" s="16"/>
       <c r="C1005" s="16"/>
       <c r="D1005" s="16"/>
@@ -20962,7 +20975,7 @@
       <c r="R1005" s="16"/>
       <c r="S1005" s="16"/>
     </row>
-    <row r="1006" ht="14.25" customHeight="1">
+    <row r="1006" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1006" s="16"/>
       <c r="C1006" s="16"/>
       <c r="D1006" s="16"/>
@@ -20982,7 +20995,7 @@
       <c r="R1006" s="16"/>
       <c r="S1006" s="16"/>
     </row>
-    <row r="1007" ht="14.25" customHeight="1">
+    <row r="1007" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1007" s="16"/>
       <c r="C1007" s="16"/>
       <c r="D1007" s="16"/>
@@ -21002,7 +21015,7 @@
       <c r="R1007" s="16"/>
       <c r="S1007" s="16"/>
     </row>
-    <row r="1008" ht="14.25" customHeight="1">
+    <row r="1008" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1008" s="16"/>
       <c r="C1008" s="16"/>
       <c r="D1008" s="16"/>
@@ -21022,7 +21035,7 @@
       <c r="R1008" s="16"/>
       <c r="S1008" s="16"/>
     </row>
-    <row r="1009" ht="14.25" customHeight="1">
+    <row r="1009" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1009" s="16"/>
       <c r="C1009" s="16"/>
       <c r="D1009" s="16"/>
@@ -21042,7 +21055,7 @@
       <c r="R1009" s="16"/>
       <c r="S1009" s="16"/>
     </row>
-    <row r="1010" ht="14.25" customHeight="1">
+    <row r="1010" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1010" s="16"/>
       <c r="C1010" s="16"/>
       <c r="D1010" s="16"/>
@@ -21062,7 +21075,7 @@
       <c r="R1010" s="16"/>
       <c r="S1010" s="16"/>
     </row>
-    <row r="1011" ht="14.25" customHeight="1">
+    <row r="1011" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1011" s="16"/>
       <c r="C1011" s="16"/>
       <c r="D1011" s="16"/>
@@ -21082,7 +21095,7 @@
       <c r="R1011" s="16"/>
       <c r="S1011" s="16"/>
     </row>
-    <row r="1012" ht="14.25" customHeight="1">
+    <row r="1012" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1012" s="16"/>
       <c r="C1012" s="16"/>
       <c r="D1012" s="16"/>
@@ -21102,7 +21115,7 @@
       <c r="R1012" s="16"/>
       <c r="S1012" s="16"/>
     </row>
-    <row r="1013" ht="14.25" customHeight="1">
+    <row r="1013" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1013" s="16"/>
       <c r="C1013" s="16"/>
       <c r="D1013" s="16"/>
@@ -21122,7 +21135,7 @@
       <c r="R1013" s="16"/>
       <c r="S1013" s="16"/>
     </row>
-    <row r="1014" ht="14.25" customHeight="1">
+    <row r="1014" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1014" s="16"/>
       <c r="C1014" s="16"/>
       <c r="D1014" s="16"/>
@@ -21142,7 +21155,7 @@
       <c r="R1014" s="16"/>
       <c r="S1014" s="16"/>
     </row>
-    <row r="1015" ht="14.25" customHeight="1">
+    <row r="1015" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1015" s="16"/>
       <c r="C1015" s="16"/>
       <c r="D1015" s="16"/>
@@ -21162,7 +21175,7 @@
       <c r="R1015" s="16"/>
       <c r="S1015" s="16"/>
     </row>
-    <row r="1016" ht="14.25" customHeight="1">
+    <row r="1016" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1016" s="16"/>
       <c r="C1016" s="16"/>
       <c r="D1016" s="16"/>
@@ -21182,7 +21195,7 @@
       <c r="R1016" s="16"/>
       <c r="S1016" s="16"/>
     </row>
-    <row r="1017" ht="14.25" customHeight="1">
+    <row r="1017" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1017" s="16"/>
       <c r="C1017" s="16"/>
       <c r="D1017" s="16"/>
@@ -21202,7 +21215,7 @@
       <c r="R1017" s="16"/>
       <c r="S1017" s="16"/>
     </row>
-    <row r="1018" ht="14.25" customHeight="1">
+    <row r="1018" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1018" s="16"/>
       <c r="C1018" s="16"/>
       <c r="D1018" s="16"/>
@@ -21222,7 +21235,7 @@
       <c r="R1018" s="16"/>
       <c r="S1018" s="16"/>
     </row>
-    <row r="1019" ht="14.25" customHeight="1">
+    <row r="1019" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1019" s="16"/>
       <c r="C1019" s="16"/>
       <c r="D1019" s="16"/>
@@ -21242,7 +21255,7 @@
       <c r="R1019" s="16"/>
       <c r="S1019" s="16"/>
     </row>
-    <row r="1020" ht="14.25" customHeight="1">
+    <row r="1020" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1020" s="16"/>
       <c r="C1020" s="16"/>
       <c r="D1020" s="16"/>
@@ -21262,7 +21275,7 @@
       <c r="R1020" s="16"/>
       <c r="S1020" s="16"/>
     </row>
-    <row r="1021" ht="14.25" customHeight="1">
+    <row r="1021" ht="14.25" customHeight="1" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B1021" s="16"/>
       <c r="C1021" s="16"/>
       <c r="D1021" s="16"/>
@@ -21288,10 +21301,10 @@
     <mergeCell ref="B5:F6"/>
     <mergeCell ref="G5:H6"/>
     <mergeCell ref="I5:J6"/>
+    <mergeCell ref="L5:M6"/>
+    <mergeCell ref="O5:S6"/>
     <mergeCell ref="K5:K6"/>
-    <mergeCell ref="L5:M6"/>
     <mergeCell ref="N5:N6"/>
-    <mergeCell ref="O5:S6"/>
     <mergeCell ref="B7:S7"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="G8:H8"/>
@@ -26364,9 +26377,7 @@
     <mergeCell ref="L1021:M1021"/>
     <mergeCell ref="O1021:S1021"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7007874015748032" right="0.7007874015748032" top="0.7519685039370079" bottom="0.7519685039370079" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600" verticalDpi="600" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" usePrinterDefaults="1" copies="1"/>
 </worksheet>
 </file>